--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G18">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G29">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G73">

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -5847,7 +5847,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N34">

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G65">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G73">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Lusail City</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lusail City</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G84">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G89">

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G84">

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU89"/>
+  <dimension ref="A1:AU90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1734,22 +1734,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G9">
@@ -1772,68 +1772,68 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N9">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G10">
@@ -1935,68 +1935,68 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-09-09 12:00:00</t>
+          <t>2026-09-09 11:00:00</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G12">
@@ -2386,22 +2386,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G13">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13">
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -2544,27 +2544,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G14">
@@ -2587,17 +2587,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N14">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2630,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-09-09 12:45:00</t>
+          <t>2026-09-09 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,27 +2707,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-09-09 12:55:00</t>
+          <t>2026-09-09 12:45:00</t>
         </is>
       </c>
     </row>
@@ -2870,27 +2870,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G16">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-09-09 13:00:00</t>
+          <t>2026-09-09 12:55:00</t>
         </is>
       </c>
     </row>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G18">
@@ -3359,27 +3359,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-09-09 13:45:00</t>
+          <t>2026-09-09 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G21">
@@ -3848,27 +3848,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G22">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-09-09 14:00:00</t>
+          <t>2026-09-09 13:45:00</t>
         </is>
       </c>
     </row>
@@ -4016,22 +4016,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G24">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G25">
@@ -4380,68 +4380,68 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N25">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y25">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC25">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AK25">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4505,22 +4505,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G26">
@@ -4543,68 +4543,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G29">
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G30">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G31">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-09-09 14:30:00</t>
+          <t>2026-09-09 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G32">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-09-09 15:00:00</t>
+          <t>2026-09-09 14:30:00</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="G33">
@@ -5804,27 +5804,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O34">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P34">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X34">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK34">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-09-09 15:30:00</t>
+          <t>2026-09-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -5967,27 +5967,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-09-09 15:45:00</t>
+          <t>2026-09-09 15:30:00</t>
         </is>
       </c>
     </row>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G36">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G37">
@@ -6336,68 +6336,68 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N37">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V37">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W37">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK37">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,69 +6499,69 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38">
+        <v>1.38</v>
+      </c>
+      <c r="O38">
+        <v>5.25</v>
+      </c>
+      <c r="P38">
+        <v>7.55</v>
+      </c>
+      <c r="Q38">
+        <v>1.75</v>
+      </c>
+      <c r="R38">
+        <v>2.47</v>
+      </c>
+      <c r="S38">
+        <v>1.25</v>
+      </c>
+      <c r="T38">
+        <v>3.35</v>
+      </c>
+      <c r="U38">
+        <v>2.34</v>
+      </c>
+      <c r="V38">
+        <v>1.53</v>
+      </c>
+      <c r="W38">
+        <v>1.09</v>
+      </c>
+      <c r="X38">
+        <v>1.02</v>
+      </c>
+      <c r="Y38">
+        <v>1.14</v>
+      </c>
+      <c r="Z38">
+        <v>5</v>
+      </c>
+      <c r="AA38">
+        <v>1.57</v>
+      </c>
+      <c r="AB38">
+        <v>2.3</v>
+      </c>
+      <c r="AC38">
+        <v>2.29</v>
+      </c>
+      <c r="AD38">
+        <v>1.57</v>
+      </c>
+      <c r="AE38">
+        <v>1.15</v>
+      </c>
+      <c r="AF38">
+        <v>1.83</v>
+      </c>
+      <c r="AG38">
         <v>1.9</v>
       </c>
-      <c r="O38">
-        <v>3.72</v>
-      </c>
-      <c r="P38">
-        <v>3.6</v>
-      </c>
-      <c r="Q38">
-        <v>0</v>
-      </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38">
-        <v>0</v>
-      </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
-      <c r="U38">
-        <v>0</v>
-      </c>
-      <c r="V38">
-        <v>0</v>
-      </c>
-      <c r="W38">
-        <v>0</v>
-      </c>
-      <c r="X38">
-        <v>0</v>
-      </c>
-      <c r="Y38">
-        <v>0</v>
-      </c>
-      <c r="Z38">
-        <v>0</v>
-      </c>
-      <c r="AA38">
-        <v>1.66</v>
-      </c>
-      <c r="AB38">
-        <v>2.2</v>
-      </c>
-      <c r="AC38">
-        <v>0</v>
-      </c>
-      <c r="AD38">
-        <v>0</v>
-      </c>
-      <c r="AE38">
-        <v>0</v>
-      </c>
-      <c r="AF38">
-        <v>0</v>
-      </c>
-      <c r="AG38">
-        <v>0</v>
-      </c>
       <c r="AH38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-09-09 16:00:00</t>
+          <t>2026-09-09 15:45:00</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="O39">
-        <v>14</v>
+        <v>3.72</v>
       </c>
       <c r="P39">
-        <v>39</v>
+        <v>3.6</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6705,10 +6705,10 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="AB39">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="AC39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="O40">
-        <v>3.6</v>
+        <v>14</v>
       </c>
       <c r="P40">
-        <v>1.91</v>
+        <v>39</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6868,10 +6868,10 @@
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="AB40">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="AC40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.75</v>
+        <v>3.9</v>
       </c>
       <c r="O41">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P41">
-        <v>4.33</v>
+        <v>1.91</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7031,10 +7031,10 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AB41">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AC41">
         <v>0</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC42">
         <v>0</v>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G43">
@@ -7314,68 +7314,68 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="O43">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P43">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T43">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U43">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V43">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W43">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y43">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z43">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA43">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB43">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AC43">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD43">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE43">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF43">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG43">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK43">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G44">
@@ -7477,68 +7477,68 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-09-09 16:45:00</t>
+          <t>2026-09-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7597,27 +7597,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G45">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-09-09 18:00:00</t>
+          <t>2026-09-09 16:45:00</t>
         </is>
       </c>
     </row>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G46">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-09-09 19:30:00</t>
+          <t>2026-09-09 18:00:00</t>
         </is>
       </c>
     </row>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G47">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G48">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-09-09 20:30:00</t>
+          <t>2026-09-09 19:30:00</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G49">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G55">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G57">
@@ -9716,27 +9716,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G58">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N58">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-09-09 21:00:00</t>
+          <t>2026-09-09 20:30:00</t>
         </is>
       </c>
     </row>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G65">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G66">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G73">
@@ -12329,22 +12329,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O74">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P74">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB74">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12492,22 +12492,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lusail City</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Lusail City</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G80">
@@ -13465,27 +13465,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G81">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-09-09 21:30:00</t>
+          <t>2026-09-09 21:00:00</t>
         </is>
       </c>
     </row>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G84">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G85">
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G86">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-09-09 23:30:00</t>
+          <t>2026-09-09 21:30:00</t>
         </is>
       </c>
     </row>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G87">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,141 +14784,304 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>New York RB</t>
+        </is>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>0</v>
+      </c>
+      <c r="R89">
+        <v>0</v>
+      </c>
+      <c r="S89">
+        <v>0</v>
+      </c>
+      <c r="T89">
+        <v>0</v>
+      </c>
+      <c r="U89">
+        <v>0</v>
+      </c>
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>0</v>
+      </c>
+      <c r="X89">
+        <v>0</v>
+      </c>
+      <c r="Y89">
+        <v>0</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+      <c r="AA89">
+        <v>0</v>
+      </c>
+      <c r="AB89">
+        <v>0</v>
+      </c>
+      <c r="AC89">
+        <v>0</v>
+      </c>
+      <c r="AD89">
+        <v>0</v>
+      </c>
+      <c r="AE89">
+        <v>0</v>
+      </c>
+      <c r="AF89">
+        <v>0</v>
+      </c>
+      <c r="AG89">
+        <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ89">
+        <v>0</v>
+      </c>
+      <c r="AK89">
+        <v>0</v>
+      </c>
+      <c r="AL89">
+        <v>0</v>
+      </c>
+      <c r="AM89">
+        <v>-1</v>
+      </c>
+      <c r="AN89">
+        <v>-1</v>
+      </c>
+      <c r="AO89">
+        <v>-1</v>
+      </c>
+      <c r="AP89">
+        <v>-1</v>
+      </c>
+      <c r="AQ89">
+        <v>0</v>
+      </c>
+      <c r="AR89">
+        <v>0</v>
+      </c>
+      <c r="AS89">
+        <v>0</v>
+      </c>
+      <c r="AT89">
+        <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>2026-09-09 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>SJ Earthquakes</t>
         </is>
       </c>
-      <c r="G89">
-        <v>0</v>
-      </c>
-      <c r="H89">
-        <v>0</v>
-      </c>
-      <c r="I89">
-        <v>0</v>
-      </c>
-      <c r="J89">
-        <v>0</v>
-      </c>
-      <c r="K89">
-        <v>0</v>
-      </c>
-      <c r="L89">
-        <v>0</v>
-      </c>
-      <c r="M89" t="inlineStr">
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N89">
-        <v>0</v>
-      </c>
-      <c r="O89">
-        <v>0</v>
-      </c>
-      <c r="P89">
-        <v>0</v>
-      </c>
-      <c r="Q89">
-        <v>0</v>
-      </c>
-      <c r="R89">
-        <v>0</v>
-      </c>
-      <c r="S89">
-        <v>0</v>
-      </c>
-      <c r="T89">
-        <v>0</v>
-      </c>
-      <c r="U89">
-        <v>0</v>
-      </c>
-      <c r="V89">
-        <v>0</v>
-      </c>
-      <c r="W89">
-        <v>0</v>
-      </c>
-      <c r="X89">
-        <v>0</v>
-      </c>
-      <c r="Y89">
-        <v>0</v>
-      </c>
-      <c r="Z89">
-        <v>0</v>
-      </c>
-      <c r="AA89">
-        <v>0</v>
-      </c>
-      <c r="AB89">
-        <v>0</v>
-      </c>
-      <c r="AC89">
-        <v>0</v>
-      </c>
-      <c r="AD89">
-        <v>0</v>
-      </c>
-      <c r="AE89">
-        <v>0</v>
-      </c>
-      <c r="AF89">
-        <v>0</v>
-      </c>
-      <c r="AG89">
-        <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ89">
-        <v>0</v>
-      </c>
-      <c r="AK89">
-        <v>0</v>
-      </c>
-      <c r="AL89">
-        <v>0</v>
-      </c>
-      <c r="AM89">
-        <v>-1</v>
-      </c>
-      <c r="AN89">
-        <v>-1</v>
-      </c>
-      <c r="AO89">
-        <v>-1</v>
-      </c>
-      <c r="AP89">
-        <v>-1</v>
-      </c>
-      <c r="AQ89">
-        <v>0</v>
-      </c>
-      <c r="AR89">
-        <v>0</v>
-      </c>
-      <c r="AS89">
-        <v>0</v>
-      </c>
-      <c r="AT89">
-        <v>0</v>
-      </c>
-      <c r="AU89" t="inlineStr">
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>0</v>
+      </c>
+      <c r="R90">
+        <v>0</v>
+      </c>
+      <c r="S90">
+        <v>0</v>
+      </c>
+      <c r="T90">
+        <v>0</v>
+      </c>
+      <c r="U90">
+        <v>0</v>
+      </c>
+      <c r="V90">
+        <v>0</v>
+      </c>
+      <c r="W90">
+        <v>0</v>
+      </c>
+      <c r="X90">
+        <v>0</v>
+      </c>
+      <c r="Y90">
+        <v>0</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+      <c r="AA90">
+        <v>0</v>
+      </c>
+      <c r="AB90">
+        <v>0</v>
+      </c>
+      <c r="AC90">
+        <v>0</v>
+      </c>
+      <c r="AD90">
+        <v>0</v>
+      </c>
+      <c r="AE90">
+        <v>0</v>
+      </c>
+      <c r="AF90">
+        <v>0</v>
+      </c>
+      <c r="AG90">
+        <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ90">
+        <v>0</v>
+      </c>
+      <c r="AK90">
+        <v>0</v>
+      </c>
+      <c r="AL90">
+        <v>0</v>
+      </c>
+      <c r="AM90">
+        <v>-1</v>
+      </c>
+      <c r="AN90">
+        <v>-1</v>
+      </c>
+      <c r="AO90">
+        <v>-1</v>
+      </c>
+      <c r="AP90">
+        <v>-1</v>
+      </c>
+      <c r="AQ90">
+        <v>0</v>
+      </c>
+      <c r="AR90">
+        <v>0</v>
+      </c>
+      <c r="AS90">
+        <v>0</v>
+      </c>
+      <c r="AT90">
+        <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
         <is>
           <t>2026-09-09 23:30:00</t>
         </is>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G30">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="O39">
-        <v>3.72</v>
+        <v>14</v>
       </c>
       <c r="P39">
-        <v>3.6</v>
+        <v>39</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6705,10 +6705,10 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="AB39">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="AC39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="O40">
-        <v>14</v>
+        <v>3.72</v>
       </c>
       <c r="P40">
-        <v>39</v>
+        <v>3.6</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6868,10 +6868,10 @@
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="AB40">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="AC40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
+        <v>1.75</v>
+      </c>
+      <c r="O41">
         <v>3.9</v>
       </c>
-      <c r="O41">
-        <v>3.6</v>
-      </c>
       <c r="P41">
-        <v>1.91</v>
+        <v>4.33</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7031,10 +7031,10 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AB41">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AC41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.75</v>
+        <v>3.9</v>
       </c>
       <c r="O42">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>4.33</v>
+        <v>1.91</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AB42">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AC42">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G56">

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G30">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G56">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G84">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G85">

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G74">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G90">

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -6499,7 +6499,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N38">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G74">

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU90"/>
+  <dimension ref="A1:AU86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lusail City</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G77">
@@ -12976,27 +12976,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G78">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>2026-09-09 21:00:00</t>
+          <t>2026-09-09 21:30:00</t>
         </is>
       </c>
     </row>
@@ -13139,27 +13139,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G79">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>2026-09-09 21:00:00</t>
+          <t>2026-09-09 21:30:00</t>
         </is>
       </c>
     </row>
@@ -13302,27 +13302,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G80">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>2026-09-09 21:00:00</t>
+          <t>2026-09-09 21:30:00</t>
         </is>
       </c>
     </row>
@@ -13465,27 +13465,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G81">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-09-09 21:00:00</t>
+          <t>2026-09-09 21:30:00</t>
         </is>
       </c>
     </row>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G82">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G83">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-09-09 21:30:00</t>
+          <t>2026-09-09 23:30:00</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G84">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-09-09 21:30:00</t>
+          <t>2026-09-09 23:30:00</t>
         </is>
       </c>
     </row>
@@ -14117,7 +14117,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G85">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-09-09 21:30:00</t>
+          <t>2026-09-09 23:30:00</t>
         </is>
       </c>
     </row>
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G86">
@@ -14430,658 +14430,6 @@
         <v>0</v>
       </c>
       <c r="AU86" t="inlineStr">
-        <is>
-          <t>2026-09-09 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>St. Louis City</t>
-        </is>
-      </c>
-      <c r="G87">
-        <v>0</v>
-      </c>
-      <c r="H87">
-        <v>0</v>
-      </c>
-      <c r="I87">
-        <v>0</v>
-      </c>
-      <c r="J87">
-        <v>0</v>
-      </c>
-      <c r="K87">
-        <v>0</v>
-      </c>
-      <c r="L87">
-        <v>0</v>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N87">
-        <v>0</v>
-      </c>
-      <c r="O87">
-        <v>0</v>
-      </c>
-      <c r="P87">
-        <v>0</v>
-      </c>
-      <c r="Q87">
-        <v>0</v>
-      </c>
-      <c r="R87">
-        <v>0</v>
-      </c>
-      <c r="S87">
-        <v>0</v>
-      </c>
-      <c r="T87">
-        <v>0</v>
-      </c>
-      <c r="U87">
-        <v>0</v>
-      </c>
-      <c r="V87">
-        <v>0</v>
-      </c>
-      <c r="W87">
-        <v>0</v>
-      </c>
-      <c r="X87">
-        <v>0</v>
-      </c>
-      <c r="Y87">
-        <v>0</v>
-      </c>
-      <c r="Z87">
-        <v>0</v>
-      </c>
-      <c r="AA87">
-        <v>0</v>
-      </c>
-      <c r="AB87">
-        <v>0</v>
-      </c>
-      <c r="AC87">
-        <v>0</v>
-      </c>
-      <c r="AD87">
-        <v>0</v>
-      </c>
-      <c r="AE87">
-        <v>0</v>
-      </c>
-      <c r="AF87">
-        <v>0</v>
-      </c>
-      <c r="AG87">
-        <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ87">
-        <v>0</v>
-      </c>
-      <c r="AK87">
-        <v>0</v>
-      </c>
-      <c r="AL87">
-        <v>0</v>
-      </c>
-      <c r="AM87">
-        <v>-1</v>
-      </c>
-      <c r="AN87">
-        <v>-1</v>
-      </c>
-      <c r="AO87">
-        <v>-1</v>
-      </c>
-      <c r="AP87">
-        <v>-1</v>
-      </c>
-      <c r="AQ87">
-        <v>0</v>
-      </c>
-      <c r="AR87">
-        <v>0</v>
-      </c>
-      <c r="AS87">
-        <v>0</v>
-      </c>
-      <c r="AT87">
-        <v>0</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>2026-09-09 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>New York RB</t>
-        </is>
-      </c>
-      <c r="G88">
-        <v>0</v>
-      </c>
-      <c r="H88">
-        <v>0</v>
-      </c>
-      <c r="I88">
-        <v>0</v>
-      </c>
-      <c r="J88">
-        <v>0</v>
-      </c>
-      <c r="K88">
-        <v>0</v>
-      </c>
-      <c r="L88">
-        <v>0</v>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N88">
-        <v>0</v>
-      </c>
-      <c r="O88">
-        <v>0</v>
-      </c>
-      <c r="P88">
-        <v>0</v>
-      </c>
-      <c r="Q88">
-        <v>0</v>
-      </c>
-      <c r="R88">
-        <v>0</v>
-      </c>
-      <c r="S88">
-        <v>0</v>
-      </c>
-      <c r="T88">
-        <v>0</v>
-      </c>
-      <c r="U88">
-        <v>0</v>
-      </c>
-      <c r="V88">
-        <v>0</v>
-      </c>
-      <c r="W88">
-        <v>0</v>
-      </c>
-      <c r="X88">
-        <v>0</v>
-      </c>
-      <c r="Y88">
-        <v>0</v>
-      </c>
-      <c r="Z88">
-        <v>0</v>
-      </c>
-      <c r="AA88">
-        <v>0</v>
-      </c>
-      <c r="AB88">
-        <v>0</v>
-      </c>
-      <c r="AC88">
-        <v>0</v>
-      </c>
-      <c r="AD88">
-        <v>0</v>
-      </c>
-      <c r="AE88">
-        <v>0</v>
-      </c>
-      <c r="AF88">
-        <v>0</v>
-      </c>
-      <c r="AG88">
-        <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ88">
-        <v>0</v>
-      </c>
-      <c r="AK88">
-        <v>0</v>
-      </c>
-      <c r="AL88">
-        <v>0</v>
-      </c>
-      <c r="AM88">
-        <v>-1</v>
-      </c>
-      <c r="AN88">
-        <v>-1</v>
-      </c>
-      <c r="AO88">
-        <v>-1</v>
-      </c>
-      <c r="AP88">
-        <v>-1</v>
-      </c>
-      <c r="AQ88">
-        <v>0</v>
-      </c>
-      <c r="AR88">
-        <v>0</v>
-      </c>
-      <c r="AS88">
-        <v>0</v>
-      </c>
-      <c r="AT88">
-        <v>0</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>2026-09-09 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>SJ Earthquakes</t>
-        </is>
-      </c>
-      <c r="G89">
-        <v>0</v>
-      </c>
-      <c r="H89">
-        <v>0</v>
-      </c>
-      <c r="I89">
-        <v>0</v>
-      </c>
-      <c r="J89">
-        <v>0</v>
-      </c>
-      <c r="K89">
-        <v>0</v>
-      </c>
-      <c r="L89">
-        <v>0</v>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N89">
-        <v>0</v>
-      </c>
-      <c r="O89">
-        <v>0</v>
-      </c>
-      <c r="P89">
-        <v>0</v>
-      </c>
-      <c r="Q89">
-        <v>0</v>
-      </c>
-      <c r="R89">
-        <v>0</v>
-      </c>
-      <c r="S89">
-        <v>0</v>
-      </c>
-      <c r="T89">
-        <v>0</v>
-      </c>
-      <c r="U89">
-        <v>0</v>
-      </c>
-      <c r="V89">
-        <v>0</v>
-      </c>
-      <c r="W89">
-        <v>0</v>
-      </c>
-      <c r="X89">
-        <v>0</v>
-      </c>
-      <c r="Y89">
-        <v>0</v>
-      </c>
-      <c r="Z89">
-        <v>0</v>
-      </c>
-      <c r="AA89">
-        <v>0</v>
-      </c>
-      <c r="AB89">
-        <v>0</v>
-      </c>
-      <c r="AC89">
-        <v>0</v>
-      </c>
-      <c r="AD89">
-        <v>0</v>
-      </c>
-      <c r="AE89">
-        <v>0</v>
-      </c>
-      <c r="AF89">
-        <v>0</v>
-      </c>
-      <c r="AG89">
-        <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ89">
-        <v>0</v>
-      </c>
-      <c r="AK89">
-        <v>0</v>
-      </c>
-      <c r="AL89">
-        <v>0</v>
-      </c>
-      <c r="AM89">
-        <v>-1</v>
-      </c>
-      <c r="AN89">
-        <v>-1</v>
-      </c>
-      <c r="AO89">
-        <v>-1</v>
-      </c>
-      <c r="AP89">
-        <v>-1</v>
-      </c>
-      <c r="AQ89">
-        <v>0</v>
-      </c>
-      <c r="AR89">
-        <v>0</v>
-      </c>
-      <c r="AS89">
-        <v>0</v>
-      </c>
-      <c r="AT89">
-        <v>0</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>2026-09-09 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>LA Galaxy</t>
-        </is>
-      </c>
-      <c r="G90">
-        <v>0</v>
-      </c>
-      <c r="H90">
-        <v>0</v>
-      </c>
-      <c r="I90">
-        <v>0</v>
-      </c>
-      <c r="J90">
-        <v>0</v>
-      </c>
-      <c r="K90">
-        <v>0</v>
-      </c>
-      <c r="L90">
-        <v>0</v>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N90">
-        <v>0</v>
-      </c>
-      <c r="O90">
-        <v>0</v>
-      </c>
-      <c r="P90">
-        <v>0</v>
-      </c>
-      <c r="Q90">
-        <v>0</v>
-      </c>
-      <c r="R90">
-        <v>0</v>
-      </c>
-      <c r="S90">
-        <v>0</v>
-      </c>
-      <c r="T90">
-        <v>0</v>
-      </c>
-      <c r="U90">
-        <v>0</v>
-      </c>
-      <c r="V90">
-        <v>0</v>
-      </c>
-      <c r="W90">
-        <v>0</v>
-      </c>
-      <c r="X90">
-        <v>0</v>
-      </c>
-      <c r="Y90">
-        <v>0</v>
-      </c>
-      <c r="Z90">
-        <v>0</v>
-      </c>
-      <c r="AA90">
-        <v>0</v>
-      </c>
-      <c r="AB90">
-        <v>0</v>
-      </c>
-      <c r="AC90">
-        <v>0</v>
-      </c>
-      <c r="AD90">
-        <v>0</v>
-      </c>
-      <c r="AE90">
-        <v>0</v>
-      </c>
-      <c r="AF90">
-        <v>0</v>
-      </c>
-      <c r="AG90">
-        <v>0</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ90">
-        <v>0</v>
-      </c>
-      <c r="AK90">
-        <v>0</v>
-      </c>
-      <c r="AL90">
-        <v>0</v>
-      </c>
-      <c r="AM90">
-        <v>-1</v>
-      </c>
-      <c r="AN90">
-        <v>-1</v>
-      </c>
-      <c r="AO90">
-        <v>-1</v>
-      </c>
-      <c r="AP90">
-        <v>-1</v>
-      </c>
-      <c r="AQ90">
-        <v>0</v>
-      </c>
-      <c r="AR90">
-        <v>0</v>
-      </c>
-      <c r="AS90">
-        <v>0</v>
-      </c>
-      <c r="AT90">
-        <v>0</v>
-      </c>
-      <c r="AU90" t="inlineStr">
         <is>
           <t>2026-09-09 23:30:00</t>
         </is>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.07</v>
+        <v>3.91</v>
       </c>
       <c r="R8">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="S8">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="T8">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="U8">
-        <v>3.21</v>
+        <v>3.8</v>
       </c>
       <c r="V8">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y8">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="Z8">
-        <v>2.49</v>
+        <v>2.21</v>
       </c>
       <c r="AA8">
-        <v>2.41</v>
+        <v>2.78</v>
       </c>
       <c r="AB8">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AC8">
-        <v>4.6</v>
+        <v>6.04</v>
       </c>
       <c r="AD8">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>2.64</v>
+        <v>2.25</v>
       </c>
       <c r="AG8">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AK8">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2591,43 +2591,43 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA14">
         <v>1.85</v>
@@ -2636,19 +2636,19 @@
         <v>1.95</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3578,34 +3578,34 @@
         <v>17</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA20">
         <v>1.25</v>
@@ -3614,19 +3614,19 @@
         <v>4</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>9.65</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X28">
         <v>0</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5208,55 +5208,55 @@
         <v>0</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X30">
         <v>0</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G50">

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU86"/>
+  <dimension ref="A1:AU84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -12650,27 +12650,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G76">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2026-09-09 21:00:00</t>
+          <t>2026-09-09 21:30:00</t>
         </is>
       </c>
     </row>
@@ -12813,27 +12813,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G77">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2026-09-09 21:00:00</t>
+          <t>2026-09-09 21:30:00</t>
         </is>
       </c>
     </row>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G79">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G80">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G81">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-09-09 21:30:00</t>
+          <t>2026-09-09 23:30:00</t>
         </is>
       </c>
     </row>
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G82">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-09-09 21:30:00</t>
+          <t>2026-09-09 23:30:00</t>
         </is>
       </c>
     </row>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G84">
@@ -14104,332 +14104,6 @@
         <v>0</v>
       </c>
       <c r="AU84" t="inlineStr">
-        <is>
-          <t>2026-09-09 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>SJ Earthquakes</t>
-        </is>
-      </c>
-      <c r="G85">
-        <v>0</v>
-      </c>
-      <c r="H85">
-        <v>0</v>
-      </c>
-      <c r="I85">
-        <v>0</v>
-      </c>
-      <c r="J85">
-        <v>0</v>
-      </c>
-      <c r="K85">
-        <v>0</v>
-      </c>
-      <c r="L85">
-        <v>0</v>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N85">
-        <v>0</v>
-      </c>
-      <c r="O85">
-        <v>0</v>
-      </c>
-      <c r="P85">
-        <v>0</v>
-      </c>
-      <c r="Q85">
-        <v>0</v>
-      </c>
-      <c r="R85">
-        <v>0</v>
-      </c>
-      <c r="S85">
-        <v>0</v>
-      </c>
-      <c r="T85">
-        <v>0</v>
-      </c>
-      <c r="U85">
-        <v>0</v>
-      </c>
-      <c r="V85">
-        <v>0</v>
-      </c>
-      <c r="W85">
-        <v>0</v>
-      </c>
-      <c r="X85">
-        <v>0</v>
-      </c>
-      <c r="Y85">
-        <v>0</v>
-      </c>
-      <c r="Z85">
-        <v>0</v>
-      </c>
-      <c r="AA85">
-        <v>0</v>
-      </c>
-      <c r="AB85">
-        <v>0</v>
-      </c>
-      <c r="AC85">
-        <v>0</v>
-      </c>
-      <c r="AD85">
-        <v>0</v>
-      </c>
-      <c r="AE85">
-        <v>0</v>
-      </c>
-      <c r="AF85">
-        <v>0</v>
-      </c>
-      <c r="AG85">
-        <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ85">
-        <v>0</v>
-      </c>
-      <c r="AK85">
-        <v>0</v>
-      </c>
-      <c r="AL85">
-        <v>0</v>
-      </c>
-      <c r="AM85">
-        <v>-1</v>
-      </c>
-      <c r="AN85">
-        <v>-1</v>
-      </c>
-      <c r="AO85">
-        <v>-1</v>
-      </c>
-      <c r="AP85">
-        <v>-1</v>
-      </c>
-      <c r="AQ85">
-        <v>0</v>
-      </c>
-      <c r="AR85">
-        <v>0</v>
-      </c>
-      <c r="AS85">
-        <v>0</v>
-      </c>
-      <c r="AT85">
-        <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>2026-09-09 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>LA Galaxy</t>
-        </is>
-      </c>
-      <c r="G86">
-        <v>0</v>
-      </c>
-      <c r="H86">
-        <v>0</v>
-      </c>
-      <c r="I86">
-        <v>0</v>
-      </c>
-      <c r="J86">
-        <v>0</v>
-      </c>
-      <c r="K86">
-        <v>0</v>
-      </c>
-      <c r="L86">
-        <v>0</v>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N86">
-        <v>0</v>
-      </c>
-      <c r="O86">
-        <v>0</v>
-      </c>
-      <c r="P86">
-        <v>0</v>
-      </c>
-      <c r="Q86">
-        <v>0</v>
-      </c>
-      <c r="R86">
-        <v>0</v>
-      </c>
-      <c r="S86">
-        <v>0</v>
-      </c>
-      <c r="T86">
-        <v>0</v>
-      </c>
-      <c r="U86">
-        <v>0</v>
-      </c>
-      <c r="V86">
-        <v>0</v>
-      </c>
-      <c r="W86">
-        <v>0</v>
-      </c>
-      <c r="X86">
-        <v>0</v>
-      </c>
-      <c r="Y86">
-        <v>0</v>
-      </c>
-      <c r="Z86">
-        <v>0</v>
-      </c>
-      <c r="AA86">
-        <v>0</v>
-      </c>
-      <c r="AB86">
-        <v>0</v>
-      </c>
-      <c r="AC86">
-        <v>0</v>
-      </c>
-      <c r="AD86">
-        <v>0</v>
-      </c>
-      <c r="AE86">
-        <v>0</v>
-      </c>
-      <c r="AF86">
-        <v>0</v>
-      </c>
-      <c r="AG86">
-        <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ86">
-        <v>0</v>
-      </c>
-      <c r="AK86">
-        <v>0</v>
-      </c>
-      <c r="AL86">
-        <v>0</v>
-      </c>
-      <c r="AM86">
-        <v>-1</v>
-      </c>
-      <c r="AN86">
-        <v>-1</v>
-      </c>
-      <c r="AO86">
-        <v>-1</v>
-      </c>
-      <c r="AP86">
-        <v>-1</v>
-      </c>
-      <c r="AQ86">
-        <v>0</v>
-      </c>
-      <c r="AR86">
-        <v>0</v>
-      </c>
-      <c r="AS86">
-        <v>0</v>
-      </c>
-      <c r="AT86">
-        <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
         <is>
           <t>2026-09-09 23:30:00</t>
         </is>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="O39">
-        <v>14</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>39</v>
+        <v>1.91</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA39">
+        <v>1.9</v>
+      </c>
+      <c r="AB39">
+        <v>1.9</v>
+      </c>
+      <c r="AC39">
+        <v>3.08</v>
+      </c>
+      <c r="AD39">
+        <v>1.33</v>
+      </c>
+      <c r="AE39">
+        <v>1.11</v>
+      </c>
+      <c r="AF39">
+        <v>1.8</v>
+      </c>
+      <c r="AG39">
+        <v>1.95</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>1.3</v>
+      </c>
+      <c r="AK39">
         <v>1.25</v>
-      </c>
-      <c r="AB39">
-        <v>4</v>
-      </c>
-      <c r="AC39">
-        <v>0</v>
-      </c>
-      <c r="AD39">
-        <v>0</v>
-      </c>
-      <c r="AE39">
-        <v>0</v>
-      </c>
-      <c r="AF39">
-        <v>0</v>
-      </c>
-      <c r="AG39">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>0</v>
-      </c>
-      <c r="AK39">
-        <v>0</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6838,34 +6838,34 @@
         <v>3.6</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA40">
         <v>1.66</v>
@@ -6874,19 +6874,19 @@
         <v>2.2</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,34 +7001,34 @@
         <v>4.33</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA41">
         <v>1.66</v>
@@ -7037,19 +7037,19 @@
         <v>2.2</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>14</v>
       </c>
       <c r="P42">
-        <v>1.91</v>
+        <v>39</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA42">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="AB42">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7644,19 +7644,19 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -7665,10 +7665,10 @@
         <v>0</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W45">
         <v>0</v>
@@ -7677,31 +7677,31 @@
         <v>0</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL58">
         <v>0</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,61 +4221,61 @@
         </is>
       </c>
       <c r="N24">
-        <v>5.9</v>
+        <v>2.87</v>
       </c>
       <c r="O24">
-        <v>3.8</v>
+        <v>2.57</v>
       </c>
       <c r="P24">
-        <v>1.45</v>
+        <v>2.69</v>
       </c>
       <c r="Q24">
-        <v>6.6</v>
+        <v>3.92</v>
       </c>
       <c r="R24">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="S24">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="T24">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="U24">
-        <v>2.85</v>
+        <v>4.33</v>
       </c>
       <c r="V24">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="W24">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="Y24">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="Z24">
-        <v>3.05</v>
+        <v>2.23</v>
       </c>
       <c r="AA24">
-        <v>2.11</v>
+        <v>2.88</v>
       </c>
       <c r="AB24">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AC24">
-        <v>3.58</v>
+        <v>5.96</v>
       </c>
       <c r="AD24">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AE24">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF24">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AG24">
         <v>1.57</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AK24">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,61 +4384,61 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.87</v>
+        <v>5.9</v>
       </c>
       <c r="O25">
-        <v>2.57</v>
+        <v>3.8</v>
       </c>
       <c r="P25">
-        <v>2.69</v>
+        <v>1.45</v>
       </c>
       <c r="Q25">
-        <v>3.92</v>
+        <v>6.6</v>
       </c>
       <c r="R25">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="T25">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="U25">
-        <v>4.33</v>
+        <v>2.85</v>
       </c>
       <c r="V25">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="W25">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="Z25">
-        <v>2.23</v>
+        <v>3.05</v>
       </c>
       <c r="AA25">
-        <v>2.88</v>
+        <v>2.11</v>
       </c>
       <c r="AB25">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AC25">
-        <v>5.96</v>
+        <v>3.58</v>
       </c>
       <c r="AD25">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AE25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF25">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AG25">
         <v>1.57</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AL25">
         <v>0</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,61 +4221,61 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.87</v>
+        <v>5.9</v>
       </c>
       <c r="O24">
-        <v>2.57</v>
+        <v>3.8</v>
       </c>
       <c r="P24">
-        <v>2.69</v>
+        <v>1.45</v>
       </c>
       <c r="Q24">
-        <v>3.92</v>
+        <v>6.6</v>
       </c>
       <c r="R24">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="S24">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="T24">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="U24">
-        <v>4.33</v>
+        <v>2.85</v>
       </c>
       <c r="V24">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="W24">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="Z24">
-        <v>2.23</v>
+        <v>3.05</v>
       </c>
       <c r="AA24">
-        <v>2.88</v>
+        <v>2.11</v>
       </c>
       <c r="AB24">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="AC24">
-        <v>5.96</v>
+        <v>3.58</v>
       </c>
       <c r="AD24">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AE24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AG24">
         <v>1.57</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,61 +4384,61 @@
         </is>
       </c>
       <c r="N25">
-        <v>5.9</v>
+        <v>2.87</v>
       </c>
       <c r="O25">
-        <v>3.8</v>
+        <v>2.57</v>
       </c>
       <c r="P25">
-        <v>1.45</v>
+        <v>2.69</v>
       </c>
       <c r="Q25">
-        <v>6.6</v>
+        <v>3.92</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="S25">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="T25">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="U25">
-        <v>2.85</v>
+        <v>4.33</v>
       </c>
       <c r="V25">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="W25">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="Y25">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="Z25">
-        <v>3.05</v>
+        <v>2.23</v>
       </c>
       <c r="AA25">
-        <v>2.11</v>
+        <v>2.88</v>
       </c>
       <c r="AB25">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="AC25">
-        <v>3.58</v>
+        <v>5.96</v>
       </c>
       <c r="AD25">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AE25">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF25">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AG25">
         <v>1.57</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AK25">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G74">

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -1622,10 +1622,10 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.91</v>
+        <v>3.7</v>
       </c>
       <c r="R8">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="S8">
         <v>1.63</v>
@@ -1643,31 +1643,31 @@
         <v>1.02</v>
       </c>
       <c r="X8">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Z8">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="AA8">
         <v>2.78</v>
       </c>
       <c r="AB8">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC8">
-        <v>6.04</v>
+        <v>6.5</v>
       </c>
       <c r="AD8">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AE8">
         <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AG8">
         <v>1.57</v>
@@ -1686,7 +1686,7 @@
         <v>1.36</v>
       </c>
       <c r="AK8">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1779,31 +1779,31 @@
         <v>1.42</v>
       </c>
       <c r="O9">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P9">
-        <v>8.300000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="Q9">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="R9">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S9">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="T9">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="U9">
         <v>3.21</v>
       </c>
       <c r="V9">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="W9">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1.04</v>
@@ -1818,10 +1818,10 @@
         <v>2.41</v>
       </c>
       <c r="AB9">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC9">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AD9">
         <v>1.13</v>
@@ -1830,10 +1830,10 @@
         <v>1.02</v>
       </c>
       <c r="AF9">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AG9">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="AK9">
         <v>2.5</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -1948,37 +1948,37 @@
         <v>7.75</v>
       </c>
       <c r="Q10">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R10">
+        <v>2.35</v>
+      </c>
+      <c r="S10">
+        <v>1.29</v>
+      </c>
+      <c r="T10">
+        <v>3.5</v>
+      </c>
+      <c r="U10">
         <v>2.5</v>
       </c>
-      <c r="S10">
-        <v>1.32</v>
-      </c>
-      <c r="T10">
-        <v>2.96</v>
-      </c>
-      <c r="U10">
-        <v>2.35</v>
-      </c>
       <c r="V10">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z10">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="AA10">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB10">
         <v>2.1</v>
@@ -1993,10 +1993,10 @@
         <v>1.12</v>
       </c>
       <c r="AF10">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AG10">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.13</v>
       </c>
       <c r="AK10">
-        <v>2.84</v>
+        <v>3.68</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2591,16 +2591,16 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="O14">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="P14">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="Q14">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="R14">
         <v>2.17</v>
@@ -2618,7 +2618,7 @@
         <v>1.46</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
         <v>1.01</v>
@@ -2627,13 +2627,13 @@
         <v>1.19</v>
       </c>
       <c r="Z14">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AA14">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB14">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AC14">
         <v>2.62</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK14">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O16">
-        <v>3.57</v>
+        <v>3.59</v>
       </c>
       <c r="P16">
         <v>2.11</v>
       </c>
       <c r="Q16">
-        <v>3.62</v>
+        <v>3.69</v>
       </c>
       <c r="R16">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T16">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U16">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z16">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="AA16">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB16">
         <v>2.04</v>
       </c>
       <c r="AC16">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="AD16">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF16">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG16">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3898,13 +3898,13 @@
         <v>1.33</v>
       </c>
       <c r="O22">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="P22">
         <v>8</v>
       </c>
       <c r="Q22">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="R22">
         <v>2.74</v>
@@ -3916,10 +3916,10 @@
         <v>4.33</v>
       </c>
       <c r="U22">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="V22">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="W22">
         <v>1.25</v>
@@ -3928,31 +3928,31 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z22">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="AA22">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AB22">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AC22">
         <v>1.88</v>
       </c>
       <c r="AD22">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AE22">
         <v>1.32</v>
       </c>
       <c r="AF22">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AG22">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.05</v>
       </c>
       <c r="AK22">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q28">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="R28">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S28">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T28">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U28">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V28">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W28">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
         <v>1.16</v>
       </c>
       <c r="Z28">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA28">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB28">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="AC28">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AD28">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE28">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF28">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG28">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>1.24</v>
       </c>
       <c r="AK28">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="O29">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q29">
-        <v>2.41</v>
+        <v>2.72</v>
       </c>
       <c r="R29">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="S29">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T29">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U29">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="V29">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="W29">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X29">
         <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z29">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AA29">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AB29">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="AC29">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AD29">
+        <v>1.57</v>
+      </c>
+      <c r="AE29">
+        <v>1.2</v>
+      </c>
+      <c r="AF29">
         <v>1.44</v>
       </c>
-      <c r="AE29">
-        <v>1.16</v>
-      </c>
-      <c r="AF29">
-        <v>1.53</v>
-      </c>
       <c r="AG29">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q30">
-        <v>2.72</v>
+        <v>2.42</v>
       </c>
       <c r="R30">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S30">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U30">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="V30">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="W30">
+        <v>1.13</v>
+      </c>
+      <c r="X30">
+        <v>1.01</v>
+      </c>
+      <c r="Y30">
+        <v>1.16</v>
+      </c>
+      <c r="Z30">
+        <v>4.8</v>
+      </c>
+      <c r="AA30">
+        <v>1.57</v>
+      </c>
+      <c r="AB30">
+        <v>2.16</v>
+      </c>
+      <c r="AC30">
+        <v>2.48</v>
+      </c>
+      <c r="AD30">
+        <v>1.45</v>
+      </c>
+      <c r="AE30">
         <v>1.14</v>
       </c>
-      <c r="X30">
-        <v>0</v>
-      </c>
-      <c r="Y30">
-        <v>1.15</v>
-      </c>
-      <c r="Z30">
-        <v>4.7</v>
-      </c>
-      <c r="AA30">
+      <c r="AF30">
         <v>1.5</v>
       </c>
-      <c r="AB30">
-        <v>2.4</v>
-      </c>
-      <c r="AC30">
-        <v>2.25</v>
-      </c>
-      <c r="AD30">
-        <v>1.57</v>
-      </c>
-      <c r="AE30">
-        <v>1.2</v>
-      </c>
-      <c r="AF30">
-        <v>1.44</v>
-      </c>
       <c r="AG30">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK30">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.25</v>
+        <v>1.74</v>
       </c>
       <c r="O35">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="P35">
         <v>3.42</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X52">
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X76">
         <v>0</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X82">
         <v>0</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X83">
         <v>0</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL84">
         <v>0</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="O36">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P36">
-        <v>2.97</v>
+        <v>2.45</v>
       </c>
       <c r="Q36">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="R36">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S36">
         <v>1.36</v>
@@ -6201,22 +6201,22 @@
         <v>2.88</v>
       </c>
       <c r="V36">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W36">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
         <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z36">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AA36">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB36">
         <v>1.78</v>
@@ -6234,7 +6234,7 @@
         <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK36">
         <v>1.62</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="O38">
         <v>5.25</v>
@@ -6512,55 +6512,55 @@
         <v>7.55</v>
       </c>
       <c r="Q38">
+        <v>1.78</v>
+      </c>
+      <c r="R38">
+        <v>2.63</v>
+      </c>
+      <c r="S38">
+        <v>1.24</v>
+      </c>
+      <c r="T38">
+        <v>3.5</v>
+      </c>
+      <c r="U38">
+        <v>2.2</v>
+      </c>
+      <c r="V38">
+        <v>1.52</v>
+      </c>
+      <c r="W38">
+        <v>1.14</v>
+      </c>
+      <c r="X38">
+        <v>1.03</v>
+      </c>
+      <c r="Y38">
+        <v>1.11</v>
+      </c>
+      <c r="Z38">
+        <v>4.8</v>
+      </c>
+      <c r="AA38">
+        <v>1.46</v>
+      </c>
+      <c r="AB38">
+        <v>2.39</v>
+      </c>
+      <c r="AC38">
+        <v>2.27</v>
+      </c>
+      <c r="AD38">
+        <v>1.61</v>
+      </c>
+      <c r="AE38">
+        <v>1.24</v>
+      </c>
+      <c r="AF38">
         <v>1.75</v>
       </c>
-      <c r="R38">
-        <v>2.47</v>
-      </c>
-      <c r="S38">
-        <v>1.25</v>
-      </c>
-      <c r="T38">
-        <v>3.35</v>
-      </c>
-      <c r="U38">
-        <v>2.34</v>
-      </c>
-      <c r="V38">
-        <v>1.53</v>
-      </c>
-      <c r="W38">
-        <v>1.09</v>
-      </c>
-      <c r="X38">
-        <v>1.02</v>
-      </c>
-      <c r="Y38">
-        <v>1.14</v>
-      </c>
-      <c r="Z38">
-        <v>5</v>
-      </c>
-      <c r="AA38">
-        <v>1.57</v>
-      </c>
-      <c r="AB38">
-        <v>2.3</v>
-      </c>
-      <c r="AC38">
-        <v>2.29</v>
-      </c>
-      <c r="AD38">
-        <v>1.57</v>
-      </c>
-      <c r="AE38">
-        <v>1.15</v>
-      </c>
-      <c r="AF38">
-        <v>1.83</v>
-      </c>
       <c r="AG38">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.18</v>
       </c>
       <c r="AK38">
-        <v>2.93</v>
+        <v>3.32</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="O43">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
-        <v>2.7</v>
+        <v>2.37</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="N44">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="O44">
         <v>4.5</v>
@@ -7496,19 +7496,19 @@
         <v>2.5</v>
       </c>
       <c r="S44">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T44">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U44">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="V44">
         <v>1.6</v>
       </c>
       <c r="W44">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X44">
         <v>1.01</v>
@@ -7517,28 +7517,28 @@
         <v>1.17</v>
       </c>
       <c r="Z44">
-        <v>4.7</v>
+        <v>4.85</v>
       </c>
       <c r="AA44">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AB44">
         <v>2.47</v>
       </c>
       <c r="AC44">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AD44">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AE44">
         <v>1.22</v>
       </c>
       <c r="AF44">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG44">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.67</v>
+        <v>2.33</v>
       </c>
       <c r="O52">
-        <v>4.66</v>
+        <v>4.06</v>
       </c>
       <c r="P52">
-        <v>3.9</v>
+        <v>2.62</v>
       </c>
       <c r="Q52">
+        <v>2.7</v>
+      </c>
+      <c r="R52">
+        <v>2.3</v>
+      </c>
+      <c r="S52">
+        <v>1.22</v>
+      </c>
+      <c r="T52">
+        <v>3.8</v>
+      </c>
+      <c r="U52">
         <v>2.15</v>
       </c>
-      <c r="R52">
-        <v>2.62</v>
-      </c>
-      <c r="S52">
+      <c r="V52">
+        <v>1.6</v>
+      </c>
+      <c r="W52">
+        <v>1.13</v>
+      </c>
+      <c r="X52">
+        <v>1.01</v>
+      </c>
+      <c r="Y52">
+        <v>1.12</v>
+      </c>
+      <c r="Z52">
+        <v>4.8</v>
+      </c>
+      <c r="AA52">
+        <v>1.55</v>
+      </c>
+      <c r="AB52">
+        <v>2.4</v>
+      </c>
+      <c r="AC52">
+        <v>2.4</v>
+      </c>
+      <c r="AD52">
+        <v>1.58</v>
+      </c>
+      <c r="AE52">
         <v>1.2</v>
       </c>
-      <c r="T52">
-        <v>4.33</v>
-      </c>
-      <c r="U52">
-        <v>1.95</v>
-      </c>
-      <c r="V52">
-        <v>1.75</v>
-      </c>
-      <c r="W52">
-        <v>1.22</v>
-      </c>
-      <c r="X52">
-        <v>0</v>
-      </c>
-      <c r="Y52">
-        <v>1.11</v>
-      </c>
-      <c r="Z52">
-        <v>6.25</v>
-      </c>
-      <c r="AA52">
-        <v>1.38</v>
-      </c>
-      <c r="AB52">
-        <v>2.87</v>
-      </c>
-      <c r="AC52">
-        <v>1.75</v>
-      </c>
-      <c r="AD52">
-        <v>1.83</v>
-      </c>
-      <c r="AE52">
-        <v>1.33</v>
-      </c>
       <c r="AF52">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="AG52">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>4.66</v>
       </c>
       <c r="P54">
+        <v>3.9</v>
+      </c>
+      <c r="Q54">
         <v>2.15</v>
       </c>
-      <c r="Q54">
-        <v>3.7</v>
-      </c>
       <c r="R54">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="S54">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T54">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="U54">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="V54">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="W54">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="X54">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y54">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z54">
-        <v>4.65</v>
+        <v>6.25</v>
       </c>
       <c r="AA54">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AB54">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="AC54">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="AD54">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AE54">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AF54">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AG54">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK54">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="O56">
-        <v>4.06</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="Q56">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="R56">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S56">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T56">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U56">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="V56">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W56">
+        <v>1.15</v>
+      </c>
+      <c r="X56">
+        <v>1.03</v>
+      </c>
+      <c r="Y56">
         <v>1.13</v>
       </c>
-      <c r="X56">
-        <v>1.01</v>
-      </c>
-      <c r="Y56">
-        <v>1.12</v>
-      </c>
       <c r="Z56">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="AA56">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB56">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC56">
         <v>2.4</v>
       </c>
       <c r="AD56">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AE56">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF56">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG56">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK56">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,80 +12697,80 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="O76">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P76">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="Q76">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="R76">
-        <v>2.58</v>
+        <v>2.21</v>
       </c>
       <c r="S76">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="T76">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="U76">
-        <v>1.82</v>
+        <v>2.45</v>
       </c>
       <c r="V76">
-        <v>1.93</v>
+        <v>1.48</v>
       </c>
       <c r="W76">
+        <v>1.11</v>
+      </c>
+      <c r="X76">
+        <v>1.04</v>
+      </c>
+      <c r="Y76">
+        <v>1.22</v>
+      </c>
+      <c r="Z76">
+        <v>4</v>
+      </c>
+      <c r="AA76">
+        <v>1.71</v>
+      </c>
+      <c r="AB76">
+        <v>2.1</v>
+      </c>
+      <c r="AC76">
+        <v>2.8</v>
+      </c>
+      <c r="AD76">
+        <v>1.42</v>
+      </c>
+      <c r="AE76">
+        <v>1.11</v>
+      </c>
+      <c r="AF76">
+        <v>1.62</v>
+      </c>
+      <c r="AG76">
+        <v>2.2</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ76">
         <v>1.25</v>
       </c>
-      <c r="X76">
-        <v>0</v>
-      </c>
-      <c r="Y76">
-        <v>1.04</v>
-      </c>
-      <c r="Z76">
-        <v>7.1</v>
-      </c>
-      <c r="AA76">
-        <v>1.28</v>
-      </c>
-      <c r="AB76">
-        <v>3.6</v>
-      </c>
-      <c r="AC76">
-        <v>1.65</v>
-      </c>
-      <c r="AD76">
-        <v>2.2</v>
-      </c>
-      <c r="AE76">
-        <v>1.44</v>
-      </c>
-      <c r="AF76">
-        <v>1.25</v>
-      </c>
-      <c r="AG76">
-        <v>3.6</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ76">
-        <v>1.22</v>
-      </c>
       <c r="AK76">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="O77">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P77">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q77">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R77">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="S77">
+        <v>1.17</v>
+      </c>
+      <c r="T77">
+        <v>4.8</v>
+      </c>
+      <c r="U77">
+        <v>1.82</v>
+      </c>
+      <c r="V77">
+        <v>1.93</v>
+      </c>
+      <c r="W77">
+        <v>1.25</v>
+      </c>
+      <c r="X77">
+        <v>0</v>
+      </c>
+      <c r="Y77">
+        <v>1.04</v>
+      </c>
+      <c r="Z77">
+        <v>7.1</v>
+      </c>
+      <c r="AA77">
         <v>1.28</v>
       </c>
-      <c r="T77">
-        <v>3.3</v>
-      </c>
-      <c r="U77">
-        <v>2.28</v>
-      </c>
-      <c r="V77">
-        <v>1.53</v>
-      </c>
-      <c r="W77">
-        <v>1.13</v>
-      </c>
-      <c r="X77">
-        <v>1.01</v>
-      </c>
-      <c r="Y77">
-        <v>1.2</v>
-      </c>
-      <c r="Z77">
-        <v>4.2</v>
-      </c>
-      <c r="AA77">
-        <v>1.66</v>
-      </c>
       <c r="AB77">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="AC77">
-        <v>2.48</v>
+        <v>1.65</v>
       </c>
       <c r="AD77">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="AE77">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AF77">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AG77">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK77">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.49</v>
+        <v>1.91</v>
       </c>
       <c r="O78">
         <v>3.5</v>
       </c>
       <c r="P78">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="Q78">
-        <v>3.05</v>
+        <v>2.45</v>
       </c>
       <c r="R78">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S78">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T78">
         <v>3.3</v>
       </c>
       <c r="U78">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="V78">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W78">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X78">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z78">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA78">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AB78">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC78">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="AD78">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE78">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF78">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG78">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
+        <v>1.29</v>
+      </c>
+      <c r="O82">
+        <v>6</v>
+      </c>
+      <c r="P82">
+        <v>8.5</v>
+      </c>
+      <c r="Q82">
         <v>1.62</v>
       </c>
-      <c r="O82">
-        <v>4.92</v>
-      </c>
-      <c r="P82">
-        <v>4.3</v>
-      </c>
-      <c r="Q82">
+      <c r="R82">
+        <v>2.75</v>
+      </c>
+      <c r="S82">
+        <v>1.18</v>
+      </c>
+      <c r="T82">
+        <v>4.33</v>
+      </c>
+      <c r="U82">
+        <v>2.01</v>
+      </c>
+      <c r="V82">
+        <v>1.75</v>
+      </c>
+      <c r="W82">
+        <v>1.2</v>
+      </c>
+      <c r="X82">
+        <v>0</v>
+      </c>
+      <c r="Y82">
+        <v>1.08</v>
+      </c>
+      <c r="Z82">
+        <v>5.55</v>
+      </c>
+      <c r="AA82">
+        <v>1.4</v>
+      </c>
+      <c r="AB82">
+        <v>2.87</v>
+      </c>
+      <c r="AC82">
         <v>1.95</v>
       </c>
-      <c r="R82">
-        <v>2.7</v>
-      </c>
-      <c r="S82">
-        <v>1.16</v>
-      </c>
-      <c r="T82">
-        <v>4.8</v>
-      </c>
-      <c r="U82">
-        <v>1.8</v>
-      </c>
-      <c r="V82">
-        <v>1.84</v>
-      </c>
-      <c r="W82">
-        <v>1.25</v>
-      </c>
-      <c r="X82">
-        <v>0</v>
-      </c>
-      <c r="Y82">
-        <v>1.05</v>
-      </c>
-      <c r="Z82">
-        <v>8</v>
-      </c>
-      <c r="AA82">
-        <v>1.3</v>
-      </c>
-      <c r="AB82">
-        <v>3.3</v>
-      </c>
-      <c r="AC82">
-        <v>1.78</v>
-      </c>
       <c r="AD82">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AE82">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="AF82">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="AG82">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AK82">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="O83">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="P83">
-        <v>8.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q83">
+        <v>2.38</v>
+      </c>
+      <c r="R83">
+        <v>2.4</v>
+      </c>
+      <c r="S83">
+        <v>1.22</v>
+      </c>
+      <c r="T83">
+        <v>3.8</v>
+      </c>
+      <c r="U83">
+        <v>2.16</v>
+      </c>
+      <c r="V83">
+        <v>1.65</v>
+      </c>
+      <c r="W83">
+        <v>1.15</v>
+      </c>
+      <c r="X83">
+        <v>1.01</v>
+      </c>
+      <c r="Y83">
+        <v>1.15</v>
+      </c>
+      <c r="Z83">
+        <v>5.25</v>
+      </c>
+      <c r="AA83">
+        <v>1.5</v>
+      </c>
+      <c r="AB83">
+        <v>2.55</v>
+      </c>
+      <c r="AC83">
+        <v>2.12</v>
+      </c>
+      <c r="AD83">
         <v>1.62</v>
       </c>
-      <c r="R83">
-        <v>2.75</v>
-      </c>
-      <c r="S83">
-        <v>1.18</v>
-      </c>
-      <c r="T83">
-        <v>4.33</v>
-      </c>
-      <c r="U83">
-        <v>2.01</v>
-      </c>
-      <c r="V83">
-        <v>1.75</v>
-      </c>
-      <c r="W83">
-        <v>1.2</v>
-      </c>
-      <c r="X83">
-        <v>0</v>
-      </c>
-      <c r="Y83">
-        <v>1.08</v>
-      </c>
-      <c r="Z83">
-        <v>5.55</v>
-      </c>
-      <c r="AA83">
-        <v>1.4</v>
-      </c>
-      <c r="AB83">
-        <v>2.87</v>
-      </c>
-      <c r="AC83">
-        <v>1.95</v>
-      </c>
-      <c r="AD83">
-        <v>1.87</v>
-      </c>
       <c r="AE83">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF83">
+        <v>1.44</v>
+      </c>
+      <c r="AG83">
+        <v>2.7</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
+        <v>1.25</v>
+      </c>
+      <c r="AK83">
         <v>1.7</v>
-      </c>
-      <c r="AG83">
-        <v>2</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.11</v>
-      </c>
-      <c r="AK83">
-        <v>3.7</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
+        <v>1.62</v>
+      </c>
+      <c r="O84">
+        <v>4.92</v>
+      </c>
+      <c r="P84">
+        <v>4.3</v>
+      </c>
+      <c r="Q84">
         <v>1.95</v>
       </c>
-      <c r="O84">
-        <v>3.5</v>
-      </c>
-      <c r="P84">
-        <v>3.2</v>
-      </c>
-      <c r="Q84">
-        <v>2.38</v>
-      </c>
       <c r="R84">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="S84">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="T84">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="U84">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="V84">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="W84">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y84">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="Z84">
-        <v>5.25</v>
+        <v>8</v>
       </c>
       <c r="AA84">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AB84">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="AC84">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="AD84">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AE84">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AF84">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AG84">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK84">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AL84">
         <v>0</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O35">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P35">
         <v>3.42</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="O52">
-        <v>4.06</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="Q52">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="R52">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S52">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T52">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U52">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="V52">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W52">
+        <v>1.15</v>
+      </c>
+      <c r="X52">
+        <v>1.03</v>
+      </c>
+      <c r="Y52">
         <v>1.13</v>
       </c>
-      <c r="X52">
-        <v>1.01</v>
-      </c>
-      <c r="Y52">
-        <v>1.12</v>
-      </c>
       <c r="Z52">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="AA52">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB52">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC52">
         <v>2.4</v>
       </c>
       <c r="AD52">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AE52">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF52">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG52">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK52">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="O53">
-        <v>4</v>
+        <v>4.66</v>
       </c>
       <c r="P53">
-        <v>2.68</v>
+        <v>3.9</v>
       </c>
       <c r="Q53">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="R53">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="S53">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T53">
-        <v>3.28</v>
+        <v>4.33</v>
       </c>
       <c r="U53">
-        <v>2.36</v>
+        <v>1.95</v>
       </c>
       <c r="V53">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="W53">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y53">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z53">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA53">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AB53">
-        <v>2.25</v>
+        <v>2.87</v>
       </c>
       <c r="AC53">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="AD53">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AE53">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AF53">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="AG53">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK53">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="O54">
-        <v>4.66</v>
+        <v>4.32</v>
       </c>
       <c r="P54">
-        <v>3.9</v>
+        <v>3.12</v>
       </c>
       <c r="Q54">
+        <v>2.52</v>
+      </c>
+      <c r="R54">
+        <v>2.4</v>
+      </c>
+      <c r="S54">
+        <v>1.22</v>
+      </c>
+      <c r="T54">
+        <v>3.8</v>
+      </c>
+      <c r="U54">
         <v>2.15</v>
       </c>
-      <c r="R54">
-        <v>2.62</v>
-      </c>
-      <c r="S54">
-        <v>1.2</v>
-      </c>
-      <c r="T54">
-        <v>4.33</v>
-      </c>
-      <c r="U54">
-        <v>1.95</v>
-      </c>
       <c r="V54">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="W54">
+        <v>1.14</v>
+      </c>
+      <c r="X54">
+        <v>1.01</v>
+      </c>
+      <c r="Y54">
+        <v>1.14</v>
+      </c>
+      <c r="Z54">
+        <v>5.5</v>
+      </c>
+      <c r="AA54">
+        <v>1.48</v>
+      </c>
+      <c r="AB54">
+        <v>2.5</v>
+      </c>
+      <c r="AC54">
+        <v>2.2</v>
+      </c>
+      <c r="AD54">
+        <v>1.62</v>
+      </c>
+      <c r="AE54">
         <v>1.22</v>
       </c>
-      <c r="X54">
-        <v>0</v>
-      </c>
-      <c r="Y54">
-        <v>1.11</v>
-      </c>
-      <c r="Z54">
-        <v>6.25</v>
-      </c>
-      <c r="AA54">
-        <v>1.38</v>
-      </c>
-      <c r="AB54">
-        <v>2.87</v>
-      </c>
-      <c r="AC54">
-        <v>1.75</v>
-      </c>
-      <c r="AD54">
-        <v>1.83</v>
-      </c>
-      <c r="AE54">
-        <v>1.33</v>
-      </c>
       <c r="AF54">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AG54">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AK54">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,19 +9274,19 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="O55">
-        <v>4.32</v>
+        <v>4.06</v>
       </c>
       <c r="P55">
-        <v>3.12</v>
+        <v>2.62</v>
       </c>
       <c r="Q55">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="R55">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S55">
         <v>1.22</v>
@@ -9298,40 +9298,40 @@
         <v>2.15</v>
       </c>
       <c r="V55">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W55">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X55">
         <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z55">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA55">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AB55">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC55">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AD55">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AE55">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF55">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG55">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,80 +9437,80 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P56">
-        <v>2.15</v>
+        <v>2.68</v>
       </c>
       <c r="Q56">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="R56">
+        <v>2.23</v>
+      </c>
+      <c r="S56">
+        <v>1.29</v>
+      </c>
+      <c r="T56">
+        <v>3.28</v>
+      </c>
+      <c r="U56">
+        <v>2.36</v>
+      </c>
+      <c r="V56">
+        <v>1.52</v>
+      </c>
+      <c r="W56">
+        <v>1.09</v>
+      </c>
+      <c r="X56">
+        <v>1.01</v>
+      </c>
+      <c r="Y56">
+        <v>1.18</v>
+      </c>
+      <c r="Z56">
+        <v>4.5</v>
+      </c>
+      <c r="AA56">
+        <v>1.62</v>
+      </c>
+      <c r="AB56">
+        <v>2.25</v>
+      </c>
+      <c r="AC56">
+        <v>2.6</v>
+      </c>
+      <c r="AD56">
+        <v>1.5</v>
+      </c>
+      <c r="AE56">
+        <v>1.16</v>
+      </c>
+      <c r="AF56">
+        <v>1.53</v>
+      </c>
+      <c r="AG56">
         <v>2.4</v>
       </c>
-      <c r="S56">
-        <v>1.25</v>
-      </c>
-      <c r="T56">
-        <v>3.5</v>
-      </c>
-      <c r="U56">
-        <v>2.31</v>
-      </c>
-      <c r="V56">
-        <v>1.57</v>
-      </c>
-      <c r="W56">
-        <v>1.15</v>
-      </c>
-      <c r="X56">
-        <v>1.03</v>
-      </c>
-      <c r="Y56">
-        <v>1.13</v>
-      </c>
-      <c r="Z56">
-        <v>4.65</v>
-      </c>
-      <c r="AA56">
-        <v>1.57</v>
-      </c>
-      <c r="AB56">
-        <v>2.35</v>
-      </c>
-      <c r="AC56">
-        <v>2.4</v>
-      </c>
-      <c r="AD56">
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <v>1.36</v>
+      </c>
+      <c r="AK56">
         <v>1.55</v>
-      </c>
-      <c r="AE56">
-        <v>1.18</v>
-      </c>
-      <c r="AF56">
-        <v>1.5</v>
-      </c>
-      <c r="AG56">
-        <v>2.45</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>1.26</v>
-      </c>
-      <c r="AK56">
-        <v>1.4</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,80 +12860,80 @@
         </is>
       </c>
       <c r="N77">
+        <v>1.91</v>
+      </c>
+      <c r="O77">
+        <v>3.5</v>
+      </c>
+      <c r="P77">
+        <v>3.3</v>
+      </c>
+      <c r="Q77">
+        <v>2.45</v>
+      </c>
+      <c r="R77">
+        <v>2.3</v>
+      </c>
+      <c r="S77">
+        <v>1.28</v>
+      </c>
+      <c r="T77">
+        <v>3.3</v>
+      </c>
+      <c r="U77">
+        <v>2.28</v>
+      </c>
+      <c r="V77">
+        <v>1.53</v>
+      </c>
+      <c r="W77">
+        <v>1.13</v>
+      </c>
+      <c r="X77">
+        <v>1.01</v>
+      </c>
+      <c r="Y77">
+        <v>1.2</v>
+      </c>
+      <c r="Z77">
+        <v>4.2</v>
+      </c>
+      <c r="AA77">
+        <v>1.66</v>
+      </c>
+      <c r="AB77">
         <v>2.15</v>
       </c>
-      <c r="O77">
-        <v>3.8</v>
-      </c>
-      <c r="P77">
-        <v>2.7</v>
-      </c>
-      <c r="Q77">
-        <v>2.5</v>
-      </c>
-      <c r="R77">
-        <v>2.58</v>
-      </c>
-      <c r="S77">
-        <v>1.17</v>
-      </c>
-      <c r="T77">
-        <v>4.8</v>
-      </c>
-      <c r="U77">
-        <v>1.82</v>
-      </c>
-      <c r="V77">
-        <v>1.93</v>
-      </c>
-      <c r="W77">
+      <c r="AC77">
+        <v>2.48</v>
+      </c>
+      <c r="AD77">
+        <v>1.45</v>
+      </c>
+      <c r="AE77">
+        <v>1.14</v>
+      </c>
+      <c r="AF77">
+        <v>1.55</v>
+      </c>
+      <c r="AG77">
+        <v>2.3</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ77">
         <v>1.25</v>
       </c>
-      <c r="X77">
-        <v>0</v>
-      </c>
-      <c r="Y77">
-        <v>1.04</v>
-      </c>
-      <c r="Z77">
-        <v>7.1</v>
-      </c>
-      <c r="AA77">
-        <v>1.28</v>
-      </c>
-      <c r="AB77">
-        <v>3.6</v>
-      </c>
-      <c r="AC77">
-        <v>1.65</v>
-      </c>
-      <c r="AD77">
-        <v>2.2</v>
-      </c>
-      <c r="AE77">
-        <v>1.44</v>
-      </c>
-      <c r="AF77">
-        <v>1.25</v>
-      </c>
-      <c r="AG77">
-        <v>3.6</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ77">
-        <v>1.22</v>
-      </c>
       <c r="AK77">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="O78">
+        <v>4.34</v>
+      </c>
+      <c r="P78">
+        <v>4.2</v>
+      </c>
+      <c r="Q78">
+        <v>2.23</v>
+      </c>
+      <c r="R78">
+        <v>2.32</v>
+      </c>
+      <c r="S78">
+        <v>1.25</v>
+      </c>
+      <c r="T78">
         <v>3.5</v>
       </c>
-      <c r="P78">
-        <v>3.3</v>
-      </c>
-      <c r="Q78">
-        <v>2.45</v>
-      </c>
-      <c r="R78">
-        <v>2.3</v>
-      </c>
-      <c r="S78">
-        <v>1.28</v>
-      </c>
-      <c r="T78">
-        <v>3.3</v>
-      </c>
       <c r="U78">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="V78">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W78">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X78">
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z78">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AA78">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AB78">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AC78">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="AD78">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE78">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AF78">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG78">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="O79">
-        <v>4.34</v>
+        <v>3.8</v>
       </c>
       <c r="P79">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q79">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="R79">
-        <v>2.32</v>
+        <v>2.58</v>
       </c>
       <c r="S79">
+        <v>1.17</v>
+      </c>
+      <c r="T79">
+        <v>4.8</v>
+      </c>
+      <c r="U79">
+        <v>1.82</v>
+      </c>
+      <c r="V79">
+        <v>1.93</v>
+      </c>
+      <c r="W79">
         <v>1.25</v>
       </c>
-      <c r="T79">
-        <v>3.5</v>
-      </c>
-      <c r="U79">
+      <c r="X79">
+        <v>0</v>
+      </c>
+      <c r="Y79">
+        <v>1.04</v>
+      </c>
+      <c r="Z79">
+        <v>7.1</v>
+      </c>
+      <c r="AA79">
+        <v>1.28</v>
+      </c>
+      <c r="AB79">
+        <v>3.6</v>
+      </c>
+      <c r="AC79">
+        <v>1.65</v>
+      </c>
+      <c r="AD79">
         <v>2.2</v>
       </c>
-      <c r="V79">
-        <v>1.57</v>
-      </c>
-      <c r="W79">
-        <v>1.15</v>
-      </c>
-      <c r="X79">
-        <v>1.01</v>
-      </c>
-      <c r="Y79">
-        <v>1.16</v>
-      </c>
-      <c r="Z79">
-        <v>5</v>
-      </c>
-      <c r="AA79">
-        <v>1.54</v>
-      </c>
-      <c r="AB79">
-        <v>2.3</v>
-      </c>
-      <c r="AC79">
-        <v>2.35</v>
-      </c>
-      <c r="AD79">
-        <v>1.46</v>
-      </c>
       <c r="AE79">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AF79">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AG79">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AL79">
         <v>0</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -1640,28 +1640,28 @@
         <v>1.2</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y8">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="Z8">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AA8">
         <v>2.78</v>
       </c>
       <c r="AB8">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC8">
-        <v>6.5</v>
+        <v>5.85</v>
       </c>
       <c r="AD8">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE8">
         <v>1.01</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK8">
         <v>1.33</v>
@@ -1791,7 +1791,7 @@
         <v>2</v>
       </c>
       <c r="S9">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="T9">
         <v>2.55</v>
@@ -1803,28 +1803,28 @@
         <v>1.32</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y9">
         <v>1.42</v>
       </c>
       <c r="Z9">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="AA9">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="AB9">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC9">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="AD9">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE9">
         <v>1.02</v>
@@ -1833,7 +1833,7 @@
         <v>2.7</v>
       </c>
       <c r="AG9">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AK9">
         <v>2.5</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="O16">
         <v>3.59</v>
@@ -2947,7 +2947,7 @@
         <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
         <v>1.18</v>
@@ -3898,7 +3898,7 @@
         <v>1.33</v>
       </c>
       <c r="O22">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="P22">
         <v>8</v>
@@ -3907,7 +3907,7 @@
         <v>1.6</v>
       </c>
       <c r="R22">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="S22">
         <v>1.18</v>
@@ -3916,10 +3916,10 @@
         <v>4.33</v>
       </c>
       <c r="U22">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="V22">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="W22">
         <v>1.25</v>
@@ -3968,7 +3968,7 @@
         <v>1.05</v>
       </c>
       <c r="AK22">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,16 +4221,16 @@
         </is>
       </c>
       <c r="N24">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="O24">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P24">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="Q24">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="R24">
         <v>2.2</v>
@@ -4239,13 +4239,13 @@
         <v>1.4</v>
       </c>
       <c r="T24">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="U24">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="V24">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
         <v>1.07</v>
@@ -4254,25 +4254,25 @@
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z24">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AA24">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AB24">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AC24">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD24">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE24">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF24">
         <v>2.25</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         <v>2.87</v>
       </c>
       <c r="O25">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="P25">
         <v>2.69</v>
@@ -4396,7 +4396,7 @@
         <v>3.92</v>
       </c>
       <c r="R25">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="S25">
         <v>1.64</v>
@@ -4405,16 +4405,16 @@
         <v>2.05</v>
       </c>
       <c r="U25">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="V25">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W25">
         <v>1.01</v>
       </c>
       <c r="X25">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Y25">
         <v>1.58</v>
@@ -4426,19 +4426,19 @@
         <v>2.88</v>
       </c>
       <c r="AB25">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AC25">
-        <v>5.96</v>
+        <v>5.65</v>
       </c>
       <c r="AD25">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AE25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF25">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AG25">
         <v>1.57</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AK25">
         <v>1.36</v>
@@ -5697,55 +5697,55 @@
         <v>15</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X33">
         <v>0</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5854,19 +5854,19 @@
         <v>3.35</v>
       </c>
       <c r="O34">
-        <v>3.65</v>
+        <v>3.73</v>
       </c>
       <c r="P34">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Q34">
         <v>3.78</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="S34">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
         <v>3.48</v>
@@ -5881,10 +5881,10 @@
         <v>1.13</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z34">
         <v>4.53</v>
@@ -5905,10 +5905,10 @@
         <v>1.16</v>
       </c>
       <c r="AF34">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG34">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
+        <v>1.77</v>
+      </c>
+      <c r="AK34">
         <v>1.24</v>
-      </c>
-      <c r="AK34">
-        <v>1.28</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -8785,31 +8785,31 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="P52">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q52">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="R52">
         <v>2.4</v>
       </c>
       <c r="S52">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U52">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="V52">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W52">
         <v>1.15</v>
@@ -8818,13 +8818,13 @@
         <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z52">
-        <v>4.65</v>
+        <v>4.25</v>
       </c>
       <c r="AA52">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB52">
         <v>2.35</v>
@@ -8836,7 +8836,7 @@
         <v>1.55</v>
       </c>
       <c r="AE52">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF52">
         <v>1.5</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK52">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.67</v>
+        <v>2.07</v>
       </c>
       <c r="O53">
-        <v>4.66</v>
+        <v>3.95</v>
       </c>
       <c r="P53">
+        <v>3.36</v>
+      </c>
+      <c r="Q53">
+        <v>2.46</v>
+      </c>
+      <c r="R53">
+        <v>2.38</v>
+      </c>
+      <c r="S53">
+        <v>1.22</v>
+      </c>
+      <c r="T53">
         <v>3.9</v>
       </c>
-      <c r="Q53">
-        <v>2.15</v>
-      </c>
-      <c r="R53">
-        <v>2.62</v>
-      </c>
-      <c r="S53">
-        <v>1.2</v>
-      </c>
-      <c r="T53">
-        <v>4.33</v>
-      </c>
       <c r="U53">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="V53">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="W53">
+        <v>1.14</v>
+      </c>
+      <c r="X53">
+        <v>1.01</v>
+      </c>
+      <c r="Y53">
+        <v>1.14</v>
+      </c>
+      <c r="Z53">
+        <v>5.5</v>
+      </c>
+      <c r="AA53">
+        <v>1.45</v>
+      </c>
+      <c r="AB53">
+        <v>2.5</v>
+      </c>
+      <c r="AC53">
+        <v>2.2</v>
+      </c>
+      <c r="AD53">
+        <v>1.65</v>
+      </c>
+      <c r="AE53">
         <v>1.22</v>
       </c>
-      <c r="X53">
-        <v>0</v>
-      </c>
-      <c r="Y53">
-        <v>1.11</v>
-      </c>
-      <c r="Z53">
-        <v>6.25</v>
-      </c>
-      <c r="AA53">
-        <v>1.38</v>
-      </c>
-      <c r="AB53">
-        <v>2.87</v>
-      </c>
-      <c r="AC53">
-        <v>1.75</v>
-      </c>
-      <c r="AD53">
-        <v>1.83</v>
-      </c>
-      <c r="AE53">
-        <v>1.33</v>
-      </c>
       <c r="AF53">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AG53">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AK53">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,19 +9111,19 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="O54">
-        <v>4.32</v>
+        <v>3.68</v>
       </c>
       <c r="P54">
-        <v>3.12</v>
+        <v>2.62</v>
       </c>
       <c r="Q54">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="R54">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S54">
         <v>1.22</v>
@@ -9132,43 +9132,43 @@
         <v>3.8</v>
       </c>
       <c r="U54">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="V54">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W54">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X54">
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z54">
-        <v>5.5</v>
+        <v>4.65</v>
       </c>
       <c r="AA54">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AB54">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC54">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AD54">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE54">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF54">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG54">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AK54">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,65 +9274,65 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="O55">
-        <v>4.06</v>
+        <v>3.5</v>
       </c>
       <c r="P55">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q55">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="R55">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S55">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T55">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="U55">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="V55">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W55">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X55">
         <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="Z55">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA55">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AB55">
+        <v>2.25</v>
+      </c>
+      <c r="AC55">
+        <v>2.6</v>
+      </c>
+      <c r="AD55">
+        <v>1.5</v>
+      </c>
+      <c r="AE55">
+        <v>1.16</v>
+      </c>
+      <c r="AF55">
+        <v>1.53</v>
+      </c>
+      <c r="AG55">
         <v>2.4</v>
       </c>
-      <c r="AC55">
-        <v>2.4</v>
-      </c>
-      <c r="AD55">
-        <v>1.58</v>
-      </c>
-      <c r="AE55">
-        <v>1.2</v>
-      </c>
-      <c r="AF55">
-        <v>1.47</v>
-      </c>
-      <c r="AG55">
-        <v>2.55</v>
-      </c>
       <c r="AH55" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK55">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="O56">
-        <v>4</v>
+        <v>4.46</v>
       </c>
       <c r="P56">
-        <v>2.68</v>
+        <v>3.9</v>
       </c>
       <c r="Q56">
-        <v>2.63</v>
+        <v>2.11</v>
       </c>
       <c r="R56">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="S56">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T56">
-        <v>3.28</v>
+        <v>4.33</v>
       </c>
       <c r="U56">
-        <v>2.36</v>
+        <v>1.95</v>
       </c>
       <c r="V56">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="W56">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y56">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z56">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA56">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AB56">
-        <v>2.25</v>
+        <v>2.87</v>
       </c>
       <c r="AC56">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="AD56">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AE56">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AF56">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="AG56">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>1.55</v>
+        <v>2.14</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="O75">
-        <v>3.4</v>
+        <v>3.66</v>
       </c>
       <c r="P75">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12697,19 +12697,19 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="O76">
         <v>3.5</v>
       </c>
       <c r="P76">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="Q76">
         <v>3.05</v>
       </c>
       <c r="R76">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="S76">
         <v>1.29</v>
@@ -12736,7 +12736,7 @@
         <v>4</v>
       </c>
       <c r="AA76">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB76">
         <v>2.1</v>
@@ -12751,7 +12751,7 @@
         <v>1.11</v>
       </c>
       <c r="AF76">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG76">
         <v>2.2</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK76">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         <v>3.5</v>
       </c>
       <c r="P77">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="Q77">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="R77">
         <v>2.3</v>
@@ -12878,13 +12878,13 @@
         <v>1.28</v>
       </c>
       <c r="T77">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="U77">
         <v>2.28</v>
       </c>
       <c r="V77">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W77">
         <v>1.13</v>
@@ -12896,22 +12896,22 @@
         <v>1.2</v>
       </c>
       <c r="Z77">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA77">
         <v>1.66</v>
       </c>
       <c r="AB77">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AC77">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="AD77">
         <v>1.45</v>
       </c>
       <c r="AE77">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF77">
         <v>1.55</v>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK77">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13026,16 +13026,16 @@
         <v>1.61</v>
       </c>
       <c r="O78">
-        <v>4.34</v>
+        <v>3.8</v>
       </c>
       <c r="P78">
         <v>4.2</v>
       </c>
       <c r="Q78">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="R78">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="S78">
         <v>1.25</v>
@@ -13071,16 +13071,16 @@
         <v>2.35</v>
       </c>
       <c r="AD78">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AE78">
         <v>1.22</v>
       </c>
       <c r="AF78">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG78">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK78">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13198,19 +13198,19 @@
         <v>2.5</v>
       </c>
       <c r="R79">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="S79">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T79">
         <v>4.8</v>
       </c>
       <c r="U79">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="V79">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="W79">
         <v>1.25</v>
@@ -13219,13 +13219,13 @@
         <v>0</v>
       </c>
       <c r="Y79">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z79">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="AA79">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AB79">
         <v>3.6</v>
@@ -13237,7 +13237,7 @@
         <v>2.2</v>
       </c>
       <c r="AE79">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF79">
         <v>1.25</v>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK79">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13696,10 +13696,10 @@
         <v>4.33</v>
       </c>
       <c r="U82">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="V82">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W82">
         <v>1.2</v>
@@ -13711,28 +13711,28 @@
         <v>1.08</v>
       </c>
       <c r="Z82">
-        <v>5.55</v>
+        <v>7</v>
       </c>
       <c r="AA82">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB82">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="AC82">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AD82">
         <v>1.87</v>
       </c>
       <c r="AE82">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF82">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG82">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AK82">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13844,10 +13844,10 @@
         <v>3.5</v>
       </c>
       <c r="P83">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q83">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R83">
         <v>2.4</v>
@@ -13859,7 +13859,7 @@
         <v>3.8</v>
       </c>
       <c r="U83">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V83">
         <v>1.65</v>
@@ -13911,7 +13911,7 @@
         <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,31 +14001,31 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="O84">
-        <v>4.92</v>
+        <v>4.26</v>
       </c>
       <c r="P84">
-        <v>4.3</v>
+        <v>3.92</v>
       </c>
       <c r="Q84">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R84">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="S84">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T84">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="U84">
         <v>1.8</v>
       </c>
       <c r="V84">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="W84">
         <v>1.25</v>
@@ -14034,22 +14034,22 @@
         <v>0</v>
       </c>
       <c r="Y84">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z84">
-        <v>8</v>
+        <v>6.76</v>
       </c>
       <c r="AA84">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AB84">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AC84">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AD84">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AE84">
         <v>1.48</v>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK84">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AL84">
         <v>0</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -2600,7 +2600,7 @@
         <v>3.09</v>
       </c>
       <c r="Q14">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="R14">
         <v>2.17</v>
@@ -2618,7 +2618,7 @@
         <v>1.46</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
         <v>1.01</v>
@@ -2648,7 +2648,7 @@
         <v>1.58</v>
       </c>
       <c r="AG14">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="O20">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q20">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R20">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="S20">
         <v>1.15</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U20">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V20">
         <v>2</v>
       </c>
       <c r="W20">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Z20">
         <v>10</v>
       </c>
       <c r="AA20">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AB20">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AC20">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AD20">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AE20">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AF20">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG20">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AK20">
-        <v>6.95</v>
+        <v>6.85</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="O21">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="P21">
         <v>9.65</v>
@@ -3747,7 +3747,7 @@
         <v>3.2</v>
       </c>
       <c r="S21">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T21">
         <v>5</v>
@@ -3765,16 +3765,16 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z21">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="AA21">
         <v>1.25</v>
       </c>
       <c r="AB21">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AC21">
         <v>1.76</v>
@@ -4550,61 +4550,61 @@
         <v>2.55</v>
       </c>
       <c r="O26">
-        <v>3.59</v>
+        <v>3.45</v>
       </c>
       <c r="P26">
         <v>2.39</v>
       </c>
       <c r="Q26">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R26">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="S26">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="U26">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="V26">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
         <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z26">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="AA26">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AB26">
         <v>2</v>
       </c>
       <c r="AC26">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="AD26">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AE26">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AG26">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AK26">
         <v>1.4</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O27">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q27">
         <v>3.1</v>
@@ -4728,46 +4728,46 @@
         <v>1.3</v>
       </c>
       <c r="T27">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="U27">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V27">
         <v>1.49</v>
       </c>
       <c r="W27">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z27">
-        <v>3.96</v>
+        <v>3.75</v>
       </c>
       <c r="AA27">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB27">
         <v>2.08</v>
       </c>
       <c r="AC27">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AD27">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE27">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF27">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AG27">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q28">
-        <v>2.41</v>
+        <v>2.51</v>
       </c>
       <c r="R28">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
         <v>1.28</v>
@@ -4894,10 +4894,10 @@
         <v>3.25</v>
       </c>
       <c r="U28">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="V28">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="W28">
         <v>1.09</v>
@@ -4915,22 +4915,22 @@
         <v>1.58</v>
       </c>
       <c r="AB28">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="AC28">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD28">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE28">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF28">
         <v>1.53</v>
       </c>
       <c r="AG28">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,25 +5045,25 @@
         <v>3.25</v>
       </c>
       <c r="Q29">
-        <v>2.72</v>
+        <v>2.57</v>
       </c>
       <c r="R29">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="S29">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T29">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="U29">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="V29">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="W29">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X29">
         <v>1.02</v>
@@ -5072,28 +5072,28 @@
         <v>1.15</v>
       </c>
       <c r="Z29">
-        <v>4.7</v>
+        <v>3.98</v>
       </c>
       <c r="AA29">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AB29">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AC29">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="AD29">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AE29">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF29">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AG29">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK29">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,25 +5199,25 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="O30">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P30">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q30">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="R30">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S30">
         <v>1.25</v>
       </c>
       <c r="T30">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="U30">
         <v>2.32</v>
@@ -5226,19 +5226,19 @@
         <v>1.52</v>
       </c>
       <c r="W30">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z30">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="AA30">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB30">
         <v>2.16</v>
@@ -5253,10 +5253,10 @@
         <v>1.14</v>
       </c>
       <c r="AF30">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG30">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK30">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.06</v>
+        <v>3.35</v>
       </c>
       <c r="O33">
-        <v>11</v>
+        <v>3.73</v>
       </c>
       <c r="P33">
-        <v>15</v>
+        <v>1.96</v>
       </c>
       <c r="Q33">
-        <v>1.32</v>
+        <v>3.78</v>
       </c>
       <c r="R33">
-        <v>3.8</v>
+        <v>2.43</v>
       </c>
       <c r="S33">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>5.85</v>
+        <v>3.48</v>
       </c>
       <c r="U33">
-        <v>1.67</v>
+        <v>2.19</v>
       </c>
       <c r="V33">
-        <v>2.07</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Z33">
-        <v>9.5</v>
+        <v>4.53</v>
       </c>
       <c r="AA33">
+        <v>1.61</v>
+      </c>
+      <c r="AB33">
+        <v>2.23</v>
+      </c>
+      <c r="AC33">
+        <v>2.49</v>
+      </c>
+      <c r="AD33">
+        <v>1.45</v>
+      </c>
+      <c r="AE33">
         <v>1.16</v>
       </c>
-      <c r="AB33">
-        <v>4.05</v>
-      </c>
-      <c r="AC33">
-        <v>1.57</v>
-      </c>
-      <c r="AD33">
-        <v>2.31</v>
-      </c>
-      <c r="AE33">
-        <v>1.52</v>
-      </c>
       <c r="AF33">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AG33">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="AK33">
-        <v>7.9</v>
+        <v>1.24</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.35</v>
+        <v>1.06</v>
       </c>
       <c r="O34">
-        <v>3.73</v>
+        <v>11</v>
       </c>
       <c r="P34">
-        <v>1.96</v>
+        <v>15</v>
       </c>
       <c r="Q34">
-        <v>3.78</v>
+        <v>1.32</v>
       </c>
       <c r="R34">
-        <v>2.43</v>
+        <v>3.8</v>
       </c>
       <c r="S34">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="T34">
-        <v>3.48</v>
+        <v>5.85</v>
       </c>
       <c r="U34">
-        <v>2.19</v>
+        <v>1.67</v>
       </c>
       <c r="V34">
+        <v>2.07</v>
+      </c>
+      <c r="W34">
+        <v>1.28</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>1.05</v>
+      </c>
+      <c r="Z34">
+        <v>9.5</v>
+      </c>
+      <c r="AA34">
+        <v>1.16</v>
+      </c>
+      <c r="AB34">
+        <v>4.05</v>
+      </c>
+      <c r="AC34">
         <v>1.57</v>
       </c>
-      <c r="W34">
-        <v>1.13</v>
-      </c>
-      <c r="X34">
-        <v>1.03</v>
-      </c>
-      <c r="Y34">
-        <v>1.15</v>
-      </c>
-      <c r="Z34">
-        <v>4.53</v>
-      </c>
-      <c r="AA34">
-        <v>1.61</v>
-      </c>
-      <c r="AB34">
-        <v>2.23</v>
-      </c>
-      <c r="AC34">
-        <v>2.49</v>
-      </c>
       <c r="AD34">
-        <v>1.45</v>
+        <v>2.31</v>
       </c>
       <c r="AE34">
-        <v>1.16</v>
+        <v>1.52</v>
       </c>
       <c r="AF34">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AG34">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="AK34">
-        <v>1.24</v>
+        <v>7.9</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="O36">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P36">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="Q36">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="R36">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="S36">
         <v>1.36</v>
@@ -6201,7 +6201,7 @@
         <v>2.88</v>
       </c>
       <c r="V36">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W36">
         <v>1.06</v>
@@ -6216,7 +6216,7 @@
         <v>3.38</v>
       </c>
       <c r="AA36">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB36">
         <v>1.78</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK36">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="O38">
         <v>5.25</v>
@@ -6512,22 +6512,22 @@
         <v>7.55</v>
       </c>
       <c r="Q38">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="R38">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="S38">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T38">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="U38">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V38">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="W38">
         <v>1.14</v>
@@ -6539,28 +6539,28 @@
         <v>1.11</v>
       </c>
       <c r="Z38">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AA38">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB38">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AC38">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AD38">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AE38">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AF38">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG38">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.18</v>
       </c>
       <c r="AK38">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,52 +6666,52 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P39">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="Q39">
-        <v>4.75</v>
+        <v>4.88</v>
       </c>
       <c r="R39">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="S39">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T39">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="U39">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="V39">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W39">
         <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z39">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AA39">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB39">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC39">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="AD39">
         <v>1.33</v>
@@ -6723,7 +6723,7 @@
         <v>1.8</v>
       </c>
       <c r="AG39">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK39">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,16 +6829,16 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="O40">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="P40">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Q40">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="R40">
         <v>2.43</v>
@@ -6853,19 +6853,19 @@
         <v>2.4</v>
       </c>
       <c r="V40">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W40">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X40">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA40">
         <v>1.66</v>
@@ -6874,10 +6874,10 @@
         <v>2.2</v>
       </c>
       <c r="AC40">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="AD40">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AE40">
         <v>1.18</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,16 +6992,16 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O41">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P41">
         <v>4.33</v>
       </c>
       <c r="Q41">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="R41">
         <v>2.38</v>
@@ -7025,28 +7025,28 @@
         <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z41">
         <v>4.6</v>
       </c>
       <c r="AA41">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB41">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC41">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AD41">
         <v>1.5</v>
       </c>
       <c r="AE41">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF41">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AG41">
         <v>2.24</v>
@@ -7155,25 +7155,25 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="O42">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P42">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Q42">
         <v>1.23</v>
       </c>
       <c r="R42">
-        <v>4.7</v>
+        <v>3.83</v>
       </c>
       <c r="S42">
         <v>1.12</v>
       </c>
       <c r="T42">
-        <v>6.15</v>
+        <v>5.5</v>
       </c>
       <c r="U42">
         <v>1.65</v>
@@ -7194,7 +7194,7 @@
         <v>8.5</v>
       </c>
       <c r="AA42">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB42">
         <v>4</v>
@@ -7206,10 +7206,10 @@
         <v>2.25</v>
       </c>
       <c r="AE42">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AF42">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AG42">
         <v>1.4</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK42">
-        <v>12</v>
+        <v>12.75</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="O43">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P43">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,7 +7490,7 @@
         <v>1.5</v>
       </c>
       <c r="Q44">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R44">
         <v>2.5</v>
@@ -7502,13 +7502,13 @@
         <v>3.8</v>
       </c>
       <c r="U44">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="V44">
         <v>1.6</v>
       </c>
       <c r="W44">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X44">
         <v>1.01</v>
@@ -7532,13 +7532,13 @@
         <v>1.58</v>
       </c>
       <c r="AE44">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF44">
         <v>1.75</v>
       </c>
       <c r="AG44">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK44">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,25 +7644,25 @@
         </is>
       </c>
       <c r="N45">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="O45">
-        <v>6.9</v>
+        <v>8.4</v>
       </c>
       <c r="P45">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Q45">
-        <v>8</v>
+        <v>11.45</v>
       </c>
       <c r="R45">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U45">
         <v>2.05</v>
@@ -7671,7 +7671,7 @@
         <v>1.66</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X45">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>1.23</v>
       </c>
       <c r="AF45">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="AG45">
         <v>1.77</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>2.1</v>
+      </c>
+      <c r="R48">
+        <v>2.26</v>
+      </c>
+      <c r="S48">
+        <v>1.4</v>
+      </c>
+      <c r="T48">
+        <v>2.75</v>
+      </c>
+      <c r="U48">
         <v>3</v>
       </c>
-      <c r="P48">
-        <v>2.45</v>
-      </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>0</v>
-      </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
-      <c r="U48">
-        <v>0</v>
-      </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.87</v>
+        <v>2.07</v>
       </c>
       <c r="O52">
-        <v>3.62</v>
+        <v>3.95</v>
       </c>
       <c r="P52">
+        <v>3.36</v>
+      </c>
+      <c r="Q52">
+        <v>2.46</v>
+      </c>
+      <c r="R52">
+        <v>2.38</v>
+      </c>
+      <c r="S52">
+        <v>1.22</v>
+      </c>
+      <c r="T52">
+        <v>3.9</v>
+      </c>
+      <c r="U52">
+        <v>2.08</v>
+      </c>
+      <c r="V52">
+        <v>1.62</v>
+      </c>
+      <c r="W52">
+        <v>1.14</v>
+      </c>
+      <c r="X52">
+        <v>1.01</v>
+      </c>
+      <c r="Y52">
+        <v>1.14</v>
+      </c>
+      <c r="Z52">
+        <v>5.5</v>
+      </c>
+      <c r="AA52">
+        <v>1.45</v>
+      </c>
+      <c r="AB52">
+        <v>2.5</v>
+      </c>
+      <c r="AC52">
         <v>2.2</v>
       </c>
-      <c r="Q52">
-        <v>3.2</v>
-      </c>
-      <c r="R52">
-        <v>2.4</v>
-      </c>
-      <c r="S52">
-        <v>1.3</v>
-      </c>
-      <c r="T52">
-        <v>3.4</v>
-      </c>
-      <c r="U52">
-        <v>2.38</v>
-      </c>
-      <c r="V52">
-        <v>1.6</v>
-      </c>
-      <c r="W52">
-        <v>1.15</v>
-      </c>
-      <c r="X52">
-        <v>1.03</v>
-      </c>
-      <c r="Y52">
-        <v>1.15</v>
-      </c>
-      <c r="Z52">
-        <v>4.25</v>
-      </c>
-      <c r="AA52">
-        <v>1.5</v>
-      </c>
-      <c r="AB52">
-        <v>2.35</v>
-      </c>
-      <c r="AC52">
-        <v>2.4</v>
-      </c>
       <c r="AD52">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AE52">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF52">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG52">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AK52">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="O53">
-        <v>3.95</v>
+        <v>3.68</v>
       </c>
       <c r="P53">
-        <v>3.36</v>
+        <v>2.62</v>
       </c>
       <c r="Q53">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="R53">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S53">
         <v>1.22</v>
       </c>
       <c r="T53">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U53">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="V53">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W53">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z53">
-        <v>5.5</v>
+        <v>4.65</v>
       </c>
       <c r="AA53">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AB53">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC53">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AD53">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AE53">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF53">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG53">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,65 +9111,65 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="O54">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q54">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="R54">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S54">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T54">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="U54">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="V54">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="W54">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X54">
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="Z54">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="AA54">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AB54">
+        <v>2.25</v>
+      </c>
+      <c r="AC54">
+        <v>2.6</v>
+      </c>
+      <c r="AD54">
+        <v>1.5</v>
+      </c>
+      <c r="AE54">
+        <v>1.16</v>
+      </c>
+      <c r="AF54">
+        <v>1.53</v>
+      </c>
+      <c r="AG54">
         <v>2.4</v>
       </c>
-      <c r="AC54">
-        <v>2.4</v>
-      </c>
-      <c r="AD54">
-        <v>1.57</v>
-      </c>
-      <c r="AE54">
-        <v>1.2</v>
-      </c>
-      <c r="AF54">
-        <v>1.47</v>
-      </c>
-      <c r="AG54">
-        <v>2.49</v>
-      </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK54">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="O55">
-        <v>3.5</v>
+        <v>4.46</v>
       </c>
       <c r="P55">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q55">
-        <v>3</v>
+        <v>2.11</v>
       </c>
       <c r="R55">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="S55">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="T55">
-        <v>3.15</v>
+        <v>4.33</v>
       </c>
       <c r="U55">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="V55">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="W55">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y55">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="Z55">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="AA55">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AB55">
-        <v>2.25</v>
+        <v>2.87</v>
       </c>
       <c r="AC55">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="AD55">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AE55">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AF55">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="AG55">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>1.53</v>
+        <v>2.14</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,80 +9437,80 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.67</v>
+        <v>2.87</v>
       </c>
       <c r="O56">
-        <v>4.46</v>
+        <v>3.62</v>
       </c>
       <c r="P56">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="Q56">
-        <v>2.11</v>
+        <v>3.2</v>
       </c>
       <c r="R56">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="S56">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T56">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="U56">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="V56">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="W56">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z56">
-        <v>6.25</v>
+        <v>4.25</v>
       </c>
       <c r="AA56">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AB56">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="AC56">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AD56">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AE56">
+        <v>1.15</v>
+      </c>
+      <c r="AF56">
+        <v>1.5</v>
+      </c>
+      <c r="AG56">
+        <v>2.45</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <v>1.28</v>
+      </c>
+      <c r="AK56">
         <v>1.36</v>
-      </c>
-      <c r="AF56">
-        <v>1.34</v>
-      </c>
-      <c r="AG56">
-        <v>2.75</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>1.22</v>
-      </c>
-      <c r="AK56">
-        <v>2.14</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9763,28 +9763,28 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="O58">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P58">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Q58">
-        <v>2.9</v>
+        <v>3.29</v>
       </c>
       <c r="R58">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="S58">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T58">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="U58">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="V58">
         <v>1.36</v>
@@ -9793,25 +9793,25 @@
         <v>1.04</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z58">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AA58">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB58">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC58">
-        <v>3.28</v>
+        <v>3.72</v>
       </c>
       <c r="AD58">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE58">
         <v>1.06</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AK58">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="O82">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="P82">
-        <v>8.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q82">
+        <v>2.5</v>
+      </c>
+      <c r="R82">
+        <v>2.4</v>
+      </c>
+      <c r="S82">
+        <v>1.22</v>
+      </c>
+      <c r="T82">
+        <v>3.8</v>
+      </c>
+      <c r="U82">
+        <v>2.1</v>
+      </c>
+      <c r="V82">
+        <v>1.65</v>
+      </c>
+      <c r="W82">
+        <v>1.15</v>
+      </c>
+      <c r="X82">
+        <v>1.01</v>
+      </c>
+      <c r="Y82">
+        <v>1.15</v>
+      </c>
+      <c r="Z82">
+        <v>5.25</v>
+      </c>
+      <c r="AA82">
+        <v>1.5</v>
+      </c>
+      <c r="AB82">
+        <v>2.55</v>
+      </c>
+      <c r="AC82">
+        <v>2.12</v>
+      </c>
+      <c r="AD82">
         <v>1.62</v>
       </c>
-      <c r="R82">
-        <v>2.75</v>
-      </c>
-      <c r="S82">
-        <v>1.18</v>
-      </c>
-      <c r="T82">
-        <v>4.33</v>
-      </c>
-      <c r="U82">
-        <v>1.95</v>
-      </c>
-      <c r="V82">
-        <v>1.8</v>
-      </c>
-      <c r="W82">
-        <v>1.2</v>
-      </c>
-      <c r="X82">
-        <v>0</v>
-      </c>
-      <c r="Y82">
-        <v>1.08</v>
-      </c>
-      <c r="Z82">
-        <v>7</v>
-      </c>
-      <c r="AA82">
-        <v>1.36</v>
-      </c>
-      <c r="AB82">
-        <v>3</v>
-      </c>
-      <c r="AC82">
-        <v>1.94</v>
-      </c>
-      <c r="AD82">
-        <v>1.87</v>
-      </c>
       <c r="AE82">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF82">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AG82">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>3.32</v>
+        <v>1.73</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="O83">
-        <v>3.5</v>
+        <v>4.26</v>
       </c>
       <c r="P83">
-        <v>3.3</v>
+        <v>3.92</v>
       </c>
       <c r="Q83">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="R83">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S83">
+        <v>1.18</v>
+      </c>
+      <c r="T83">
+        <v>4.6</v>
+      </c>
+      <c r="U83">
+        <v>1.8</v>
+      </c>
+      <c r="V83">
+        <v>1.85</v>
+      </c>
+      <c r="W83">
+        <v>1.25</v>
+      </c>
+      <c r="X83">
+        <v>0</v>
+      </c>
+      <c r="Y83">
+        <v>1.11</v>
+      </c>
+      <c r="Z83">
+        <v>6.76</v>
+      </c>
+      <c r="AA83">
+        <v>1.37</v>
+      </c>
+      <c r="AB83">
+        <v>3.1</v>
+      </c>
+      <c r="AC83">
+        <v>1.83</v>
+      </c>
+      <c r="AD83">
+        <v>1.84</v>
+      </c>
+      <c r="AE83">
+        <v>1.48</v>
+      </c>
+      <c r="AF83">
+        <v>1.38</v>
+      </c>
+      <c r="AG83">
+        <v>2.9</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
         <v>1.22</v>
       </c>
-      <c r="T83">
-        <v>3.8</v>
-      </c>
-      <c r="U83">
-        <v>2.1</v>
-      </c>
-      <c r="V83">
-        <v>1.65</v>
-      </c>
-      <c r="W83">
-        <v>1.15</v>
-      </c>
-      <c r="X83">
-        <v>1.01</v>
-      </c>
-      <c r="Y83">
-        <v>1.15</v>
-      </c>
-      <c r="Z83">
-        <v>5.25</v>
-      </c>
-      <c r="AA83">
-        <v>1.5</v>
-      </c>
-      <c r="AB83">
-        <v>2.55</v>
-      </c>
-      <c r="AC83">
-        <v>2.12</v>
-      </c>
-      <c r="AD83">
-        <v>1.62</v>
-      </c>
-      <c r="AE83">
-        <v>1.25</v>
-      </c>
-      <c r="AF83">
-        <v>1.44</v>
-      </c>
-      <c r="AG83">
-        <v>2.7</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.25</v>
-      </c>
       <c r="AK83">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.77</v>
+        <v>1.29</v>
       </c>
       <c r="O84">
-        <v>4.26</v>
+        <v>6</v>
       </c>
       <c r="P84">
-        <v>3.92</v>
+        <v>8.5</v>
       </c>
       <c r="Q84">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="R84">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="S84">
         <v>1.18</v>
       </c>
       <c r="T84">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="U84">
+        <v>1.95</v>
+      </c>
+      <c r="V84">
         <v>1.8</v>
       </c>
-      <c r="V84">
-        <v>1.85</v>
-      </c>
       <c r="W84">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X84">
         <v>0</v>
       </c>
       <c r="Y84">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z84">
-        <v>6.76</v>
+        <v>7</v>
       </c>
       <c r="AA84">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB84">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AC84">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AD84">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AE84">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AF84">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AG84">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK84">
-        <v>2.05</v>
+        <v>3.32</v>
       </c>
       <c r="AL84">
         <v>0</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="O10">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P10">
         <v>7.75</v>
@@ -1954,49 +1954,49 @@
         <v>2.35</v>
       </c>
       <c r="S10">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T10">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U10">
         <v>2.5</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
         <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z10">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AA10">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB10">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="AC10">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="AD10">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AE10">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF10">
-        <v>1.87</v>
+        <v>2.13</v>
       </c>
       <c r="AG10">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.13</v>
       </c>
       <c r="AK10">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -3895,31 +3895,31 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="O22">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="P22">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Q22">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R22">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="S22">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T22">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="U22">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="V22">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="W22">
         <v>1.25</v>
@@ -3928,31 +3928,31 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z22">
-        <v>5.75</v>
+        <v>6.7</v>
       </c>
       <c r="AA22">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AB22">
-        <v>2.8</v>
+        <v>3.54</v>
       </c>
       <c r="AC22">
         <v>1.88</v>
       </c>
       <c r="AD22">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AE22">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AF22">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG22">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AK22">
-        <v>3.48</v>
+        <v>3.88</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -7644,25 +7644,25 @@
         </is>
       </c>
       <c r="N45">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="O45">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="P45">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Q45">
-        <v>11.45</v>
+        <v>11.5</v>
       </c>
       <c r="R45">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="S45">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="T45">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="U45">
         <v>2.05</v>
@@ -7671,10 +7671,10 @@
         <v>1.66</v>
       </c>
       <c r="W45">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
         <v>1.1</v>
@@ -7683,7 +7683,7 @@
         <v>5.6</v>
       </c>
       <c r="AA45">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AB45">
         <v>2.6</v>
@@ -7698,7 +7698,7 @@
         <v>1.23</v>
       </c>
       <c r="AF45">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AG45">
         <v>1.77</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK45">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7970,61 +7970,61 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="O47">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="P47">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="Q47">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="R47">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="S47">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T47">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="U47">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="V47">
         <v>1.3</v>
       </c>
       <c r="W47">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X47">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z47">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="AA47">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AB47">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC47">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AD47">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE47">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF47">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG47">
         <v>1.75</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK47">
         <v>1.44</v>
@@ -8145,52 +8145,52 @@
         <v>2.1</v>
       </c>
       <c r="R48">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="S48">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T48">
         <v>2.75</v>
       </c>
       <c r="U48">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V48">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W48">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z48">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AA48">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB48">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC48">
-        <v>3.6</v>
+        <v>3.76</v>
       </c>
       <c r="AD48">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE48">
         <v>1.05</v>
       </c>
       <c r="AF48">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AG48">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK48">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8794,7 +8794,7 @@
         <v>3.36</v>
       </c>
       <c r="Q52">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R52">
         <v>2.38</v>
@@ -8806,7 +8806,7 @@
         <v>3.9</v>
       </c>
       <c r="U52">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="V52">
         <v>1.62</v>
@@ -8824,7 +8824,7 @@
         <v>5.5</v>
       </c>
       <c r="AA52">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AB52">
         <v>2.5</v>
@@ -8836,7 +8836,7 @@
         <v>1.65</v>
       </c>
       <c r="AE52">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF52">
         <v>1.4</v>
@@ -8960,7 +8960,7 @@
         <v>2.7</v>
       </c>
       <c r="R53">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S53">
         <v>1.22</v>
@@ -8969,10 +8969,10 @@
         <v>3.8</v>
       </c>
       <c r="U53">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="V53">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W53">
         <v>1.13</v>
@@ -8981,10 +8981,10 @@
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z53">
-        <v>4.65</v>
+        <v>5.25</v>
       </c>
       <c r="AA53">
         <v>1.55</v>
@@ -9021,7 +9021,7 @@
         <v>1.29</v>
       </c>
       <c r="AK53">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>2.6</v>
       </c>
       <c r="Q54">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R54">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S54">
         <v>1.31</v>
@@ -9168,7 +9168,7 @@
         <v>1.53</v>
       </c>
       <c r="AG54">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.44</v>
       </c>
       <c r="AK54">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9280,13 +9280,13 @@
         <v>4.46</v>
       </c>
       <c r="P55">
-        <v>3.9</v>
+        <v>4.41</v>
       </c>
       <c r="Q55">
         <v>2.11</v>
       </c>
       <c r="R55">
-        <v>2.55</v>
+        <v>2.78</v>
       </c>
       <c r="S55">
         <v>1.2</v>
@@ -9295,10 +9295,10 @@
         <v>4.33</v>
       </c>
       <c r="U55">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V55">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W55">
         <v>1.22</v>
@@ -9316,16 +9316,16 @@
         <v>1.38</v>
       </c>
       <c r="AB55">
-        <v>2.87</v>
+        <v>3.07</v>
       </c>
       <c r="AC55">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AD55">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AE55">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF55">
         <v>1.34</v>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK55">
         <v>2.14</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="O56">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q56">
         <v>3.2</v>
@@ -9452,19 +9452,19 @@
         <v>2.4</v>
       </c>
       <c r="S56">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T56">
         <v>3.4</v>
       </c>
       <c r="U56">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="V56">
         <v>1.6</v>
       </c>
       <c r="W56">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X56">
         <v>1.03</v>
@@ -9476,7 +9476,7 @@
         <v>4.25</v>
       </c>
       <c r="AA56">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB56">
         <v>2.35</v>
@@ -9494,7 +9494,7 @@
         <v>1.5</v>
       </c>
       <c r="AG56">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="O58">
+        <v>3.25</v>
+      </c>
+      <c r="P58">
+        <v>2.8</v>
+      </c>
+      <c r="Q58">
+        <v>2.95</v>
+      </c>
+      <c r="R58">
+        <v>2</v>
+      </c>
+      <c r="S58">
+        <v>1.35</v>
+      </c>
+      <c r="T58">
         <v>3</v>
       </c>
-      <c r="P58">
+      <c r="U58">
         <v>2.7</v>
       </c>
-      <c r="Q58">
-        <v>3.29</v>
-      </c>
-      <c r="R58">
-        <v>1.96</v>
-      </c>
-      <c r="S58">
-        <v>1.44</v>
-      </c>
-      <c r="T58">
-        <v>2.56</v>
-      </c>
-      <c r="U58">
-        <v>2.85</v>
-      </c>
       <c r="V58">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W58">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z58">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AA58">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AB58">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AC58">
-        <v>3.72</v>
+        <v>3.28</v>
       </c>
       <c r="AD58">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE58">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF58">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG58">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AK58">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="O76">
         <v>3.5</v>
@@ -12736,7 +12736,7 @@
         <v>4</v>
       </c>
       <c r="AA76">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AB76">
         <v>2.1</v>
@@ -12751,7 +12751,7 @@
         <v>1.11</v>
       </c>
       <c r="AF76">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG76">
         <v>2.2</v>
@@ -12770,7 +12770,7 @@
         <v>1.29</v>
       </c>
       <c r="AK76">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12869,10 +12869,10 @@
         <v>3.8</v>
       </c>
       <c r="Q77">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R77">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="S77">
         <v>1.28</v>
@@ -12884,10 +12884,10 @@
         <v>2.28</v>
       </c>
       <c r="V77">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W77">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X77">
         <v>1.01</v>
@@ -12896,25 +12896,25 @@
         <v>1.2</v>
       </c>
       <c r="Z77">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AA77">
         <v>1.66</v>
       </c>
       <c r="AB77">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AC77">
-        <v>2.42</v>
+        <v>2.51</v>
       </c>
       <c r="AD77">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AE77">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AF77">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG77">
         <v>2.3</v>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK77">
         <v>1.85</v>
@@ -13032,7 +13032,7 @@
         <v>4.2</v>
       </c>
       <c r="Q78">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="R78">
         <v>2.45</v>
@@ -13080,7 +13080,7 @@
         <v>1.6</v>
       </c>
       <c r="AG78">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK78">
         <v>2.05</v>
@@ -13237,7 +13237,7 @@
         <v>2.2</v>
       </c>
       <c r="AE79">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AF79">
         <v>1.25</v>
@@ -13349,61 +13349,61 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="O80">
         <v>3.1</v>
       </c>
       <c r="P80">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="Q80">
-        <v>2.52</v>
+        <v>2.67</v>
       </c>
       <c r="R80">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="S80">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T80">
         <v>2.5</v>
       </c>
       <c r="U80">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="V80">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="W80">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X80">
         <v>1.05</v>
       </c>
       <c r="Y80">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="Z80">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AA80">
         <v>2.35</v>
       </c>
       <c r="AB80">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC80">
-        <v>4.44</v>
+        <v>4.05</v>
       </c>
       <c r="AD80">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE80">
         <v>1.02</v>
       </c>
       <c r="AF80">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AG80">
         <v>1.69</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AK80">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13515,10 +13515,10 @@
         <v>1.49</v>
       </c>
       <c r="O81">
-        <v>5</v>
+        <v>4.78</v>
       </c>
       <c r="P81">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13681,10 +13681,10 @@
         <v>3.5</v>
       </c>
       <c r="P82">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="Q82">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R82">
         <v>2.4</v>
@@ -13696,7 +13696,7 @@
         <v>3.8</v>
       </c>
       <c r="U82">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V82">
         <v>1.65</v>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK82">
         <v>1.73</v>
@@ -13850,7 +13850,7 @@
         <v>2</v>
       </c>
       <c r="R83">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="S83">
         <v>1.18</v>
@@ -13862,10 +13862,10 @@
         <v>1.8</v>
       </c>
       <c r="V83">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="W83">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X83">
         <v>0</v>
@@ -13874,13 +13874,13 @@
         <v>1.11</v>
       </c>
       <c r="Z83">
-        <v>6.76</v>
+        <v>6.66</v>
       </c>
       <c r="AA83">
         <v>1.37</v>
       </c>
       <c r="AB83">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="AC83">
         <v>1.83</v>
@@ -13911,7 +13911,7 @@
         <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14040,16 +14040,16 @@
         <v>7</v>
       </c>
       <c r="AA84">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB84">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="AC84">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AD84">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AE84">
         <v>1.3</v>
@@ -14058,7 +14058,7 @@
         <v>1.65</v>
       </c>
       <c r="AG84">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU84"/>
+  <dimension ref="A1:AU85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1622,55 +1622,55 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R8">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="S8">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="T8">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="U8">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="V8">
         <v>1.2</v>
       </c>
       <c r="W8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y8">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Z8">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AA8">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AB8">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AC8">
-        <v>5.85</v>
+        <v>6.1</v>
       </c>
       <c r="AD8">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="AG8">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AK8">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,22 +1776,22 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="O9">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P9">
-        <v>6.2</v>
+        <v>8.5</v>
       </c>
       <c r="Q9">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R9">
         <v>2</v>
       </c>
       <c r="S9">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="T9">
         <v>2.55</v>
@@ -1803,34 +1803,34 @@
         <v>1.32</v>
       </c>
       <c r="W9">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
         <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="Z9">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="AA9">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="AB9">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC9">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AD9">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE9">
         <v>1.02</v>
       </c>
       <c r="AF9">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AG9">
         <v>1.44</v>
@@ -1945,13 +1945,13 @@
         <v>4.4</v>
       </c>
       <c r="P10">
-        <v>7.75</v>
+        <v>14</v>
       </c>
       <c r="Q10">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="R10">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="S10">
         <v>1.25</v>
@@ -1960,10 +1960,10 @@
         <v>3.45</v>
       </c>
       <c r="U10">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W10">
         <v>1.07</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK10">
-        <v>3.1</v>
+        <v>3.56</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="O14">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="P14">
-        <v>3.09</v>
+        <v>3.55</v>
       </c>
       <c r="Q14">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="R14">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="S14">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T14">
-        <v>2.99</v>
+        <v>2.82</v>
       </c>
       <c r="U14">
         <v>2.5</v>
       </c>
       <c r="V14">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z14">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AA14">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AB14">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="AC14">
-        <v>2.62</v>
+        <v>3.03</v>
       </c>
       <c r="AD14">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE14">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AG14">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.26</v>
       </c>
       <c r="AK14">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="O15">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P15">
-        <v>4.54</v>
+        <v>4.34</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2917,43 +2917,43 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.13</v>
+        <v>2.93</v>
       </c>
       <c r="O16">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="P16">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="Q16">
-        <v>3.69</v>
+        <v>3.42</v>
       </c>
       <c r="R16">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S16">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T16">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U16">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V16">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
         <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
         <v>1.18</v>
       </c>
       <c r="Z16">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="AA16">
         <v>1.73</v>
@@ -2962,19 +2962,19 @@
         <v>2.04</v>
       </c>
       <c r="AC16">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="AD16">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE16">
         <v>1.15</v>
       </c>
       <c r="AF16">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK16">
         <v>1.33</v>
@@ -3038,22 +3038,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G17">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3522,27 +3522,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.14</v>
+        <v>2.5</v>
       </c>
       <c r="O20">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="P20">
-        <v>14</v>
+        <v>2.25</v>
       </c>
       <c r="Q20">
-        <v>1.36</v>
+        <v>3</v>
       </c>
       <c r="R20">
-        <v>3.99</v>
+        <v>2.5</v>
       </c>
       <c r="S20">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T20">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="U20">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="V20">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="W20">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="AA20">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AB20">
-        <v>4.25</v>
+        <v>2.88</v>
       </c>
       <c r="AC20">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="AD20">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AE20">
-        <v>1.61</v>
+        <v>1.26</v>
       </c>
       <c r="AF20">
-        <v>1.76</v>
+        <v>1.38</v>
       </c>
       <c r="AG20">
-        <v>1.77</v>
+        <v>2.77</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AK20">
-        <v>6.85</v>
+        <v>1.42</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-09-09 13:45:00</t>
+          <t>2026-09-09 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="O21">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="P21">
-        <v>9.65</v>
+        <v>16.5</v>
       </c>
       <c r="Q21">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="R21">
-        <v>3.2</v>
+        <v>4.22</v>
       </c>
       <c r="S21">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="T21">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U21">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="V21">
-        <v>1.98</v>
+        <v>2.27</v>
       </c>
       <c r="W21">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Z21">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AA21">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AB21">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AC21">
-        <v>1.76</v>
+        <v>1.45</v>
       </c>
       <c r="AD21">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="AE21">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="AF21">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG21">
-        <v>2.19</v>
+        <v>1.77</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK21">
-        <v>4.25</v>
+        <v>8</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="O22">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="P22">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Q22">
         <v>1.57</v>
       </c>
       <c r="R22">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="S22">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T22">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="U22">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="V22">
         <v>1.91</v>
       </c>
       <c r="W22">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z22">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA22">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AB22">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="AC22">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AD22">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AE22">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AF22">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG22">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK22">
-        <v>3.88</v>
+        <v>4.22</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4011,27 +4011,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-09-09 14:00:00</t>
+          <t>2026-09-09 13:45:00</t>
         </is>
       </c>
     </row>
@@ -4179,22 +4179,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK24">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.87</v>
+        <v>5.9</v>
       </c>
       <c r="O25">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="P25">
-        <v>2.69</v>
+        <v>1.4</v>
       </c>
       <c r="Q25">
-        <v>3.92</v>
+        <v>6.5</v>
       </c>
       <c r="R25">
+        <v>2.2</v>
+      </c>
+      <c r="S25">
+        <v>1.39</v>
+      </c>
+      <c r="T25">
+        <v>2.7</v>
+      </c>
+      <c r="U25">
+        <v>3</v>
+      </c>
+      <c r="V25">
+        <v>1.36</v>
+      </c>
+      <c r="W25">
+        <v>1.04</v>
+      </c>
+      <c r="X25">
+        <v>1.01</v>
+      </c>
+      <c r="Y25">
+        <v>1.3</v>
+      </c>
+      <c r="Z25">
+        <v>3.22</v>
+      </c>
+      <c r="AA25">
+        <v>1.96</v>
+      </c>
+      <c r="AB25">
         <v>1.75</v>
       </c>
-      <c r="S25">
-        <v>1.64</v>
-      </c>
-      <c r="T25">
-        <v>2.05</v>
-      </c>
-      <c r="U25">
-        <v>4</v>
-      </c>
-      <c r="V25">
-        <v>1.2</v>
-      </c>
-      <c r="W25">
-        <v>1.01</v>
-      </c>
-      <c r="X25">
-        <v>1.09</v>
-      </c>
-      <c r="Y25">
+      <c r="AC25">
+        <v>3.34</v>
+      </c>
+      <c r="AD25">
+        <v>1.24</v>
+      </c>
+      <c r="AE25">
+        <v>1.06</v>
+      </c>
+      <c r="AF25">
+        <v>2.21</v>
+      </c>
+      <c r="AG25">
         <v>1.58</v>
       </c>
-      <c r="Z25">
-        <v>2.23</v>
-      </c>
-      <c r="AA25">
-        <v>2.88</v>
-      </c>
-      <c r="AB25">
-        <v>1.35</v>
-      </c>
-      <c r="AC25">
-        <v>5.65</v>
-      </c>
-      <c r="AD25">
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>1.22</v>
+      </c>
+      <c r="AK25">
         <v>1.08</v>
-      </c>
-      <c r="AE25">
-        <v>1.03</v>
-      </c>
-      <c r="AF25">
-        <v>2.25</v>
-      </c>
-      <c r="AG25">
-        <v>1.57</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.39</v>
-      </c>
-      <c r="AK25">
-        <v>1.36</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G26">
@@ -4543,68 +4543,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="O26">
-        <v>3.45</v>
+        <v>2.75</v>
       </c>
       <c r="P26">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="Q26">
-        <v>3.1</v>
+        <v>3.92</v>
       </c>
       <c r="R26">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="T26">
-        <v>3.05</v>
+        <v>2.05</v>
       </c>
       <c r="U26">
-        <v>2.47</v>
+        <v>3.98</v>
       </c>
       <c r="V26">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y26">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="Z26">
-        <v>3.75</v>
+        <v>2.23</v>
       </c>
       <c r="AA26">
-        <v>1.7</v>
+        <v>2.96</v>
       </c>
       <c r="AB26">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="AC26">
-        <v>2.9</v>
+        <v>5.96</v>
       </c>
       <c r="AD26">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="AE26">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AF26">
-        <v>1.56</v>
+        <v>2.25</v>
       </c>
       <c r="AG26">
-        <v>2.24</v>
+        <v>1.59</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="AK26">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4668,22 +4668,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G27">
@@ -4706,68 +4706,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N27">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="O27">
         <v>3.4</v>
       </c>
       <c r="P27">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="Q27">
-        <v>3.1</v>
+        <v>4.07</v>
       </c>
       <c r="R27">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T27">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U27">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V27">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X27">
         <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z27">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="AA27">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB27">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AC27">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="AD27">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE27">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="O28">
         <v>3.4</v>
       </c>
       <c r="P28">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q28">
-        <v>2.51</v>
+        <v>3.1</v>
       </c>
       <c r="R28">
         <v>2.3</v>
       </c>
       <c r="S28">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>3.25</v>
+        <v>2.87</v>
       </c>
       <c r="U28">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="V28">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="W28">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z28">
-        <v>4.5</v>
+        <v>4.03</v>
       </c>
       <c r="AA28">
+        <v>1.75</v>
+      </c>
+      <c r="AB28">
+        <v>2.04</v>
+      </c>
+      <c r="AC28">
+        <v>2.66</v>
+      </c>
+      <c r="AD28">
+        <v>1.37</v>
+      </c>
+      <c r="AE28">
+        <v>1.12</v>
+      </c>
+      <c r="AF28">
         <v>1.58</v>
       </c>
-      <c r="AB28">
-        <v>2.14</v>
-      </c>
-      <c r="AC28">
-        <v>2.6</v>
-      </c>
-      <c r="AD28">
-        <v>1.48</v>
-      </c>
-      <c r="AE28">
-        <v>1.18</v>
-      </c>
-      <c r="AF28">
-        <v>1.53</v>
-      </c>
       <c r="AG28">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q29">
-        <v>2.57</v>
+        <v>2.52</v>
       </c>
       <c r="R29">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="S29">
         <v>1.29</v>
       </c>
       <c r="T29">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U29">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="V29">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W29">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X29">
         <v>1.02</v>
       </c>
       <c r="Y29">
+        <v>1.16</v>
+      </c>
+      <c r="Z29">
+        <v>4.5</v>
+      </c>
+      <c r="AA29">
+        <v>1.61</v>
+      </c>
+      <c r="AB29">
+        <v>2.25</v>
+      </c>
+      <c r="AC29">
+        <v>2.6</v>
+      </c>
+      <c r="AD29">
+        <v>1.48</v>
+      </c>
+      <c r="AE29">
         <v>1.15</v>
       </c>
-      <c r="Z29">
-        <v>3.98</v>
-      </c>
-      <c r="AA29">
-        <v>1.67</v>
-      </c>
-      <c r="AB29">
-        <v>2.15</v>
-      </c>
-      <c r="AC29">
-        <v>2.49</v>
-      </c>
-      <c r="AD29">
-        <v>1.42</v>
-      </c>
-      <c r="AE29">
-        <v>1.18</v>
-      </c>
       <c r="AF29">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AG29">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK29">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.82</v>
+        <v>2.01</v>
       </c>
       <c r="O30">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P30">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q30">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="R30">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="S30">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T30">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="U30">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="V30">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W30">
+        <v>1.09</v>
+      </c>
+      <c r="X30">
+        <v>1.02</v>
+      </c>
+      <c r="Y30">
         <v>1.15</v>
       </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
-        <v>1.18</v>
-      </c>
       <c r="Z30">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="AA30">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB30">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AC30">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="AD30">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE30">
         <v>1.14</v>
       </c>
       <c r="AF30">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG30">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AK30">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5320,22 +5320,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G32">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-09-09 14:30:00</t>
+          <t>2026-09-09 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AK33">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-09-09 15:00:00</t>
+          <t>2026-09-09 14:30:00</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.06</v>
+        <v>3.4</v>
       </c>
       <c r="O34">
-        <v>11</v>
+        <v>3.8</v>
       </c>
       <c r="P34">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Q34">
-        <v>1.32</v>
+        <v>3.86</v>
       </c>
       <c r="R34">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>5.85</v>
+        <v>3.25</v>
       </c>
       <c r="U34">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="V34">
-        <v>2.07</v>
+        <v>1.51</v>
       </c>
       <c r="W34">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>9.5</v>
+        <v>3.86</v>
       </c>
       <c r="AA34">
-        <v>1.16</v>
+        <v>1.68</v>
       </c>
       <c r="AB34">
-        <v>4.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC34">
-        <v>1.57</v>
+        <v>2.7</v>
       </c>
       <c r="AD34">
-        <v>2.31</v>
+        <v>1.43</v>
       </c>
       <c r="AE34">
-        <v>1.52</v>
+        <v>1.12</v>
       </c>
       <c r="AF34">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="AG34">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>7.9</v>
+        <v>1.24</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5967,27 +5967,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="O35">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="P35">
-        <v>3.42</v>
+        <v>7.75</v>
       </c>
       <c r="Q35">
-        <v>3.14</v>
+        <v>1.62</v>
       </c>
       <c r="R35">
-        <v>1.75</v>
+        <v>2.9</v>
       </c>
       <c r="S35">
-        <v>1.66</v>
+        <v>1.17</v>
       </c>
       <c r="T35">
-        <v>2.08</v>
+        <v>4.8</v>
       </c>
       <c r="U35">
-        <v>4</v>
+        <v>1.81</v>
       </c>
       <c r="V35">
-        <v>1.18</v>
+        <v>1.95</v>
       </c>
       <c r="W35">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="X35">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.61</v>
+        <v>1.04</v>
       </c>
       <c r="Z35">
-        <v>2.27</v>
+        <v>6.95</v>
       </c>
       <c r="AA35">
-        <v>2.78</v>
+        <v>1.25</v>
       </c>
       <c r="AB35">
-        <v>1.36</v>
+        <v>3.16</v>
       </c>
       <c r="AC35">
-        <v>5.5</v>
+        <v>1.77</v>
       </c>
       <c r="AD35">
-        <v>1.07</v>
+        <v>1.94</v>
       </c>
       <c r="AE35">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="AF35">
-        <v>2.28</v>
+        <v>1.57</v>
       </c>
       <c r="AG35">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="AK35">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-09-09 15:30:00</t>
+          <t>2026-09-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6130,27 +6130,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.74</v>
+        <v>1.85</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="P36">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="Q36">
-        <v>3.38</v>
+        <v>2.69</v>
       </c>
       <c r="R36">
-        <v>2.24</v>
+        <v>1.79</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="T36">
-        <v>2.8</v>
+        <v>2.13</v>
       </c>
       <c r="U36">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="V36">
-        <v>1.41</v>
+        <v>1.16</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="Y36">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="Z36">
-        <v>3.38</v>
+        <v>2.09</v>
       </c>
       <c r="AA36">
-        <v>1.95</v>
+        <v>2.92</v>
       </c>
       <c r="AB36">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="AC36">
-        <v>3.45</v>
+        <v>5.95</v>
       </c>
       <c r="AD36">
-        <v>1.27</v>
+        <v>1.1</v>
       </c>
       <c r="AE36">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>2.51</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>1.46</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK36">
-        <v>1.42</v>
+        <v>1.74</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-09-09 15:45:00</t>
+          <t>2026-09-09 15:30:00</t>
         </is>
       </c>
     </row>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.07</v>
+        <v>2.55</v>
       </c>
       <c r="O37">
         <v>3.4</v>
       </c>
       <c r="P37">
-        <v>3.36</v>
+        <v>2.39</v>
       </c>
       <c r="Q37">
-        <v>2.5</v>
+        <v>3.49</v>
       </c>
       <c r="R37">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="S37">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T37">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="U37">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="V37">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W37">
         <v>1.06</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z37">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AA37">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB37">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AC37">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="AD37">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF37">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AG37">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK37">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.32</v>
+        <v>1.92</v>
       </c>
       <c r="O38">
-        <v>5.25</v>
+        <v>3.43</v>
       </c>
       <c r="P38">
-        <v>7.55</v>
+        <v>3.18</v>
       </c>
       <c r="Q38">
-        <v>1.72</v>
+        <v>2.6</v>
       </c>
       <c r="R38">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="T38">
-        <v>3.64</v>
+        <v>2.9</v>
       </c>
       <c r="U38">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="V38">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
         <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="Z38">
-        <v>4.95</v>
+        <v>3.55</v>
       </c>
       <c r="AA38">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AB38">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AC38">
-        <v>2.19</v>
+        <v>2.85</v>
       </c>
       <c r="AD38">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AE38">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG38">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>3.25</v>
+        <v>1.75</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,65 +6666,65 @@
         </is>
       </c>
       <c r="N39">
-        <v>4.33</v>
+        <v>1.3</v>
       </c>
       <c r="O39">
-        <v>3.7</v>
+        <v>5.75</v>
       </c>
       <c r="P39">
-        <v>1.82</v>
+        <v>8.5</v>
       </c>
       <c r="Q39">
-        <v>4.88</v>
+        <v>1.71</v>
       </c>
       <c r="R39">
-        <v>2.27</v>
+        <v>2.97</v>
       </c>
       <c r="S39">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="T39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U39">
-        <v>2.9</v>
+        <v>2.11</v>
       </c>
       <c r="V39">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
+        <v>1.1</v>
+      </c>
+      <c r="Z39">
+        <v>5.25</v>
+      </c>
+      <c r="AA39">
+        <v>1.57</v>
+      </c>
+      <c r="AB39">
+        <v>2.75</v>
+      </c>
+      <c r="AC39">
+        <v>2.15</v>
+      </c>
+      <c r="AD39">
+        <v>1.53</v>
+      </c>
+      <c r="AE39">
         <v>1.28</v>
       </c>
-      <c r="Z39">
-        <v>3.55</v>
-      </c>
-      <c r="AA39">
+      <c r="AF39">
+        <v>1.7</v>
+      </c>
+      <c r="AG39">
         <v>1.95</v>
       </c>
-      <c r="AB39">
-        <v>1.87</v>
-      </c>
-      <c r="AC39">
-        <v>3.24</v>
-      </c>
-      <c r="AD39">
-        <v>1.33</v>
-      </c>
-      <c r="AE39">
-        <v>1.11</v>
-      </c>
-      <c r="AF39">
-        <v>1.8</v>
-      </c>
-      <c r="AG39">
-        <v>1.93</v>
-      </c>
       <c r="AH39" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.23</v>
+        <v>1.12</v>
       </c>
       <c r="AK39">
-        <v>1.18</v>
+        <v>3.38</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-09-09 16:00:00</t>
+          <t>2026-09-09 15:45:00</t>
         </is>
       </c>
     </row>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,31 +6829,31 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.87</v>
+        <v>4.5</v>
       </c>
       <c r="O40">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P40">
-        <v>3.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q40">
-        <v>2.41</v>
+        <v>4.4</v>
       </c>
       <c r="R40">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="S40">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="T40">
-        <v>3.28</v>
+        <v>3.01</v>
       </c>
       <c r="U40">
-        <v>2.4</v>
+        <v>2.81</v>
       </c>
       <c r="V40">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="W40">
         <v>1.08</v>
@@ -6862,47 +6862,47 @@
         <v>1.01</v>
       </c>
       <c r="Y40">
+        <v>1.28</v>
+      </c>
+      <c r="Z40">
+        <v>3.55</v>
+      </c>
+      <c r="AA40">
+        <v>1.95</v>
+      </c>
+      <c r="AB40">
+        <v>1.87</v>
+      </c>
+      <c r="AC40">
+        <v>3.2</v>
+      </c>
+      <c r="AD40">
+        <v>1.29</v>
+      </c>
+      <c r="AE40">
+        <v>1.11</v>
+      </c>
+      <c r="AF40">
+        <v>1.8</v>
+      </c>
+      <c r="AG40">
+        <v>1.95</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>1.23</v>
+      </c>
+      <c r="AK40">
         <v>1.18</v>
-      </c>
-      <c r="Z40">
-        <v>4.4</v>
-      </c>
-      <c r="AA40">
-        <v>1.66</v>
-      </c>
-      <c r="AB40">
-        <v>2.2</v>
-      </c>
-      <c r="AC40">
-        <v>2.59</v>
-      </c>
-      <c r="AD40">
-        <v>1.49</v>
-      </c>
-      <c r="AE40">
-        <v>1.18</v>
-      </c>
-      <c r="AF40">
-        <v>1.57</v>
-      </c>
-      <c r="AG40">
-        <v>2.3</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.25</v>
-      </c>
-      <c r="AK40">
-        <v>1.85</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="O41">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P41">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="Q41">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R41">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S41">
         <v>1.28</v>
@@ -7025,19 +7025,19 @@
         <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z41">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AA41">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AB41">
         <v>2.3</v>
       </c>
       <c r="AC41">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AD41">
         <v>1.5</v>
@@ -7049,7 +7049,7 @@
         <v>1.59</v>
       </c>
       <c r="AG41">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
         <v>2.12</v>
@@ -7155,25 +7155,25 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="O42">
         <v>16</v>
       </c>
       <c r="P42">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q42">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="R42">
-        <v>3.83</v>
+        <v>4.75</v>
       </c>
       <c r="S42">
         <v>1.12</v>
       </c>
       <c r="T42">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="U42">
         <v>1.65</v>
@@ -7206,10 +7206,10 @@
         <v>2.25</v>
       </c>
       <c r="AE42">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AF42">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AG42">
         <v>1.4</v>
@@ -7228,7 +7228,7 @@
         <v>1.01</v>
       </c>
       <c r="AK42">
-        <v>12.75</v>
+        <v>13</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.06</v>
+        <v>1.82</v>
       </c>
       <c r="O43">
-        <v>3.42</v>
+        <v>3.85</v>
       </c>
       <c r="P43">
-        <v>2.23</v>
+        <v>3.75</v>
       </c>
       <c r="Q43">
-        <v>3.78</v>
+        <v>2.38</v>
       </c>
       <c r="R43">
-        <v>2.11</v>
+        <v>2.43</v>
       </c>
       <c r="S43">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="T43">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="U43">
-        <v>2.77</v>
+        <v>2.4</v>
       </c>
       <c r="V43">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="W43">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z43">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA43">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="AB43">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="AC43">
-        <v>3.18</v>
+        <v>2.62</v>
       </c>
       <c r="AD43">
-        <v>1.27</v>
+        <v>1.51</v>
       </c>
       <c r="AE43">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AG43">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.35</v>
+        <v>1.93</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="O44">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>1.5</v>
+        <v>2.13</v>
       </c>
       <c r="Q44">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="R44">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S44">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="T44">
-        <v>3.8</v>
+        <v>2.66</v>
       </c>
       <c r="U44">
-        <v>2.27</v>
+        <v>2.86</v>
       </c>
       <c r="V44">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W44">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z44">
-        <v>4.85</v>
+        <v>3.3</v>
       </c>
       <c r="AA44">
-        <v>1.48</v>
+        <v>1.99</v>
       </c>
       <c r="AB44">
-        <v>2.47</v>
+        <v>1.9</v>
       </c>
       <c r="AC44">
-        <v>2.33</v>
+        <v>3.05</v>
       </c>
       <c r="AD44">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="AE44">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF44">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG44">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AK44">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>15</v>
+        <v>5.9</v>
       </c>
       <c r="O45">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="P45">
-        <v>1.15</v>
+        <v>1.48</v>
       </c>
       <c r="Q45">
-        <v>11.5</v>
+        <v>5.58</v>
       </c>
       <c r="R45">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="S45">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="T45">
-        <v>3.34</v>
+        <v>3.9</v>
       </c>
       <c r="U45">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V45">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="W45">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z45">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AA45">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB45">
         <v>2.6</v>
       </c>
       <c r="AC45">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AD45">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE45">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AF45">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AG45">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AK45">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-09-09 16:45:00</t>
+          <t>2026-09-09 16:00:00</t>
         </is>
       </c>
     </row>
@@ -7760,27 +7760,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-09-09 18:00:00</t>
+          <t>2026-09-09 16:45:00</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O47">
-        <v>2.89</v>
+        <v>3.15</v>
       </c>
       <c r="P47">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="Q47">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S47">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T47">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U47">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="V47">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W47">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X47">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y47">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z47">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA47">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB47">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC47">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AD47">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE47">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF47">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG47">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK47">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-09-09 19:30:00</t>
+          <t>2026-09-09 18:00:00</t>
         </is>
       </c>
     </row>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q48">
-        <v>2.1</v>
+        <v>3.71</v>
       </c>
       <c r="R48">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="S48">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="T48">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="U48">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="V48">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W48">
         <v>1.03</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y48">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="Z48">
-        <v>2.97</v>
+        <v>2.52</v>
       </c>
       <c r="AA48">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="AB48">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AC48">
-        <v>3.76</v>
+        <v>4.64</v>
       </c>
       <c r="AD48">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AE48">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF48">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AG48">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.1</v>
+        <v>1.43</v>
       </c>
       <c r="AK48">
-        <v>2.25</v>
+        <v>1.36</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G49">
@@ -8305,55 +8305,55 @@
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-09-09 20:30:00</t>
+          <t>2026-09-09 19:30:00</t>
         </is>
       </c>
     </row>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G51">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S52">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T52">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U52">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V52">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W52">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z52">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA52">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB52">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC52">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD52">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE52">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF52">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG52">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK52">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.27</v>
+        <v>1.53</v>
       </c>
       <c r="O53">
-        <v>3.68</v>
+        <v>4.15</v>
       </c>
       <c r="P53">
-        <v>2.62</v>
+        <v>4.05</v>
       </c>
       <c r="Q53">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="R53">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="S53">
+        <v>1.2</v>
+      </c>
+      <c r="T53">
+        <v>4.4</v>
+      </c>
+      <c r="U53">
+        <v>1.95</v>
+      </c>
+      <c r="V53">
+        <v>1.75</v>
+      </c>
+      <c r="W53">
         <v>1.22</v>
       </c>
-      <c r="T53">
-        <v>3.8</v>
-      </c>
-      <c r="U53">
-        <v>2.2</v>
-      </c>
-      <c r="V53">
-        <v>1.6</v>
-      </c>
-      <c r="W53">
-        <v>1.13</v>
-      </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y53">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z53">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="AA53">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AB53">
-        <v>2.4</v>
+        <v>2.89</v>
       </c>
       <c r="AC53">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AD53">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AE53">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AF53">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AG53">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK53">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,61 +9111,61 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>3.63</v>
       </c>
       <c r="P54">
-        <v>2.6</v>
+        <v>2.09</v>
       </c>
       <c r="Q54">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="R54">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S54">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T54">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="U54">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="V54">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W54">
         <v>1.08</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z54">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA54">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB54">
         <v>2.25</v>
       </c>
       <c r="AC54">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AD54">
         <v>1.5</v>
       </c>
       <c r="AE54">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF54">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG54">
         <v>2.3</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK54">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="O55">
-        <v>4.46</v>
+        <v>3.73</v>
       </c>
       <c r="P55">
-        <v>4.41</v>
+        <v>2.58</v>
       </c>
       <c r="Q55">
-        <v>2.11</v>
+        <v>2.65</v>
       </c>
       <c r="R55">
-        <v>2.78</v>
+        <v>2.32</v>
       </c>
       <c r="S55">
+        <v>1.24</v>
+      </c>
+      <c r="T55">
+        <v>3.5</v>
+      </c>
+      <c r="U55">
+        <v>2.17</v>
+      </c>
+      <c r="V55">
+        <v>1.59</v>
+      </c>
+      <c r="W55">
+        <v>1.13</v>
+      </c>
+      <c r="X55">
+        <v>1.01</v>
+      </c>
+      <c r="Y55">
+        <v>1.16</v>
+      </c>
+      <c r="Z55">
+        <v>4.9</v>
+      </c>
+      <c r="AA55">
+        <v>1.55</v>
+      </c>
+      <c r="AB55">
+        <v>2.4</v>
+      </c>
+      <c r="AC55">
+        <v>2.4</v>
+      </c>
+      <c r="AD55">
+        <v>1.58</v>
+      </c>
+      <c r="AE55">
         <v>1.2</v>
       </c>
-      <c r="T55">
-        <v>4.33</v>
-      </c>
-      <c r="U55">
-        <v>1.94</v>
-      </c>
-      <c r="V55">
-        <v>1.74</v>
-      </c>
-      <c r="W55">
-        <v>1.22</v>
-      </c>
-      <c r="X55">
-        <v>0</v>
-      </c>
-      <c r="Y55">
-        <v>1.11</v>
-      </c>
-      <c r="Z55">
-        <v>6.25</v>
-      </c>
-      <c r="AA55">
-        <v>1.38</v>
-      </c>
-      <c r="AB55">
-        <v>3.07</v>
-      </c>
-      <c r="AC55">
-        <v>1.92</v>
-      </c>
-      <c r="AD55">
-        <v>1.85</v>
-      </c>
-      <c r="AE55">
-        <v>1.33</v>
-      </c>
       <c r="AF55">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="AG55">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK55">
-        <v>2.14</v>
+        <v>1.61</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,65 +9437,65 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.63</v>
       </c>
       <c r="P56">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="Q56">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R56">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S56">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T56">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U56">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="V56">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="W56">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X56">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z56">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA56">
+        <v>1.7</v>
+      </c>
+      <c r="AB56">
+        <v>2.2</v>
+      </c>
+      <c r="AC56">
+        <v>2.63</v>
+      </c>
+      <c r="AD56">
+        <v>1.42</v>
+      </c>
+      <c r="AE56">
+        <v>1.16</v>
+      </c>
+      <c r="AF56">
         <v>1.57</v>
       </c>
-      <c r="AB56">
+      <c r="AG56">
         <v>2.35</v>
       </c>
-      <c r="AC56">
-        <v>2.4</v>
-      </c>
-      <c r="AD56">
-        <v>1.55</v>
-      </c>
-      <c r="AE56">
-        <v>1.15</v>
-      </c>
-      <c r="AF56">
-        <v>1.5</v>
-      </c>
-      <c r="AG56">
-        <v>2.31</v>
-      </c>
       <c r="AH56" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AK56">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="O57">
-        <v>3.2</v>
+        <v>3.97</v>
       </c>
       <c r="P57">
-        <v>2.6</v>
+        <v>3.27</v>
       </c>
       <c r="Q57">
-        <v>3.37</v>
+        <v>2.49</v>
       </c>
       <c r="R57">
-        <v>1.96</v>
+        <v>2.39</v>
       </c>
       <c r="S57">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="T57">
-        <v>2.56</v>
+        <v>3.8</v>
       </c>
       <c r="U57">
-        <v>3.04</v>
+        <v>2.13</v>
       </c>
       <c r="V57">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="W57">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="X57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="Z57">
-        <v>2.97</v>
+        <v>5.5</v>
       </c>
       <c r="AA57">
-        <v>2.06</v>
+        <v>1.48</v>
       </c>
       <c r="AB57">
-        <v>1.76</v>
+        <v>2.7</v>
       </c>
       <c r="AC57">
-        <v>3.72</v>
+        <v>2.2</v>
       </c>
       <c r="AD57">
-        <v>1.27</v>
+        <v>1.69</v>
       </c>
       <c r="AE57">
-        <v>1.06</v>
+        <v>1.29</v>
       </c>
       <c r="AF57">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AG57">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AK57">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="O58">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P58">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q58">
-        <v>2.95</v>
+        <v>3.37</v>
       </c>
       <c r="R58">
         <v>2</v>
       </c>
       <c r="S58">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="T58">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="U58">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="V58">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W58">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z58">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AA58">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AB58">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AC58">
-        <v>3.28</v>
+        <v>3.72</v>
       </c>
       <c r="AD58">
         <v>1.25</v>
       </c>
       <c r="AE58">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF58">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG58">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK58">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9879,27 +9879,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G59">
@@ -9922,68 +9922,68 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-09-09 21:00:00</t>
+          <t>2026-09-09 20:30:00</t>
         </is>
       </c>
     </row>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G66">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G67">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G74">
@@ -12492,22 +12492,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O75">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P75">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB75">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.64</v>
+        <v>2.15</v>
       </c>
       <c r="O76">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="P76">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q76">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R76">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S76">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T76">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U76">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V76">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W76">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X76">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y76">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z76">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA76">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AB76">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC76">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD76">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE76">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF76">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG76">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK76">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2026-09-09 21:30:00</t>
+          <t>2026-09-09 21:00:00</t>
         </is>
       </c>
     </row>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="O77">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P77">
-        <v>3.8</v>
+        <v>2.51</v>
       </c>
       <c r="Q77">
-        <v>2.36</v>
+        <v>3.15</v>
       </c>
       <c r="R77">
-        <v>2.49</v>
+        <v>2.14</v>
       </c>
       <c r="S77">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T77">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U77">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="V77">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W77">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y77">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z77">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="AA77">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AB77">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC77">
-        <v>2.51</v>
+        <v>3</v>
       </c>
       <c r="AD77">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AE77">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AG77">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK77">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,31 +13023,31 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="O78">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P78">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q78">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="R78">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="S78">
         <v>1.25</v>
       </c>
       <c r="T78">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U78">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V78">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="W78">
         <v>1.15</v>
@@ -13056,31 +13056,31 @@
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z78">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA78">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AB78">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AC78">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="AD78">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AE78">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF78">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AG78">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
+        <v>1.7</v>
+      </c>
+      <c r="O79">
+        <v>3.7</v>
+      </c>
+      <c r="P79">
+        <v>4.25</v>
+      </c>
+      <c r="Q79">
+        <v>2.24</v>
+      </c>
+      <c r="R79">
+        <v>2.46</v>
+      </c>
+      <c r="S79">
+        <v>1.28</v>
+      </c>
+      <c r="T79">
+        <v>3.3</v>
+      </c>
+      <c r="U79">
+        <v>2.3</v>
+      </c>
+      <c r="V79">
+        <v>1.57</v>
+      </c>
+      <c r="W79">
+        <v>1.12</v>
+      </c>
+      <c r="X79">
+        <v>1.01</v>
+      </c>
+      <c r="Y79">
+        <v>1.17</v>
+      </c>
+      <c r="Z79">
+        <v>4.8</v>
+      </c>
+      <c r="AA79">
+        <v>1.56</v>
+      </c>
+      <c r="AB79">
         <v>2.15</v>
       </c>
-      <c r="O79">
-        <v>3.8</v>
-      </c>
-      <c r="P79">
-        <v>2.7</v>
-      </c>
-      <c r="Q79">
-        <v>2.5</v>
-      </c>
-      <c r="R79">
-        <v>2.52</v>
-      </c>
-      <c r="S79">
-        <v>1.16</v>
-      </c>
-      <c r="T79">
-        <v>4.8</v>
-      </c>
-      <c r="U79">
-        <v>1.86</v>
-      </c>
-      <c r="V79">
-        <v>1.88</v>
-      </c>
-      <c r="W79">
-        <v>1.25</v>
-      </c>
-      <c r="X79">
-        <v>0</v>
-      </c>
-      <c r="Y79">
-        <v>1.06</v>
-      </c>
-      <c r="Z79">
-        <v>6.7</v>
-      </c>
-      <c r="AA79">
-        <v>1.24</v>
-      </c>
-      <c r="AB79">
-        <v>3.6</v>
-      </c>
       <c r="AC79">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="AD79">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AE79">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AF79">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AG79">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK79">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="O80">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="P80">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q80">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="R80">
-        <v>1.94</v>
+        <v>2.79</v>
       </c>
       <c r="S80">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="T80">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="U80">
-        <v>3.06</v>
+        <v>1.9</v>
       </c>
       <c r="V80">
-        <v>1.32</v>
+        <v>1.81</v>
       </c>
       <c r="W80">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="X80">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y80">
-        <v>1.39</v>
+        <v>1.07</v>
       </c>
       <c r="Z80">
-        <v>2.59</v>
+        <v>6.7</v>
       </c>
       <c r="AA80">
-        <v>2.35</v>
+        <v>1.3</v>
       </c>
       <c r="AB80">
-        <v>1.58</v>
+        <v>3.5</v>
       </c>
       <c r="AC80">
-        <v>4.05</v>
+        <v>1.72</v>
       </c>
       <c r="AD80">
-        <v>1.16</v>
+        <v>2.1</v>
       </c>
       <c r="AE80">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="AF80">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="AG80">
-        <v>1.69</v>
+        <v>3.45</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AK80">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13465,12 +13465,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="O81">
-        <v>4.78</v>
+        <v>3.2</v>
       </c>
       <c r="P81">
-        <v>5.7</v>
+        <v>3.35</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-09-09 23:30:00</t>
+          <t>2026-09-09 21:30:00</t>
         </is>
       </c>
     </row>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,80 +13675,80 @@
         </is>
       </c>
       <c r="N82">
+        <v>1.67</v>
+      </c>
+      <c r="O82">
+        <v>4.12</v>
+      </c>
+      <c r="P82">
+        <v>3.86</v>
+      </c>
+      <c r="Q82">
+        <v>2.29</v>
+      </c>
+      <c r="R82">
+        <v>2.67</v>
+      </c>
+      <c r="S82">
+        <v>1.2</v>
+      </c>
+      <c r="T82">
+        <v>3.88</v>
+      </c>
+      <c r="U82">
+        <v>1.94</v>
+      </c>
+      <c r="V82">
+        <v>1.72</v>
+      </c>
+      <c r="W82">
+        <v>1.2</v>
+      </c>
+      <c r="X82">
+        <v>0</v>
+      </c>
+      <c r="Y82">
+        <v>1.08</v>
+      </c>
+      <c r="Z82">
+        <v>5.45</v>
+      </c>
+      <c r="AA82">
+        <v>1.4</v>
+      </c>
+      <c r="AB82">
+        <v>2.88</v>
+      </c>
+      <c r="AC82">
+        <v>1.99</v>
+      </c>
+      <c r="AD82">
+        <v>1.76</v>
+      </c>
+      <c r="AE82">
+        <v>1.37</v>
+      </c>
+      <c r="AF82">
+        <v>1.41</v>
+      </c>
+      <c r="AG82">
+        <v>2.8</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ82">
+        <v>1.18</v>
+      </c>
+      <c r="AK82">
         <v>1.95</v>
-      </c>
-      <c r="O82">
-        <v>3.5</v>
-      </c>
-      <c r="P82">
-        <v>3.02</v>
-      </c>
-      <c r="Q82">
-        <v>2.55</v>
-      </c>
-      <c r="R82">
-        <v>2.4</v>
-      </c>
-      <c r="S82">
-        <v>1.22</v>
-      </c>
-      <c r="T82">
-        <v>3.8</v>
-      </c>
-      <c r="U82">
-        <v>2.15</v>
-      </c>
-      <c r="V82">
-        <v>1.65</v>
-      </c>
-      <c r="W82">
-        <v>1.15</v>
-      </c>
-      <c r="X82">
-        <v>1.01</v>
-      </c>
-      <c r="Y82">
-        <v>1.15</v>
-      </c>
-      <c r="Z82">
-        <v>5.25</v>
-      </c>
-      <c r="AA82">
-        <v>1.5</v>
-      </c>
-      <c r="AB82">
-        <v>2.55</v>
-      </c>
-      <c r="AC82">
-        <v>2.12</v>
-      </c>
-      <c r="AD82">
-        <v>1.62</v>
-      </c>
-      <c r="AE82">
-        <v>1.25</v>
-      </c>
-      <c r="AF82">
-        <v>1.44</v>
-      </c>
-      <c r="AG82">
-        <v>2.7</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ82">
-        <v>1.2</v>
-      </c>
-      <c r="AK82">
-        <v>1.73</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="O83">
-        <v>4.26</v>
+        <v>6.09</v>
       </c>
       <c r="P83">
-        <v>3.92</v>
+        <v>7</v>
       </c>
       <c r="Q83">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="R83">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="S83">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T83">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="U83">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="V83">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W83">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="X83">
         <v>0</v>
       </c>
       <c r="Y83">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z83">
-        <v>6.66</v>
+        <v>6.98</v>
       </c>
       <c r="AA83">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AB83">
-        <v>3.06</v>
+        <v>3.4</v>
       </c>
       <c r="AC83">
         <v>1.83</v>
       </c>
       <c r="AD83">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AE83">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AF83">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AG83">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK83">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,28 +14001,28 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="O84">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="P84">
-        <v>8.5</v>
+        <v>5.9</v>
       </c>
       <c r="Q84">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="R84">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S84">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T84">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="U84">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="V84">
         <v>1.8</v>
@@ -14034,31 +14034,31 @@
         <v>0</v>
       </c>
       <c r="Y84">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z84">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="AA84">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB84">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="AC84">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AD84">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AE84">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF84">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AG84">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AK84">
-        <v>3.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14104,6 +14104,169 @@
         <v>0</v>
       </c>
       <c r="AU84" t="inlineStr">
+        <is>
+          <t>2026-09-09 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N85">
+        <v>2.15</v>
+      </c>
+      <c r="O85">
+        <v>3.78</v>
+      </c>
+      <c r="P85">
+        <v>2.99</v>
+      </c>
+      <c r="Q85">
+        <v>2.7</v>
+      </c>
+      <c r="R85">
+        <v>2.4</v>
+      </c>
+      <c r="S85">
+        <v>1.22</v>
+      </c>
+      <c r="T85">
+        <v>3.8</v>
+      </c>
+      <c r="U85">
+        <v>2.23</v>
+      </c>
+      <c r="V85">
+        <v>1.64</v>
+      </c>
+      <c r="W85">
+        <v>1.15</v>
+      </c>
+      <c r="X85">
+        <v>1.01</v>
+      </c>
+      <c r="Y85">
+        <v>1.15</v>
+      </c>
+      <c r="Z85">
+        <v>5.25</v>
+      </c>
+      <c r="AA85">
+        <v>1.53</v>
+      </c>
+      <c r="AB85">
+        <v>2.55</v>
+      </c>
+      <c r="AC85">
+        <v>2.12</v>
+      </c>
+      <c r="AD85">
+        <v>1.62</v>
+      </c>
+      <c r="AE85">
+        <v>1.25</v>
+      </c>
+      <c r="AF85">
+        <v>1.42</v>
+      </c>
+      <c r="AG85">
+        <v>2.61</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ85">
+        <v>1.25</v>
+      </c>
+      <c r="AK85">
+        <v>1.67</v>
+      </c>
+      <c r="AL85">
+        <v>0</v>
+      </c>
+      <c r="AM85">
+        <v>-1</v>
+      </c>
+      <c r="AN85">
+        <v>-1</v>
+      </c>
+      <c r="AO85">
+        <v>-1</v>
+      </c>
+      <c r="AP85">
+        <v>-1</v>
+      </c>
+      <c r="AQ85">
+        <v>0</v>
+      </c>
+      <c r="AR85">
+        <v>0</v>
+      </c>
+      <c r="AS85">
+        <v>0</v>
+      </c>
+      <c r="AT85">
+        <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
         <is>
           <t>2026-09-09 23:30:00</t>
         </is>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3">
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="O3">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>4.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q3">
-        <v>2.05</v>
+        <v>3.02</v>
       </c>
       <c r="R3">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="S3">
+        <v>1.44</v>
+      </c>
+      <c r="T3">
+        <v>2.72</v>
+      </c>
+      <c r="U3">
+        <v>3.15</v>
+      </c>
+      <c r="V3">
+        <v>1.31</v>
+      </c>
+      <c r="W3">
+        <v>1.01</v>
+      </c>
+      <c r="X3">
+        <v>1.01</v>
+      </c>
+      <c r="Y3">
+        <v>1.36</v>
+      </c>
+      <c r="Z3">
+        <v>2.9</v>
+      </c>
+      <c r="AA3">
+        <v>2.14</v>
+      </c>
+      <c r="AB3">
+        <v>1.66</v>
+      </c>
+      <c r="AC3">
+        <v>3.99</v>
+      </c>
+      <c r="AD3">
+        <v>1.2</v>
+      </c>
+      <c r="AE3">
+        <v>1.02</v>
+      </c>
+      <c r="AF3">
+        <v>1.83</v>
+      </c>
+      <c r="AG3">
+        <v>1.84</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
         <v>1.33</v>
       </c>
-      <c r="T3">
-        <v>3.22</v>
-      </c>
-      <c r="U3">
-        <v>2.47</v>
-      </c>
-      <c r="V3">
-        <v>1.48</v>
-      </c>
-      <c r="W3">
-        <v>1.08</v>
-      </c>
-      <c r="X3">
-        <v>1.03</v>
-      </c>
-      <c r="Y3">
-        <v>1.21</v>
-      </c>
-      <c r="Z3">
-        <v>3.62</v>
-      </c>
-      <c r="AA3">
-        <v>1.75</v>
-      </c>
-      <c r="AB3">
-        <v>2.05</v>
-      </c>
-      <c r="AC3">
-        <v>2.8</v>
-      </c>
-      <c r="AD3">
-        <v>1.34</v>
-      </c>
-      <c r="AE3">
-        <v>1.14</v>
-      </c>
-      <c r="AF3">
-        <v>1.79</v>
-      </c>
-      <c r="AG3">
-        <v>1.92</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.2</v>
-      </c>
       <c r="AK3">
-        <v>2.28</v>
+        <v>1.56</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="O5">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="P5">
-        <v>2.9</v>
+        <v>4.85</v>
       </c>
       <c r="Q5">
-        <v>3.02</v>
+        <v>2.05</v>
       </c>
       <c r="R5">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="S5">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>2.72</v>
+        <v>3.22</v>
       </c>
       <c r="U5">
-        <v>3.15</v>
+        <v>2.47</v>
       </c>
       <c r="V5">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>2.9</v>
+        <v>3.62</v>
       </c>
       <c r="AA5">
-        <v>2.14</v>
+        <v>1.75</v>
       </c>
       <c r="AB5">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="AC5">
-        <v>3.99</v>
+        <v>2.8</v>
       </c>
       <c r="AD5">
+        <v>1.34</v>
+      </c>
+      <c r="AE5">
+        <v>1.14</v>
+      </c>
+      <c r="AF5">
+        <v>1.79</v>
+      </c>
+      <c r="AG5">
+        <v>1.92</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.2</v>
       </c>
-      <c r="AE5">
-        <v>1.02</v>
-      </c>
-      <c r="AF5">
-        <v>1.83</v>
-      </c>
-      <c r="AG5">
-        <v>1.84</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.33</v>
-      </c>
       <c r="AK5">
-        <v>1.56</v>
+        <v>2.28</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1622,10 +1622,10 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="R8">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S8">
         <v>1.64</v>
@@ -1634,31 +1634,31 @@
         <v>2.11</v>
       </c>
       <c r="U8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V8">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
         <v>1.08</v>
       </c>
       <c r="Y8">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Z8">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AA8">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AB8">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC8">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="AD8">
         <v>1.06</v>
@@ -1667,7 +1667,7 @@
         <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="AG8">
         <v>1.55</v>
@@ -1686,7 +1686,7 @@
         <v>1.35</v>
       </c>
       <c r="AK8">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="O9">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P9">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q9">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="R9">
         <v>2</v>
       </c>
       <c r="S9">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="T9">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="U9">
-        <v>3.21</v>
+        <v>3.5</v>
       </c>
       <c r="V9">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y9">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Z9">
-        <v>2.61</v>
+        <v>2.56</v>
       </c>
       <c r="AA9">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="AB9">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AC9">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AD9">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AG9">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1945,7 +1945,7 @@
         <v>4.4</v>
       </c>
       <c r="P10">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="Q10">
         <v>1.56</v>
@@ -1957,13 +1957,13 @@
         <v>1.25</v>
       </c>
       <c r="T10">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V10">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W10">
         <v>1.07</v>
@@ -2591,52 +2591,52 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="O14">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="P14">
-        <v>3.55</v>
+        <v>3.74</v>
       </c>
       <c r="Q14">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="R14">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="S14">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T14">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="U14">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V14">
         <v>1.45</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z14">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA14">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB14">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC14">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="AD14">
         <v>1.36</v>
@@ -2645,10 +2645,10 @@
         <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AG14">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK14">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O15">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P15">
-        <v>4.34</v>
+        <v>4.2</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,34 +2917,34 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="O16">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
         <v>2.25</v>
       </c>
       <c r="Q16">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="R16">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S16">
         <v>1.29</v>
       </c>
       <c r="T16">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U16">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
         <v>1.03</v>
@@ -2953,13 +2953,13 @@
         <v>1.18</v>
       </c>
       <c r="Z16">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="AA16">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB16">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC16">
         <v>2.8</v>
@@ -2971,10 +2971,10 @@
         <v>1.15</v>
       </c>
       <c r="AF16">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG16">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="AK16">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="O25">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P25">
         <v>1.4</v>
       </c>
       <c r="Q25">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
         <v>1.39</v>
       </c>
       <c r="T25">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="U25">
         <v>3</v>
       </c>
       <c r="V25">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z25">
         <v>3.22</v>
       </c>
       <c r="AA25">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AB25">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC25">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD25">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE25">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF25">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AG25">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>2.53</v>
       </c>
       <c r="AK25">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="O26">
         <v>2.75</v>
       </c>
       <c r="P26">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="Q26">
-        <v>3.92</v>
+        <v>3.84</v>
       </c>
       <c r="R26">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="S26">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="T26">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="U26">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="V26">
         <v>1.17</v>
       </c>
       <c r="W26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X26">
         <v>1.09</v>
       </c>
       <c r="Y26">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Z26">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AA26">
         <v>2.96</v>
       </c>
       <c r="AB26">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AC26">
-        <v>5.96</v>
+        <v>6</v>
       </c>
       <c r="AD26">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE26">
         <v>1.01</v>
       </c>
       <c r="AF26">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG26">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AK26">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q27">
-        <v>4.07</v>
+        <v>4.03</v>
       </c>
       <c r="R27">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="S27">
         <v>1.31</v>
@@ -4746,7 +4746,7 @@
         <v>1.26</v>
       </c>
       <c r="Z27">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="AA27">
         <v>1.8</v>
@@ -4767,7 +4767,7 @@
         <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O34">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q34">
-        <v>3.86</v>
+        <v>3.98</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S34">
         <v>1.29</v>
       </c>
       <c r="T34">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="V34">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
+        <v>1.17</v>
+      </c>
+      <c r="Z34">
+        <v>4.5</v>
+      </c>
+      <c r="AA34">
+        <v>1.65</v>
+      </c>
+      <c r="AB34">
+        <v>2.1</v>
+      </c>
+      <c r="AC34">
+        <v>2.5</v>
+      </c>
+      <c r="AD34">
+        <v>1.49</v>
+      </c>
+      <c r="AE34">
         <v>1.18</v>
       </c>
-      <c r="Z34">
-        <v>3.86</v>
-      </c>
-      <c r="AA34">
-        <v>1.68</v>
-      </c>
-      <c r="AB34">
-        <v>2.06</v>
-      </c>
-      <c r="AC34">
-        <v>2.7</v>
-      </c>
-      <c r="AD34">
-        <v>1.43</v>
-      </c>
-      <c r="AE34">
-        <v>1.12</v>
-      </c>
       <c r="AF34">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG34">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="O35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P35">
-        <v>7.75</v>
+        <v>11</v>
       </c>
       <c r="Q35">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="R35">
-        <v>2.9</v>
+        <v>3.21</v>
       </c>
       <c r="S35">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T35">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="U35">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V35">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="W35">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
+        <v>1.03</v>
+      </c>
+      <c r="Z35">
+        <v>7.3</v>
+      </c>
+      <c r="AA35">
+        <v>1.3</v>
+      </c>
+      <c r="AB35">
+        <v>3.5</v>
+      </c>
+      <c r="AC35">
+        <v>1.62</v>
+      </c>
+      <c r="AD35">
+        <v>2.17</v>
+      </c>
+      <c r="AE35">
+        <v>1.5</v>
+      </c>
+      <c r="AF35">
+        <v>1.66</v>
+      </c>
+      <c r="AG35">
+        <v>2.1</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.04</v>
       </c>
-      <c r="Z35">
-        <v>6.95</v>
-      </c>
-      <c r="AA35">
-        <v>1.25</v>
-      </c>
-      <c r="AB35">
-        <v>3.16</v>
-      </c>
-      <c r="AC35">
-        <v>1.77</v>
-      </c>
-      <c r="AD35">
-        <v>1.94</v>
-      </c>
-      <c r="AE35">
-        <v>1.38</v>
-      </c>
-      <c r="AF35">
-        <v>1.57</v>
-      </c>
-      <c r="AG35">
-        <v>2.2</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.05</v>
-      </c>
       <c r="AK35">
-        <v>3.5</v>
+        <v>4.46</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6340,31 +6340,31 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="O37">
         <v>3.4</v>
       </c>
       <c r="P37">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="Q37">
-        <v>3.49</v>
+        <v>3.3</v>
       </c>
       <c r="R37">
         <v>2.24</v>
       </c>
       <c r="S37">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="T37">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="U37">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="V37">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W37">
         <v>1.06</v>
@@ -6376,13 +6376,13 @@
         <v>1.3</v>
       </c>
       <c r="Z37">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AA37">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB37">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AC37">
         <v>2.95</v>
@@ -6394,7 +6394,7 @@
         <v>1.11</v>
       </c>
       <c r="AF37">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG37">
         <v>2.15</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AK37">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,28 +6512,28 @@
         <v>3.18</v>
       </c>
       <c r="Q38">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="R38">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S38">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T38">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U38">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="V38">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
         <v>1.26</v>
@@ -6554,13 +6554,13 @@
         <v>1.33</v>
       </c>
       <c r="AE38">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF38">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG38">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK38">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6669,77 +6669,77 @@
         <v>1.3</v>
       </c>
       <c r="O39">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="P39">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="Q39">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="R39">
-        <v>2.97</v>
+        <v>2.69</v>
       </c>
       <c r="S39">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T39">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U39">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="V39">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="W39">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
+        <v>1.13</v>
+      </c>
+      <c r="Z39">
+        <v>5.94</v>
+      </c>
+      <c r="AA39">
+        <v>1.43</v>
+      </c>
+      <c r="AB39">
+        <v>2.8</v>
+      </c>
+      <c r="AC39">
+        <v>2.11</v>
+      </c>
+      <c r="AD39">
+        <v>1.72</v>
+      </c>
+      <c r="AE39">
+        <v>1.25</v>
+      </c>
+      <c r="AF39">
+        <v>1.65</v>
+      </c>
+      <c r="AG39">
+        <v>2.02</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
         <v>1.1</v>
       </c>
-      <c r="Z39">
-        <v>5.25</v>
-      </c>
-      <c r="AA39">
-        <v>1.57</v>
-      </c>
-      <c r="AB39">
-        <v>2.75</v>
-      </c>
-      <c r="AC39">
-        <v>2.15</v>
-      </c>
-      <c r="AD39">
-        <v>1.53</v>
-      </c>
-      <c r="AE39">
-        <v>1.28</v>
-      </c>
-      <c r="AF39">
-        <v>1.7</v>
-      </c>
-      <c r="AG39">
-        <v>1.95</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.12</v>
-      </c>
       <c r="AK39">
-        <v>3.38</v>
+        <v>2.95</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7481,19 +7481,19 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="O44">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="P44">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q44">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="R44">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S44">
         <v>1.4</v>
@@ -7508,7 +7508,7 @@
         <v>1.4</v>
       </c>
       <c r="W44">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X44">
         <v>1.03</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK44">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,25 +7644,25 @@
         </is>
       </c>
       <c r="N45">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O45">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P45">
         <v>1.48</v>
       </c>
       <c r="Q45">
-        <v>5.58</v>
+        <v>5.75</v>
       </c>
       <c r="R45">
-        <v>2.69</v>
+        <v>2.48</v>
       </c>
       <c r="S45">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T45">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="U45">
         <v>2.2</v>
@@ -7671,7 +7671,7 @@
         <v>1.63</v>
       </c>
       <c r="W45">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X45">
         <v>1.02</v>
@@ -7680,28 +7680,28 @@
         <v>1.09</v>
       </c>
       <c r="Z45">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA45">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB45">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AC45">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="AD45">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AE45">
         <v>1.21</v>
       </c>
       <c r="AF45">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG45">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK45">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7810,28 +7810,28 @@
         <v>15</v>
       </c>
       <c r="O46">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="P46">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Q46">
-        <v>11.5</v>
+        <v>7.62</v>
       </c>
       <c r="R46">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="S46">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="T46">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="U46">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="V46">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="W46">
         <v>1.14</v>
@@ -7840,31 +7840,31 @@
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z46">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AA46">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AB46">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC46">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD46">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AE46">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF46">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AG46">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.1</v>
       </c>
       <c r="AK46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7979,16 +7979,16 @@
         <v>2.6</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U47">
         <v>0</v>
@@ -8003,31 +8003,31 @@
         <v>0</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE47">
         <v>0</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8468,16 +8468,16 @@
         <v>2.75</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U50">
         <v>0</v>
@@ -8492,31 +8492,31 @@
         <v>0</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE50">
         <v>0</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,80 +8948,80 @@
         </is>
       </c>
       <c r="N53">
+        <v>2.98</v>
+      </c>
+      <c r="O53">
+        <v>3.52</v>
+      </c>
+      <c r="P53">
+        <v>2.3</v>
+      </c>
+      <c r="Q53">
+        <v>3.3</v>
+      </c>
+      <c r="R53">
+        <v>2.3</v>
+      </c>
+      <c r="S53">
+        <v>1.3</v>
+      </c>
+      <c r="T53">
+        <v>3.4</v>
+      </c>
+      <c r="U53">
+        <v>2.5</v>
+      </c>
+      <c r="V53">
+        <v>1.51</v>
+      </c>
+      <c r="W53">
+        <v>1.1</v>
+      </c>
+      <c r="X53">
+        <v>1.03</v>
+      </c>
+      <c r="Y53">
+        <v>1.16</v>
+      </c>
+      <c r="Z53">
+        <v>4.15</v>
+      </c>
+      <c r="AA53">
+        <v>1.65</v>
+      </c>
+      <c r="AB53">
+        <v>2.1</v>
+      </c>
+      <c r="AC53">
+        <v>2.55</v>
+      </c>
+      <c r="AD53">
+        <v>1.5</v>
+      </c>
+      <c r="AE53">
+        <v>1.13</v>
+      </c>
+      <c r="AF53">
         <v>1.53</v>
       </c>
-      <c r="O53">
-        <v>4.15</v>
-      </c>
-      <c r="P53">
-        <v>4.05</v>
-      </c>
-      <c r="Q53">
-        <v>2.1</v>
-      </c>
-      <c r="R53">
-        <v>2.55</v>
-      </c>
-      <c r="S53">
-        <v>1.2</v>
-      </c>
-      <c r="T53">
-        <v>4.4</v>
-      </c>
-      <c r="U53">
-        <v>1.95</v>
-      </c>
-      <c r="V53">
-        <v>1.75</v>
-      </c>
-      <c r="W53">
-        <v>1.22</v>
-      </c>
-      <c r="X53">
-        <v>0</v>
-      </c>
-      <c r="Y53">
-        <v>1.11</v>
-      </c>
-      <c r="Z53">
-        <v>6.25</v>
-      </c>
-      <c r="AA53">
-        <v>1.38</v>
-      </c>
-      <c r="AB53">
-        <v>2.89</v>
-      </c>
-      <c r="AC53">
-        <v>1.92</v>
-      </c>
-      <c r="AD53">
-        <v>1.81</v>
-      </c>
-      <c r="AE53">
+      <c r="AG53">
+        <v>2.28</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>1.25</v>
+      </c>
+      <c r="AK53">
         <v>1.36</v>
-      </c>
-      <c r="AF53">
-        <v>1.4</v>
-      </c>
-      <c r="AG53">
-        <v>2.75</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.22</v>
-      </c>
-      <c r="AK53">
-        <v>2.15</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="O54">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>2.09</v>
+        <v>2.8</v>
       </c>
       <c r="Q54">
-        <v>3.66</v>
+        <v>2.75</v>
       </c>
       <c r="R54">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S54">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="T54">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="U54">
-        <v>2.49</v>
+        <v>2.17</v>
       </c>
       <c r="V54">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="W54">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X54">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
         <v>1.16</v>
       </c>
       <c r="Z54">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="AA54">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AB54">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC54">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AD54">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE54">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF54">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AG54">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK54">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="O55">
-        <v>3.73</v>
+        <v>3.4</v>
       </c>
       <c r="P55">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="Q55">
-        <v>2.65</v>
+        <v>3.14</v>
       </c>
       <c r="R55">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S55">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="T55">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="U55">
-        <v>2.17</v>
+        <v>2.53</v>
       </c>
       <c r="V55">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="W55">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X55">
         <v>1.01</v>
       </c>
       <c r="Y55">
+        <v>1.2</v>
+      </c>
+      <c r="Z55">
+        <v>4.2</v>
+      </c>
+      <c r="AA55">
+        <v>1.7</v>
+      </c>
+      <c r="AB55">
+        <v>2.2</v>
+      </c>
+      <c r="AC55">
+        <v>2.63</v>
+      </c>
+      <c r="AD55">
+        <v>1.45</v>
+      </c>
+      <c r="AE55">
         <v>1.16</v>
       </c>
-      <c r="Z55">
-        <v>4.9</v>
-      </c>
-      <c r="AA55">
-        <v>1.55</v>
-      </c>
-      <c r="AB55">
-        <v>2.4</v>
-      </c>
-      <c r="AC55">
-        <v>2.4</v>
-      </c>
-      <c r="AD55">
-        <v>1.58</v>
-      </c>
-      <c r="AE55">
-        <v>1.2</v>
-      </c>
       <c r="AF55">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AG55">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK55">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="O56">
-        <v>3.63</v>
+        <v>3.97</v>
       </c>
       <c r="P56">
-        <v>2.31</v>
+        <v>3.27</v>
       </c>
       <c r="Q56">
-        <v>3.1</v>
+        <v>2.49</v>
       </c>
       <c r="R56">
-        <v>2.2</v>
+        <v>2.61</v>
       </c>
       <c r="S56">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="T56">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="U56">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="V56">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="W56">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X56">
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="Z56">
-        <v>4.2</v>
+        <v>5.83</v>
       </c>
       <c r="AA56">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AB56">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AC56">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="AD56">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="AE56">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AF56">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG56">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="O57">
-        <v>3.97</v>
+        <v>3.2</v>
       </c>
       <c r="P57">
-        <v>3.27</v>
+        <v>2.84</v>
       </c>
       <c r="Q57">
-        <v>2.49</v>
+        <v>2.71</v>
       </c>
       <c r="R57">
-        <v>2.39</v>
+        <v>2.06</v>
       </c>
       <c r="S57">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="T57">
-        <v>3.8</v>
+        <v>2.63</v>
       </c>
       <c r="U57">
-        <v>2.13</v>
+        <v>2.69</v>
       </c>
       <c r="V57">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="W57">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
+        <v>1.28</v>
+      </c>
+      <c r="Z57">
+        <v>3.3</v>
+      </c>
+      <c r="AA57">
+        <v>2</v>
+      </c>
+      <c r="AB57">
+        <v>1.87</v>
+      </c>
+      <c r="AC57">
+        <v>3.5</v>
+      </c>
+      <c r="AD57">
+        <v>1.25</v>
+      </c>
+      <c r="AE57">
         <v>1.11</v>
       </c>
-      <c r="Z57">
-        <v>5.5</v>
-      </c>
-      <c r="AA57">
-        <v>1.48</v>
-      </c>
-      <c r="AB57">
-        <v>2.7</v>
-      </c>
-      <c r="AC57">
-        <v>2.2</v>
-      </c>
-      <c r="AD57">
-        <v>1.69</v>
-      </c>
-      <c r="AE57">
-        <v>1.29</v>
-      </c>
       <c r="AF57">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="AG57">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK57">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="O59">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="P59">
-        <v>2.84</v>
+        <v>4</v>
       </c>
       <c r="Q59">
-        <v>2.71</v>
+        <v>2.1</v>
       </c>
       <c r="R59">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="S59">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="T59">
-        <v>2.63</v>
+        <v>4.4</v>
       </c>
       <c r="U59">
-        <v>2.69</v>
+        <v>1.92</v>
       </c>
       <c r="V59">
-        <v>1.39</v>
+        <v>1.76</v>
       </c>
       <c r="W59">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="X59">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y59">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="Z59">
-        <v>3.3</v>
+        <v>6.73</v>
       </c>
       <c r="AA59">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="AB59">
-        <v>1.87</v>
+        <v>3.07</v>
       </c>
       <c r="AC59">
-        <v>3.5</v>
+        <v>1.92</v>
       </c>
       <c r="AD59">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="AE59">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AF59">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="AG59">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AK59">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-09-09 20:30:00</t>
+          <t>2026-09-09 20:45:00</t>
         </is>
       </c>
     </row>
@@ -12700,7 +12700,7 @@
         <v>2.15</v>
       </c>
       <c r="O76">
-        <v>3.61</v>
+        <v>3.68</v>
       </c>
       <c r="P76">
         <v>2.65</v>
@@ -12866,28 +12866,28 @@
         <v>3.4</v>
       </c>
       <c r="P77">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="Q77">
         <v>3.15</v>
       </c>
       <c r="R77">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="S77">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T77">
         <v>3.2</v>
       </c>
       <c r="U77">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="V77">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W77">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X77">
         <v>1.04</v>
@@ -12902,7 +12902,7 @@
         <v>1.85</v>
       </c>
       <c r="AB77">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC77">
         <v>3</v>
@@ -12911,7 +12911,7 @@
         <v>1.38</v>
       </c>
       <c r="AE77">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF77">
         <v>1.67</v>
@@ -13029,10 +13029,10 @@
         <v>3.7</v>
       </c>
       <c r="P78">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="Q78">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R78">
         <v>2.58</v>
@@ -13059,7 +13059,7 @@
         <v>1.13</v>
       </c>
       <c r="Z78">
-        <v>5.4</v>
+        <v>4.95</v>
       </c>
       <c r="AA78">
         <v>1.5</v>
@@ -13074,13 +13074,13 @@
         <v>1.62</v>
       </c>
       <c r="AE78">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF78">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG78">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13195,25 +13195,25 @@
         <v>4.25</v>
       </c>
       <c r="Q79">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="R79">
         <v>2.46</v>
       </c>
       <c r="S79">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T79">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U79">
         <v>2.3</v>
       </c>
       <c r="V79">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W79">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X79">
         <v>1.01</v>
@@ -13243,7 +13243,7 @@
         <v>1.62</v>
       </c>
       <c r="AG79">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="O80">
         <v>3.9</v>
@@ -13358,22 +13358,22 @@
         <v>2.6</v>
       </c>
       <c r="Q80">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="R80">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="S80">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T80">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U80">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="V80">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="W80">
         <v>1.25</v>
@@ -13385,25 +13385,25 @@
         <v>1.07</v>
       </c>
       <c r="Z80">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="AA80">
         <v>1.3</v>
       </c>
       <c r="AB80">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="AC80">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AD80">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AE80">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AF80">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AG80">
         <v>3.45</v>
@@ -13675,19 +13675,19 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O82">
-        <v>4.12</v>
+        <v>4.16</v>
       </c>
       <c r="P82">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="Q82">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="R82">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="S82">
         <v>1.2</v>
@@ -13696,22 +13696,22 @@
         <v>3.88</v>
       </c>
       <c r="U82">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="V82">
         <v>1.72</v>
       </c>
       <c r="W82">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X82">
         <v>0</v>
       </c>
       <c r="Y82">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z82">
-        <v>5.45</v>
+        <v>6.08</v>
       </c>
       <c r="AA82">
         <v>1.4</v>
@@ -13720,19 +13720,19 @@
         <v>2.88</v>
       </c>
       <c r="AC82">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AD82">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AE82">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AF82">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AG82">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.18</v>
       </c>
       <c r="AK82">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13841,31 +13841,31 @@
         <v>1.33</v>
       </c>
       <c r="O83">
-        <v>6.09</v>
+        <v>5.25</v>
       </c>
       <c r="P83">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="Q83">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R83">
-        <v>2.85</v>
+        <v>3.11</v>
       </c>
       <c r="S83">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T83">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="U83">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="V83">
         <v>1.83</v>
       </c>
       <c r="W83">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X83">
         <v>0</v>
@@ -13886,7 +13886,7 @@
         <v>1.83</v>
       </c>
       <c r="AD83">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AE83">
         <v>1.36</v>
@@ -13895,7 +13895,7 @@
         <v>1.65</v>
       </c>
       <c r="AG83">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AK83">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.32</v>
+        <v>2.15</v>
       </c>
       <c r="O84">
-        <v>5.1</v>
+        <v>3.78</v>
       </c>
       <c r="P84">
-        <v>5.9</v>
+        <v>2.97</v>
       </c>
       <c r="Q84">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="R84">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="S84">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T84">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="U84">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="V84">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="W84">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z84">
-        <v>6.7</v>
+        <v>4.95</v>
       </c>
       <c r="AA84">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AB84">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC84">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="AD84">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="AE84">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF84">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AG84">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AK84">
-        <v>2.88</v>
+        <v>1.67</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,65 +14164,65 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.15</v>
+        <v>1.43</v>
       </c>
       <c r="O85">
-        <v>3.78</v>
+        <v>5</v>
       </c>
       <c r="P85">
-        <v>2.99</v>
+        <v>6.55</v>
       </c>
       <c r="Q85">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="R85">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="S85">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T85">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="U85">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="V85">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="W85">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y85">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z85">
-        <v>5.25</v>
+        <v>6.7</v>
       </c>
       <c r="AA85">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AB85">
+        <v>3.1</v>
+      </c>
+      <c r="AC85">
+        <v>1.94</v>
+      </c>
+      <c r="AD85">
+        <v>1.89</v>
+      </c>
+      <c r="AE85">
+        <v>1.33</v>
+      </c>
+      <c r="AF85">
+        <v>1.47</v>
+      </c>
+      <c r="AG85">
         <v>2.55</v>
       </c>
-      <c r="AC85">
-        <v>2.12</v>
-      </c>
-      <c r="AD85">
-        <v>1.62</v>
-      </c>
-      <c r="AE85">
-        <v>1.25</v>
-      </c>
-      <c r="AF85">
-        <v>1.42</v>
-      </c>
-      <c r="AG85">
-        <v>2.61</v>
-      </c>
       <c r="AH85" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK85">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="AL85">
         <v>0</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -641,13 +641,13 @@
         <v>3.2</v>
       </c>
       <c r="P2">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q2">
-        <v>3.24</v>
+        <v>2.92</v>
       </c>
       <c r="R2">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="S2">
         <v>1.4</v>
@@ -656,43 +656,43 @@
         <v>2.75</v>
       </c>
       <c r="U2">
-        <v>3.19</v>
+        <v>2.89</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
+        <v>1.05</v>
+      </c>
+      <c r="X2">
         <v>1.07</v>
       </c>
-      <c r="X2">
-        <v>1.03</v>
-      </c>
       <c r="Y2">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z2">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AA2">
         <v>2.14</v>
       </c>
       <c r="AB2">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC2">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="AD2">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE2">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF2">
         <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AK2">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,55 +798,55 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="O3">
         <v>3.2</v>
       </c>
       <c r="P3">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="Q3">
-        <v>3.02</v>
+        <v>3.07</v>
       </c>
       <c r="R3">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="S3">
         <v>1.44</v>
       </c>
       <c r="T3">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="U3">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="V3">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z3">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA3">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AB3">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AC3">
         <v>3.99</v>
       </c>
       <c r="AD3">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE3">
         <v>1.02</v>
@@ -855,7 +855,7 @@
         <v>1.83</v>
       </c>
       <c r="AG3">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -964,61 +964,61 @@
         <v>3.58</v>
       </c>
       <c r="O4">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q4">
-        <v>4.84</v>
+        <v>3.98</v>
       </c>
       <c r="R4">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="S4">
         <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U4">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="V4">
+        <v>1.33</v>
+      </c>
+      <c r="W4">
+        <v>1.05</v>
+      </c>
+      <c r="X4">
+        <v>1.02</v>
+      </c>
+      <c r="Y4">
         <v>1.35</v>
       </c>
-      <c r="W4">
-        <v>1.07</v>
-      </c>
-      <c r="X4">
-        <v>1.05</v>
-      </c>
-      <c r="Y4">
-        <v>1.3</v>
-      </c>
       <c r="Z4">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="AA4">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="AB4">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AC4">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AD4">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE4">
         <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG4">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AK4">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="O5">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P5">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="Q5">
         <v>2.05</v>
       </c>
       <c r="R5">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T5">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="U5">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V5">
         <v>1.48</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z5">
-        <v>3.62</v>
+        <v>3.74</v>
       </c>
       <c r="AA5">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB5">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AC5">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="AD5">
         <v>1.34</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF5">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AG5">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2926,55 +2926,55 @@
         <v>2.25</v>
       </c>
       <c r="Q16">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="R16">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="S16">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U16">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V16">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z16">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AA16">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AB16">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="AC16">
         <v>2.8</v>
       </c>
       <c r="AD16">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE16">
         <v>1.15</v>
       </c>
       <c r="AF16">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.58</v>
+        <v>1.26</v>
       </c>
       <c r="AK16">
         <v>1.36</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.9</v>
+        <v>1.15</v>
       </c>
       <c r="O18">
-        <v>3.8</v>
+        <v>6.75</v>
       </c>
       <c r="P18">
-        <v>1.66</v>
+        <v>12</v>
       </c>
       <c r="Q18">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="R18">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="S18">
+        <v>1.14</v>
+      </c>
+      <c r="T18">
+        <v>4.3</v>
+      </c>
+      <c r="U18">
+        <v>1.83</v>
+      </c>
+      <c r="V18">
+        <v>1.83</v>
+      </c>
+      <c r="W18">
         <v>1.22</v>
-      </c>
-      <c r="T18">
-        <v>3.75</v>
-      </c>
-      <c r="U18">
-        <v>2.22</v>
-      </c>
-      <c r="V18">
-        <v>1.62</v>
-      </c>
-      <c r="W18">
-        <v>1.14</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Z18">
+        <v>6.55</v>
+      </c>
+      <c r="AA18">
+        <v>1.25</v>
+      </c>
+      <c r="AB18">
+        <v>3.4</v>
+      </c>
+      <c r="AC18">
+        <v>1.77</v>
+      </c>
+      <c r="AD18">
+        <v>1.94</v>
+      </c>
+      <c r="AE18">
+        <v>1.38</v>
+      </c>
+      <c r="AF18">
+        <v>1.89</v>
+      </c>
+      <c r="AG18">
+        <v>1.8</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.06</v>
+      </c>
+      <c r="AK18">
         <v>5</v>
-      </c>
-      <c r="AA18">
-        <v>1.47</v>
-      </c>
-      <c r="AB18">
-        <v>2.63</v>
-      </c>
-      <c r="AC18">
-        <v>2.23</v>
-      </c>
-      <c r="AD18">
-        <v>1.57</v>
-      </c>
-      <c r="AE18">
-        <v>1.19</v>
-      </c>
-      <c r="AF18">
-        <v>1.52</v>
-      </c>
-      <c r="AG18">
-        <v>2.34</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.17</v>
-      </c>
-      <c r="AK18">
-        <v>1.2</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.11</v>
+        <v>3.8</v>
       </c>
       <c r="O19">
-        <v>8</v>
+        <v>3.75</v>
       </c>
       <c r="P19">
-        <v>13</v>
+        <v>1.7</v>
       </c>
       <c r="Q19">
-        <v>1.41</v>
+        <v>4.2</v>
       </c>
       <c r="R19">
-        <v>3.24</v>
+        <v>2.36</v>
       </c>
       <c r="S19">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="T19">
-        <v>4.3</v>
+        <v>3.34</v>
       </c>
       <c r="U19">
-        <v>1.8</v>
+        <v>2.24</v>
       </c>
       <c r="V19">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="W19">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z19">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA19">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AB19">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AC19">
-        <v>1.76</v>
+        <v>2.32</v>
       </c>
       <c r="AD19">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AE19">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AF19">
-        <v>2.01</v>
+        <v>1.53</v>
       </c>
       <c r="AG19">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AK19">
-        <v>5.4</v>
+        <v>1.17</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O20">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q20">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="R20">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
+        <v>1.21</v>
+      </c>
+      <c r="T20">
+        <v>3.6</v>
+      </c>
+      <c r="U20">
+        <v>2.17</v>
+      </c>
+      <c r="V20">
+        <v>1.61</v>
+      </c>
+      <c r="W20">
+        <v>1.13</v>
+      </c>
+      <c r="X20">
+        <v>1.01</v>
+      </c>
+      <c r="Y20">
+        <v>1.12</v>
+      </c>
+      <c r="Z20">
+        <v>4.7</v>
+      </c>
+      <c r="AA20">
+        <v>1.57</v>
+      </c>
+      <c r="AB20">
+        <v>2.28</v>
+      </c>
+      <c r="AC20">
+        <v>2.34</v>
+      </c>
+      <c r="AD20">
+        <v>1.53</v>
+      </c>
+      <c r="AE20">
         <v>1.17</v>
-      </c>
-      <c r="T20">
-        <v>4.5</v>
-      </c>
-      <c r="U20">
-        <v>2.1</v>
-      </c>
-      <c r="V20">
-        <v>1.67</v>
-      </c>
-      <c r="W20">
-        <v>1.17</v>
-      </c>
-      <c r="X20">
-        <v>1</v>
-      </c>
-      <c r="Y20">
-        <v>1.09</v>
-      </c>
-      <c r="Z20">
-        <v>5.8</v>
-      </c>
-      <c r="AA20">
-        <v>1.4</v>
-      </c>
-      <c r="AB20">
-        <v>2.88</v>
-      </c>
-      <c r="AC20">
-        <v>1.95</v>
-      </c>
-      <c r="AD20">
-        <v>1.7</v>
-      </c>
-      <c r="AE20">
-        <v>1.26</v>
       </c>
       <c r="AF20">
         <v>1.38</v>
       </c>
       <c r="AG20">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="O21">
-        <v>11.5</v>
+        <v>6.7</v>
       </c>
       <c r="P21">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="R21">
-        <v>4.22</v>
+        <v>3.2</v>
       </c>
       <c r="S21">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="T21">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="U21">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="V21">
-        <v>2.27</v>
+        <v>1.93</v>
       </c>
       <c r="W21">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Z21">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AA21">
+        <v>1.25</v>
+      </c>
+      <c r="AB21">
+        <v>4</v>
+      </c>
+      <c r="AC21">
+        <v>1.72</v>
+      </c>
+      <c r="AD21">
+        <v>2.26</v>
+      </c>
+      <c r="AE21">
+        <v>1.54</v>
+      </c>
+      <c r="AF21">
+        <v>1.58</v>
+      </c>
+      <c r="AG21">
+        <v>2.26</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.13</v>
       </c>
-      <c r="AB21">
-        <v>4.5</v>
-      </c>
-      <c r="AC21">
-        <v>1.45</v>
-      </c>
-      <c r="AD21">
-        <v>2.4</v>
-      </c>
-      <c r="AE21">
-        <v>1.68</v>
-      </c>
-      <c r="AF21">
-        <v>1.75</v>
-      </c>
-      <c r="AG21">
-        <v>1.77</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.05</v>
-      </c>
       <c r="AK21">
-        <v>8</v>
+        <v>4.24</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="O22">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="P22">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="Q22">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="R22">
-        <v>3.2</v>
+        <v>4.19</v>
       </c>
       <c r="S22">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="U22">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="V22">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="W22">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="X22">
+        <v>1</v>
+      </c>
+      <c r="Y22">
         <v>1.01</v>
       </c>
-      <c r="Y22">
-        <v>1.04</v>
-      </c>
       <c r="Z22">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA22">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AB22">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AC22">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AD22">
-        <v>2.21</v>
+        <v>2.63</v>
       </c>
       <c r="AE22">
-        <v>1.52</v>
+        <v>1.79</v>
       </c>
       <c r="AF22">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AG22">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK22">
-        <v>4.22</v>
+        <v>8.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4873,25 +4873,25 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="Q28">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="R28">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T28">
-        <v>2.87</v>
+        <v>3.05</v>
       </c>
       <c r="U28">
         <v>2.5</v>
@@ -4900,37 +4900,37 @@
         <v>1.49</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z28">
-        <v>4.03</v>
+        <v>3.75</v>
       </c>
       <c r="AA28">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB28">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC28">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="AD28">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE28">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF28">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG28">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK28">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,40 +5036,40 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="Q29">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="R29">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="S29">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T29">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U29">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="V29">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W29">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
         <v>4.5</v>
@@ -5078,22 +5078,22 @@
         <v>1.61</v>
       </c>
       <c r="AB29">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC29">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AD29">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE29">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AG29">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="O30">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
         <v>3.25</v>
       </c>
       <c r="Q30">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R30">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U30">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="V30">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="W30">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
+        <v>1.16</v>
+      </c>
+      <c r="Z30">
+        <v>4.5</v>
+      </c>
+      <c r="AA30">
+        <v>1.65</v>
+      </c>
+      <c r="AB30">
+        <v>2.27</v>
+      </c>
+      <c r="AC30">
+        <v>2.6</v>
+      </c>
+      <c r="AD30">
+        <v>1.5</v>
+      </c>
+      <c r="AE30">
         <v>1.15</v>
       </c>
-      <c r="Z30">
-        <v>4</v>
-      </c>
-      <c r="AA30">
-        <v>1.66</v>
-      </c>
-      <c r="AB30">
-        <v>2.15</v>
-      </c>
-      <c r="AC30">
-        <v>2.61</v>
-      </c>
-      <c r="AD30">
-        <v>1.47</v>
-      </c>
-      <c r="AE30">
-        <v>1.14</v>
-      </c>
       <c r="AF30">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AG30">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.26</v>
       </c>
       <c r="AK30">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,65 +5362,65 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="O31">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P31">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="Q31">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="R31">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S31">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U31">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V31">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W31">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="AA31">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AB31">
+        <v>2.2</v>
+      </c>
+      <c r="AC31">
+        <v>2.65</v>
+      </c>
+      <c r="AD31">
+        <v>1.48</v>
+      </c>
+      <c r="AE31">
+        <v>1.2</v>
+      </c>
+      <c r="AF31">
+        <v>1.57</v>
+      </c>
+      <c r="AG31">
         <v>2.25</v>
       </c>
-      <c r="AC31">
-        <v>2.48</v>
-      </c>
-      <c r="AD31">
-        <v>1.45</v>
-      </c>
-      <c r="AE31">
-        <v>1.18</v>
-      </c>
-      <c r="AF31">
-        <v>1.55</v>
-      </c>
-      <c r="AG31">
-        <v>2.3</v>
-      </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK31">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5857,43 +5857,43 @@
         <v>3.6</v>
       </c>
       <c r="P34">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Q34">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="R34">
-        <v>2.24</v>
+        <v>2.39</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U34">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="V34">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
         <v>4.5</v>
       </c>
       <c r="AA34">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB34">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC34">
         <v>2.5</v>
@@ -5902,13 +5902,13 @@
         <v>1.49</v>
       </c>
       <c r="AE34">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF34">
         <v>1.57</v>
       </c>
       <c r="AG34">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK34">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,55 +6023,55 @@
         <v>11</v>
       </c>
       <c r="Q35">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="R35">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="S35">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T35">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="U35">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="V35">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="W35">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z35">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="AA35">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AB35">
         <v>3.5</v>
       </c>
       <c r="AC35">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AD35">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="AE35">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AF35">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG35">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.04</v>
       </c>
       <c r="AK35">
-        <v>4.46</v>
+        <v>5</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,61 +6177,61 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="O36">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="P36">
         <v>4.2</v>
       </c>
       <c r="Q36">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="R36">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="S36">
         <v>1.68</v>
       </c>
       <c r="T36">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="U36">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="V36">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W36">
         <v>1.03</v>
       </c>
       <c r="X36">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Y36">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="Z36">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="AA36">
         <v>2.92</v>
       </c>
       <c r="AB36">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC36">
         <v>5.95</v>
       </c>
       <c r="AD36">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE36">
         <v>1.02</v>
       </c>
       <c r="AF36">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="AG36">
         <v>1.46</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AK36">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6835,58 +6835,58 @@
         <v>3.7</v>
       </c>
       <c r="P40">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="Q40">
-        <v>4.4</v>
+        <v>5.29</v>
       </c>
       <c r="R40">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="S40">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T40">
-        <v>3.01</v>
+        <v>2.89</v>
       </c>
       <c r="U40">
-        <v>2.81</v>
+        <v>2.92</v>
       </c>
       <c r="V40">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W40">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z40">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AA40">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB40">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC40">
-        <v>3.2</v>
+        <v>3.39</v>
       </c>
       <c r="AD40">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE40">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF40">
         <v>1.8</v>
       </c>
       <c r="AG40">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.23</v>
+        <v>2.1</v>
       </c>
       <c r="AK40">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,65 +6992,65 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="O41">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="P41">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q41">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="R41">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="S41">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T41">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U41">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V41">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W41">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
         <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="AA41">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB41">
+        <v>2.2</v>
+      </c>
+      <c r="AC41">
+        <v>2.6</v>
+      </c>
+      <c r="AD41">
+        <v>1.53</v>
+      </c>
+      <c r="AE41">
+        <v>1.14</v>
+      </c>
+      <c r="AF41">
+        <v>1.53</v>
+      </c>
+      <c r="AG41">
         <v>2.3</v>
       </c>
-      <c r="AC41">
-        <v>2.55</v>
-      </c>
-      <c r="AD41">
-        <v>1.5</v>
-      </c>
-      <c r="AE41">
-        <v>1.17</v>
-      </c>
-      <c r="AF41">
-        <v>1.59</v>
-      </c>
-      <c r="AG41">
-        <v>2.21</v>
-      </c>
       <c r="AH41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.06</v>
+        <v>1.68</v>
       </c>
       <c r="O42">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="P42">
-        <v>39</v>
+        <v>4.6</v>
       </c>
       <c r="Q42">
-        <v>1.22</v>
+        <v>2.2</v>
       </c>
       <c r="R42">
-        <v>4.75</v>
+        <v>2.39</v>
       </c>
       <c r="S42">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="T42">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="U42">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="V42">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="W42">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="Z42">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA42">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AB42">
-        <v>4</v>
+        <v>2.21</v>
       </c>
       <c r="AC42">
-        <v>1.62</v>
+        <v>2.63</v>
       </c>
       <c r="AD42">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AE42">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="AF42">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG42">
-        <v>1.4</v>
+        <v>2.24</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AK42">
-        <v>13</v>
+        <v>2.19</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.82</v>
+        <v>1.06</v>
       </c>
       <c r="O43">
-        <v>3.85</v>
+        <v>13</v>
       </c>
       <c r="P43">
-        <v>3.75</v>
+        <v>30</v>
       </c>
       <c r="Q43">
-        <v>2.38</v>
+        <v>1.22</v>
       </c>
       <c r="R43">
-        <v>2.43</v>
+        <v>4.7</v>
       </c>
       <c r="S43">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="T43">
-        <v>3.28</v>
+        <v>6</v>
       </c>
       <c r="U43">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="V43">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="W43">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y43">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="Z43">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA43">
-        <v>1.66</v>
+        <v>1.2</v>
       </c>
       <c r="AB43">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="AC43">
-        <v>2.62</v>
+        <v>1.51</v>
       </c>
       <c r="AD43">
-        <v>1.51</v>
+        <v>2.5</v>
       </c>
       <c r="AE43">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="AF43">
-        <v>1.57</v>
+        <v>2.44</v>
       </c>
       <c r="AG43">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AK43">
-        <v>1.93</v>
+        <v>12.5</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7810,28 +7810,28 @@
         <v>15</v>
       </c>
       <c r="O46">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="P46">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Q46">
-        <v>7.62</v>
+        <v>11</v>
       </c>
       <c r="R46">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="S46">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>4</v>
+        <v>3.42</v>
       </c>
       <c r="U46">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="V46">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="W46">
         <v>1.14</v>
@@ -7840,16 +7840,16 @@
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z46">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA46">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AB46">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AC46">
         <v>2.2</v>
@@ -7858,13 +7858,13 @@
         <v>1.73</v>
       </c>
       <c r="AE46">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF46">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AG46">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.1</v>
+        <v>5.45</v>
       </c>
       <c r="AK46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7979,10 +7979,10 @@
         <v>2.6</v>
       </c>
       <c r="Q47">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="R47">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S47">
         <v>1.35</v>
@@ -7991,16 +7991,16 @@
         <v>2.65</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
         <v>1.29</v>
@@ -8021,7 +8021,7 @@
         <v>1.25</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF47">
         <v>1.73</v>
@@ -8043,7 +8043,7 @@
         <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="O48">
         <v>3</v>
       </c>
       <c r="P48">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="Q48">
         <v>3.71</v>
@@ -8151,13 +8151,13 @@
         <v>1.5</v>
       </c>
       <c r="T48">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="U48">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="V48">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W48">
         <v>1.03</v>
@@ -8169,25 +8169,25 @@
         <v>1.41</v>
       </c>
       <c r="Z48">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="AA48">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AB48">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC48">
-        <v>4.64</v>
+        <v>4.35</v>
       </c>
       <c r="AD48">
         <v>1.19</v>
       </c>
       <c r="AE48">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF48">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AG48">
         <v>1.75</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AK48">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,19 +8305,19 @@
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="R49">
         <v>2.15</v>
       </c>
       <c r="S49">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T49">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="U49">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="V49">
         <v>1.34</v>
@@ -8326,10 +8326,10 @@
         <v>1.05</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z49">
         <v>3.1</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AK49">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8480,16 +8480,16 @@
         <v>2.63</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
         <v>1.29</v>
@@ -8510,7 +8510,7 @@
         <v>1.25</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF50">
         <v>1.75</v>
@@ -8532,7 +8532,7 @@
         <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.98</v>
+        <v>2.25</v>
       </c>
       <c r="O53">
-        <v>3.52</v>
+        <v>3.74</v>
       </c>
       <c r="P53">
-        <v>2.3</v>
+        <v>2.89</v>
       </c>
       <c r="Q53">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="R53">
         <v>2.3</v>
       </c>
       <c r="S53">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T53">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="U53">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="V53">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="W53">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z53">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="AA53">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB53">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AC53">
+        <v>2.4</v>
+      </c>
+      <c r="AD53">
+        <v>1.58</v>
+      </c>
+      <c r="AE53">
+        <v>1.24</v>
+      </c>
+      <c r="AF53">
+        <v>1.5</v>
+      </c>
+      <c r="AG53">
         <v>2.55</v>
-      </c>
-      <c r="AD53">
-        <v>1.5</v>
-      </c>
-      <c r="AE53">
-        <v>1.13</v>
-      </c>
-      <c r="AF53">
-        <v>1.53</v>
-      </c>
-      <c r="AG53">
-        <v>2.28</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P54">
-        <v>2.8</v>
+        <v>3.27</v>
       </c>
       <c r="Q54">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="R54">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="S54">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T54">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U54">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="V54">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="W54">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X54">
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z54">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA54">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AB54">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AC54">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="AD54">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AE54">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF54">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG54">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK54">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="O55">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P55">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q55">
-        <v>3.14</v>
+        <v>3.48</v>
       </c>
       <c r="R55">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="S55">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T55">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U55">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="V55">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W55">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y55">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z55">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA55">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB55">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AC55">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD55">
         <v>1.45</v>
       </c>
       <c r="AE55">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF55">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG55">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.29</v>
+        <v>1.61</v>
       </c>
       <c r="AK55">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.11</v>
+        <v>2.55</v>
       </c>
       <c r="O56">
-        <v>3.97</v>
+        <v>3.4</v>
       </c>
       <c r="P56">
-        <v>3.27</v>
+        <v>2.4</v>
       </c>
       <c r="Q56">
-        <v>2.49</v>
+        <v>3</v>
       </c>
       <c r="R56">
-        <v>2.61</v>
+        <v>2.33</v>
       </c>
       <c r="S56">
+        <v>1.31</v>
+      </c>
+      <c r="T56">
+        <v>3.15</v>
+      </c>
+      <c r="U56">
+        <v>2.36</v>
+      </c>
+      <c r="V56">
+        <v>1.5</v>
+      </c>
+      <c r="W56">
+        <v>1.08</v>
+      </c>
+      <c r="X56">
+        <v>1.04</v>
+      </c>
+      <c r="Y56">
         <v>1.22</v>
       </c>
-      <c r="T56">
-        <v>4.1</v>
-      </c>
-      <c r="U56">
-        <v>2.12</v>
-      </c>
-      <c r="V56">
+      <c r="Z56">
+        <v>3.98</v>
+      </c>
+      <c r="AA56">
         <v>1.7</v>
       </c>
-      <c r="W56">
-        <v>1.17</v>
-      </c>
-      <c r="X56">
-        <v>1.01</v>
-      </c>
-      <c r="Y56">
-        <v>1.13</v>
-      </c>
-      <c r="Z56">
-        <v>5.83</v>
-      </c>
-      <c r="AA56">
-        <v>1.46</v>
-      </c>
       <c r="AB56">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AC56">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AD56">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="AE56">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AF56">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AG56">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK56">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9603,13 +9603,13 @@
         <v>2.3</v>
       </c>
       <c r="O57">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P57">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="Q57">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="R57">
         <v>2.06</v>
@@ -9621,43 +9621,43 @@
         <v>2.63</v>
       </c>
       <c r="U57">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="V57">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W57">
         <v>1.05</v>
       </c>
       <c r="X57">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y57">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z57">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA57">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB57">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC57">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AD57">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE57">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF57">
         <v>1.74</v>
       </c>
       <c r="AG57">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.34</v>
       </c>
       <c r="AK57">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,55 +9763,55 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O58">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P58">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="Q58">
-        <v>3.37</v>
+        <v>3.46</v>
       </c>
       <c r="R58">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S58">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T58">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U58">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="V58">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W58">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X58">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
         <v>1.3</v>
       </c>
       <c r="Z58">
-        <v>3.04</v>
+        <v>3.35</v>
       </c>
       <c r="AA58">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AB58">
         <v>1.76</v>
       </c>
       <c r="AC58">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="AD58">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE58">
         <v>1.06</v>
@@ -9820,7 +9820,7 @@
         <v>1.75</v>
       </c>
       <c r="AG58">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AK58">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9932,7 +9932,7 @@
         <v>4.5</v>
       </c>
       <c r="P59">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="Q59">
         <v>2.1</v>
@@ -9941,40 +9941,40 @@
         <v>2.55</v>
       </c>
       <c r="S59">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T59">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="U59">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="V59">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="W59">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X59">
         <v>0</v>
       </c>
       <c r="Y59">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z59">
-        <v>6.73</v>
+        <v>6.25</v>
       </c>
       <c r="AA59">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AB59">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="AC59">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AD59">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AE59">
         <v>1.36</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK59">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N69">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N70">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N71">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N72">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N73">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N74">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="O76">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="P76">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12869,55 +12869,55 @@
         <v>2.7</v>
       </c>
       <c r="Q77">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="R77">
         <v>2.12</v>
       </c>
       <c r="S77">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T77">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U77">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="V77">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W77">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X77">
         <v>1.04</v>
       </c>
       <c r="Y77">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z77">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="AA77">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB77">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC77">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="AD77">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE77">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF77">
         <v>1.67</v>
       </c>
       <c r="AG77">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK77">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13029,25 +13029,25 @@
         <v>3.7</v>
       </c>
       <c r="P78">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="Q78">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="R78">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="S78">
         <v>1.25</v>
       </c>
       <c r="T78">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="U78">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V78">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W78">
         <v>1.15</v>
@@ -13056,19 +13056,19 @@
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z78">
-        <v>4.95</v>
+        <v>5.39</v>
       </c>
       <c r="AA78">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB78">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AC78">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AD78">
         <v>1.62</v>
@@ -13077,10 +13077,10 @@
         <v>1.21</v>
       </c>
       <c r="AF78">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG78">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13189,34 +13189,34 @@
         <v>1.7</v>
       </c>
       <c r="O79">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P79">
         <v>4.25</v>
       </c>
       <c r="Q79">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="R79">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="S79">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T79">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="U79">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V79">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W79">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X79">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y79">
         <v>1.17</v>
@@ -13231,19 +13231,19 @@
         <v>2.15</v>
       </c>
       <c r="AC79">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="AD79">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE79">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF79">
         <v>1.62</v>
       </c>
       <c r="AG79">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK79">
         <v>2</v>
@@ -13349,61 +13349,61 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="O80">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P80">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="Q80">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="R80">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="S80">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T80">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U80">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V80">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="W80">
+        <v>1.28</v>
+      </c>
+      <c r="X80">
+        <v>0</v>
+      </c>
+      <c r="Y80">
+        <v>1.05</v>
+      </c>
+      <c r="Z80">
+        <v>7.2</v>
+      </c>
+      <c r="AA80">
         <v>1.25</v>
       </c>
-      <c r="X80">
-        <v>0</v>
-      </c>
-      <c r="Y80">
-        <v>1.07</v>
-      </c>
-      <c r="Z80">
-        <v>6.9</v>
-      </c>
-      <c r="AA80">
-        <v>1.3</v>
-      </c>
       <c r="AB80">
-        <v>3.52</v>
+        <v>3.38</v>
       </c>
       <c r="AC80">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AD80">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AE80">
         <v>1.45</v>
       </c>
       <c r="AF80">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AG80">
         <v>3.45</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13518,10 +13518,10 @@
         <v>3.2</v>
       </c>
       <c r="P81">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="Q81">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="R81">
         <v>2</v>
@@ -13530,40 +13530,40 @@
         <v>1.46</v>
       </c>
       <c r="T81">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U81">
-        <v>3.06</v>
+        <v>3.4</v>
       </c>
       <c r="V81">
         <v>1.29</v>
       </c>
       <c r="W81">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X81">
         <v>1.05</v>
       </c>
       <c r="Y81">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z81">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="AA81">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AB81">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC81">
-        <v>4.6</v>
+        <v>4.37</v>
       </c>
       <c r="AD81">
         <v>1.17</v>
       </c>
       <c r="AE81">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF81">
         <v>2</v>
@@ -13585,7 +13585,7 @@
         <v>1.31</v>
       </c>
       <c r="AK81">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,61 +13675,61 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="O82">
-        <v>4.16</v>
+        <v>3.95</v>
       </c>
       <c r="P82">
-        <v>3.82</v>
+        <v>3.55</v>
       </c>
       <c r="Q82">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="R82">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="S82">
         <v>1.2</v>
       </c>
       <c r="T82">
-        <v>3.88</v>
+        <v>4.33</v>
       </c>
       <c r="U82">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="V82">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="W82">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X82">
         <v>0</v>
       </c>
       <c r="Y82">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z82">
-        <v>6.08</v>
+        <v>6.17</v>
       </c>
       <c r="AA82">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AB82">
         <v>2.88</v>
       </c>
       <c r="AC82">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AD82">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AE82">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AF82">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG82">
         <v>2.62</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK82">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,55 +13838,55 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="O83">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="P83">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q83">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="R83">
-        <v>3.11</v>
+        <v>2.85</v>
       </c>
       <c r="S83">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T83">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U83">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="V83">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="W83">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X83">
         <v>0</v>
       </c>
       <c r="Y83">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z83">
-        <v>6.98</v>
+        <v>6.1</v>
       </c>
       <c r="AA83">
         <v>1.33</v>
       </c>
       <c r="AB83">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AC83">
+        <v>1.84</v>
+      </c>
+      <c r="AD83">
         <v>1.83</v>
-      </c>
-      <c r="AD83">
-        <v>1.93</v>
       </c>
       <c r="AE83">
         <v>1.36</v>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK83">
         <v>3.4</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.15</v>
+        <v>1.41</v>
       </c>
       <c r="O84">
-        <v>3.78</v>
+        <v>4.9</v>
       </c>
       <c r="P84">
-        <v>2.97</v>
+        <v>6.3</v>
       </c>
       <c r="Q84">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="R84">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="S84">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="T84">
-        <v>3.75</v>
+        <v>4.35</v>
       </c>
       <c r="U84">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="V84">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="W84">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y84">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z84">
-        <v>4.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA84">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AB84">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AC84">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AD84">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AE84">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AF84">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AG84">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AK84">
-        <v>1.67</v>
+        <v>2.73</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="O85">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="P85">
-        <v>6.55</v>
+        <v>2.75</v>
       </c>
       <c r="Q85">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="R85">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="S85">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T85">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="U85">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="V85">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="W85">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z85">
-        <v>6.7</v>
+        <v>5.25</v>
       </c>
       <c r="AA85">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AB85">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="AC85">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="AD85">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="AE85">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AF85">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG85">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>2.88</v>
+        <v>1.62</v>
       </c>
       <c r="AL85">
         <v>0</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.82</v>
+        <v>1.06</v>
       </c>
       <c r="O41">
-        <v>3.85</v>
+        <v>13</v>
       </c>
       <c r="P41">
-        <v>3.75</v>
+        <v>30</v>
       </c>
       <c r="Q41">
-        <v>2.45</v>
+        <v>1.22</v>
       </c>
       <c r="R41">
-        <v>2.43</v>
+        <v>4.7</v>
       </c>
       <c r="S41">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="T41">
-        <v>3.28</v>
+        <v>6</v>
       </c>
       <c r="U41">
-        <v>2.28</v>
+        <v>1.57</v>
       </c>
       <c r="V41">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y41">
+        <v>1</v>
+      </c>
+      <c r="Z41">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AA41">
         <v>1.2</v>
       </c>
-      <c r="Z41">
-        <v>4.5</v>
-      </c>
-      <c r="AA41">
-        <v>1.61</v>
-      </c>
       <c r="AB41">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="AC41">
-        <v>2.6</v>
+        <v>1.51</v>
       </c>
       <c r="AD41">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AE41">
-        <v>1.14</v>
+        <v>1.63</v>
       </c>
       <c r="AF41">
-        <v>1.53</v>
+        <v>2.44</v>
       </c>
       <c r="AG41">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AK41">
-        <v>1.95</v>
+        <v>12.5</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,80 +7318,80 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.06</v>
+        <v>1.82</v>
       </c>
       <c r="O43">
-        <v>13</v>
+        <v>3.85</v>
       </c>
       <c r="P43">
-        <v>30</v>
+        <v>3.75</v>
       </c>
       <c r="Q43">
-        <v>1.22</v>
+        <v>2.45</v>
       </c>
       <c r="R43">
-        <v>4.7</v>
+        <v>2.43</v>
       </c>
       <c r="S43">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="T43">
-        <v>6</v>
+        <v>3.28</v>
       </c>
       <c r="U43">
+        <v>2.28</v>
+      </c>
+      <c r="V43">
         <v>1.57</v>
       </c>
-      <c r="V43">
-        <v>2.25</v>
-      </c>
       <c r="W43">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="Z43">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="AA43">
+        <v>1.61</v>
+      </c>
+      <c r="AB43">
+        <v>2.2</v>
+      </c>
+      <c r="AC43">
+        <v>2.6</v>
+      </c>
+      <c r="AD43">
+        <v>1.53</v>
+      </c>
+      <c r="AE43">
+        <v>1.14</v>
+      </c>
+      <c r="AF43">
+        <v>1.53</v>
+      </c>
+      <c r="AG43">
+        <v>2.3</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
         <v>1.2</v>
       </c>
-      <c r="AB43">
-        <v>5</v>
-      </c>
-      <c r="AC43">
-        <v>1.51</v>
-      </c>
-      <c r="AD43">
-        <v>2.5</v>
-      </c>
-      <c r="AE43">
-        <v>1.63</v>
-      </c>
-      <c r="AF43">
-        <v>2.44</v>
-      </c>
-      <c r="AG43">
-        <v>1.47</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>1.02</v>
-      </c>
       <c r="AK43">
-        <v>12.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P48">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q48">
-        <v>3.71</v>
+        <v>2.02</v>
       </c>
       <c r="R48">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="S48">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="T48">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U48">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="V48">
+        <v>1.34</v>
+      </c>
+      <c r="W48">
+        <v>1.05</v>
+      </c>
+      <c r="X48">
+        <v>1.03</v>
+      </c>
+      <c r="Y48">
+        <v>1.38</v>
+      </c>
+      <c r="Z48">
+        <v>3.1</v>
+      </c>
+      <c r="AA48">
+        <v>2.02</v>
+      </c>
+      <c r="AB48">
+        <v>1.68</v>
+      </c>
+      <c r="AC48">
+        <v>3.5</v>
+      </c>
+      <c r="AD48">
         <v>1.27</v>
       </c>
-      <c r="W48">
-        <v>1.03</v>
-      </c>
-      <c r="X48">
-        <v>1.06</v>
-      </c>
-      <c r="Y48">
-        <v>1.41</v>
-      </c>
-      <c r="Z48">
-        <v>2.48</v>
-      </c>
-      <c r="AA48">
-        <v>2.18</v>
-      </c>
-      <c r="AB48">
-        <v>1.55</v>
-      </c>
-      <c r="AC48">
-        <v>4.35</v>
-      </c>
-      <c r="AD48">
-        <v>1.19</v>
-      </c>
       <c r="AE48">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF48">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG48">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AK48">
-        <v>1.42</v>
+        <v>2.31</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q49">
-        <v>2.02</v>
+        <v>3.71</v>
       </c>
       <c r="R49">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="S49">
+        <v>1.5</v>
+      </c>
+      <c r="T49">
+        <v>2.5</v>
+      </c>
+      <c r="U49">
+        <v>3.3</v>
+      </c>
+      <c r="V49">
+        <v>1.27</v>
+      </c>
+      <c r="W49">
+        <v>1.03</v>
+      </c>
+      <c r="X49">
+        <v>1.06</v>
+      </c>
+      <c r="Y49">
         <v>1.41</v>
       </c>
-      <c r="T49">
-        <v>2.53</v>
-      </c>
-      <c r="U49">
-        <v>2.9</v>
-      </c>
-      <c r="V49">
+      <c r="Z49">
+        <v>2.48</v>
+      </c>
+      <c r="AA49">
+        <v>2.18</v>
+      </c>
+      <c r="AB49">
+        <v>1.55</v>
+      </c>
+      <c r="AC49">
+        <v>4.35</v>
+      </c>
+      <c r="AD49">
+        <v>1.19</v>
+      </c>
+      <c r="AE49">
+        <v>1.05</v>
+      </c>
+      <c r="AF49">
+        <v>1.91</v>
+      </c>
+      <c r="AG49">
+        <v>1.75</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
         <v>1.34</v>
       </c>
-      <c r="W49">
-        <v>1.05</v>
-      </c>
-      <c r="X49">
-        <v>1.03</v>
-      </c>
-      <c r="Y49">
-        <v>1.38</v>
-      </c>
-      <c r="Z49">
-        <v>3.1</v>
-      </c>
-      <c r="AA49">
-        <v>2.02</v>
-      </c>
-      <c r="AB49">
-        <v>1.68</v>
-      </c>
-      <c r="AC49">
-        <v>3.5</v>
-      </c>
-      <c r="AD49">
-        <v>1.27</v>
-      </c>
-      <c r="AE49">
-        <v>1.07</v>
-      </c>
-      <c r="AF49">
-        <v>1.93</v>
-      </c>
-      <c r="AG49">
-        <v>1.66</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.24</v>
-      </c>
       <c r="AK49">
-        <v>2.31</v>
+        <v>1.42</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.41</v>
+        <v>1.7</v>
       </c>
       <c r="O50">
-        <v>3.15</v>
+        <v>3.58</v>
       </c>
       <c r="P50">
-        <v>2.75</v>
+        <v>4.32</v>
       </c>
       <c r="Q50">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S50">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T50">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U50">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="V50">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W50">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z50">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA50">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB50">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC50">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD50">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE50">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF50">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG50">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK50">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
+        <v>2.41</v>
+      </c>
+      <c r="O51">
+        <v>3.15</v>
+      </c>
+      <c r="P51">
+        <v>2.75</v>
+      </c>
+      <c r="Q51">
+        <v>2.9</v>
+      </c>
+      <c r="R51">
+        <v>2.12</v>
+      </c>
+      <c r="S51">
+        <v>1.36</v>
+      </c>
+      <c r="T51">
+        <v>2.63</v>
+      </c>
+      <c r="U51">
+        <v>2.74</v>
+      </c>
+      <c r="V51">
+        <v>1.37</v>
+      </c>
+      <c r="W51">
+        <v>1.06</v>
+      </c>
+      <c r="X51">
+        <v>1.01</v>
+      </c>
+      <c r="Y51">
+        <v>1.29</v>
+      </c>
+      <c r="Z51">
+        <v>3.05</v>
+      </c>
+      <c r="AA51">
+        <v>1.94</v>
+      </c>
+      <c r="AB51">
         <v>1.7</v>
       </c>
-      <c r="O51">
-        <v>3.58</v>
-      </c>
-      <c r="P51">
-        <v>4.32</v>
-      </c>
-      <c r="Q51">
-        <v>0</v>
-      </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
-        <v>0</v>
-      </c>
-      <c r="T51">
-        <v>0</v>
-      </c>
-      <c r="U51">
-        <v>0</v>
-      </c>
-      <c r="V51">
-        <v>0</v>
-      </c>
-      <c r="W51">
-        <v>0</v>
-      </c>
-      <c r="X51">
-        <v>0</v>
-      </c>
-      <c r="Y51">
-        <v>0</v>
-      </c>
-      <c r="Z51">
-        <v>0</v>
-      </c>
-      <c r="AA51">
-        <v>1.9</v>
-      </c>
-      <c r="AB51">
-        <v>1.9</v>
-      </c>
       <c r="AC51">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,80 +9111,80 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.11</v>
+        <v>2.55</v>
       </c>
       <c r="O54">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
-        <v>3.27</v>
+        <v>2.4</v>
       </c>
       <c r="Q54">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="R54">
-        <v>2.61</v>
+        <v>2.33</v>
       </c>
       <c r="S54">
+        <v>1.31</v>
+      </c>
+      <c r="T54">
+        <v>3.15</v>
+      </c>
+      <c r="U54">
+        <v>2.36</v>
+      </c>
+      <c r="V54">
+        <v>1.5</v>
+      </c>
+      <c r="W54">
+        <v>1.08</v>
+      </c>
+      <c r="X54">
+        <v>1.04</v>
+      </c>
+      <c r="Y54">
         <v>1.22</v>
       </c>
-      <c r="T54">
-        <v>3.75</v>
-      </c>
-      <c r="U54">
-        <v>2.04</v>
-      </c>
-      <c r="V54">
+      <c r="Z54">
+        <v>3.98</v>
+      </c>
+      <c r="AA54">
         <v>1.7</v>
       </c>
-      <c r="W54">
-        <v>1.18</v>
-      </c>
-      <c r="X54">
-        <v>1.01</v>
-      </c>
-      <c r="Y54">
-        <v>1.08</v>
-      </c>
-      <c r="Z54">
-        <v>5.5</v>
-      </c>
-      <c r="AA54">
+      <c r="AB54">
+        <v>2.1</v>
+      </c>
+      <c r="AC54">
+        <v>2.63</v>
+      </c>
+      <c r="AD54">
+        <v>1.4</v>
+      </c>
+      <c r="AE54">
+        <v>1.16</v>
+      </c>
+      <c r="AF54">
+        <v>1.53</v>
+      </c>
+      <c r="AG54">
+        <v>2.3</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ54">
+        <v>1.3</v>
+      </c>
+      <c r="AK54">
         <v>1.44</v>
-      </c>
-      <c r="AB54">
-        <v>2.7</v>
-      </c>
-      <c r="AC54">
-        <v>2.13</v>
-      </c>
-      <c r="AD54">
-        <v>1.69</v>
-      </c>
-      <c r="AE54">
-        <v>1.25</v>
-      </c>
-      <c r="AF54">
-        <v>1.4</v>
-      </c>
-      <c r="AG54">
-        <v>2.7</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ54">
-        <v>1.22</v>
-      </c>
-      <c r="AK54">
-        <v>1.67</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,80 +9437,80 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="O56">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P56">
+        <v>3.27</v>
+      </c>
+      <c r="Q56">
         <v>2.4</v>
       </c>
-      <c r="Q56">
-        <v>3</v>
-      </c>
       <c r="R56">
-        <v>2.33</v>
+        <v>2.61</v>
       </c>
       <c r="S56">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T56">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="U56">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="V56">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="W56">
+        <v>1.18</v>
+      </c>
+      <c r="X56">
+        <v>1.01</v>
+      </c>
+      <c r="Y56">
         <v>1.08</v>
       </c>
-      <c r="X56">
-        <v>1.04</v>
-      </c>
-      <c r="Y56">
+      <c r="Z56">
+        <v>5.5</v>
+      </c>
+      <c r="AA56">
+        <v>1.44</v>
+      </c>
+      <c r="AB56">
+        <v>2.7</v>
+      </c>
+      <c r="AC56">
+        <v>2.13</v>
+      </c>
+      <c r="AD56">
+        <v>1.69</v>
+      </c>
+      <c r="AE56">
+        <v>1.25</v>
+      </c>
+      <c r="AF56">
+        <v>1.4</v>
+      </c>
+      <c r="AG56">
+        <v>2.7</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
         <v>1.22</v>
       </c>
-      <c r="Z56">
-        <v>3.98</v>
-      </c>
-      <c r="AA56">
-        <v>1.7</v>
-      </c>
-      <c r="AB56">
-        <v>2.1</v>
-      </c>
-      <c r="AC56">
-        <v>2.63</v>
-      </c>
-      <c r="AD56">
-        <v>1.4</v>
-      </c>
-      <c r="AE56">
-        <v>1.16</v>
-      </c>
-      <c r="AF56">
-        <v>1.53</v>
-      </c>
-      <c r="AG56">
-        <v>2.3</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>1.3</v>
-      </c>
       <c r="AK56">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL56">
         <v>0</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="O42">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P42">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q42">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="R42">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="S42">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U42">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V42">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W42">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z42">
         <v>4.5</v>
       </c>
       <c r="AA42">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB42">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AC42">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD42">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE42">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG42">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK42">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="O43">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P43">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q43">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="R43">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="S43">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T43">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U43">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V43">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X43">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z43">
         <v>4.5</v>
       </c>
       <c r="AA43">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB43">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AC43">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD43">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE43">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF43">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AG43">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK43">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,65 +9274,65 @@
         </is>
       </c>
       <c r="N55">
+        <v>2.11</v>
+      </c>
+      <c r="O55">
+        <v>3.7</v>
+      </c>
+      <c r="P55">
+        <v>3.27</v>
+      </c>
+      <c r="Q55">
+        <v>2.4</v>
+      </c>
+      <c r="R55">
+        <v>2.61</v>
+      </c>
+      <c r="S55">
+        <v>1.22</v>
+      </c>
+      <c r="T55">
+        <v>3.75</v>
+      </c>
+      <c r="U55">
+        <v>2.04</v>
+      </c>
+      <c r="V55">
+        <v>1.7</v>
+      </c>
+      <c r="W55">
+        <v>1.18</v>
+      </c>
+      <c r="X55">
+        <v>1.01</v>
+      </c>
+      <c r="Y55">
+        <v>1.08</v>
+      </c>
+      <c r="Z55">
+        <v>5.5</v>
+      </c>
+      <c r="AA55">
+        <v>1.44</v>
+      </c>
+      <c r="AB55">
         <v>2.7</v>
       </c>
-      <c r="O55">
-        <v>3.5</v>
-      </c>
-      <c r="P55">
-        <v>2.3</v>
-      </c>
-      <c r="Q55">
-        <v>3.48</v>
-      </c>
-      <c r="R55">
-        <v>2.39</v>
-      </c>
-      <c r="S55">
-        <v>1.29</v>
-      </c>
-      <c r="T55">
-        <v>3.3</v>
-      </c>
-      <c r="U55">
-        <v>2.34</v>
-      </c>
-      <c r="V55">
-        <v>1.51</v>
-      </c>
-      <c r="W55">
-        <v>1.11</v>
-      </c>
-      <c r="X55">
-        <v>1.03</v>
-      </c>
-      <c r="Y55">
-        <v>1.16</v>
-      </c>
-      <c r="Z55">
-        <v>4.15</v>
-      </c>
-      <c r="AA55">
-        <v>1.68</v>
-      </c>
-      <c r="AB55">
-        <v>2.14</v>
-      </c>
       <c r="AC55">
+        <v>2.13</v>
+      </c>
+      <c r="AD55">
+        <v>1.69</v>
+      </c>
+      <c r="AE55">
+        <v>1.25</v>
+      </c>
+      <c r="AF55">
+        <v>1.4</v>
+      </c>
+      <c r="AG55">
         <v>2.7</v>
       </c>
-      <c r="AD55">
-        <v>1.45</v>
-      </c>
-      <c r="AE55">
-        <v>1.13</v>
-      </c>
-      <c r="AF55">
-        <v>1.53</v>
-      </c>
-      <c r="AG55">
-        <v>2.3</v>
-      </c>
       <c r="AH55" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.11</v>
+        <v>2.7</v>
       </c>
       <c r="O56">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>3.27</v>
+        <v>2.3</v>
       </c>
       <c r="Q56">
-        <v>2.4</v>
+        <v>3.48</v>
       </c>
       <c r="R56">
-        <v>2.61</v>
+        <v>2.39</v>
       </c>
       <c r="S56">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T56">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="U56">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="V56">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="W56">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z56">
-        <v>5.5</v>
+        <v>4.15</v>
       </c>
       <c r="AA56">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AB56">
+        <v>2.14</v>
+      </c>
+      <c r="AC56">
         <v>2.7</v>
       </c>
-      <c r="AC56">
-        <v>2.13</v>
-      </c>
       <c r="AD56">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="AE56">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AF56">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AG56">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="AK56">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AL56">
         <v>0</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -1622,10 +1622,10 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.65</v>
+        <v>4.18</v>
       </c>
       <c r="R8">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S8">
         <v>1.64</v>
@@ -1634,22 +1634,22 @@
         <v>2.11</v>
       </c>
       <c r="U8">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="V8">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W8">
         <v>1.01</v>
       </c>
       <c r="X8">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Y8">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="Z8">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AA8">
         <v>2.83</v>
@@ -1658,16 +1658,16 @@
         <v>1.33</v>
       </c>
       <c r="AC8">
-        <v>6.05</v>
+        <v>6.1</v>
       </c>
       <c r="AD8">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE8">
         <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AG8">
         <v>1.55</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AK8">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,61 +1776,61 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="O9">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="P9">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="Q9">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R9">
         <v>2</v>
       </c>
       <c r="S9">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="T9">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="U9">
         <v>3.5</v>
       </c>
       <c r="V9">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y9">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Z9">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="AA9">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AB9">
         <v>1.49</v>
       </c>
       <c r="AC9">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AD9">
         <v>1.18</v>
       </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AG9">
         <v>1.4</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AK9">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1945,28 +1945,28 @@
         <v>4.4</v>
       </c>
       <c r="P10">
-        <v>9.6</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q10">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R10">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="S10">
         <v>1.25</v>
       </c>
       <c r="T10">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U10">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X10">
         <v>1.02</v>
@@ -1975,16 +1975,16 @@
         <v>1.16</v>
       </c>
       <c r="Z10">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AA10">
         <v>1.61</v>
       </c>
       <c r="AB10">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AC10">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AD10">
         <v>1.5</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AK10">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="O14">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="P14">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="Q14">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="R14">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="S14">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T14">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="U14">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V14">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
         <v>1.25</v>
       </c>
       <c r="Z14">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="AA14">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AB14">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC14">
-        <v>2.7</v>
+        <v>3.03</v>
       </c>
       <c r="AD14">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE14">
         <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK14">
         <v>1.83</v>
@@ -2920,7 +2920,7 @@
         <v>2.85</v>
       </c>
       <c r="O16">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P16">
         <v>2.25</v>
@@ -2929,7 +2929,7 @@
         <v>3.4</v>
       </c>
       <c r="R16">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="S16">
         <v>1.3</v>
@@ -2953,28 +2953,28 @@
         <v>1.22</v>
       </c>
       <c r="Z16">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA16">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AB16">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AC16">
         <v>2.8</v>
       </c>
       <c r="AD16">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE16">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF16">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG16">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="O21">
         <v>6.7</v>
@@ -3744,52 +3744,52 @@
         <v>1.57</v>
       </c>
       <c r="R21">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="S21">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T21">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="U21">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="V21">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="W21">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Z21">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA21">
         <v>1.25</v>
       </c>
       <c r="AB21">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AC21">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AD21">
         <v>2.26</v>
       </c>
       <c r="AE21">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AF21">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.13</v>
       </c>
       <c r="AK21">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="O22">
         <v>12</v>
       </c>
       <c r="P22">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="Q22">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="R22">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="S22">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="T22">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="U22">
         <v>1.61</v>
       </c>
       <c r="V22">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="W22">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X22">
         <v>1</v>
       </c>
       <c r="Y22">
+        <v>1.02</v>
+      </c>
+      <c r="Z22">
+        <v>12</v>
+      </c>
+      <c r="AA22">
+        <v>1.12</v>
+      </c>
+      <c r="AB22">
+        <v>5</v>
+      </c>
+      <c r="AC22">
+        <v>1.43</v>
+      </c>
+      <c r="AD22">
+        <v>2.85</v>
+      </c>
+      <c r="AE22">
+        <v>1.75</v>
+      </c>
+      <c r="AF22">
+        <v>1.83</v>
+      </c>
+      <c r="AG22">
+        <v>1.89</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
         <v>1.01</v>
       </c>
-      <c r="Z22">
-        <v>11.5</v>
-      </c>
-      <c r="AA22">
-        <v>1.2</v>
-      </c>
-      <c r="AB22">
-        <v>4.5</v>
-      </c>
-      <c r="AC22">
-        <v>1.4</v>
-      </c>
-      <c r="AD22">
-        <v>2.63</v>
-      </c>
-      <c r="AE22">
-        <v>1.79</v>
-      </c>
-      <c r="AF22">
-        <v>1.81</v>
-      </c>
-      <c r="AG22">
-        <v>1.9</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.05</v>
-      </c>
       <c r="AK22">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="O23">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="P23">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="Q23">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R23">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="S23">
         <v>1.17</v>
@@ -4079,10 +4079,10 @@
         <v>4.5</v>
       </c>
       <c r="U23">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="V23">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="W23">
         <v>1.25</v>
@@ -4091,31 +4091,31 @@
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z23">
-        <v>6.5</v>
+        <v>6.85</v>
       </c>
       <c r="AA23">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AB23">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AC23">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AD23">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AE23">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AF23">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.07</v>
       </c>
       <c r="AK23">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>6.5</v>
+        <v>7.75</v>
       </c>
       <c r="O25">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P25">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q25">
-        <v>6.8</v>
+        <v>8.33</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S25">
         <v>1.39</v>
       </c>
       <c r="T25">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="U25">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="V25">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W25">
         <v>1.05</v>
@@ -4417,31 +4417,31 @@
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z25">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="AA25">
         <v>2.05</v>
       </c>
       <c r="AB25">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC25">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD25">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE25">
         <v>1.05</v>
       </c>
       <c r="AF25">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AG25">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="AK25">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,61 +4547,61 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O26">
         <v>2.75</v>
       </c>
       <c r="P26">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="Q26">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="R26">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="S26">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="T26">
         <v>2.07</v>
       </c>
       <c r="U26">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="V26">
         <v>1.17</v>
       </c>
       <c r="W26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X26">
         <v>1.09</v>
       </c>
       <c r="Y26">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Z26">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AA26">
-        <v>2.96</v>
+        <v>2.85</v>
       </c>
       <c r="AB26">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AC26">
         <v>6</v>
       </c>
       <c r="AD26">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE26">
         <v>1.01</v>
       </c>
       <c r="AF26">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AG26">
         <v>1.58</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AK26">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,25 +4710,25 @@
         </is>
       </c>
       <c r="N27">
+        <v>3.2</v>
+      </c>
+      <c r="O27">
         <v>3.3</v>
       </c>
-      <c r="O27">
-        <v>3.5</v>
-      </c>
       <c r="P27">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="Q27">
-        <v>4.03</v>
+        <v>3.75</v>
       </c>
       <c r="R27">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S27">
         <v>1.31</v>
       </c>
       <c r="T27">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U27">
         <v>2.44</v>
@@ -4737,13 +4737,13 @@
         <v>1.48</v>
       </c>
       <c r="W27">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
         <v>3.75</v>
@@ -4755,7 +4755,7 @@
         <v>2</v>
       </c>
       <c r="AC27">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AD27">
         <v>1.35</v>
@@ -4767,7 +4767,7 @@
         <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O34">
         <v>3.6</v>
@@ -5860,13 +5860,13 @@
         <v>1.87</v>
       </c>
       <c r="Q34">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R34">
         <v>2.39</v>
       </c>
       <c r="S34">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T34">
         <v>3.25</v>
@@ -5875,40 +5875,40 @@
         <v>2.4</v>
       </c>
       <c r="V34">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA34">
         <v>1.66</v>
       </c>
       <c r="AB34">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC34">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="AD34">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE34">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
         <v>1.57</v>
       </c>
       <c r="AG34">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6014,34 +6014,34 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="O35">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="P35">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="R35">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="S35">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="T35">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="U35">
         <v>1.76</v>
       </c>
       <c r="V35">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="W35">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X35">
         <v>1.01</v>
@@ -6053,16 +6053,16 @@
         <v>8.5</v>
       </c>
       <c r="AA35">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AB35">
         <v>3.5</v>
       </c>
       <c r="AC35">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AD35">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="AE35">
         <v>1.45</v>
@@ -6071,7 +6071,7 @@
         <v>1.67</v>
       </c>
       <c r="AG35">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK35">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P37">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="Q37">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R37">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="S37">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="U37">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="V37">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W37">
         <v>1.06</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z37">
-        <v>3.1</v>
+        <v>3.71</v>
       </c>
       <c r="AA37">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB37">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC37">
         <v>2.95</v>
       </c>
       <c r="AD37">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE37">
         <v>1.11</v>
       </c>
       <c r="AF37">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG37">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O38">
-        <v>3.43</v>
+        <v>3.6</v>
       </c>
       <c r="P38">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="Q38">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="R38">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="S38">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U38">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="V38">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y38">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z38">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="AA38">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AB38">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC38">
-        <v>2.85</v>
+        <v>2.72</v>
       </c>
       <c r="AD38">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE38">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF38">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG38">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.26</v>
       </c>
       <c r="AK38">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="O39">
         <v>5.5</v>
@@ -6675,46 +6675,46 @@
         <v>8</v>
       </c>
       <c r="Q39">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R39">
         <v>2.69</v>
       </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T39">
         <v>3.75</v>
       </c>
       <c r="U39">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="V39">
         <v>1.75</v>
       </c>
       <c r="W39">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z39">
-        <v>5.94</v>
+        <v>5.2</v>
       </c>
       <c r="AA39">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB39">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AC39">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AD39">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AE39">
         <v>1.25</v>
@@ -6723,7 +6723,7 @@
         <v>1.65</v>
       </c>
       <c r="AG39">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AK39">
-        <v>2.95</v>
+        <v>3.32</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="O40">
-        <v>3.7</v>
+        <v>3.77</v>
       </c>
       <c r="P40">
         <v>1.74</v>
       </c>
       <c r="Q40">
-        <v>5.29</v>
+        <v>5.15</v>
       </c>
       <c r="R40">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="S40">
         <v>1.41</v>
@@ -6853,40 +6853,40 @@
         <v>2.92</v>
       </c>
       <c r="V40">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z40">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AA40">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AB40">
         <v>1.88</v>
       </c>
       <c r="AC40">
-        <v>3.39</v>
+        <v>3.2</v>
       </c>
       <c r="AD40">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE40">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF40">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG40">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AK40">
         <v>1.14</v>
@@ -6995,61 +6995,61 @@
         <v>1.06</v>
       </c>
       <c r="O41">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P41">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q41">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="R41">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="S41">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="T41">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="U41">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="V41">
         <v>2.25</v>
       </c>
       <c r="W41">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="X41">
         <v>1</v>
       </c>
       <c r="Y41">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Z41">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AA41">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AB41">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AC41">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AD41">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AE41">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AF41">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AG41">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.02</v>
       </c>
       <c r="AK41">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="O42">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P42">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q42">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="R42">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T42">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="U42">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="V42">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W42">
         <v>1.11</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z42">
         <v>4.5</v>
       </c>
       <c r="AA42">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB42">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AC42">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD42">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF42">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AG42">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="O43">
+        <v>3.9</v>
+      </c>
+      <c r="P43">
         <v>4</v>
       </c>
-      <c r="P43">
-        <v>4.6</v>
-      </c>
       <c r="Q43">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R43">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="S43">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T43">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U43">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V43">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W43">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z43">
         <v>4.5</v>
       </c>
       <c r="AA43">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB43">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="AC43">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="AD43">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE43">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF43">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG43">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK43">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="O44">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q44">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R44">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="S44">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T44">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="U44">
-        <v>2.86</v>
+        <v>2.65</v>
       </c>
       <c r="V44">
         <v>1.4</v>
       </c>
       <c r="W44">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X44">
         <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z44">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA44">
         <v>1.99</v>
       </c>
       <c r="AB44">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC44">
-        <v>3.05</v>
+        <v>3.31</v>
       </c>
       <c r="AD44">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE44">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF44">
         <v>1.71</v>
       </c>
       <c r="AG44">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AK44">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="O45">
         <v>4.6</v>
       </c>
       <c r="P45">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="Q45">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="R45">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="S45">
         <v>1.22</v>
       </c>
       <c r="T45">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="U45">
         <v>2.2</v>
       </c>
       <c r="V45">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W45">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X45">
         <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z45">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA45">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB45">
         <v>2.62</v>
       </c>
       <c r="AC45">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AD45">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE45">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF45">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG45">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK45">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,34 +7807,34 @@
         </is>
       </c>
       <c r="N46">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O46">
         <v>7.5</v>
       </c>
       <c r="P46">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Q46">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R46">
         <v>3</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U46">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V46">
         <v>1.56</v>
       </c>
       <c r="W46">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X46">
         <v>1.01</v>
@@ -7843,13 +7843,13 @@
         <v>1.1</v>
       </c>
       <c r="Z46">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AA46">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AB46">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="AC46">
         <v>2.2</v>
@@ -7861,10 +7861,10 @@
         <v>1.22</v>
       </c>
       <c r="AF46">
-        <v>1.98</v>
+        <v>2.22</v>
       </c>
       <c r="AG46">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>5.45</v>
+        <v>1.09</v>
       </c>
       <c r="AK46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="Q48">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="R48">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S48">
         <v>1.41</v>
       </c>
       <c r="T48">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="U48">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="V48">
         <v>1.34</v>
       </c>
       <c r="W48">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X48">
         <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z48">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA48">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB48">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC48">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AD48">
         <v>1.27</v>
       </c>
       <c r="AE48">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF48">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AG48">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK48">
         <v>2.31</v>
@@ -8296,16 +8296,16 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.85</v>
+        <v>2.57</v>
       </c>
       <c r="O49">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="P49">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="Q49">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="R49">
         <v>1.9</v>
@@ -8317,43 +8317,43 @@
         <v>2.5</v>
       </c>
       <c r="U49">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="V49">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W49">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X49">
         <v>1.06</v>
       </c>
       <c r="Y49">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="Z49">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AA49">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="AB49">
         <v>1.55</v>
       </c>
       <c r="AC49">
-        <v>4.35</v>
+        <v>4.64</v>
       </c>
       <c r="AD49">
         <v>1.19</v>
       </c>
       <c r="AE49">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF49">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG49">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK49">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,58 +9111,58 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O54">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q54">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="R54">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="S54">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T54">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U54">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V54">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W54">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X54">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z54">
-        <v>3.98</v>
+        <v>4.15</v>
       </c>
       <c r="AA54">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB54">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC54">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD54">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE54">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF54">
         <v>1.53</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="AK54">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,80 +9274,80 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.11</v>
+        <v>2.55</v>
       </c>
       <c r="O55">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P55">
-        <v>3.27</v>
+        <v>2.4</v>
       </c>
       <c r="Q55">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="R55">
-        <v>2.61</v>
+        <v>2.33</v>
       </c>
       <c r="S55">
+        <v>1.31</v>
+      </c>
+      <c r="T55">
+        <v>3.15</v>
+      </c>
+      <c r="U55">
+        <v>2.36</v>
+      </c>
+      <c r="V55">
+        <v>1.5</v>
+      </c>
+      <c r="W55">
+        <v>1.08</v>
+      </c>
+      <c r="X55">
+        <v>1.04</v>
+      </c>
+      <c r="Y55">
         <v>1.22</v>
       </c>
-      <c r="T55">
-        <v>3.75</v>
-      </c>
-      <c r="U55">
-        <v>2.04</v>
-      </c>
-      <c r="V55">
+      <c r="Z55">
+        <v>3.98</v>
+      </c>
+      <c r="AA55">
         <v>1.7</v>
       </c>
-      <c r="W55">
-        <v>1.18</v>
-      </c>
-      <c r="X55">
-        <v>1.01</v>
-      </c>
-      <c r="Y55">
-        <v>1.08</v>
-      </c>
-      <c r="Z55">
-        <v>5.5</v>
-      </c>
-      <c r="AA55">
+      <c r="AB55">
+        <v>2.1</v>
+      </c>
+      <c r="AC55">
+        <v>2.63</v>
+      </c>
+      <c r="AD55">
+        <v>1.4</v>
+      </c>
+      <c r="AE55">
+        <v>1.16</v>
+      </c>
+      <c r="AF55">
+        <v>1.53</v>
+      </c>
+      <c r="AG55">
+        <v>2.3</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55">
+        <v>1.3</v>
+      </c>
+      <c r="AK55">
         <v>1.44</v>
-      </c>
-      <c r="AB55">
-        <v>2.7</v>
-      </c>
-      <c r="AC55">
-        <v>2.13</v>
-      </c>
-      <c r="AD55">
-        <v>1.69</v>
-      </c>
-      <c r="AE55">
-        <v>1.25</v>
-      </c>
-      <c r="AF55">
-        <v>1.4</v>
-      </c>
-      <c r="AG55">
-        <v>2.7</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ55">
-        <v>1.22</v>
-      </c>
-      <c r="AK55">
-        <v>1.67</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,65 +9437,65 @@
         </is>
       </c>
       <c r="N56">
+        <v>2.11</v>
+      </c>
+      <c r="O56">
+        <v>3.7</v>
+      </c>
+      <c r="P56">
+        <v>3.27</v>
+      </c>
+      <c r="Q56">
+        <v>2.4</v>
+      </c>
+      <c r="R56">
+        <v>2.61</v>
+      </c>
+      <c r="S56">
+        <v>1.22</v>
+      </c>
+      <c r="T56">
+        <v>3.75</v>
+      </c>
+      <c r="U56">
+        <v>2.04</v>
+      </c>
+      <c r="V56">
+        <v>1.7</v>
+      </c>
+      <c r="W56">
+        <v>1.18</v>
+      </c>
+      <c r="X56">
+        <v>1.01</v>
+      </c>
+      <c r="Y56">
+        <v>1.08</v>
+      </c>
+      <c r="Z56">
+        <v>5.5</v>
+      </c>
+      <c r="AA56">
+        <v>1.44</v>
+      </c>
+      <c r="AB56">
         <v>2.7</v>
       </c>
-      <c r="O56">
-        <v>3.5</v>
-      </c>
-      <c r="P56">
-        <v>2.3</v>
-      </c>
-      <c r="Q56">
-        <v>3.48</v>
-      </c>
-      <c r="R56">
-        <v>2.39</v>
-      </c>
-      <c r="S56">
-        <v>1.29</v>
-      </c>
-      <c r="T56">
-        <v>3.3</v>
-      </c>
-      <c r="U56">
-        <v>2.34</v>
-      </c>
-      <c r="V56">
-        <v>1.51</v>
-      </c>
-      <c r="W56">
-        <v>1.11</v>
-      </c>
-      <c r="X56">
-        <v>1.03</v>
-      </c>
-      <c r="Y56">
-        <v>1.16</v>
-      </c>
-      <c r="Z56">
-        <v>4.15</v>
-      </c>
-      <c r="AA56">
-        <v>1.68</v>
-      </c>
-      <c r="AB56">
-        <v>2.14</v>
-      </c>
       <c r="AC56">
+        <v>2.13</v>
+      </c>
+      <c r="AD56">
+        <v>1.69</v>
+      </c>
+      <c r="AE56">
+        <v>1.25</v>
+      </c>
+      <c r="AF56">
+        <v>1.4</v>
+      </c>
+      <c r="AG56">
         <v>2.7</v>
       </c>
-      <c r="AD56">
-        <v>1.45</v>
-      </c>
-      <c r="AE56">
-        <v>1.13</v>
-      </c>
-      <c r="AF56">
-        <v>1.53</v>
-      </c>
-      <c r="AG56">
-        <v>2.3</v>
-      </c>
       <c r="AH56" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="O57">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P57">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="Q57">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="R57">
         <v>2.06</v>
       </c>
       <c r="S57">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T57">
-        <v>2.63</v>
+        <v>2.85</v>
       </c>
       <c r="U57">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="V57">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W57">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X57">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
+        <v>1.26</v>
+      </c>
+      <c r="Z57">
+        <v>3.2</v>
+      </c>
+      <c r="AA57">
+        <v>1.93</v>
+      </c>
+      <c r="AB57">
+        <v>1.83</v>
+      </c>
+      <c r="AC57">
+        <v>3.4</v>
+      </c>
+      <c r="AD57">
         <v>1.27</v>
       </c>
-      <c r="Z57">
-        <v>3.14</v>
-      </c>
-      <c r="AA57">
-        <v>1.98</v>
-      </c>
-      <c r="AB57">
-        <v>1.8</v>
-      </c>
-      <c r="AC57">
-        <v>3.35</v>
-      </c>
-      <c r="AD57">
-        <v>1.29</v>
-      </c>
       <c r="AE57">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF57">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AG57">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AK57">
         <v>1.47</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="O58">
         <v>3.1</v>
       </c>
       <c r="P58">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="Q58">
         <v>3.46</v>
@@ -9778,65 +9778,65 @@
         <v>2.05</v>
       </c>
       <c r="S58">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T58">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="U58">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="V58">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W58">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y58">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z58">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AA58">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AB58">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AC58">
         <v>3.5</v>
       </c>
       <c r="AD58">
+        <v>1.29</v>
+      </c>
+      <c r="AE58">
+        <v>1.07</v>
+      </c>
+      <c r="AF58">
+        <v>1.73</v>
+      </c>
+      <c r="AG58">
+        <v>2.02</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
         <v>1.26</v>
       </c>
-      <c r="AE58">
-        <v>1.06</v>
-      </c>
-      <c r="AF58">
-        <v>1.75</v>
-      </c>
-      <c r="AG58">
-        <v>1.97</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.34</v>
-      </c>
       <c r="AK58">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="O81">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P81">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q81">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R81">
         <v>2</v>
       </c>
       <c r="S81">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T81">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="U81">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="V81">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W81">
         <v>1.06</v>
       </c>
       <c r="X81">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y81">
         <v>1.36</v>
       </c>
       <c r="Z81">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AA81">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AB81">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC81">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
       <c r="AD81">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE81">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF81">
         <v>2</v>
       </c>
       <c r="AG81">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK81">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AL81">
         <v>0</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -638,61 +638,61 @@
         <v>2.38</v>
       </c>
       <c r="O2">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
         <v>2.6</v>
       </c>
       <c r="Q2">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="R2">
         <v>1.96</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T2">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U2">
         <v>2.89</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
+        <v>1.02</v>
+      </c>
+      <c r="X2">
         <v>1.05</v>
       </c>
-      <c r="X2">
-        <v>1.07</v>
-      </c>
       <c r="Y2">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z2">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AA2">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AB2">
         <v>1.7</v>
       </c>
       <c r="AC2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD2">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE2">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
         <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AK2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="O3">
         <v>3.2</v>
       </c>
       <c r="P3">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="Q3">
         <v>3.07</v>
@@ -816,37 +816,37 @@
         <v>1.44</v>
       </c>
       <c r="T3">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="U3">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="V3">
         <v>1.32</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
         <v>1.38</v>
       </c>
       <c r="Z3">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="AA3">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="AB3">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AC3">
-        <v>3.99</v>
+        <v>3.76</v>
       </c>
       <c r="AD3">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE3">
         <v>1.02</v>
@@ -855,7 +855,7 @@
         <v>1.83</v>
       </c>
       <c r="AG3">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
         <v>1.54</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="P4">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Q4">
         <v>3.98</v>
@@ -976,49 +976,49 @@
         <v>1.99</v>
       </c>
       <c r="S4">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="U4">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z4">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="AA4">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AB4">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AC4">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="AD4">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AG4">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1124,28 +1124,28 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="O5">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P5">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="Q5">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R5">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S5">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T5">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="U5">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V5">
         <v>1.48</v>
@@ -1154,19 +1154,19 @@
         <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z5">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="AA5">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB5">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AC5">
         <v>2.95</v>
@@ -1178,10 +1178,10 @@
         <v>1.15</v>
       </c>
       <c r="AF5">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AG5">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK5">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N14">
@@ -2600,22 +2600,22 @@
         <v>3.62</v>
       </c>
       <c r="Q14">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R14">
         <v>2.16</v>
       </c>
       <c r="S14">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T14">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="U14">
         <v>2.5</v>
       </c>
       <c r="V14">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W14">
         <v>1.07</v>
@@ -2627,19 +2627,19 @@
         <v>1.25</v>
       </c>
       <c r="Z14">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="AA14">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AB14">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AC14">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="AD14">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE14">
         <v>1.11</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>1.86</v>
       </c>
       <c r="AC15">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AD15">
         <v>1.3</v>
@@ -2808,10 +2808,10 @@
         <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG15">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="O18">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="P18">
         <v>12</v>
       </c>
       <c r="Q18">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R18">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="S18">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="T18">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="U18">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="V18">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="W18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z18">
-        <v>6.55</v>
+        <v>6.2</v>
       </c>
       <c r="AA18">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AB18">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="AC18">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AD18">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AE18">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AF18">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AG18">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK18">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,7 +3415,7 @@
         <v>1.7</v>
       </c>
       <c r="Q19">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R19">
         <v>2.36</v>
@@ -3439,10 +3439,10 @@
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="AA19">
         <v>1.6</v>
@@ -3454,16 +3454,16 @@
         <v>2.32</v>
       </c>
       <c r="AD19">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AE19">
         <v>1.18</v>
       </c>
       <c r="AF19">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG19">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O20">
         <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q20">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="R20">
         <v>2.3</v>
       </c>
       <c r="S20">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T20">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U20">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="V20">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z20">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AA20">
         <v>1.57</v>
       </c>
       <c r="AB20">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="AC20">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="AD20">
         <v>1.53</v>
       </c>
       <c r="AE20">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF20">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AG20">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4706,68 +4706,68 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O27">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q27">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="R27">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S27">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
         <v>3.2</v>
       </c>
       <c r="U27">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V27">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z27">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AA27">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB27">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC27">
         <v>3.08</v>
       </c>
       <c r="AD27">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE27">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF27">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG27">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,16 +4873,16 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="O28">
         <v>3.3</v>
       </c>
       <c r="P28">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q28">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="R28">
         <v>2.18</v>
@@ -4891,46 +4891,46 @@
         <v>1.35</v>
       </c>
       <c r="T28">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="U28">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V28">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W28">
         <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
         <v>1.25</v>
       </c>
       <c r="Z28">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA28">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB28">
         <v>2.05</v>
       </c>
       <c r="AC28">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="AD28">
         <v>1.36</v>
       </c>
       <c r="AE28">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF28">
         <v>1.57</v>
       </c>
       <c r="AG28">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="O29">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P29">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="Q29">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="R29">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="S29">
         <v>1.28</v>
       </c>
       <c r="T29">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U29">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V29">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W29">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
         <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.5</v>
+        <v>4.76</v>
       </c>
       <c r="AA29">
         <v>1.61</v>
       </c>
       <c r="AB29">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AC29">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="AD29">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE29">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF29">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AG29">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK29">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
+        <v>3.65</v>
+      </c>
+      <c r="Q30">
+        <v>2.27</v>
+      </c>
+      <c r="R30">
+        <v>2.23</v>
+      </c>
+      <c r="S30">
+        <v>1.29</v>
+      </c>
+      <c r="T30">
         <v>3.25</v>
       </c>
-      <c r="Q30">
-        <v>2.5</v>
-      </c>
-      <c r="R30">
-        <v>2.25</v>
-      </c>
-      <c r="S30">
-        <v>1.3</v>
-      </c>
-      <c r="T30">
-        <v>3.4</v>
-      </c>
       <c r="U30">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="V30">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
         <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z30">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA30">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB30">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AC30">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AD30">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE30">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF30">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG30">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK30">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,31 +5362,31 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O31">
-        <v>3.65</v>
+        <v>3.31</v>
       </c>
       <c r="P31">
-        <v>3.45</v>
+        <v>2.83</v>
       </c>
       <c r="Q31">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="R31">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="S31">
         <v>1.3</v>
       </c>
       <c r="T31">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U31">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V31">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W31">
         <v>1.09</v>
@@ -5395,31 +5395,31 @@
         <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z31">
         <v>4.33</v>
       </c>
       <c r="AA31">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB31">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC31">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="AD31">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE31">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF31">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG31">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.26</v>
       </c>
       <c r="AK31">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6177,28 +6177,28 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="O36">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="P36">
         <v>4.2</v>
       </c>
       <c r="Q36">
-        <v>3.25</v>
+        <v>2.64</v>
       </c>
       <c r="R36">
         <v>1.83</v>
       </c>
       <c r="S36">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="T36">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="U36">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="V36">
         <v>1.2</v>
@@ -6207,25 +6207,25 @@
         <v>1.03</v>
       </c>
       <c r="X36">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y36">
         <v>1.54</v>
       </c>
       <c r="Z36">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="AA36">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AB36">
         <v>1.36</v>
       </c>
       <c r="AC36">
-        <v>5.95</v>
+        <v>5.7</v>
       </c>
       <c r="AD36">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE36">
         <v>1.02</v>
@@ -6234,7 +6234,7 @@
         <v>2.3</v>
       </c>
       <c r="AG36">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AK36">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7970,58 +7970,58 @@
         </is>
       </c>
       <c r="N47">
+        <v>2.4</v>
+      </c>
+      <c r="O47">
+        <v>3</v>
+      </c>
+      <c r="P47">
+        <v>2.7</v>
+      </c>
+      <c r="Q47">
+        <v>3</v>
+      </c>
+      <c r="R47">
+        <v>2.05</v>
+      </c>
+      <c r="S47">
+        <v>1.45</v>
+      </c>
+      <c r="T47">
         <v>2.5</v>
       </c>
-      <c r="O47">
-        <v>3.15</v>
-      </c>
-      <c r="P47">
-        <v>2.6</v>
-      </c>
-      <c r="Q47">
-        <v>3.14</v>
-      </c>
-      <c r="R47">
-        <v>2</v>
-      </c>
-      <c r="S47">
-        <v>1.35</v>
-      </c>
-      <c r="T47">
-        <v>2.65</v>
-      </c>
       <c r="U47">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="V47">
         <v>1.32</v>
       </c>
       <c r="W47">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X47">
+        <v>1.05</v>
+      </c>
+      <c r="Y47">
+        <v>1.35</v>
+      </c>
+      <c r="Z47">
+        <v>2.74</v>
+      </c>
+      <c r="AA47">
+        <v>2.16</v>
+      </c>
+      <c r="AB47">
+        <v>1.62</v>
+      </c>
+      <c r="AC47">
+        <v>3.8</v>
+      </c>
+      <c r="AD47">
+        <v>1.2</v>
+      </c>
+      <c r="AE47">
         <v>1.03</v>
-      </c>
-      <c r="Y47">
-        <v>1.29</v>
-      </c>
-      <c r="Z47">
-        <v>3.1</v>
-      </c>
-      <c r="AA47">
-        <v>1.93</v>
-      </c>
-      <c r="AB47">
-        <v>1.71</v>
-      </c>
-      <c r="AC47">
-        <v>3.3</v>
-      </c>
-      <c r="AD47">
-        <v>1.25</v>
-      </c>
-      <c r="AE47">
-        <v>1.04</v>
       </c>
       <c r="AF47">
         <v>1.73</v>
@@ -8043,7 +8043,7 @@
         <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="O50">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="P50">
-        <v>4.32</v>
+        <v>3.05</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA50">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AB50">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.41</v>
+        <v>1.6</v>
       </c>
       <c r="O51">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="P51">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q51">
-        <v>2.9</v>
+        <v>2.17</v>
       </c>
       <c r="R51">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T51">
-        <v>2.63</v>
+        <v>2.97</v>
       </c>
       <c r="U51">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="V51">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W51">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
+        <v>1.22</v>
+      </c>
+      <c r="Z51">
+        <v>3.5</v>
+      </c>
+      <c r="AA51">
+        <v>1.82</v>
+      </c>
+      <c r="AB51">
+        <v>1.88</v>
+      </c>
+      <c r="AC51">
+        <v>3.04</v>
+      </c>
+      <c r="AD51">
         <v>1.29</v>
-      </c>
-      <c r="Z51">
-        <v>3.05</v>
-      </c>
-      <c r="AA51">
-        <v>1.94</v>
-      </c>
-      <c r="AB51">
-        <v>1.7</v>
-      </c>
-      <c r="AC51">
-        <v>3.3</v>
-      </c>
-      <c r="AD51">
-        <v>1.25</v>
       </c>
       <c r="AE51">
         <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG51">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK51">
-        <v>1.47</v>
+        <v>2.14</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,25 +8948,25 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="O53">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="P53">
-        <v>2.89</v>
+        <v>2.53</v>
       </c>
       <c r="Q53">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="R53">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S53">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T53">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U53">
         <v>2.2</v>
@@ -8975,22 +8975,22 @@
         <v>1.6</v>
       </c>
       <c r="W53">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z53">
-        <v>5</v>
+        <v>5.01</v>
       </c>
       <c r="AA53">
         <v>1.57</v>
       </c>
       <c r="AB53">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AC53">
         <v>2.4</v>
@@ -9002,7 +9002,7 @@
         <v>1.24</v>
       </c>
       <c r="AF53">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AG53">
         <v>2.55</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK53">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9117,43 +9117,43 @@
         <v>3.5</v>
       </c>
       <c r="P54">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q54">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="R54">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="S54">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T54">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U54">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V54">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W54">
         <v>1.11</v>
       </c>
       <c r="X54">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z54">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="AA54">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AB54">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AC54">
         <v>2.7</v>
@@ -9162,13 +9162,13 @@
         <v>1.45</v>
       </c>
       <c r="AE54">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF54">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG54">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,80 +9274,80 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O55">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="P55">
+        <v>2.9</v>
+      </c>
+      <c r="Q55">
+        <v>2.5</v>
+      </c>
+      <c r="R55">
         <v>2.4</v>
       </c>
-      <c r="Q55">
-        <v>3</v>
-      </c>
-      <c r="R55">
-        <v>2.33</v>
-      </c>
       <c r="S55">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="T55">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="U55">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="V55">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="W55">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X55">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
+        <v>1.13</v>
+      </c>
+      <c r="Z55">
+        <v>6</v>
+      </c>
+      <c r="AA55">
+        <v>1.44</v>
+      </c>
+      <c r="AB55">
+        <v>2.7</v>
+      </c>
+      <c r="AC55">
+        <v>2.2</v>
+      </c>
+      <c r="AD55">
+        <v>1.65</v>
+      </c>
+      <c r="AE55">
+        <v>1.25</v>
+      </c>
+      <c r="AF55">
+        <v>1.4</v>
+      </c>
+      <c r="AG55">
+        <v>2.7</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55">
         <v>1.22</v>
       </c>
-      <c r="Z55">
-        <v>3.98</v>
-      </c>
-      <c r="AA55">
-        <v>1.7</v>
-      </c>
-      <c r="AB55">
-        <v>2.1</v>
-      </c>
-      <c r="AC55">
-        <v>2.63</v>
-      </c>
-      <c r="AD55">
-        <v>1.4</v>
-      </c>
-      <c r="AE55">
-        <v>1.16</v>
-      </c>
-      <c r="AF55">
-        <v>1.53</v>
-      </c>
-      <c r="AG55">
-        <v>2.3</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ55">
-        <v>1.3</v>
-      </c>
       <c r="AK55">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,80 +9437,80 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="O56">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
       <c r="P56">
-        <v>3.27</v>
+        <v>2.37</v>
       </c>
       <c r="Q56">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="R56">
-        <v>2.61</v>
+        <v>2.14</v>
       </c>
       <c r="S56">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T56">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="U56">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="V56">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="W56">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X56">
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="Z56">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA56">
+        <v>1.7</v>
+      </c>
+      <c r="AB56">
+        <v>2.2</v>
+      </c>
+      <c r="AC56">
+        <v>2.63</v>
+      </c>
+      <c r="AD56">
         <v>1.44</v>
       </c>
-      <c r="AB56">
-        <v>2.7</v>
-      </c>
-      <c r="AC56">
-        <v>2.13</v>
-      </c>
-      <c r="AD56">
-        <v>1.69</v>
-      </c>
       <c r="AE56">
+        <v>1.16</v>
+      </c>
+      <c r="AF56">
+        <v>1.53</v>
+      </c>
+      <c r="AG56">
+        <v>2.26</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
         <v>1.25</v>
       </c>
-      <c r="AF56">
-        <v>1.4</v>
-      </c>
-      <c r="AG56">
-        <v>2.7</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>1.22</v>
-      </c>
       <c r="AK56">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9926,19 +9926,19 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="O59">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P59">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="Q59">
         <v>2.1</v>
       </c>
       <c r="R59">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="S59">
         <v>1.18</v>
@@ -9950,34 +9950,34 @@
         <v>2</v>
       </c>
       <c r="V59">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="W59">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X59">
         <v>0</v>
       </c>
       <c r="Y59">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z59">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="AA59">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AB59">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AC59">
         <v>1.96</v>
       </c>
       <c r="AD59">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AE59">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF59">
         <v>1.4</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK59">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N68">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="O76">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="P76">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="O77">
         <v>3.4</v>
       </c>
       <c r="P77">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="Q77">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="R77">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S77">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T77">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="U77">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="V77">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W77">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X77">
         <v>1.04</v>
       </c>
       <c r="Y77">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z77">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="AA77">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AB77">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC77">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="AD77">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AE77">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF77">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG77">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK77">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13029,58 +13029,58 @@
         <v>3.7</v>
       </c>
       <c r="P78">
-        <v>3.7</v>
+        <v>3.18</v>
       </c>
       <c r="Q78">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="R78">
         <v>2.4</v>
       </c>
       <c r="S78">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T78">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="U78">
         <v>2.23</v>
       </c>
       <c r="V78">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W78">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X78">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y78">
         <v>1.17</v>
       </c>
       <c r="Z78">
-        <v>5.39</v>
+        <v>5</v>
       </c>
       <c r="AA78">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AB78">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AC78">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="AD78">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE78">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AF78">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG78">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK78">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,80 +13186,80 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.7</v>
+        <v>2.14</v>
       </c>
       <c r="O79">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="P79">
-        <v>4.25</v>
+        <v>2.97</v>
       </c>
       <c r="Q79">
+        <v>2.35</v>
+      </c>
+      <c r="R79">
+        <v>2.57</v>
+      </c>
+      <c r="S79">
+        <v>1.14</v>
+      </c>
+      <c r="T79">
+        <v>5.25</v>
+      </c>
+      <c r="U79">
+        <v>1.78</v>
+      </c>
+      <c r="V79">
+        <v>2.02</v>
+      </c>
+      <c r="W79">
+        <v>1.29</v>
+      </c>
+      <c r="X79">
+        <v>0</v>
+      </c>
+      <c r="Y79">
+        <v>1.05</v>
+      </c>
+      <c r="Z79">
+        <v>7.4</v>
+      </c>
+      <c r="AA79">
+        <v>1.28</v>
+      </c>
+      <c r="AB79">
+        <v>3.52</v>
+      </c>
+      <c r="AC79">
+        <v>1.64</v>
+      </c>
+      <c r="AD79">
         <v>2.2</v>
       </c>
-      <c r="R79">
-        <v>2.35</v>
-      </c>
-      <c r="S79">
-        <v>1.29</v>
-      </c>
-      <c r="T79">
-        <v>3.28</v>
-      </c>
-      <c r="U79">
-        <v>2.28</v>
-      </c>
-      <c r="V79">
-        <v>1.51</v>
-      </c>
-      <c r="W79">
-        <v>1.08</v>
-      </c>
-      <c r="X79">
-        <v>1.04</v>
-      </c>
-      <c r="Y79">
-        <v>1.17</v>
-      </c>
-      <c r="Z79">
-        <v>4.8</v>
-      </c>
-      <c r="AA79">
-        <v>1.56</v>
-      </c>
-      <c r="AB79">
-        <v>2.15</v>
-      </c>
-      <c r="AC79">
-        <v>2.66</v>
-      </c>
-      <c r="AD79">
-        <v>1.48</v>
-      </c>
       <c r="AE79">
-        <v>1.14</v>
+        <v>1.54</v>
       </c>
       <c r="AF79">
+        <v>1.25</v>
+      </c>
+      <c r="AG79">
+        <v>3.55</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
+        <v>1.18</v>
+      </c>
+      <c r="AK79">
         <v>1.62</v>
-      </c>
-      <c r="AG79">
-        <v>2.15</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79">
-        <v>1.24</v>
-      </c>
-      <c r="AK79">
-        <v>2</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
+        <v>1.7</v>
+      </c>
+      <c r="O80">
+        <v>3.9</v>
+      </c>
+      <c r="P80">
+        <v>3.98</v>
+      </c>
+      <c r="Q80">
+        <v>2.2</v>
+      </c>
+      <c r="R80">
+        <v>2.3</v>
+      </c>
+      <c r="S80">
+        <v>1.3</v>
+      </c>
+      <c r="T80">
+        <v>3.4</v>
+      </c>
+      <c r="U80">
+        <v>2.4</v>
+      </c>
+      <c r="V80">
+        <v>1.51</v>
+      </c>
+      <c r="W80">
+        <v>1.1</v>
+      </c>
+      <c r="X80">
+        <v>1.01</v>
+      </c>
+      <c r="Y80">
+        <v>1.21</v>
+      </c>
+      <c r="Z80">
+        <v>4.39</v>
+      </c>
+      <c r="AA80">
+        <v>1.68</v>
+      </c>
+      <c r="AB80">
         <v>2.15</v>
       </c>
-      <c r="O80">
-        <v>4</v>
-      </c>
-      <c r="P80">
-        <v>2.87</v>
-      </c>
-      <c r="Q80">
-        <v>2.5</v>
-      </c>
-      <c r="R80">
-        <v>2.65</v>
-      </c>
-      <c r="S80">
-        <v>1.17</v>
-      </c>
-      <c r="T80">
-        <v>5.5</v>
-      </c>
-      <c r="U80">
-        <v>1.8</v>
-      </c>
-      <c r="V80">
-        <v>1.9</v>
-      </c>
-      <c r="W80">
-        <v>1.28</v>
-      </c>
-      <c r="X80">
-        <v>0</v>
-      </c>
-      <c r="Y80">
-        <v>1.05</v>
-      </c>
-      <c r="Z80">
-        <v>7.2</v>
-      </c>
-      <c r="AA80">
-        <v>1.25</v>
-      </c>
-      <c r="AB80">
-        <v>3.38</v>
-      </c>
       <c r="AC80">
-        <v>1.68</v>
+        <v>2.63</v>
       </c>
       <c r="AD80">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="AE80">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="AF80">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AG80">
-        <v>3.45</v>
+        <v>2.15</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK80">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13675,19 +13675,19 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="O82">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="P82">
-        <v>3.55</v>
+        <v>3.92</v>
       </c>
       <c r="Q82">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="R82">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="S82">
         <v>1.2</v>
@@ -13696,37 +13696,37 @@
         <v>4.33</v>
       </c>
       <c r="U82">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V82">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="W82">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X82">
         <v>0</v>
       </c>
       <c r="Y82">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z82">
-        <v>6.17</v>
+        <v>7</v>
       </c>
       <c r="AA82">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AB82">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AC82">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AD82">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE82">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF82">
         <v>1.4</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK82">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,10 +13838,10 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="O83">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="P83">
         <v>7.5</v>
@@ -13850,22 +13850,22 @@
         <v>1.62</v>
       </c>
       <c r="R83">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="S83">
         <v>1.19</v>
       </c>
       <c r="T83">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="U83">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="V83">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="W83">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X83">
         <v>0</v>
@@ -13874,22 +13874,22 @@
         <v>1.07</v>
       </c>
       <c r="Z83">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="AA83">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB83">
         <v>3.1</v>
       </c>
       <c r="AC83">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AD83">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AE83">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF83">
         <v>1.65</v>
@@ -13911,7 +13911,7 @@
         <v>1.09</v>
       </c>
       <c r="AK83">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,31 +14001,31 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="O84">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="P84">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="Q84">
         <v>1.75</v>
       </c>
       <c r="R84">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S84">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T84">
-        <v>4.35</v>
+        <v>4.1</v>
       </c>
       <c r="U84">
         <v>1.95</v>
       </c>
       <c r="V84">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W84">
         <v>1.2</v>
@@ -14037,28 +14037,28 @@
         <v>1.07</v>
       </c>
       <c r="Z84">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="AA84">
         <v>1.38</v>
       </c>
       <c r="AB84">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="AC84">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AD84">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE84">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AF84">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG84">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AK84">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,28 +14164,28 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="O85">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="P85">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="Q85">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="R85">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="S85">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T85">
         <v>3.75</v>
       </c>
       <c r="U85">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V85">
         <v>1.63</v>
@@ -14209,13 +14209,13 @@
         <v>2.55</v>
       </c>
       <c r="AC85">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AD85">
         <v>1.62</v>
       </c>
       <c r="AE85">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF85">
         <v>1.44</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK85">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL85">
         <v>0</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P2">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q2">
         <v>3.28</v>
@@ -650,46 +650,46 @@
         <v>1.96</v>
       </c>
       <c r="S2">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U2">
         <v>2.89</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W2">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z2">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AA2">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AB2">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC2">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AD2">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE2">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF2">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG2">
         <v>1.85</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AK2">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,55 +807,55 @@
         <v>2.95</v>
       </c>
       <c r="Q3">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="R3">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
         <v>1.44</v>
       </c>
       <c r="T3">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="U3">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="AA3">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AB3">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC3">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="AD3">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
         <v>1.83</v>
       </c>
       <c r="AG3">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK3">
         <v>1.54</v>
@@ -961,40 +961,40 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="O4">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Q4">
-        <v>3.98</v>
+        <v>4.64</v>
       </c>
       <c r="R4">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="S4">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="U4">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="V4">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z4">
         <v>3.25</v>
@@ -1003,22 +1003,22 @@
         <v>2.09</v>
       </c>
       <c r="AB4">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC4">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD4">
         <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG4">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.8</v>
       </c>
       <c r="AK4">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1139,49 +1139,49 @@
         <v>2.27</v>
       </c>
       <c r="S5">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T5">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U5">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V5">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="AA5">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AC5">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="AD5">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE5">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG5">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
         <v>2.35</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="O23">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="P23">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="Q23">
         <v>1.57</v>
@@ -4073,16 +4073,16 @@
         <v>3</v>
       </c>
       <c r="S23">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T23">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="U23">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V23">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="W23">
         <v>1.25</v>
@@ -4091,31 +4091,31 @@
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z23">
-        <v>6.85</v>
+        <v>7.5</v>
       </c>
       <c r="AA23">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AB23">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AC23">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AD23">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="AE23">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AF23">
         <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>3.7</v>
+        <v>4.12</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.06</v>
+        <v>1.7</v>
       </c>
       <c r="O41">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="P41">
-        <v>29</v>
+        <v>4.6</v>
       </c>
       <c r="Q41">
-        <v>1.24</v>
+        <v>2.19</v>
       </c>
       <c r="R41">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="S41">
+        <v>1.29</v>
+      </c>
+      <c r="T41">
+        <v>3.4</v>
+      </c>
+      <c r="U41">
+        <v>2.37</v>
+      </c>
+      <c r="V41">
+        <v>1.59</v>
+      </c>
+      <c r="W41">
         <v>1.11</v>
       </c>
-      <c r="T41">
-        <v>5.75</v>
-      </c>
-      <c r="U41">
+      <c r="X41">
+        <v>1.01</v>
+      </c>
+      <c r="Y41">
+        <v>1.15</v>
+      </c>
+      <c r="Z41">
+        <v>4.5</v>
+      </c>
+      <c r="AA41">
+        <v>1.6</v>
+      </c>
+      <c r="AB41">
+        <v>2.23</v>
+      </c>
+      <c r="AC41">
+        <v>2.63</v>
+      </c>
+      <c r="AD41">
         <v>1.56</v>
       </c>
-      <c r="V41">
-        <v>2.25</v>
-      </c>
-      <c r="W41">
-        <v>1.38</v>
-      </c>
-      <c r="X41">
-        <v>1</v>
-      </c>
-      <c r="Y41">
-        <v>1.06</v>
-      </c>
-      <c r="Z41">
-        <v>8.5</v>
-      </c>
-      <c r="AA41">
-        <v>1.18</v>
-      </c>
-      <c r="AB41">
-        <v>4.75</v>
-      </c>
-      <c r="AC41">
-        <v>1.5</v>
-      </c>
-      <c r="AD41">
-        <v>2.38</v>
-      </c>
       <c r="AE41">
-        <v>1.72</v>
+        <v>1.15</v>
       </c>
       <c r="AF41">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="AG41">
-        <v>1.5</v>
+        <v>2.28</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>10</v>
+        <v>2.17</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,31 +7155,31 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="O42">
+        <v>3.9</v>
+      </c>
+      <c r="P42">
         <v>4</v>
       </c>
-      <c r="P42">
-        <v>4.6</v>
-      </c>
       <c r="Q42">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="R42">
+        <v>2.49</v>
+      </c>
+      <c r="S42">
+        <v>1.32</v>
+      </c>
+      <c r="T42">
+        <v>3.28</v>
+      </c>
+      <c r="U42">
         <v>2.4</v>
       </c>
-      <c r="S42">
-        <v>1.29</v>
-      </c>
-      <c r="T42">
-        <v>3.4</v>
-      </c>
-      <c r="U42">
-        <v>2.37</v>
-      </c>
       <c r="V42">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="W42">
         <v>1.11</v>
@@ -7188,31 +7188,31 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z42">
         <v>4.5</v>
       </c>
       <c r="AA42">
+        <v>1.63</v>
+      </c>
+      <c r="AB42">
+        <v>2.36</v>
+      </c>
+      <c r="AC42">
+        <v>2.58</v>
+      </c>
+      <c r="AD42">
+        <v>1.53</v>
+      </c>
+      <c r="AE42">
+        <v>1.2</v>
+      </c>
+      <c r="AF42">
         <v>1.6</v>
       </c>
-      <c r="AB42">
-        <v>2.23</v>
-      </c>
-      <c r="AC42">
-        <v>2.63</v>
-      </c>
-      <c r="AD42">
-        <v>1.56</v>
-      </c>
-      <c r="AE42">
-        <v>1.15</v>
-      </c>
-      <c r="AF42">
-        <v>1.67</v>
-      </c>
       <c r="AG42">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK42">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.81</v>
+        <v>1.06</v>
       </c>
       <c r="O43">
-        <v>3.9</v>
+        <v>17</v>
       </c>
       <c r="P43">
+        <v>29</v>
+      </c>
+      <c r="Q43">
+        <v>1.24</v>
+      </c>
+      <c r="R43">
         <v>4</v>
       </c>
-      <c r="Q43">
-        <v>2.3</v>
-      </c>
-      <c r="R43">
-        <v>2.49</v>
-      </c>
       <c r="S43">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="T43">
-        <v>3.28</v>
+        <v>5.75</v>
       </c>
       <c r="U43">
-        <v>2.4</v>
+        <v>1.56</v>
       </c>
       <c r="V43">
-        <v>1.54</v>
+        <v>2.25</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y43">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="Z43">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA43">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="AB43">
-        <v>2.36</v>
+        <v>4.75</v>
       </c>
       <c r="AC43">
-        <v>2.58</v>
+        <v>1.5</v>
       </c>
       <c r="AD43">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AE43">
-        <v>1.2</v>
+        <v>1.72</v>
       </c>
       <c r="AF43">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="AG43">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="AK43">
-        <v>2.02</v>
+        <v>10</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,80 +9274,80 @@
         </is>
       </c>
       <c r="N55">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="O55">
-        <v>3.88</v>
+        <v>3.63</v>
       </c>
       <c r="P55">
-        <v>2.9</v>
+        <v>2.37</v>
       </c>
       <c r="Q55">
+        <v>3</v>
+      </c>
+      <c r="R55">
+        <v>2.14</v>
+      </c>
+      <c r="S55">
+        <v>1.31</v>
+      </c>
+      <c r="T55">
+        <v>3.15</v>
+      </c>
+      <c r="U55">
         <v>2.5</v>
       </c>
-      <c r="R55">
-        <v>2.4</v>
-      </c>
-      <c r="S55">
-        <v>1.2</v>
-      </c>
-      <c r="T55">
-        <v>4</v>
-      </c>
-      <c r="U55">
-        <v>2.04</v>
-      </c>
       <c r="V55">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="W55">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X55">
         <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z55">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AA55">
+        <v>1.7</v>
+      </c>
+      <c r="AB55">
+        <v>2.2</v>
+      </c>
+      <c r="AC55">
+        <v>2.63</v>
+      </c>
+      <c r="AD55">
         <v>1.44</v>
       </c>
-      <c r="AB55">
-        <v>2.7</v>
-      </c>
-      <c r="AC55">
-        <v>2.2</v>
-      </c>
-      <c r="AD55">
-        <v>1.65</v>
-      </c>
       <c r="AE55">
+        <v>1.16</v>
+      </c>
+      <c r="AF55">
+        <v>1.53</v>
+      </c>
+      <c r="AG55">
+        <v>2.26</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55">
         <v>1.25</v>
       </c>
-      <c r="AF55">
-        <v>1.4</v>
-      </c>
-      <c r="AG55">
-        <v>2.7</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ55">
-        <v>1.22</v>
-      </c>
       <c r="AK55">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,80 +9437,80 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="O56">
-        <v>3.63</v>
+        <v>3.88</v>
       </c>
       <c r="P56">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
       <c r="Q56">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R56">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="S56">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="T56">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="U56">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="V56">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="W56">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X56">
         <v>1.01</v>
       </c>
       <c r="Y56">
+        <v>1.13</v>
+      </c>
+      <c r="Z56">
+        <v>6</v>
+      </c>
+      <c r="AA56">
+        <v>1.44</v>
+      </c>
+      <c r="AB56">
+        <v>2.7</v>
+      </c>
+      <c r="AC56">
+        <v>2.2</v>
+      </c>
+      <c r="AD56">
+        <v>1.65</v>
+      </c>
+      <c r="AE56">
+        <v>1.25</v>
+      </c>
+      <c r="AF56">
+        <v>1.4</v>
+      </c>
+      <c r="AG56">
+        <v>2.7</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
         <v>1.22</v>
       </c>
-      <c r="Z56">
-        <v>4.2</v>
-      </c>
-      <c r="AA56">
-        <v>1.7</v>
-      </c>
-      <c r="AB56">
-        <v>2.2</v>
-      </c>
-      <c r="AC56">
-        <v>2.63</v>
-      </c>
-      <c r="AD56">
-        <v>1.44</v>
-      </c>
-      <c r="AE56">
-        <v>1.16</v>
-      </c>
-      <c r="AF56">
-        <v>1.53</v>
-      </c>
-      <c r="AG56">
-        <v>2.26</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>1.25</v>
-      </c>
       <c r="AK56">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="O78">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P78">
-        <v>3.18</v>
+        <v>2.97</v>
       </c>
       <c r="Q78">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="R78">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="S78">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T78">
-        <v>3.58</v>
+        <v>5.25</v>
       </c>
       <c r="U78">
-        <v>2.23</v>
+        <v>1.78</v>
       </c>
       <c r="V78">
-        <v>1.61</v>
+        <v>2.02</v>
       </c>
       <c r="W78">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="X78">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y78">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="Z78">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AA78">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AB78">
-        <v>2.4</v>
+        <v>3.52</v>
       </c>
       <c r="AC78">
-        <v>2.36</v>
+        <v>1.64</v>
       </c>
       <c r="AD78">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AE78">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="AF78">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AG78">
-        <v>2.55</v>
+        <v>3.55</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>1.18</v>
       </c>
       <c r="AK78">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="O79">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P79">
-        <v>2.97</v>
+        <v>3.98</v>
       </c>
       <c r="Q79">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="R79">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="S79">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="T79">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="U79">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="V79">
-        <v>2.02</v>
+        <v>1.51</v>
       </c>
       <c r="W79">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="Z79">
-        <v>7.4</v>
+        <v>4.39</v>
       </c>
       <c r="AA79">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AB79">
-        <v>3.52</v>
+        <v>2.15</v>
       </c>
       <c r="AC79">
-        <v>1.64</v>
+        <v>2.63</v>
       </c>
       <c r="AD79">
-        <v>2.2</v>
+        <v>1.47</v>
       </c>
       <c r="AE79">
-        <v>1.54</v>
+        <v>1.18</v>
       </c>
       <c r="AF79">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AG79">
-        <v>3.55</v>
+        <v>2.15</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK79">
-        <v>1.62</v>
+        <v>1.97</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,80 +13349,80 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="O80">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P80">
-        <v>3.98</v>
+        <v>3.18</v>
       </c>
       <c r="Q80">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R80">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S80">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T80">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="U80">
+        <v>2.23</v>
+      </c>
+      <c r="V80">
+        <v>1.61</v>
+      </c>
+      <c r="W80">
+        <v>1.13</v>
+      </c>
+      <c r="X80">
+        <v>1.04</v>
+      </c>
+      <c r="Y80">
+        <v>1.17</v>
+      </c>
+      <c r="Z80">
+        <v>5</v>
+      </c>
+      <c r="AA80">
+        <v>1.53</v>
+      </c>
+      <c r="AB80">
         <v>2.4</v>
       </c>
-      <c r="V80">
-        <v>1.51</v>
-      </c>
-      <c r="W80">
-        <v>1.1</v>
-      </c>
-      <c r="X80">
-        <v>1.01</v>
-      </c>
-      <c r="Y80">
-        <v>1.21</v>
-      </c>
-      <c r="Z80">
-        <v>4.39</v>
-      </c>
-      <c r="AA80">
-        <v>1.68</v>
-      </c>
-      <c r="AB80">
-        <v>2.15</v>
-      </c>
       <c r="AC80">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="AD80">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AE80">
+        <v>1.24</v>
+      </c>
+      <c r="AF80">
+        <v>1.45</v>
+      </c>
+      <c r="AG80">
+        <v>2.55</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ80">
         <v>1.18</v>
       </c>
-      <c r="AF80">
-        <v>1.62</v>
-      </c>
-      <c r="AG80">
-        <v>2.15</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ80">
-        <v>1.21</v>
-      </c>
       <c r="AK80">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AL80">
         <v>0</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -1613,28 +1613,28 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q8">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="R8">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S8">
         <v>1.64</v>
       </c>
       <c r="T8">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="U8">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="V8">
         <v>1.2</v>
@@ -1643,31 +1643,31 @@
         <v>1.01</v>
       </c>
       <c r="X8">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Y8">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Z8">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AA8">
         <v>2.83</v>
       </c>
       <c r="AB8">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AC8">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="AD8">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AG8">
         <v>1.55</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AK8">
         <v>1.31</v>
@@ -1779,58 +1779,58 @@
         <v>1.43</v>
       </c>
       <c r="O9">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="P9">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="R9">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S9">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="T9">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="U9">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="V9">
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="Z9">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AA9">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="AB9">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AC9">
-        <v>4.65</v>
+        <v>4.45</v>
       </c>
       <c r="AD9">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AG9">
         <v>1.4</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AK9">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
+        <v>1.85</v>
+      </c>
+      <c r="O15">
+        <v>3.25</v>
+      </c>
+      <c r="P15">
+        <v>3.6</v>
+      </c>
+      <c r="Q15">
+        <v>2.49</v>
+      </c>
+      <c r="R15">
+        <v>2.04</v>
+      </c>
+      <c r="S15">
+        <v>1.4</v>
+      </c>
+      <c r="T15">
+        <v>2.6</v>
+      </c>
+      <c r="U15">
+        <v>2.86</v>
+      </c>
+      <c r="V15">
+        <v>1.36</v>
+      </c>
+      <c r="W15">
+        <v>1.05</v>
+      </c>
+      <c r="X15">
+        <v>1.02</v>
+      </c>
+      <c r="Y15">
+        <v>1.31</v>
+      </c>
+      <c r="Z15">
+        <v>2.92</v>
+      </c>
+      <c r="AA15">
+        <v>2.01</v>
+      </c>
+      <c r="AB15">
         <v>1.7</v>
       </c>
-      <c r="O15">
-        <v>3.5</v>
-      </c>
-      <c r="P15">
-        <v>4.2</v>
-      </c>
-      <c r="Q15">
-        <v>2.24</v>
-      </c>
-      <c r="R15">
-        <v>2.15</v>
-      </c>
-      <c r="S15">
-        <v>1.34</v>
-      </c>
-      <c r="T15">
-        <v>2.83</v>
-      </c>
-      <c r="U15">
-        <v>2.6</v>
-      </c>
-      <c r="V15">
-        <v>1.4</v>
-      </c>
-      <c r="W15">
-        <v>1.08</v>
-      </c>
-      <c r="X15">
-        <v>1.01</v>
-      </c>
-      <c r="Y15">
-        <v>1.24</v>
-      </c>
-      <c r="Z15">
-        <v>3.34</v>
-      </c>
-      <c r="AA15">
+      <c r="AC15">
+        <v>3.42</v>
+      </c>
+      <c r="AD15">
+        <v>1.23</v>
+      </c>
+      <c r="AE15">
+        <v>1.05</v>
+      </c>
+      <c r="AF15">
+        <v>1.73</v>
+      </c>
+      <c r="AG15">
+        <v>1.93</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>1.25</v>
+      </c>
+      <c r="AK15">
         <v>1.83</v>
-      </c>
-      <c r="AB15">
-        <v>1.86</v>
-      </c>
-      <c r="AC15">
-        <v>3</v>
-      </c>
-      <c r="AD15">
-        <v>1.3</v>
-      </c>
-      <c r="AE15">
-        <v>1.08</v>
-      </c>
-      <c r="AF15">
-        <v>1.76</v>
-      </c>
-      <c r="AG15">
-        <v>1.91</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.22</v>
-      </c>
-      <c r="AK15">
-        <v>2</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,61 +2917,61 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="O16">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q16">
         <v>3.4</v>
       </c>
       <c r="R16">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S16">
         <v>1.3</v>
       </c>
       <c r="T16">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="U16">
         <v>2.45</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z16">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA16">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB16">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AC16">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AD16">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE16">
         <v>1.14</v>
       </c>
       <c r="AF16">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG16">
         <v>2.15</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="AK16">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>7.75</v>
+        <v>5.8</v>
       </c>
       <c r="O25">
         <v>4.1</v>
       </c>
       <c r="P25">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Q25">
-        <v>8.33</v>
+        <v>7</v>
       </c>
       <c r="R25">
         <v>2.19</v>
       </c>
       <c r="S25">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T25">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="U25">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="V25">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W25">
         <v>1.05</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y25">
         <v>1.3</v>
       </c>
       <c r="Z25">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AA25">
         <v>2.05</v>
       </c>
       <c r="AB25">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC25">
-        <v>3.34</v>
+        <v>3.51</v>
       </c>
       <c r="AD25">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE25">
         <v>1.05</v>
       </c>
       <c r="AF25">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AG25">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>2.75</v>
+        <v>1.13</v>
       </c>
       <c r="AK25">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4553,31 +4553,31 @@
         <v>2.75</v>
       </c>
       <c r="P26">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q26">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R26">
         <v>1.85</v>
       </c>
       <c r="S26">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="T26">
         <v>2.07</v>
       </c>
       <c r="U26">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="V26">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W26">
         <v>1.01</v>
       </c>
       <c r="X26">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Y26">
         <v>1.62</v>
@@ -4586,10 +4586,10 @@
         <v>2.23</v>
       </c>
       <c r="AA26">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AB26">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AC26">
         <v>6</v>
@@ -4601,10 +4601,10 @@
         <v>1.01</v>
       </c>
       <c r="AF26">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AG26">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AK26">
         <v>1.36</v>
@@ -5851,58 +5851,58 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P34">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q34">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="R34">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
         <v>1.24</v>
       </c>
       <c r="T34">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="U34">
         <v>2.4</v>
       </c>
       <c r="V34">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W34">
         <v>1.09</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z34">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA34">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB34">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AC34">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AD34">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE34">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF34">
         <v>1.57</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="O35">
-        <v>6.4</v>
+        <v>6.91</v>
       </c>
       <c r="P35">
-        <v>10</v>
+        <v>13.8</v>
       </c>
       <c r="Q35">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="R35">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="S35">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="T35">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="U35">
         <v>1.76</v>
       </c>
       <c r="V35">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="W35">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z35">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA35">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AB35">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AC35">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AD35">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="AE35">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AF35">
         <v>1.67</v>
       </c>
       <c r="AG35">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK35">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,31 +6992,31 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="O41">
+        <v>3.9</v>
+      </c>
+      <c r="P41">
         <v>4</v>
       </c>
-      <c r="P41">
-        <v>4.6</v>
-      </c>
       <c r="Q41">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="R41">
+        <v>2.49</v>
+      </c>
+      <c r="S41">
+        <v>1.32</v>
+      </c>
+      <c r="T41">
+        <v>3.28</v>
+      </c>
+      <c r="U41">
         <v>2.4</v>
       </c>
-      <c r="S41">
-        <v>1.29</v>
-      </c>
-      <c r="T41">
-        <v>3.4</v>
-      </c>
-      <c r="U41">
-        <v>2.37</v>
-      </c>
       <c r="V41">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="W41">
         <v>1.11</v>
@@ -7025,31 +7025,31 @@
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z41">
         <v>4.5</v>
       </c>
       <c r="AA41">
+        <v>1.63</v>
+      </c>
+      <c r="AB41">
+        <v>2.36</v>
+      </c>
+      <c r="AC41">
+        <v>2.58</v>
+      </c>
+      <c r="AD41">
+        <v>1.53</v>
+      </c>
+      <c r="AE41">
+        <v>1.2</v>
+      </c>
+      <c r="AF41">
         <v>1.6</v>
       </c>
-      <c r="AB41">
-        <v>2.23</v>
-      </c>
-      <c r="AC41">
-        <v>2.63</v>
-      </c>
-      <c r="AD41">
-        <v>1.56</v>
-      </c>
-      <c r="AE41">
-        <v>1.15</v>
-      </c>
-      <c r="AF41">
-        <v>1.67</v>
-      </c>
       <c r="AG41">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK41">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.81</v>
+        <v>1.06</v>
       </c>
       <c r="O42">
-        <v>3.9</v>
+        <v>17</v>
       </c>
       <c r="P42">
+        <v>29</v>
+      </c>
+      <c r="Q42">
+        <v>1.24</v>
+      </c>
+      <c r="R42">
         <v>4</v>
       </c>
-      <c r="Q42">
-        <v>2.3</v>
-      </c>
-      <c r="R42">
-        <v>2.49</v>
-      </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="T42">
-        <v>3.28</v>
+        <v>5.75</v>
       </c>
       <c r="U42">
-        <v>2.4</v>
+        <v>1.56</v>
       </c>
       <c r="V42">
-        <v>1.54</v>
+        <v>2.25</v>
       </c>
       <c r="W42">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="Z42">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA42">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="AB42">
-        <v>2.36</v>
+        <v>4.75</v>
       </c>
       <c r="AC42">
-        <v>2.58</v>
+        <v>1.5</v>
       </c>
       <c r="AD42">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AE42">
-        <v>1.2</v>
+        <v>1.72</v>
       </c>
       <c r="AF42">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="AG42">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="AK42">
-        <v>2.02</v>
+        <v>10</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.06</v>
+        <v>1.7</v>
       </c>
       <c r="O43">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="P43">
-        <v>29</v>
+        <v>4.6</v>
       </c>
       <c r="Q43">
-        <v>1.24</v>
+        <v>2.19</v>
       </c>
       <c r="R43">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="S43">
+        <v>1.29</v>
+      </c>
+      <c r="T43">
+        <v>3.4</v>
+      </c>
+      <c r="U43">
+        <v>2.37</v>
+      </c>
+      <c r="V43">
+        <v>1.59</v>
+      </c>
+      <c r="W43">
         <v>1.11</v>
       </c>
-      <c r="T43">
-        <v>5.75</v>
-      </c>
-      <c r="U43">
+      <c r="X43">
+        <v>1.01</v>
+      </c>
+      <c r="Y43">
+        <v>1.15</v>
+      </c>
+      <c r="Z43">
+        <v>4.5</v>
+      </c>
+      <c r="AA43">
+        <v>1.6</v>
+      </c>
+      <c r="AB43">
+        <v>2.23</v>
+      </c>
+      <c r="AC43">
+        <v>2.63</v>
+      </c>
+      <c r="AD43">
         <v>1.56</v>
       </c>
-      <c r="V43">
-        <v>2.25</v>
-      </c>
-      <c r="W43">
-        <v>1.38</v>
-      </c>
-      <c r="X43">
-        <v>1</v>
-      </c>
-      <c r="Y43">
-        <v>1.06</v>
-      </c>
-      <c r="Z43">
-        <v>8.5</v>
-      </c>
-      <c r="AA43">
-        <v>1.18</v>
-      </c>
-      <c r="AB43">
-        <v>4.75</v>
-      </c>
-      <c r="AC43">
-        <v>1.5</v>
-      </c>
-      <c r="AD43">
-        <v>2.38</v>
-      </c>
       <c r="AE43">
-        <v>1.72</v>
+        <v>1.15</v>
       </c>
       <c r="AF43">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="AG43">
-        <v>1.5</v>
+        <v>2.28</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>10</v>
+        <v>2.17</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8948,19 +8948,19 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="O53">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="P53">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="Q53">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="R53">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S53">
         <v>1.25</v>
@@ -8969,7 +8969,7 @@
         <v>3.75</v>
       </c>
       <c r="U53">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V53">
         <v>1.6</v>
@@ -8978,34 +8978,34 @@
         <v>1.13</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z53">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="AA53">
         <v>1.57</v>
       </c>
       <c r="AB53">
+        <v>2.43</v>
+      </c>
+      <c r="AC53">
         <v>2.35</v>
       </c>
-      <c r="AC53">
-        <v>2.4</v>
-      </c>
       <c r="AD53">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE53">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF53">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AG53">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
+        <v>2.01</v>
+      </c>
+      <c r="O54">
+        <v>3.83</v>
+      </c>
+      <c r="P54">
+        <v>2.72</v>
+      </c>
+      <c r="Q54">
+        <v>2.4</v>
+      </c>
+      <c r="R54">
+        <v>2.61</v>
+      </c>
+      <c r="S54">
+        <v>1.22</v>
+      </c>
+      <c r="T54">
+        <v>4.1</v>
+      </c>
+      <c r="U54">
+        <v>2.05</v>
+      </c>
+      <c r="V54">
+        <v>1.62</v>
+      </c>
+      <c r="W54">
+        <v>1.17</v>
+      </c>
+      <c r="X54">
+        <v>1.02</v>
+      </c>
+      <c r="Y54">
+        <v>1.14</v>
+      </c>
+      <c r="Z54">
+        <v>6.1</v>
+      </c>
+      <c r="AA54">
+        <v>1.44</v>
+      </c>
+      <c r="AB54">
         <v>2.7</v>
       </c>
-      <c r="O54">
-        <v>3.5</v>
-      </c>
-      <c r="P54">
-        <v>2.18</v>
-      </c>
-      <c r="Q54">
-        <v>3.47</v>
-      </c>
-      <c r="R54">
-        <v>2.42</v>
-      </c>
-      <c r="S54">
-        <v>1.25</v>
-      </c>
-      <c r="T54">
-        <v>3.6</v>
-      </c>
-      <c r="U54">
-        <v>2.32</v>
-      </c>
-      <c r="V54">
-        <v>1.52</v>
-      </c>
-      <c r="W54">
-        <v>1.11</v>
-      </c>
-      <c r="X54">
-        <v>1.01</v>
-      </c>
-      <c r="Y54">
-        <v>1.15</v>
-      </c>
-      <c r="Z54">
-        <v>4.3</v>
-      </c>
-      <c r="AA54">
-        <v>1.6</v>
-      </c>
-      <c r="AB54">
-        <v>2.2</v>
-      </c>
       <c r="AC54">
+        <v>2.02</v>
+      </c>
+      <c r="AD54">
+        <v>1.73</v>
+      </c>
+      <c r="AE54">
+        <v>1.23</v>
+      </c>
+      <c r="AF54">
+        <v>1.36</v>
+      </c>
+      <c r="AG54">
         <v>2.7</v>
-      </c>
-      <c r="AD54">
-        <v>1.45</v>
-      </c>
-      <c r="AE54">
-        <v>1.14</v>
-      </c>
-      <c r="AF54">
-        <v>1.5</v>
-      </c>
-      <c r="AG54">
-        <v>2.33</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.35</v>
+        <v>3.04</v>
       </c>
       <c r="O55">
-        <v>3.63</v>
+        <v>3.55</v>
       </c>
       <c r="P55">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="Q55">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="R55">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="S55">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T55">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="U55">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V55">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W55">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X55">
         <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z55">
-        <v>4.2</v>
+        <v>4.54</v>
       </c>
       <c r="AA55">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB55">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AC55">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="AD55">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE55">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF55">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG55">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AK55">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,80 +9437,80 @@
         </is>
       </c>
       <c r="N56">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O56">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="Q56">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R56">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S56">
+        <v>1.3</v>
+      </c>
+      <c r="T56">
+        <v>3.25</v>
+      </c>
+      <c r="U56">
+        <v>2.44</v>
+      </c>
+      <c r="V56">
+        <v>1.49</v>
+      </c>
+      <c r="W56">
+        <v>1.08</v>
+      </c>
+      <c r="X56">
+        <v>1.04</v>
+      </c>
+      <c r="Y56">
         <v>1.2</v>
       </c>
-      <c r="T56">
+      <c r="Z56">
         <v>4</v>
       </c>
-      <c r="U56">
-        <v>2.04</v>
-      </c>
-      <c r="V56">
-        <v>1.65</v>
-      </c>
-      <c r="W56">
-        <v>1.14</v>
-      </c>
-      <c r="X56">
-        <v>1.01</v>
-      </c>
-      <c r="Y56">
-        <v>1.13</v>
-      </c>
-      <c r="Z56">
-        <v>6</v>
-      </c>
       <c r="AA56">
+        <v>1.7</v>
+      </c>
+      <c r="AB56">
+        <v>2.14</v>
+      </c>
+      <c r="AC56">
+        <v>2.65</v>
+      </c>
+      <c r="AD56">
+        <v>1.45</v>
+      </c>
+      <c r="AE56">
+        <v>1.16</v>
+      </c>
+      <c r="AF56">
+        <v>1.53</v>
+      </c>
+      <c r="AG56">
+        <v>2.3</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <v>1.3</v>
+      </c>
+      <c r="AK56">
         <v>1.44</v>
-      </c>
-      <c r="AB56">
-        <v>2.7</v>
-      </c>
-      <c r="AC56">
-        <v>2.2</v>
-      </c>
-      <c r="AD56">
-        <v>1.65</v>
-      </c>
-      <c r="AE56">
-        <v>1.25</v>
-      </c>
-      <c r="AF56">
-        <v>1.4</v>
-      </c>
-      <c r="AG56">
-        <v>2.7</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>1.22</v>
-      </c>
-      <c r="AK56">
-        <v>1.67</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="O59">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="P59">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="Q59">
         <v>2.1</v>
@@ -9941,22 +9941,22 @@
         <v>2.54</v>
       </c>
       <c r="S59">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T59">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="U59">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V59">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="W59">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
         <v>1.08</v>
@@ -9965,25 +9965,25 @@
         <v>7.5</v>
       </c>
       <c r="AA59">
+        <v>1.38</v>
+      </c>
+      <c r="AB59">
+        <v>3</v>
+      </c>
+      <c r="AC59">
+        <v>1.9</v>
+      </c>
+      <c r="AD59">
+        <v>1.87</v>
+      </c>
+      <c r="AE59">
+        <v>1.32</v>
+      </c>
+      <c r="AF59">
         <v>1.36</v>
       </c>
-      <c r="AB59">
-        <v>3.1</v>
-      </c>
-      <c r="AC59">
-        <v>1.96</v>
-      </c>
-      <c r="AD59">
-        <v>1.86</v>
-      </c>
-      <c r="AE59">
-        <v>1.33</v>
-      </c>
-      <c r="AF59">
-        <v>1.4</v>
-      </c>
       <c r="AG59">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK59">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.61</v>
+        <v>2.31</v>
       </c>
       <c r="O77">
         <v>3.4</v>
@@ -12869,52 +12869,52 @@
         <v>2.48</v>
       </c>
       <c r="Q77">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="R77">
         <v>2.1</v>
       </c>
       <c r="S77">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T77">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="U77">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="V77">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W77">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X77">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y77">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z77">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AA77">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AB77">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AC77">
         <v>3.3</v>
       </c>
       <c r="AD77">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE77">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF77">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG77">
         <v>2.1</v>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK77">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,61 +13023,61 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="O78">
-        <v>4.2</v>
+        <v>4.21</v>
       </c>
       <c r="P78">
         <v>2.97</v>
       </c>
       <c r="Q78">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="R78">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="S78">
         <v>1.14</v>
       </c>
       <c r="T78">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="U78">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V78">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="W78">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z78">
         <v>7.4</v>
       </c>
       <c r="AA78">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB78">
         <v>3.52</v>
       </c>
       <c r="AC78">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AD78">
         <v>2.2</v>
       </c>
       <c r="AE78">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AF78">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AG78">
         <v>3.55</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,58 +13186,58 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O79">
+        <v>3.85</v>
+      </c>
+      <c r="P79">
         <v>3.9</v>
       </c>
-      <c r="P79">
-        <v>3.98</v>
-      </c>
       <c r="Q79">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="R79">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S79">
         <v>1.3</v>
       </c>
       <c r="T79">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U79">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="V79">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="W79">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X79">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y79">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z79">
-        <v>4.39</v>
+        <v>4.5</v>
       </c>
       <c r="AA79">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB79">
         <v>2.15</v>
       </c>
       <c r="AC79">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="AD79">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AE79">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF79">
         <v>1.62</v>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK79">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,37 +13349,37 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="O80">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P80">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="Q80">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="R80">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S80">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T80">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="U80">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="V80">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W80">
         <v>1.13</v>
       </c>
       <c r="X80">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
         <v>1.17</v>
@@ -13388,22 +13388,22 @@
         <v>5</v>
       </c>
       <c r="AA80">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB80">
         <v>2.4</v>
       </c>
       <c r="AC80">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AD80">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE80">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AF80">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG80">
         <v>2.55</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="O82">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="P82">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="Q82">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R82">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="S82">
         <v>1.2</v>
       </c>
       <c r="T82">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U82">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="V82">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W82">
         <v>1.18</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z82">
-        <v>7</v>
+        <v>6.31</v>
       </c>
       <c r="AA82">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB82">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AC82">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AD82">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AE82">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AF82">
         <v>1.4</v>
       </c>
       <c r="AG82">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK82">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,43 +13838,43 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="O83">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="P83">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="Q83">
         <v>1.62</v>
       </c>
       <c r="R83">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="S83">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T83">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U83">
         <v>1.91</v>
       </c>
       <c r="V83">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W83">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z83">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA83">
         <v>1.36</v>
@@ -13883,16 +13883,16 @@
         <v>3.1</v>
       </c>
       <c r="AC83">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AD83">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AE83">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF83">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG83">
         <v>2.23</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AK83">
-        <v>3.6</v>
+        <v>2.98</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="O84">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P84">
         <v>5.5</v>
       </c>
       <c r="Q84">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="R84">
         <v>2.7</v>
       </c>
       <c r="S84">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T84">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="U84">
         <v>1.95</v>
       </c>
       <c r="V84">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="W84">
         <v>1.2</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z84">
-        <v>6.49</v>
+        <v>7.5</v>
       </c>
       <c r="AA84">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AB84">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
       <c r="AC84">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AD84">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE84">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AF84">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG84">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK84">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="O85">
-        <v>3.68</v>
+        <v>3.77</v>
       </c>
       <c r="P85">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="Q85">
-        <v>2.44</v>
+        <v>2.79</v>
       </c>
       <c r="R85">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="S85">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T85">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U85">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V85">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="W85">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X85">
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z85">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA85">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB85">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AC85">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD85">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE85">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF85">
         <v>1.44</v>
       </c>
       <c r="AG85">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK85">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL85">
         <v>0</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="O10">
-        <v>4.4</v>
+        <v>4.95</v>
       </c>
       <c r="P10">
-        <v>8.449999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="Q10">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="R10">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="S10">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.45</v>
+        <v>3.08</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="V10">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="W10">
         <v>1.13</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA10">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB10">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC10">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD10">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AE10">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF10">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AG10">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.15</v>
       </c>
       <c r="AK10">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2600,10 +2600,10 @@
         <v>3.62</v>
       </c>
       <c r="Q14">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R14">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S14">
         <v>1.34</v>
@@ -2621,34 +2621,34 @@
         <v>1.07</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z14">
-        <v>3.76</v>
+        <v>3.58</v>
       </c>
       <c r="AA14">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB14">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC14">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AD14">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE14">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF14">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG14">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK14">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,58 +3243,58 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="O18">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="P18">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="Q18">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="R18">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="S18">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="T18">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="U18">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="V18">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W18">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z18">
-        <v>6.2</v>
+        <v>6.55</v>
       </c>
       <c r="AA18">
         <v>1.33</v>
       </c>
       <c r="AB18">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AC18">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AD18">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AE18">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AF18">
         <v>1.95</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK18">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>1.7</v>
       </c>
       <c r="Q19">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="R19">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="S19">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
         <v>3.34</v>
       </c>
       <c r="U19">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V19">
         <v>1.57</v>
       </c>
       <c r="W19">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
         <v>1.13</v>
       </c>
       <c r="Z19">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AA19">
         <v>1.6</v>
       </c>
       <c r="AB19">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AC19">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AD19">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AE19">
         <v>1.18</v>
       </c>
       <c r="AF19">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG19">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P20">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Q20">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="S20">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="U20">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="V20">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W20">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z20">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AA20">
         <v>1.57</v>
       </c>
       <c r="AB20">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AC20">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AD20">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE20">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AF20">
         <v>1.45</v>
       </c>
       <c r="AG20">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AK20">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="O21">
         <v>6.7</v>
@@ -3744,52 +3744,52 @@
         <v>1.57</v>
       </c>
       <c r="R21">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="S21">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T21">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="U21">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="V21">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="W21">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y21">
         <v>1.04</v>
       </c>
       <c r="Z21">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="AA21">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB21">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AC21">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AD21">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AE21">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG21">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.13</v>
       </c>
       <c r="AK21">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,43 +3895,43 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="O22">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P22">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="Q22">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="R22">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="S22">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="T22">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="U22">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="V22">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="W22">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X22">
         <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Z22">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="AA22">
         <v>1.12</v>
@@ -3943,16 +3943,16 @@
         <v>1.43</v>
       </c>
       <c r="AD22">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="AE22">
+        <v>1.82</v>
+      </c>
+      <c r="AF22">
         <v>1.75</v>
       </c>
-      <c r="AF22">
-        <v>1.83</v>
-      </c>
       <c r="AG22">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.01</v>
       </c>
       <c r="AK22">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="O23">
         <v>6.8</v>
       </c>
       <c r="P23">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Q23">
         <v>1.57</v>
@@ -4073,7 +4073,7 @@
         <v>3</v>
       </c>
       <c r="S23">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T23">
         <v>4.6</v>
@@ -4710,52 +4710,52 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O27">
         <v>3.4</v>
       </c>
       <c r="P27">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q27">
-        <v>3.92</v>
+        <v>3.45</v>
       </c>
       <c r="R27">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="S27">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U27">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V27">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W27">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
         <v>3.58</v>
       </c>
       <c r="AA27">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB27">
         <v>1.95</v>
       </c>
       <c r="AC27">
-        <v>3.08</v>
+        <v>2.81</v>
       </c>
       <c r="AD27">
         <v>1.33</v>
@@ -4764,7 +4764,7 @@
         <v>1.09</v>
       </c>
       <c r="AF27">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AG27">
         <v>2.14</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
         <v>1.3</v>
@@ -4879,58 +4879,58 @@
         <v>3.3</v>
       </c>
       <c r="P28">
-        <v>2.9</v>
+        <v>2.58</v>
       </c>
       <c r="Q28">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="R28">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="S28">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T28">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="U28">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="V28">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W28">
         <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
         <v>1.25</v>
       </c>
       <c r="Z28">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA28">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB28">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AC28">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="AD28">
         <v>1.36</v>
       </c>
       <c r="AE28">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF28">
         <v>1.57</v>
       </c>
       <c r="AG28">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK28">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5039,61 +5039,61 @@
         <v>1.69</v>
       </c>
       <c r="O29">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P29">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="Q29">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="R29">
         <v>2.18</v>
       </c>
       <c r="S29">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T29">
         <v>3.5</v>
       </c>
       <c r="U29">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V29">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
         <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.76</v>
+        <v>4.5</v>
       </c>
       <c r="AA29">
         <v>1.61</v>
       </c>
       <c r="AB29">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AC29">
         <v>2.63</v>
       </c>
       <c r="AD29">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AE29">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF29">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AG29">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5208,31 +5208,31 @@
         <v>3.65</v>
       </c>
       <c r="Q30">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="R30">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U30">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="V30">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W30">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
         <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z30">
         <v>4.3</v>
@@ -5241,22 +5241,22 @@
         <v>1.61</v>
       </c>
       <c r="AB30">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AC30">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AD30">
         <v>1.49</v>
       </c>
       <c r="AE30">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF30">
         <v>1.53</v>
       </c>
       <c r="AG30">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.24</v>
       </c>
       <c r="AK30">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,16 +5362,16 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="O31">
-        <v>3.31</v>
+        <v>3.6</v>
       </c>
       <c r="P31">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="Q31">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R31">
         <v>2.42</v>
@@ -5380,13 +5380,13 @@
         <v>1.3</v>
       </c>
       <c r="T31">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U31">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V31">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W31">
         <v>1.09</v>
@@ -5395,25 +5395,25 @@
         <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="AA31">
         <v>1.66</v>
       </c>
       <c r="AB31">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AC31">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AD31">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE31">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF31">
         <v>1.55</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK31">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,65 +6340,65 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.79</v>
+        <v>1.95</v>
       </c>
       <c r="O37">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P37">
-        <v>2.23</v>
+        <v>3.75</v>
       </c>
       <c r="Q37">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="R37">
+        <v>2.3</v>
+      </c>
+      <c r="S37">
+        <v>1.29</v>
+      </c>
+      <c r="T37">
+        <v>3.3</v>
+      </c>
+      <c r="U37">
+        <v>2.4</v>
+      </c>
+      <c r="V37">
+        <v>1.48</v>
+      </c>
+      <c r="W37">
+        <v>1.08</v>
+      </c>
+      <c r="X37">
+        <v>1</v>
+      </c>
+      <c r="Y37">
+        <v>1.2</v>
+      </c>
+      <c r="Z37">
+        <v>3.78</v>
+      </c>
+      <c r="AA37">
+        <v>1.73</v>
+      </c>
+      <c r="AB37">
+        <v>2.1</v>
+      </c>
+      <c r="AC37">
+        <v>2.68</v>
+      </c>
+      <c r="AD37">
+        <v>1.34</v>
+      </c>
+      <c r="AE37">
+        <v>1.13</v>
+      </c>
+      <c r="AF37">
+        <v>1.63</v>
+      </c>
+      <c r="AG37">
         <v>2.15</v>
       </c>
-      <c r="S37">
-        <v>1.32</v>
-      </c>
-      <c r="T37">
-        <v>3.05</v>
-      </c>
-      <c r="U37">
-        <v>2.63</v>
-      </c>
-      <c r="V37">
-        <v>1.4</v>
-      </c>
-      <c r="W37">
-        <v>1.06</v>
-      </c>
-      <c r="X37">
-        <v>1.05</v>
-      </c>
-      <c r="Y37">
-        <v>1.24</v>
-      </c>
-      <c r="Z37">
-        <v>3.71</v>
-      </c>
-      <c r="AA37">
-        <v>1.87</v>
-      </c>
-      <c r="AB37">
-        <v>1.87</v>
-      </c>
-      <c r="AC37">
-        <v>2.95</v>
-      </c>
-      <c r="AD37">
-        <v>1.33</v>
-      </c>
-      <c r="AE37">
-        <v>1.11</v>
-      </c>
-      <c r="AF37">
-        <v>1.69</v>
-      </c>
-      <c r="AG37">
-        <v>2.05</v>
-      </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="AK37">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="O38">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q38">
-        <v>2.45</v>
+        <v>3.35</v>
       </c>
       <c r="R38">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T38">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U38">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="V38">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W38">
         <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y38">
         <v>1.24</v>
       </c>
       <c r="Z38">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="AA38">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AB38">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AC38">
-        <v>2.72</v>
+        <v>2.95</v>
       </c>
       <c r="AD38">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE38">
         <v>1.11</v>
       </c>
       <c r="AF38">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG38">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK38">
-        <v>1.88</v>
+        <v>1.38</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,10 +6675,10 @@
         <v>8</v>
       </c>
       <c r="Q39">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R39">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="S39">
         <v>1.21</v>
@@ -6690,19 +6690,19 @@
         <v>2.07</v>
       </c>
       <c r="V39">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="W39">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z39">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AA39">
         <v>1.4</v>
@@ -6711,16 +6711,16 @@
         <v>2.7</v>
       </c>
       <c r="AC39">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AD39">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AE39">
         <v>1.25</v>
       </c>
       <c r="AF39">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG39">
         <v>2.01</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AK39">
         <v>3.32</v>
@@ -6832,40 +6832,40 @@
         <v>4.54</v>
       </c>
       <c r="O40">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="P40">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q40">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="R40">
         <v>2.18</v>
       </c>
       <c r="S40">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T40">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="U40">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="V40">
         <v>1.41</v>
       </c>
       <c r="W40">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y40">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z40">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="AA40">
         <v>1.94</v>
@@ -6874,10 +6874,10 @@
         <v>1.88</v>
       </c>
       <c r="AC40">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD40">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE40">
         <v>1.11</v>
@@ -6886,7 +6886,7 @@
         <v>1.83</v>
       </c>
       <c r="AG40">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AK40">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.81</v>
+        <v>1.03</v>
       </c>
       <c r="O41">
-        <v>3.9</v>
+        <v>17</v>
       </c>
       <c r="P41">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="Q41">
-        <v>2.3</v>
+        <v>1.24</v>
       </c>
       <c r="R41">
-        <v>2.49</v>
+        <v>4.75</v>
       </c>
       <c r="S41">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="T41">
-        <v>3.28</v>
+        <v>6.4</v>
       </c>
       <c r="U41">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="V41">
-        <v>1.54</v>
+        <v>2.25</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="Z41">
+        <v>8.5</v>
+      </c>
+      <c r="AA41">
+        <v>1.18</v>
+      </c>
+      <c r="AB41">
         <v>4.5</v>
       </c>
-      <c r="AA41">
-        <v>1.63</v>
-      </c>
-      <c r="AB41">
-        <v>2.36</v>
-      </c>
       <c r="AC41">
-        <v>2.58</v>
+        <v>1.5</v>
       </c>
       <c r="AD41">
-        <v>1.53</v>
+        <v>2.6</v>
       </c>
       <c r="AE41">
-        <v>1.2</v>
+        <v>1.68</v>
       </c>
       <c r="AF41">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="AG41">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="AK41">
-        <v>2.02</v>
+        <v>10</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.06</v>
+        <v>1.7</v>
       </c>
       <c r="O42">
-        <v>17</v>
+        <v>4.1</v>
       </c>
       <c r="P42">
-        <v>29</v>
+        <v>4.6</v>
       </c>
       <c r="Q42">
-        <v>1.24</v>
+        <v>2.2</v>
       </c>
       <c r="R42">
-        <v>4</v>
+        <v>2.58</v>
       </c>
       <c r="S42">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="T42">
-        <v>5.75</v>
+        <v>3.5</v>
       </c>
       <c r="U42">
-        <v>1.56</v>
+        <v>2.35</v>
       </c>
       <c r="V42">
+        <v>1.6</v>
+      </c>
+      <c r="W42">
+        <v>1.13</v>
+      </c>
+      <c r="X42">
+        <v>1.01</v>
+      </c>
+      <c r="Y42">
+        <v>1.2</v>
+      </c>
+      <c r="Z42">
+        <v>4.5</v>
+      </c>
+      <c r="AA42">
+        <v>1.59</v>
+      </c>
+      <c r="AB42">
         <v>2.25</v>
       </c>
-      <c r="W42">
-        <v>1.38</v>
-      </c>
-      <c r="X42">
-        <v>1</v>
-      </c>
-      <c r="Y42">
-        <v>1.06</v>
-      </c>
-      <c r="Z42">
-        <v>8.5</v>
-      </c>
-      <c r="AA42">
-        <v>1.18</v>
-      </c>
-      <c r="AB42">
-        <v>4.75</v>
-      </c>
       <c r="AC42">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD42">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="AE42">
-        <v>1.72</v>
+        <v>1.16</v>
       </c>
       <c r="AF42">
-        <v>2.45</v>
+        <v>1.6</v>
       </c>
       <c r="AG42">
-        <v>1.5</v>
+        <v>2.28</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="AK42">
-        <v>10</v>
+        <v>2.17</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="O43">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P43">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q43">
-        <v>2.19</v>
+        <v>2.46</v>
       </c>
       <c r="R43">
+        <v>2.31</v>
+      </c>
+      <c r="S43">
+        <v>1.32</v>
+      </c>
+      <c r="T43">
+        <v>3.28</v>
+      </c>
+      <c r="U43">
         <v>2.4</v>
       </c>
-      <c r="S43">
-        <v>1.29</v>
-      </c>
-      <c r="T43">
-        <v>3.4</v>
-      </c>
-      <c r="U43">
-        <v>2.37</v>
-      </c>
       <c r="V43">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W43">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
         <v>1.15</v>
       </c>
       <c r="Z43">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA43">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB43">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AC43">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD43">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AE43">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF43">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG43">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,61 +7481,61 @@
         </is>
       </c>
       <c r="N44">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="O44">
         <v>3.4</v>
       </c>
       <c r="P44">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q44">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="R44">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S44">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T44">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="U44">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="V44">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W44">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
         <v>1.3</v>
       </c>
       <c r="Z44">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AA44">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AB44">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC44">
-        <v>3.31</v>
+        <v>3.18</v>
       </c>
       <c r="AD44">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE44">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF44">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG44">
         <v>2.05</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AK44">
         <v>1.3</v>
@@ -7644,43 +7644,43 @@
         </is>
       </c>
       <c r="N45">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="O45">
         <v>4.6</v>
       </c>
       <c r="P45">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="Q45">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="R45">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="S45">
         <v>1.22</v>
       </c>
       <c r="T45">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U45">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V45">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W45">
         <v>1.14</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z45">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA45">
         <v>1.5</v>
@@ -7689,19 +7689,19 @@
         <v>2.62</v>
       </c>
       <c r="AC45">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AD45">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AE45">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF45">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG45">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7810,31 +7810,31 @@
         <v>13</v>
       </c>
       <c r="O46">
-        <v>7.5</v>
+        <v>7.05</v>
       </c>
       <c r="P46">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Q46">
         <v>10</v>
       </c>
       <c r="R46">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T46">
         <v>3.5</v>
       </c>
       <c r="U46">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V46">
         <v>1.56</v>
       </c>
       <c r="W46">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X46">
         <v>1.01</v>
@@ -7843,28 +7843,28 @@
         <v>1.1</v>
       </c>
       <c r="Z46">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="AA46">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AB46">
         <v>2.51</v>
       </c>
       <c r="AC46">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AD46">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE46">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF46">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AG46">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="O48">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P48">
-        <v>5.45</v>
+        <v>4.85</v>
       </c>
       <c r="Q48">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="R48">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S48">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T48">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="U48">
         <v>2.82</v>
       </c>
       <c r="V48">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W48">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y48">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="Z48">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA48">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB48">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC48">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AD48">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE48">
         <v>1.08</v>
       </c>
       <c r="AF48">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG48">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.18</v>
       </c>
       <c r="AK48">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,31 +8296,31 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.57</v>
+        <v>2.74</v>
       </c>
       <c r="O49">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="P49">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="Q49">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R49">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="S49">
         <v>1.5</v>
       </c>
       <c r="T49">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U49">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="V49">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W49">
         <v>1.01</v>
@@ -8332,25 +8332,25 @@
         <v>1.46</v>
       </c>
       <c r="Z49">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AA49">
         <v>2.4</v>
       </c>
       <c r="AB49">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AC49">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="AD49">
         <v>1.19</v>
       </c>
       <c r="AE49">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG49">
         <v>1.73</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AK49">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -8800,34 +8800,34 @@
         <v>2.3</v>
       </c>
       <c r="S52">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T52">
         <v>3.6</v>
       </c>
       <c r="U52">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V52">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W52">
+        <v>1.13</v>
+      </c>
+      <c r="X52">
+        <v>1.02</v>
+      </c>
+      <c r="Y52">
         <v>1.14</v>
       </c>
-      <c r="X52">
-        <v>1.01</v>
-      </c>
-      <c r="Y52">
-        <v>1.13</v>
-      </c>
       <c r="Z52">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="AA52">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB52">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AC52">
         <v>2.23</v>
@@ -8836,13 +8836,13 @@
         <v>1.57</v>
       </c>
       <c r="AE52">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF52">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AG52">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AK52">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8957,7 +8957,7 @@
         <v>2.8</v>
       </c>
       <c r="Q53">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R53">
         <v>2.3</v>
@@ -8969,7 +8969,7 @@
         <v>3.75</v>
       </c>
       <c r="U53">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V53">
         <v>1.6</v>
@@ -8978,7 +8978,7 @@
         <v>1.13</v>
       </c>
       <c r="X53">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
         <v>1.17</v>
@@ -8990,10 +8990,10 @@
         <v>1.57</v>
       </c>
       <c r="AB53">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="AC53">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="AD53">
         <v>1.57</v>
@@ -9021,7 +9021,7 @@
         <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,25 +9111,25 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O54">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="P54">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="Q54">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="R54">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="S54">
         <v>1.22</v>
       </c>
       <c r="T54">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="U54">
         <v>2.05</v>
@@ -9141,7 +9141,7 @@
         <v>1.17</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
         <v>1.14</v>
@@ -9162,7 +9162,7 @@
         <v>1.73</v>
       </c>
       <c r="AE54">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF54">
         <v>1.36</v>
@@ -9184,7 +9184,7 @@
         <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.04</v>
+        <v>2.5</v>
       </c>
       <c r="O55">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P55">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="Q55">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="R55">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S55">
         <v>1.3</v>
       </c>
       <c r="T55">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U55">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V55">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W55">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y55">
         <v>1.2</v>
       </c>
       <c r="Z55">
-        <v>4.54</v>
+        <v>4.2</v>
       </c>
       <c r="AA55">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AB55">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AC55">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="AD55">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE55">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF55">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG55">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AK55">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="O56">
         <v>3.5</v>
       </c>
       <c r="P56">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="Q56">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="R56">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S56">
         <v>1.3</v>
       </c>
       <c r="T56">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U56">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V56">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W56">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X56">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z56">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AA56">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB56">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC56">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="AD56">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE56">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF56">
         <v>1.53</v>
       </c>
       <c r="AG56">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AK56">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="O57">
         <v>3.2</v>
@@ -9612,25 +9612,25 @@
         <v>2.95</v>
       </c>
       <c r="R57">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S57">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T57">
+        <v>2.7</v>
+      </c>
+      <c r="U57">
         <v>2.85</v>
       </c>
-      <c r="U57">
-        <v>2.62</v>
-      </c>
       <c r="V57">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W57">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
         <v>1.26</v>
@@ -9645,19 +9645,19 @@
         <v>1.83</v>
       </c>
       <c r="AC57">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AD57">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE57">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF57">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG57">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK57">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,16 +9763,16 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="O58">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P58">
         <v>2.6</v>
       </c>
       <c r="Q58">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="R58">
         <v>2.05</v>
@@ -9781,7 +9781,7 @@
         <v>1.37</v>
       </c>
       <c r="T58">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="U58">
         <v>2.8</v>
@@ -9790,34 +9790,34 @@
         <v>1.38</v>
       </c>
       <c r="W58">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X58">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z58">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA58">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AB58">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AC58">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AD58">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE58">
         <v>1.07</v>
       </c>
       <c r="AF58">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG58">
         <v>2.02</v>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
         <v>1.44</v>
@@ -9926,10 +9926,10 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="O59">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="P59">
         <v>3.9</v>
@@ -12697,10 +12697,10 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="O76">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="P76">
         <v>2.65</v>
@@ -12911,7 +12911,7 @@
         <v>1.4</v>
       </c>
       <c r="AE77">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF77">
         <v>1.66</v>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="O78">
-        <v>4.21</v>
+        <v>4.26</v>
       </c>
       <c r="P78">
         <v>2.97</v>
@@ -13035,13 +13035,13 @@
         <v>2.5</v>
       </c>
       <c r="R78">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="S78">
         <v>1.14</v>
       </c>
       <c r="T78">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="U78">
         <v>1.77</v>
@@ -13059,13 +13059,13 @@
         <v>1.07</v>
       </c>
       <c r="Z78">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AA78">
         <v>1.25</v>
       </c>
       <c r="AB78">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="AC78">
         <v>1.65</v>
@@ -13077,7 +13077,7 @@
         <v>1.5</v>
       </c>
       <c r="AF78">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AG78">
         <v>3.55</v>
@@ -13201,16 +13201,16 @@
         <v>2.22</v>
       </c>
       <c r="S79">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T79">
         <v>3.6</v>
       </c>
       <c r="U79">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="V79">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W79">
         <v>1.11</v>
@@ -13225,7 +13225,7 @@
         <v>4.5</v>
       </c>
       <c r="AA79">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB79">
         <v>2.15</v>
@@ -13349,16 +13349,16 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="O80">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P80">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q80">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="R80">
         <v>2.5</v>
@@ -13367,16 +13367,16 @@
         <v>1.25</v>
       </c>
       <c r="T80">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="U80">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="V80">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W80">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X80">
         <v>1.03</v>
@@ -13397,13 +13397,13 @@
         <v>2.35</v>
       </c>
       <c r="AD80">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE80">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF80">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG80">
         <v>2.55</v>
@@ -13512,61 +13512,61 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="O81">
         <v>3.25</v>
       </c>
       <c r="P81">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q81">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R81">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S81">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T81">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="U81">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="V81">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W81">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X81">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y81">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z81">
         <v>2.88</v>
       </c>
       <c r="AA81">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB81">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC81">
         <v>4.33</v>
       </c>
       <c r="AD81">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE81">
         <v>1.03</v>
       </c>
       <c r="AF81">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG81">
         <v>1.72</v>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK81">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13678,10 +13678,10 @@
         <v>1.8</v>
       </c>
       <c r="O82">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="P82">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="Q82">
         <v>2.2</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK82">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="O83">
         <v>5</v>
       </c>
       <c r="P83">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Q83">
         <v>1.62</v>
@@ -13865,7 +13865,7 @@
         <v>1.8</v>
       </c>
       <c r="W83">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X83">
         <v>1.01</v>
@@ -13886,16 +13886,16 @@
         <v>1.9</v>
       </c>
       <c r="AD83">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AE83">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AF83">
         <v>1.62</v>
       </c>
       <c r="AG83">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.14</v>
       </c>
       <c r="AK83">
-        <v>2.98</v>
+        <v>2.89</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14007,19 +14007,19 @@
         <v>5</v>
       </c>
       <c r="P84">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q84">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="R84">
         <v>2.7</v>
       </c>
       <c r="S84">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T84">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U84">
         <v>1.95</v>
@@ -14034,7 +14034,7 @@
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z84">
         <v>7.5</v>
@@ -14052,7 +14052,7 @@
         <v>1.83</v>
       </c>
       <c r="AE84">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AF84">
         <v>1.47</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="O85">
-        <v>3.77</v>
+        <v>3.7</v>
       </c>
       <c r="P85">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="Q85">
         <v>2.79</v>
@@ -14182,16 +14182,16 @@
         <v>1.22</v>
       </c>
       <c r="T85">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U85">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V85">
         <v>1.66</v>
       </c>
       <c r="W85">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X85">
         <v>1.01</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.52</v>
+        <v>2.39</v>
       </c>
       <c r="O2">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
         <v>2.65</v>
@@ -647,7 +647,7 @@
         <v>3.28</v>
       </c>
       <c r="R2">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S2">
         <v>1.4</v>
@@ -656,7 +656,7 @@
         <v>2.75</v>
       </c>
       <c r="U2">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="V2">
         <v>1.32</v>
@@ -674,13 +674,13 @@
         <v>2.9</v>
       </c>
       <c r="AA2">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AB2">
         <v>1.68</v>
       </c>
       <c r="AC2">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AD2">
         <v>1.2</v>
@@ -689,7 +689,7 @@
         <v>1.03</v>
       </c>
       <c r="AF2">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG2">
         <v>1.85</v>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="O3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
         <v>2.95</v>
       </c>
       <c r="Q3">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="R3">
         <v>2.1</v>
@@ -822,7 +822,7 @@
         <v>2.89</v>
       </c>
       <c r="V3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
         <v>1.05</v>
@@ -837,7 +837,7 @@
         <v>3.15</v>
       </c>
       <c r="AA3">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AB3">
         <v>1.67</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Q4">
         <v>4.64</v>
@@ -976,10 +976,10 @@
         <v>2.08</v>
       </c>
       <c r="S4">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T4">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="U4">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
         <v>1.33</v>
@@ -1009,13 +1009,13 @@
         <v>3.6</v>
       </c>
       <c r="AD4">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE4">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG4">
         <v>1.86</v>
@@ -1133,25 +1133,25 @@
         <v>4.85</v>
       </c>
       <c r="Q5">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="R5">
         <v>2.27</v>
       </c>
       <c r="S5">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T5">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U5">
         <v>2.5</v>
       </c>
       <c r="V5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
         <v>1.02</v>
@@ -1160,22 +1160,22 @@
         <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="AA5">
         <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC5">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="AD5">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE5">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF5">
         <v>1.8</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="O8">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="P8">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="Q8">
         <v>4.11</v>
@@ -1655,7 +1655,7 @@
         <v>2.83</v>
       </c>
       <c r="AB8">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AC8">
         <v>6.05</v>
@@ -1800,19 +1800,19 @@
         <v>3.38</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="W9">
         <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y9">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z9">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AA9">
         <v>2.34</v>
@@ -1827,7 +1827,7 @@
         <v>1.15</v>
       </c>
       <c r="AE9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
         <v>2.7</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK9">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N10">
@@ -1945,10 +1945,10 @@
         <v>4.95</v>
       </c>
       <c r="P10">
-        <v>12.9</v>
+        <v>10.8</v>
       </c>
       <c r="Q10">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R10">
         <v>2.6</v>
@@ -1972,13 +1972,13 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z10">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AA10">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB10">
         <v>2.15</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2757,28 +2757,28 @@
         <v>1.85</v>
       </c>
       <c r="O15">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
         <v>3.6</v>
       </c>
       <c r="Q15">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="R15">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="S15">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T15">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="U15">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="V15">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W15">
         <v>1.05</v>
@@ -2787,47 +2787,47 @@
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z15">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AA15">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AB15">
+        <v>1.75</v>
+      </c>
+      <c r="AC15">
+        <v>3.28</v>
+      </c>
+      <c r="AD15">
+        <v>1.25</v>
+      </c>
+      <c r="AE15">
+        <v>1.06</v>
+      </c>
+      <c r="AF15">
+        <v>1.78</v>
+      </c>
+      <c r="AG15">
+        <v>1.89</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>1.24</v>
+      </c>
+      <c r="AK15">
         <v>1.7</v>
-      </c>
-      <c r="AC15">
-        <v>3.42</v>
-      </c>
-      <c r="AD15">
-        <v>1.23</v>
-      </c>
-      <c r="AE15">
-        <v>1.05</v>
-      </c>
-      <c r="AF15">
-        <v>1.73</v>
-      </c>
-      <c r="AG15">
-        <v>1.93</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.25</v>
-      </c>
-      <c r="AK15">
-        <v>1.83</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2932,10 +2932,10 @@
         <v>2.2</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U16">
         <v>2.45</v>
@@ -2947,19 +2947,19 @@
         <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z16">
         <v>4.2</v>
       </c>
       <c r="AA16">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB16">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AC16">
         <v>2.74</v>
@@ -2974,7 +2974,7 @@
         <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.54</v>
       </c>
       <c r="AK16">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
+        <v>3.8</v>
+      </c>
+      <c r="O18">
+        <v>3.75</v>
+      </c>
+      <c r="P18">
+        <v>1.7</v>
+      </c>
+      <c r="Q18">
+        <v>4.3</v>
+      </c>
+      <c r="R18">
+        <v>2.48</v>
+      </c>
+      <c r="S18">
+        <v>1.25</v>
+      </c>
+      <c r="T18">
+        <v>3.34</v>
+      </c>
+      <c r="U18">
+        <v>2.2</v>
+      </c>
+      <c r="V18">
+        <v>1.57</v>
+      </c>
+      <c r="W18">
+        <v>1.14</v>
+      </c>
+      <c r="X18">
+        <v>1.03</v>
+      </c>
+      <c r="Y18">
         <v>1.13</v>
       </c>
-      <c r="O18">
-        <v>6.5</v>
-      </c>
-      <c r="P18">
-        <v>15.5</v>
-      </c>
-      <c r="Q18">
-        <v>1.41</v>
-      </c>
-      <c r="R18">
-        <v>3.4</v>
-      </c>
-      <c r="S18">
-        <v>1.14</v>
-      </c>
-      <c r="T18">
-        <v>4.3</v>
-      </c>
-      <c r="U18">
-        <v>1.87</v>
-      </c>
-      <c r="V18">
-        <v>1.83</v>
-      </c>
-      <c r="W18">
+      <c r="Z18">
+        <v>4.6</v>
+      </c>
+      <c r="AA18">
+        <v>1.6</v>
+      </c>
+      <c r="AB18">
+        <v>2.26</v>
+      </c>
+      <c r="AC18">
+        <v>2.34</v>
+      </c>
+      <c r="AD18">
+        <v>1.57</v>
+      </c>
+      <c r="AE18">
+        <v>1.18</v>
+      </c>
+      <c r="AF18">
+        <v>1.53</v>
+      </c>
+      <c r="AG18">
+        <v>2.3</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.25</v>
+      </c>
+      <c r="AK18">
         <v>1.22</v>
-      </c>
-      <c r="X18">
-        <v>1.01</v>
-      </c>
-      <c r="Y18">
-        <v>1.05</v>
-      </c>
-      <c r="Z18">
-        <v>6.55</v>
-      </c>
-      <c r="AA18">
-        <v>1.33</v>
-      </c>
-      <c r="AB18">
-        <v>3.2</v>
-      </c>
-      <c r="AC18">
-        <v>1.77</v>
-      </c>
-      <c r="AD18">
-        <v>1.99</v>
-      </c>
-      <c r="AE18">
-        <v>1.39</v>
-      </c>
-      <c r="AF18">
-        <v>1.95</v>
-      </c>
-      <c r="AG18">
-        <v>1.75</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.06</v>
-      </c>
-      <c r="AK18">
-        <v>5.5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.8</v>
+        <v>1.13</v>
       </c>
       <c r="O19">
-        <v>3.75</v>
+        <v>6.5</v>
       </c>
       <c r="P19">
-        <v>1.7</v>
+        <v>15.5</v>
       </c>
       <c r="Q19">
+        <v>1.41</v>
+      </c>
+      <c r="R19">
+        <v>3.4</v>
+      </c>
+      <c r="S19">
+        <v>1.14</v>
+      </c>
+      <c r="T19">
         <v>4.3</v>
       </c>
-      <c r="R19">
-        <v>2.48</v>
-      </c>
-      <c r="S19">
-        <v>1.25</v>
-      </c>
-      <c r="T19">
-        <v>3.34</v>
-      </c>
       <c r="U19">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="V19">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="W19">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Z19">
-        <v>4.6</v>
+        <v>6.55</v>
       </c>
       <c r="AA19">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AB19">
-        <v>2.26</v>
+        <v>3.2</v>
       </c>
       <c r="AC19">
-        <v>2.34</v>
+        <v>1.77</v>
       </c>
       <c r="AD19">
-        <v>1.57</v>
+        <v>1.99</v>
       </c>
       <c r="AE19">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="AF19">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AG19">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK19">
-        <v>1.22</v>
+        <v>5.5</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3741,16 +3741,16 @@
         <v>10</v>
       </c>
       <c r="Q21">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R21">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="S21">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T21">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="U21">
         <v>1.81</v>
@@ -3768,25 +3768,25 @@
         <v>1.04</v>
       </c>
       <c r="Z21">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="AA21">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AB21">
         <v>3.7</v>
       </c>
       <c r="AC21">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AD21">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AE21">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AF21">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
         <v>2.3</v>
@@ -3805,7 +3805,7 @@
         <v>1.13</v>
       </c>
       <c r="AK21">
-        <v>4.24</v>
+        <v>3.8</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,7 +3904,7 @@
         <v>25</v>
       </c>
       <c r="Q22">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R22">
         <v>4</v>
@@ -3916,10 +3916,10 @@
         <v>6.7</v>
       </c>
       <c r="U22">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="V22">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="W22">
         <v>1.36</v>
@@ -3940,13 +3940,13 @@
         <v>5</v>
       </c>
       <c r="AC22">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AD22">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AE22">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AF22">
         <v>1.75</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4894,7 +4894,7 @@
         <v>3.05</v>
       </c>
       <c r="U28">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="V28">
         <v>1.45</v>
@@ -4903,22 +4903,22 @@
         <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z28">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="AA28">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB28">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC28">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="AD28">
         <v>1.36</v>
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="O29">
         <v>3.8</v>
       </c>
       <c r="P29">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q29">
         <v>2.26</v>
       </c>
       <c r="R29">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S29">
         <v>1.25</v>
@@ -5093,7 +5093,7 @@
         <v>1.56</v>
       </c>
       <c r="AG29">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>3.5</v>
       </c>
       <c r="P30">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q30">
         <v>2.4</v>
@@ -5220,13 +5220,13 @@
         <v>3.4</v>
       </c>
       <c r="U30">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V30">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
         <v>1.04</v>
@@ -5241,10 +5241,10 @@
         <v>1.61</v>
       </c>
       <c r="AB30">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AC30">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AD30">
         <v>1.49</v>
@@ -5256,7 +5256,7 @@
         <v>1.53</v>
       </c>
       <c r="AG30">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="O31">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="P31">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q31">
         <v>2.62</v>
       </c>
       <c r="R31">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="S31">
         <v>1.3</v>
@@ -5392,16 +5392,16 @@
         <v>1.09</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z31">
-        <v>4.7</v>
+        <v>4.42</v>
       </c>
       <c r="AA31">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB31">
         <v>2.16</v>
@@ -5413,7 +5413,7 @@
         <v>1.44</v>
       </c>
       <c r="AE31">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF31">
         <v>1.55</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK31">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="N34">
+        <v>3.75</v>
+      </c>
+      <c r="O34">
         <v>3.73</v>
-      </c>
-      <c r="O34">
-        <v>3.75</v>
       </c>
       <c r="P34">
         <v>1.9</v>
@@ -5884,7 +5884,7 @@
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z34">
         <v>4.5</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="O35">
-        <v>6.91</v>
+        <v>7.47</v>
       </c>
       <c r="P35">
-        <v>13.8</v>
+        <v>11.34</v>
       </c>
       <c r="Q35">
         <v>1.55</v>
@@ -6035,10 +6035,10 @@
         <v>4.8</v>
       </c>
       <c r="U35">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="V35">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W35">
         <v>1.19</v>
@@ -6047,10 +6047,10 @@
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Z35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA35">
         <v>1.28</v>
@@ -6062,13 +6062,13 @@
         <v>1.82</v>
       </c>
       <c r="AD35">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AE35">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AF35">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG35">
         <v>2</v>
@@ -6177,28 +6177,28 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="O36">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P36">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q36">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="R36">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="S36">
         <v>1.65</v>
       </c>
       <c r="T36">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="U36">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="V36">
         <v>1.2</v>
@@ -6207,34 +6207,34 @@
         <v>1.03</v>
       </c>
       <c r="X36">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y36">
         <v>1.54</v>
       </c>
       <c r="Z36">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AA36">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AB36">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AC36">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AD36">
         <v>1.08</v>
       </c>
       <c r="AE36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF36">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AG36">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AK36">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="O37">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P37">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -6361,7 +6361,7 @@
         <v>3.3</v>
       </c>
       <c r="U37">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="V37">
         <v>1.48</v>
@@ -6376,13 +6376,13 @@
         <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="AA37">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB37">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC37">
         <v>2.68</v>
@@ -6391,13 +6391,13 @@
         <v>1.34</v>
       </c>
       <c r="AE37">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF37">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="O38">
         <v>3.4</v>
@@ -6512,10 +6512,10 @@
         <v>2.4</v>
       </c>
       <c r="Q38">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R38">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S38">
         <v>1.32</v>
@@ -6524,13 +6524,13 @@
         <v>3</v>
       </c>
       <c r="U38">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="V38">
         <v>1.42</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
         <v>1.05</v>
@@ -6542,7 +6542,7 @@
         <v>3.45</v>
       </c>
       <c r="AA38">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AB38">
         <v>1.87</v>
@@ -6557,7 +6557,7 @@
         <v>1.11</v>
       </c>
       <c r="AF38">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG38">
         <v>2.05</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK38">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.54</v>
+        <v>4.99</v>
       </c>
       <c r="O40">
         <v>3.78</v>
       </c>
       <c r="P40">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="Q40">
         <v>5.2</v>
@@ -6865,7 +6865,7 @@
         <v>1.3</v>
       </c>
       <c r="Z40">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AA40">
         <v>1.94</v>
@@ -6874,7 +6874,7 @@
         <v>1.88</v>
       </c>
       <c r="AC40">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD40">
         <v>1.33</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AK40">
         <v>1.18</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="O41">
         <v>17</v>
@@ -7043,7 +7043,7 @@
         <v>2.6</v>
       </c>
       <c r="AE41">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AF41">
         <v>2.5</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="O43">
         <v>3.8</v>
@@ -7327,7 +7327,7 @@
         <v>3.7</v>
       </c>
       <c r="Q43">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="R43">
         <v>2.31</v>
@@ -7369,7 +7369,7 @@
         <v>1.47</v>
       </c>
       <c r="AE43">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF43">
         <v>1.62</v>
@@ -7490,7 +7490,7 @@
         <v>2.3</v>
       </c>
       <c r="Q44">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="R44">
         <v>2.06</v>
@@ -7529,16 +7529,16 @@
         <v>3.18</v>
       </c>
       <c r="AD44">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE44">
         <v>1.06</v>
       </c>
       <c r="AF44">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG44">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK44">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="O47">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P47">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q47">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="R47">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S47">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T47">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U47">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="V47">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W47">
+        <v>1.05</v>
+      </c>
+      <c r="X47">
         <v>1.03</v>
       </c>
-      <c r="X47">
-        <v>1.05</v>
-      </c>
       <c r="Y47">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z47">
         <v>2.74</v>
       </c>
       <c r="AA47">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AB47">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC47">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD47">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE47">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF47">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG47">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK47">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O50">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P50">
         <v>3.05</v>
       </c>
       <c r="Q50">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="R50">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
         <v>1.33</v>
       </c>
       <c r="T50">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U50">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V50">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y50">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z50">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA50">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB50">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC50">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AD50">
         <v>1.36</v>
       </c>
       <c r="AE50">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF50">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG50">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
         <v>1.59</v>
@@ -8622,52 +8622,52 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="O51">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P51">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q51">
+        <v>2.23</v>
+      </c>
+      <c r="R51">
         <v>2.17</v>
       </c>
-      <c r="R51">
-        <v>2.16</v>
-      </c>
       <c r="S51">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T51">
-        <v>2.97</v>
+        <v>2.77</v>
       </c>
       <c r="U51">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="V51">
         <v>1.43</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA51">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB51">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AC51">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AD51">
         <v>1.29</v>
@@ -8676,7 +8676,7 @@
         <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG51">
         <v>1.91</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AK51">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8960,22 +8960,22 @@
         <v>2.45</v>
       </c>
       <c r="R53">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S53">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T53">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U53">
         <v>2.31</v>
       </c>
       <c r="V53">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W53">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X53">
         <v>1.01</v>
@@ -8987,10 +8987,10 @@
         <v>5</v>
       </c>
       <c r="AA53">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB53">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AC53">
         <v>2.41</v>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK53">
         <v>1.6</v>
@@ -9132,7 +9132,7 @@
         <v>3.9</v>
       </c>
       <c r="U54">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="V54">
         <v>1.62</v>
@@ -9446,10 +9446,10 @@
         <v>2.25</v>
       </c>
       <c r="Q56">
-        <v>3.14</v>
+        <v>3.49</v>
       </c>
       <c r="R56">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="S56">
         <v>1.3</v>
@@ -9458,10 +9458,10 @@
         <v>3.4</v>
       </c>
       <c r="U56">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V56">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W56">
         <v>1.1</v>
@@ -9476,10 +9476,10 @@
         <v>4.5</v>
       </c>
       <c r="AA56">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB56">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC56">
         <v>2.48</v>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="O59">
         <v>4.2</v>
@@ -9938,7 +9938,7 @@
         <v>2.1</v>
       </c>
       <c r="R59">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="S59">
         <v>1.19</v>
@@ -9965,10 +9965,10 @@
         <v>7.5</v>
       </c>
       <c r="AA59">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AB59">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AC59">
         <v>1.9</v>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N75">
@@ -12872,7 +12872,7 @@
         <v>3.1</v>
       </c>
       <c r="R77">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S77">
         <v>1.32</v>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK77">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,19 +13023,19 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="O78">
         <v>4.26</v>
       </c>
       <c r="P78">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="Q78">
         <v>2.5</v>
       </c>
       <c r="R78">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="S78">
         <v>1.14</v>
@@ -13044,13 +13044,13 @@
         <v>5.25</v>
       </c>
       <c r="U78">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="V78">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="W78">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X78">
         <v>1.01</v>
@@ -13059,7 +13059,7 @@
         <v>1.07</v>
       </c>
       <c r="Z78">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="AA78">
         <v>1.25</v>
@@ -13080,7 +13080,7 @@
         <v>1.23</v>
       </c>
       <c r="AG78">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13201,16 +13201,16 @@
         <v>2.22</v>
       </c>
       <c r="S79">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T79">
         <v>3.6</v>
       </c>
       <c r="U79">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="V79">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W79">
         <v>1.11</v>
@@ -13225,7 +13225,7 @@
         <v>4.5</v>
       </c>
       <c r="AA79">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB79">
         <v>2.15</v>
@@ -13243,7 +13243,7 @@
         <v>1.62</v>
       </c>
       <c r="AG79">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>3.75</v>
       </c>
       <c r="U80">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="V80">
         <v>1.61</v>
@@ -13400,13 +13400,13 @@
         <v>1.57</v>
       </c>
       <c r="AE80">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF80">
         <v>1.44</v>
       </c>
       <c r="AG80">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13681,19 +13681,19 @@
         <v>3.8</v>
       </c>
       <c r="P82">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
       <c r="Q82">
         <v>2.2</v>
       </c>
       <c r="R82">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S82">
         <v>1.2</v>
       </c>
       <c r="T82">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U82">
         <v>2</v>
@@ -13708,25 +13708,25 @@
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z82">
-        <v>6.31</v>
+        <v>6.41</v>
       </c>
       <c r="AA82">
         <v>1.4</v>
       </c>
       <c r="AB82">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="AC82">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD82">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE82">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AF82">
         <v>1.4</v>
@@ -13844,16 +13844,16 @@
         <v>5</v>
       </c>
       <c r="P83">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q83">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="R83">
         <v>2.8</v>
       </c>
       <c r="S83">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T83">
         <v>4.33</v>
@@ -13862,10 +13862,10 @@
         <v>1.91</v>
       </c>
       <c r="V83">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="W83">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X83">
         <v>1.01</v>
@@ -13883,13 +13883,13 @@
         <v>3.1</v>
       </c>
       <c r="AC83">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD83">
         <v>1.76</v>
       </c>
       <c r="AE83">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AF83">
         <v>1.62</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK83">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="O84">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="P84">
-        <v>6.4</v>
+        <v>6.55</v>
       </c>
       <c r="Q84">
         <v>1.81</v>
@@ -14016,7 +14016,7 @@
         <v>2.7</v>
       </c>
       <c r="S84">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T84">
         <v>4.5</v>
@@ -14046,13 +14046,13 @@
         <v>3.13</v>
       </c>
       <c r="AC84">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AD84">
         <v>1.83</v>
       </c>
       <c r="AE84">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AF84">
         <v>1.47</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="O85">
         <v>3.7</v>
       </c>
       <c r="P85">
-        <v>2.68</v>
+        <v>2.95</v>
       </c>
       <c r="Q85">
         <v>2.79</v>
@@ -14182,13 +14182,13 @@
         <v>1.22</v>
       </c>
       <c r="T85">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U85">
         <v>2.16</v>
       </c>
       <c r="V85">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W85">
         <v>1.14</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,80 +2265,80 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="O12">
         <v>3.15</v>
       </c>
       <c r="P12">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="Q12">
+        <v>3.8</v>
+      </c>
+      <c r="R12">
+        <v>2.1</v>
+      </c>
+      <c r="S12">
+        <v>1.36</v>
+      </c>
+      <c r="T12">
+        <v>2.75</v>
+      </c>
+      <c r="U12">
+        <v>2.79</v>
+      </c>
+      <c r="V12">
+        <v>1.35</v>
+      </c>
+      <c r="W12">
+        <v>1.06</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+      <c r="Y12">
+        <v>1.29</v>
+      </c>
+      <c r="Z12">
+        <v>3.25</v>
+      </c>
+      <c r="AA12">
+        <v>1.91</v>
+      </c>
+      <c r="AB12">
+        <v>1.75</v>
+      </c>
+      <c r="AC12">
         <v>3.3</v>
       </c>
-      <c r="R12">
-        <v>2.2</v>
-      </c>
-      <c r="S12">
+      <c r="AD12">
+        <v>1.25</v>
+      </c>
+      <c r="AE12">
+        <v>1.06</v>
+      </c>
+      <c r="AF12">
+        <v>1.73</v>
+      </c>
+      <c r="AG12">
+        <v>1.95</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
         <v>1.33</v>
       </c>
-      <c r="T12">
-        <v>2.89</v>
-      </c>
-      <c r="U12">
-        <v>2.5</v>
-      </c>
-      <c r="V12">
-        <v>1.4</v>
-      </c>
-      <c r="W12">
-        <v>1.08</v>
-      </c>
-      <c r="X12">
-        <v>1.04</v>
-      </c>
-      <c r="Y12">
-        <v>1.25</v>
-      </c>
-      <c r="Z12">
-        <v>3.6</v>
-      </c>
-      <c r="AA12">
-        <v>1.8</v>
-      </c>
-      <c r="AB12">
-        <v>1.85</v>
-      </c>
-      <c r="AC12">
-        <v>2.9</v>
-      </c>
-      <c r="AD12">
-        <v>1.33</v>
-      </c>
-      <c r="AE12">
-        <v>1.11</v>
-      </c>
-      <c r="AF12">
-        <v>1.62</v>
-      </c>
-      <c r="AG12">
-        <v>2.1</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
+      <c r="AK12">
         <v>1.3</v>
-      </c>
-      <c r="AK12">
-        <v>1.33</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,65 +2428,65 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="O13">
         <v>3.15</v>
       </c>
       <c r="P13">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="Q13">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R13">
+        <v>2.2</v>
+      </c>
+      <c r="S13">
+        <v>1.33</v>
+      </c>
+      <c r="T13">
+        <v>2.89</v>
+      </c>
+      <c r="U13">
+        <v>2.5</v>
+      </c>
+      <c r="V13">
+        <v>1.4</v>
+      </c>
+      <c r="W13">
+        <v>1.08</v>
+      </c>
+      <c r="X13">
+        <v>1.04</v>
+      </c>
+      <c r="Y13">
+        <v>1.25</v>
+      </c>
+      <c r="Z13">
+        <v>3.6</v>
+      </c>
+      <c r="AA13">
+        <v>1.8</v>
+      </c>
+      <c r="AB13">
+        <v>1.85</v>
+      </c>
+      <c r="AC13">
+        <v>2.9</v>
+      </c>
+      <c r="AD13">
+        <v>1.33</v>
+      </c>
+      <c r="AE13">
+        <v>1.11</v>
+      </c>
+      <c r="AF13">
+        <v>1.62</v>
+      </c>
+      <c r="AG13">
         <v>2.1</v>
       </c>
-      <c r="S13">
-        <v>1.36</v>
-      </c>
-      <c r="T13">
-        <v>2.75</v>
-      </c>
-      <c r="U13">
-        <v>2.79</v>
-      </c>
-      <c r="V13">
-        <v>1.35</v>
-      </c>
-      <c r="W13">
-        <v>1.06</v>
-      </c>
-      <c r="X13">
-        <v>1</v>
-      </c>
-      <c r="Y13">
-        <v>1.29</v>
-      </c>
-      <c r="Z13">
-        <v>3.25</v>
-      </c>
-      <c r="AA13">
-        <v>1.91</v>
-      </c>
-      <c r="AB13">
-        <v>1.75</v>
-      </c>
-      <c r="AC13">
-        <v>3.3</v>
-      </c>
-      <c r="AD13">
-        <v>1.25</v>
-      </c>
-      <c r="AE13">
-        <v>1.06</v>
-      </c>
-      <c r="AF13">
-        <v>1.73</v>
-      </c>
-      <c r="AG13">
-        <v>1.95</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
+        <v>1.3</v>
+      </c>
+      <c r="AK13">
         <v>1.33</v>
-      </c>
-      <c r="AK13">
-        <v>1.3</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
+        <v>2.2</v>
+      </c>
+      <c r="O19">
+        <v>3.55</v>
+      </c>
+      <c r="P19">
+        <v>2.6</v>
+      </c>
+      <c r="Q19">
+        <v>2.91</v>
+      </c>
+      <c r="R19">
+        <v>2.41</v>
+      </c>
+      <c r="S19">
+        <v>1.25</v>
+      </c>
+      <c r="T19">
+        <v>3.45</v>
+      </c>
+      <c r="U19">
+        <v>2.17</v>
+      </c>
+      <c r="V19">
+        <v>1.64</v>
+      </c>
+      <c r="W19">
         <v>1.13</v>
-      </c>
-      <c r="O19">
-        <v>6.5</v>
-      </c>
-      <c r="P19">
-        <v>15.5</v>
-      </c>
-      <c r="Q19">
-        <v>1.41</v>
-      </c>
-      <c r="R19">
-        <v>3.4</v>
-      </c>
-      <c r="S19">
-        <v>1.14</v>
-      </c>
-      <c r="T19">
-        <v>4.3</v>
-      </c>
-      <c r="U19">
-        <v>1.87</v>
-      </c>
-      <c r="V19">
-        <v>1.83</v>
-      </c>
-      <c r="W19">
-        <v>1.22</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Z19">
-        <v>6.55</v>
+        <v>4.7</v>
       </c>
       <c r="AA19">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AB19">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="AC19">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="AD19">
-        <v>1.99</v>
+        <v>1.5</v>
       </c>
       <c r="AE19">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="AF19">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AG19">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="AK19">
-        <v>5.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.2</v>
+        <v>1.13</v>
       </c>
       <c r="O20">
-        <v>3.55</v>
+        <v>6.5</v>
       </c>
       <c r="P20">
-        <v>2.6</v>
+        <v>15.5</v>
       </c>
       <c r="Q20">
-        <v>2.91</v>
+        <v>1.41</v>
       </c>
       <c r="R20">
-        <v>2.41</v>
+        <v>3.4</v>
       </c>
       <c r="S20">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="T20">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="U20">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="V20">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Z20">
-        <v>4.7</v>
+        <v>6.55</v>
       </c>
       <c r="AA20">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AB20">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="AC20">
-        <v>2.38</v>
+        <v>1.77</v>
       </c>
       <c r="AD20">
-        <v>1.5</v>
+        <v>1.99</v>
       </c>
       <c r="AE20">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="AF20">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AG20">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.38</v>
+        <v>1.06</v>
       </c>
       <c r="AK20">
-        <v>1.55</v>
+        <v>5.5</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -7979,16 +7979,16 @@
         <v>2.75</v>
       </c>
       <c r="Q47">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="R47">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S47">
         <v>1.44</v>
       </c>
       <c r="T47">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U47">
         <v>3.08</v>
@@ -8000,7 +8000,7 @@
         <v>1.05</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y47">
         <v>1.29</v>
@@ -8018,7 +8018,7 @@
         <v>4</v>
       </c>
       <c r="AD47">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE47">
         <v>1.06</v>
@@ -8043,7 +8043,7 @@
         <v>1.36</v>
       </c>
       <c r="AK47">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="O48">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P48">
-        <v>4.85</v>
+        <v>5.45</v>
       </c>
       <c r="Q48">
         <v>2.02</v>
@@ -8151,7 +8151,7 @@
         <v>1.42</v>
       </c>
       <c r="T48">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="U48">
         <v>2.82</v>
@@ -8160,7 +8160,7 @@
         <v>1.33</v>
       </c>
       <c r="W48">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X48">
         <v>1.06</v>
@@ -8172,13 +8172,13 @@
         <v>3</v>
       </c>
       <c r="AA48">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AB48">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC48">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AD48">
         <v>1.22</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK48">
         <v>2.29</v>
@@ -8296,10 +8296,10 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="O49">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P49">
         <v>2.4</v>
@@ -8332,16 +8332,16 @@
         <v>1.46</v>
       </c>
       <c r="Z49">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AA49">
         <v>2.4</v>
       </c>
       <c r="AB49">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AC49">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AD49">
         <v>1.19</v>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AK49">
         <v>1.4</v>
@@ -8474,13 +8474,13 @@
         <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T50">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="U50">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V50">
         <v>1.42</v>
@@ -8495,10 +8495,10 @@
         <v>1.29</v>
       </c>
       <c r="Z50">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA50">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB50">
         <v>1.95</v>
@@ -8510,7 +8510,7 @@
         <v>1.36</v>
       </c>
       <c r="AE50">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF50">
         <v>1.62</v>
@@ -8622,40 +8622,40 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="O51">
         <v>3.7</v>
       </c>
       <c r="P51">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="Q51">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="R51">
         <v>2.17</v>
       </c>
       <c r="S51">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T51">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="U51">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="V51">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
         <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
         <v>3.6</v>
@@ -8664,19 +8664,19 @@
         <v>1.8</v>
       </c>
       <c r="AB51">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AC51">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD51">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE51">
         <v>1.07</v>
       </c>
       <c r="AF51">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG51">
         <v>1.91</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
         <v>2.2</v>
@@ -9600,16 +9600,16 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="O57">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P57">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="Q57">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="R57">
         <v>2.05</v>
@@ -9633,16 +9633,16 @@
         <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z57">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA57">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB57">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC57">
         <v>3.45</v>
@@ -9673,7 +9673,7 @@
         <v>1.36</v>
       </c>
       <c r="AK57">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9769,7 +9769,7 @@
         <v>3.05</v>
       </c>
       <c r="P58">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q58">
         <v>3.2</v>
@@ -9781,43 +9781,43 @@
         <v>1.37</v>
       </c>
       <c r="T58">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U58">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="V58">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W58">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y58">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z58">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AA58">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB58">
         <v>1.75</v>
       </c>
       <c r="AC58">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD58">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE58">
         <v>1.07</v>
       </c>
       <c r="AF58">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG58">
         <v>2.02</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="O81">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P81">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="Q81">
         <v>2.52</v>
@@ -13566,7 +13566,7 @@
         <v>1.03</v>
       </c>
       <c r="AF81">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG81">
         <v>1.72</v>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="AK81">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AL81">
         <v>0</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -1613,52 +1613,52 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="O8">
         <v>2.75</v>
       </c>
       <c r="P8">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q8">
-        <v>4.11</v>
+        <v>4.39</v>
       </c>
       <c r="R8">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="S8">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="T8">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="U8">
         <v>4.33</v>
       </c>
       <c r="V8">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W8">
         <v>1.01</v>
       </c>
       <c r="X8">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Y8">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="Z8">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AA8">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AB8">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC8">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="AD8">
         <v>1.06</v>
@@ -1667,7 +1667,7 @@
         <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="AG8">
         <v>1.55</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AK8">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="O9">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P9">
-        <v>7</v>
+        <v>7.97</v>
       </c>
       <c r="Q9">
         <v>2.01</v>
@@ -1791,7 +1791,7 @@
         <v>2.05</v>
       </c>
       <c r="S9">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="T9">
         <v>2.33</v>
@@ -1800,19 +1800,19 @@
         <v>3.38</v>
       </c>
       <c r="V9">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
         <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z9">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="AA9">
         <v>2.34</v>
@@ -1821,16 +1821,16 @@
         <v>1.53</v>
       </c>
       <c r="AC9">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AD9">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE9">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF9">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="AG9">
         <v>1.4</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AK9">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O10">
-        <v>4.95</v>
+        <v>5.33</v>
       </c>
       <c r="P10">
         <v>10.8</v>
       </c>
       <c r="Q10">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="R10">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="S10">
         <v>1.3</v>
@@ -1960,16 +1960,16 @@
         <v>3.08</v>
       </c>
       <c r="U10">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="V10">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W10">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
         <v>1.16</v>
@@ -1984,7 +1984,7 @@
         <v>2.15</v>
       </c>
       <c r="AC10">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AD10">
         <v>1.45</v>
@@ -1993,10 +1993,10 @@
         <v>1.17</v>
       </c>
       <c r="AF10">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG10">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK10">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="O16">
         <v>3.6</v>
@@ -2932,13 +2932,13 @@
         <v>2.2</v>
       </c>
       <c r="S16">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T16">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U16">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="V16">
         <v>1.45</v>
@@ -2950,10 +2950,10 @@
         <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z16">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA16">
         <v>1.7</v>
@@ -2974,7 +2974,7 @@
         <v>1.57</v>
       </c>
       <c r="AG16">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AK16">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.2</v>
+        <v>1.13</v>
       </c>
       <c r="O19">
-        <v>3.55</v>
+        <v>6.5</v>
       </c>
       <c r="P19">
-        <v>2.6</v>
+        <v>15.5</v>
       </c>
       <c r="Q19">
-        <v>2.91</v>
+        <v>1.41</v>
       </c>
       <c r="R19">
-        <v>2.41</v>
+        <v>3.4</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="T19">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="U19">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="V19">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Z19">
-        <v>4.7</v>
+        <v>6.55</v>
       </c>
       <c r="AA19">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AB19">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="AC19">
-        <v>2.38</v>
+        <v>1.77</v>
       </c>
       <c r="AD19">
-        <v>1.5</v>
+        <v>1.99</v>
       </c>
       <c r="AE19">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="AF19">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AG19">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.38</v>
+        <v>1.06</v>
       </c>
       <c r="AK19">
-        <v>1.55</v>
+        <v>5.5</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
+        <v>2.2</v>
+      </c>
+      <c r="O20">
+        <v>3.55</v>
+      </c>
+      <c r="P20">
+        <v>2.6</v>
+      </c>
+      <c r="Q20">
+        <v>2.91</v>
+      </c>
+      <c r="R20">
+        <v>2.41</v>
+      </c>
+      <c r="S20">
+        <v>1.25</v>
+      </c>
+      <c r="T20">
+        <v>3.45</v>
+      </c>
+      <c r="U20">
+        <v>2.17</v>
+      </c>
+      <c r="V20">
+        <v>1.64</v>
+      </c>
+      <c r="W20">
         <v>1.13</v>
-      </c>
-      <c r="O20">
-        <v>6.5</v>
-      </c>
-      <c r="P20">
-        <v>15.5</v>
-      </c>
-      <c r="Q20">
-        <v>1.41</v>
-      </c>
-      <c r="R20">
-        <v>3.4</v>
-      </c>
-      <c r="S20">
-        <v>1.14</v>
-      </c>
-      <c r="T20">
-        <v>4.3</v>
-      </c>
-      <c r="U20">
-        <v>1.87</v>
-      </c>
-      <c r="V20">
-        <v>1.83</v>
-      </c>
-      <c r="W20">
-        <v>1.22</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Z20">
-        <v>6.55</v>
+        <v>4.7</v>
       </c>
       <c r="AA20">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AB20">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="AC20">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="AD20">
-        <v>1.99</v>
+        <v>1.5</v>
       </c>
       <c r="AE20">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="AF20">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AG20">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="AK20">
-        <v>5.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4058,31 +4058,31 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="O23">
-        <v>6.8</v>
+        <v>6.35</v>
       </c>
       <c r="P23">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="Q23">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="R23">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="S23">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T23">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="U23">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V23">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="W23">
         <v>1.25</v>
@@ -4094,28 +4094,28 @@
         <v>1.05</v>
       </c>
       <c r="Z23">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA23">
         <v>1.3</v>
       </c>
       <c r="AB23">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AC23">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AD23">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AE23">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG23">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AK23">
-        <v>4.12</v>
+        <v>3.45</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="O25">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="P25">
+        <v>2.6</v>
+      </c>
+      <c r="Q25">
+        <v>4</v>
+      </c>
+      <c r="R25">
+        <v>1.83</v>
+      </c>
+      <c r="S25">
+        <v>1.55</v>
+      </c>
+      <c r="T25">
+        <v>2.15</v>
+      </c>
+      <c r="U25">
+        <v>4.25</v>
+      </c>
+      <c r="V25">
+        <v>1.15</v>
+      </c>
+      <c r="W25">
+        <v>1.01</v>
+      </c>
+      <c r="X25">
+        <v>1.11</v>
+      </c>
+      <c r="Y25">
+        <v>1.6</v>
+      </c>
+      <c r="Z25">
+        <v>2.11</v>
+      </c>
+      <c r="AA25">
+        <v>2.75</v>
+      </c>
+      <c r="AB25">
+        <v>1.38</v>
+      </c>
+      <c r="AC25">
+        <v>6.25</v>
+      </c>
+      <c r="AD25">
+        <v>1.06</v>
+      </c>
+      <c r="AE25">
+        <v>1.02</v>
+      </c>
+      <c r="AF25">
+        <v>2.2</v>
+      </c>
+      <c r="AG25">
+        <v>1.53</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
         <v>1.4</v>
       </c>
-      <c r="Q25">
-        <v>7</v>
-      </c>
-      <c r="R25">
-        <v>2.19</v>
-      </c>
-      <c r="S25">
-        <v>1.41</v>
-      </c>
-      <c r="T25">
-        <v>2.8</v>
-      </c>
-      <c r="U25">
-        <v>2.88</v>
-      </c>
-      <c r="V25">
+      <c r="AK25">
         <v>1.33</v>
-      </c>
-      <c r="W25">
-        <v>1.05</v>
-      </c>
-      <c r="X25">
-        <v>1.06</v>
-      </c>
-      <c r="Y25">
-        <v>1.3</v>
-      </c>
-      <c r="Z25">
-        <v>3.04</v>
-      </c>
-      <c r="AA25">
-        <v>2.05</v>
-      </c>
-      <c r="AB25">
-        <v>1.75</v>
-      </c>
-      <c r="AC25">
-        <v>3.51</v>
-      </c>
-      <c r="AD25">
-        <v>1.25</v>
-      </c>
-      <c r="AE25">
-        <v>1.05</v>
-      </c>
-      <c r="AF25">
-        <v>2.25</v>
-      </c>
-      <c r="AG25">
-        <v>1.58</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.13</v>
-      </c>
-      <c r="AK25">
-        <v>1.09</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,61 +4547,61 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.75</v>
+        <v>6.72</v>
       </c>
       <c r="O26">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="P26">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="Q26">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="R26">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="S26">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="T26">
-        <v>2.07</v>
+        <v>2.8</v>
       </c>
       <c r="U26">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="V26">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="W26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X26">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="Z26">
-        <v>2.23</v>
+        <v>2.97</v>
       </c>
       <c r="AA26">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="AB26">
-        <v>1.38</v>
+        <v>1.73</v>
       </c>
       <c r="AC26">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="AD26">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AE26">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF26">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AG26">
         <v>1.57</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AK26">
-        <v>1.36</v>
+        <v>1.07</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,65 +5525,65 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.3</v>
+        <v>1.24</v>
       </c>
       <c r="O32">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="P32">
-        <v>3.08</v>
+        <v>11.5</v>
       </c>
       <c r="Q32">
-        <v>3.12</v>
+        <v>1.67</v>
       </c>
       <c r="R32">
-        <v>1.76</v>
+        <v>2.5</v>
       </c>
       <c r="S32">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="T32">
-        <v>2.14</v>
+        <v>2.95</v>
       </c>
       <c r="U32">
-        <v>3.8</v>
+        <v>2.68</v>
       </c>
       <c r="V32">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="W32">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="Z32">
-        <v>2.39</v>
+        <v>3.5</v>
       </c>
       <c r="AA32">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="AB32">
+        <v>1.91</v>
+      </c>
+      <c r="AC32">
+        <v>3.2</v>
+      </c>
+      <c r="AD32">
+        <v>1.3</v>
+      </c>
+      <c r="AE32">
+        <v>1.11</v>
+      </c>
+      <c r="AF32">
+        <v>2.5</v>
+      </c>
+      <c r="AG32">
         <v>1.44</v>
       </c>
-      <c r="AC32">
-        <v>5.5</v>
-      </c>
-      <c r="AD32">
-        <v>1.11</v>
-      </c>
-      <c r="AE32">
-        <v>1.01</v>
-      </c>
-      <c r="AF32">
-        <v>2.09</v>
-      </c>
-      <c r="AG32">
-        <v>1.63</v>
-      </c>
       <c r="AH32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AK32">
-        <v>1.49</v>
+        <v>3.75</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-09-09 14:00:00</t>
+          <t>2026-09-09 14:30:00</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,80 +5688,80 @@
         </is>
       </c>
       <c r="N33">
+        <v>3.8</v>
+      </c>
+      <c r="O33">
+        <v>3.75</v>
+      </c>
+      <c r="P33">
+        <v>1.86</v>
+      </c>
+      <c r="Q33">
+        <v>4.15</v>
+      </c>
+      <c r="R33">
+        <v>2.44</v>
+      </c>
+      <c r="S33">
         <v>1.24</v>
       </c>
-      <c r="O33">
-        <v>5</v>
-      </c>
-      <c r="P33">
-        <v>12.5</v>
-      </c>
-      <c r="Q33">
-        <v>1.67</v>
-      </c>
-      <c r="R33">
-        <v>2.5</v>
-      </c>
-      <c r="S33">
-        <v>1.33</v>
-      </c>
       <c r="T33">
-        <v>2.92</v>
+        <v>3.32</v>
       </c>
       <c r="U33">
-        <v>2.49</v>
+        <v>2.26</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W33">
         <v>1.09</v>
       </c>
       <c r="X33">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
+        <v>1.2</v>
+      </c>
+      <c r="Z33">
+        <v>4</v>
+      </c>
+      <c r="AA33">
+        <v>1.65</v>
+      </c>
+      <c r="AB33">
+        <v>2.16</v>
+      </c>
+      <c r="AC33">
+        <v>2.63</v>
+      </c>
+      <c r="AD33">
+        <v>1.4</v>
+      </c>
+      <c r="AE33">
+        <v>1.15</v>
+      </c>
+      <c r="AF33">
+        <v>1.57</v>
+      </c>
+      <c r="AG33">
+        <v>2.2</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
         <v>1.25</v>
       </c>
-      <c r="Z33">
-        <v>3.5</v>
-      </c>
-      <c r="AA33">
-        <v>1.83</v>
-      </c>
-      <c r="AB33">
-        <v>1.91</v>
-      </c>
-      <c r="AC33">
-        <v>3</v>
-      </c>
-      <c r="AD33">
-        <v>1.3</v>
-      </c>
-      <c r="AE33">
-        <v>1.11</v>
-      </c>
-      <c r="AF33">
-        <v>2.45</v>
-      </c>
-      <c r="AG33">
-        <v>1.5</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33">
-        <v>1.17</v>
-      </c>
       <c r="AK33">
-        <v>3.6</v>
+        <v>1.25</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-09-09 14:30:00</t>
+          <t>2026-09-09 15:00:00</t>
         </is>
       </c>
     </row>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,80 +5851,80 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.75</v>
+        <v>1.16</v>
       </c>
       <c r="O34">
-        <v>3.73</v>
+        <v>7.29</v>
       </c>
       <c r="P34">
+        <v>11.06</v>
+      </c>
+      <c r="Q34">
+        <v>1.5</v>
+      </c>
+      <c r="R34">
+        <v>2.8</v>
+      </c>
+      <c r="S34">
+        <v>1.17</v>
+      </c>
+      <c r="T34">
+        <v>4.33</v>
+      </c>
+      <c r="U34">
         <v>1.9</v>
       </c>
-      <c r="Q34">
-        <v>4.1</v>
-      </c>
-      <c r="R34">
-        <v>2.3</v>
-      </c>
-      <c r="S34">
-        <v>1.24</v>
-      </c>
-      <c r="T34">
-        <v>3.32</v>
-      </c>
-      <c r="U34">
-        <v>2.4</v>
-      </c>
       <c r="V34">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="W34">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="Z34">
+        <v>8</v>
+      </c>
+      <c r="AA34">
+        <v>1.25</v>
+      </c>
+      <c r="AB34">
+        <v>3.4</v>
+      </c>
+      <c r="AC34">
+        <v>1.73</v>
+      </c>
+      <c r="AD34">
+        <v>1.95</v>
+      </c>
+      <c r="AE34">
+        <v>1.4</v>
+      </c>
+      <c r="AF34">
+        <v>1.78</v>
+      </c>
+      <c r="AG34">
+        <v>1.93</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>1.04</v>
+      </c>
+      <c r="AK34">
         <v>4.5</v>
-      </c>
-      <c r="AA34">
-        <v>1.65</v>
-      </c>
-      <c r="AB34">
-        <v>2.16</v>
-      </c>
-      <c r="AC34">
-        <v>2.59</v>
-      </c>
-      <c r="AD34">
-        <v>1.44</v>
-      </c>
-      <c r="AE34">
-        <v>1.14</v>
-      </c>
-      <c r="AF34">
-        <v>1.57</v>
-      </c>
-      <c r="AG34">
-        <v>2.19</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>1.25</v>
-      </c>
-      <c r="AK34">
-        <v>1.25</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.14</v>
+        <v>2.35</v>
       </c>
       <c r="O35">
-        <v>7.47</v>
+        <v>2.5</v>
       </c>
       <c r="P35">
-        <v>11.34</v>
+        <v>3.4</v>
       </c>
       <c r="Q35">
-        <v>1.55</v>
+        <v>3.12</v>
       </c>
       <c r="R35">
-        <v>3.08</v>
+        <v>1.91</v>
       </c>
       <c r="S35">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="T35">
-        <v>4.8</v>
+        <v>2.25</v>
       </c>
       <c r="U35">
-        <v>1.83</v>
+        <v>3.8</v>
       </c>
       <c r="V35">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="W35">
-        <v>1.19</v>
+        <v>1.02</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y35">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="Z35">
-        <v>7</v>
+        <v>2.36</v>
       </c>
       <c r="AA35">
-        <v>1.28</v>
+        <v>2.62</v>
       </c>
       <c r="AB35">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC35">
-        <v>1.82</v>
+        <v>4.75</v>
       </c>
       <c r="AD35">
-        <v>1.85</v>
+        <v>1.12</v>
       </c>
       <c r="AE35">
+        <v>1.02</v>
+      </c>
+      <c r="AF35">
+        <v>2.09</v>
+      </c>
+      <c r="AG35">
+        <v>1.63</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.36</v>
       </c>
-      <c r="AF35">
-        <v>1.7</v>
-      </c>
-      <c r="AG35">
-        <v>2</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.04</v>
-      </c>
       <c r="AK35">
-        <v>4.2</v>
+        <v>1.57</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="O37">
-        <v>3.75</v>
+        <v>3.52</v>
       </c>
       <c r="P37">
-        <v>3.9</v>
+        <v>3.18</v>
       </c>
       <c r="Q37">
         <v>2.3</v>
@@ -6361,10 +6361,10 @@
         <v>3.3</v>
       </c>
       <c r="U37">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="V37">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W37">
         <v>1.08</v>
@@ -6373,47 +6373,47 @@
         <v>1</v>
       </c>
       <c r="Y37">
+        <v>1.22</v>
+      </c>
+      <c r="Z37">
+        <v>3.7</v>
+      </c>
+      <c r="AA37">
+        <v>1.75</v>
+      </c>
+      <c r="AB37">
+        <v>2.19</v>
+      </c>
+      <c r="AC37">
+        <v>2.72</v>
+      </c>
+      <c r="AD37">
+        <v>1.41</v>
+      </c>
+      <c r="AE37">
+        <v>1.16</v>
+      </c>
+      <c r="AF37">
+        <v>1.67</v>
+      </c>
+      <c r="AG37">
+        <v>2.1</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
         <v>1.2</v>
       </c>
-      <c r="Z37">
-        <v>3.76</v>
-      </c>
-      <c r="AA37">
-        <v>1.74</v>
-      </c>
-      <c r="AB37">
-        <v>2</v>
-      </c>
-      <c r="AC37">
-        <v>2.68</v>
-      </c>
-      <c r="AD37">
-        <v>1.34</v>
-      </c>
-      <c r="AE37">
-        <v>1.11</v>
-      </c>
-      <c r="AF37">
-        <v>1.62</v>
-      </c>
-      <c r="AG37">
-        <v>2.3</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.18</v>
-      </c>
       <c r="AK37">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="O38">
         <v>3.4</v>
@@ -6515,7 +6515,7 @@
         <v>3.25</v>
       </c>
       <c r="R38">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S38">
         <v>1.32</v>
@@ -6527,7 +6527,7 @@
         <v>2.63</v>
       </c>
       <c r="V38">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W38">
         <v>1.06</v>
@@ -6536,7 +6536,7 @@
         <v>1.05</v>
       </c>
       <c r="Y38">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
         <v>3.45</v>
@@ -6548,7 +6548,7 @@
         <v>1.87</v>
       </c>
       <c r="AC38">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="AD38">
         <v>1.33</v>
@@ -6557,10 +6557,10 @@
         <v>1.11</v>
       </c>
       <c r="AF38">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AG38">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,40 +6666,40 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="O39">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="P39">
         <v>8</v>
       </c>
       <c r="Q39">
+        <v>1.73</v>
+      </c>
+      <c r="R39">
+        <v>2.69</v>
+      </c>
+      <c r="S39">
+        <v>1.2</v>
+      </c>
+      <c r="T39">
+        <v>3.9</v>
+      </c>
+      <c r="U39">
+        <v>2.13</v>
+      </c>
+      <c r="V39">
         <v>1.72</v>
       </c>
-      <c r="R39">
-        <v>2.7</v>
-      </c>
-      <c r="S39">
-        <v>1.21</v>
-      </c>
-      <c r="T39">
-        <v>3.75</v>
-      </c>
-      <c r="U39">
-        <v>2.07</v>
-      </c>
-      <c r="V39">
-        <v>1.7</v>
-      </c>
       <c r="W39">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z39">
         <v>6</v>
@@ -6708,22 +6708,22 @@
         <v>1.4</v>
       </c>
       <c r="AB39">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC39">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD39">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE39">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF39">
         <v>1.7</v>
       </c>
       <c r="AG39">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK39">
         <v>3.32</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="O42">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="P42">
+        <v>3.7</v>
+      </c>
+      <c r="Q42">
+        <v>2.3</v>
+      </c>
+      <c r="R42">
+        <v>2.31</v>
+      </c>
+      <c r="S42">
+        <v>1.32</v>
+      </c>
+      <c r="T42">
+        <v>3.28</v>
+      </c>
+      <c r="U42">
+        <v>2.4</v>
+      </c>
+      <c r="V42">
+        <v>1.58</v>
+      </c>
+      <c r="W42">
+        <v>1.12</v>
+      </c>
+      <c r="X42">
+        <v>1.02</v>
+      </c>
+      <c r="Y42">
+        <v>1.15</v>
+      </c>
+      <c r="Z42">
         <v>4.6</v>
       </c>
-      <c r="Q42">
-        <v>2.2</v>
-      </c>
-      <c r="R42">
-        <v>2.58</v>
-      </c>
-      <c r="S42">
-        <v>1.29</v>
-      </c>
-      <c r="T42">
-        <v>3.5</v>
-      </c>
-      <c r="U42">
-        <v>2.35</v>
-      </c>
-      <c r="V42">
-        <v>1.6</v>
-      </c>
-      <c r="W42">
-        <v>1.13</v>
-      </c>
-      <c r="X42">
-        <v>1.01</v>
-      </c>
-      <c r="Y42">
-        <v>1.2</v>
-      </c>
-      <c r="Z42">
-        <v>4.5</v>
-      </c>
       <c r="AA42">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AB42">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AC42">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AD42">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AE42">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF42">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG42">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O43">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P43">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q43">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R43">
-        <v>2.31</v>
+        <v>2.58</v>
       </c>
       <c r="S43">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T43">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U43">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="V43">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W43">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z43">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA43">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AB43">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AC43">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AD43">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AE43">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF43">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG43">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="O44">
         <v>3.4</v>
@@ -7490,16 +7490,16 @@
         <v>2.3</v>
       </c>
       <c r="Q44">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="R44">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S44">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T44">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="U44">
         <v>2.77</v>
@@ -7508,7 +7508,7 @@
         <v>1.34</v>
       </c>
       <c r="W44">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X44">
         <v>1.01</v>
@@ -7517,28 +7517,28 @@
         <v>1.3</v>
       </c>
       <c r="Z44">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AA44">
         <v>1.91</v>
       </c>
       <c r="AB44">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC44">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="AD44">
         <v>1.27</v>
       </c>
       <c r="AE44">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF44">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG44">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK44">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,31 +7644,31 @@
         </is>
       </c>
       <c r="N45">
-        <v>6.25</v>
+        <v>4.8</v>
       </c>
       <c r="O45">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P45">
         <v>1.45</v>
       </c>
       <c r="Q45">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R45">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="S45">
         <v>1.22</v>
       </c>
       <c r="T45">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="U45">
         <v>2.25</v>
       </c>
       <c r="V45">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W45">
         <v>1.14</v>
@@ -7677,16 +7677,16 @@
         <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z45">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA45">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB45">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC45">
         <v>2.23</v>
@@ -7695,13 +7695,13 @@
         <v>1.63</v>
       </c>
       <c r="AE45">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF45">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG45">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK45">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7810,10 +7810,10 @@
         <v>13</v>
       </c>
       <c r="O46">
-        <v>7.05</v>
+        <v>7.5</v>
       </c>
       <c r="P46">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Q46">
         <v>10</v>
@@ -7822,7 +7822,7 @@
         <v>2.8</v>
       </c>
       <c r="S46">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="T46">
         <v>3.5</v>
@@ -7831,34 +7831,34 @@
         <v>2.16</v>
       </c>
       <c r="V46">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="W46">
         <v>1.14</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z46">
-        <v>5.15</v>
+        <v>4.82</v>
       </c>
       <c r="AA46">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AB46">
         <v>2.51</v>
       </c>
       <c r="AC46">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AD46">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AE46">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF46">
         <v>2.1</v>
@@ -7880,7 +7880,7 @@
         <v>1.1</v>
       </c>
       <c r="AK46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="O48">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P48">
-        <v>5.45</v>
+        <v>5.1</v>
       </c>
       <c r="Q48">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="R48">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="S48">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T48">
-        <v>2.54</v>
+        <v>2.69</v>
       </c>
       <c r="U48">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="V48">
+        <v>1.32</v>
+      </c>
+      <c r="W48">
+        <v>1.02</v>
+      </c>
+      <c r="X48">
+        <v>1.02</v>
+      </c>
+      <c r="Y48">
         <v>1.33</v>
       </c>
-      <c r="W48">
-        <v>1.05</v>
-      </c>
-      <c r="X48">
-        <v>1.06</v>
-      </c>
-      <c r="Y48">
-        <v>1.38</v>
-      </c>
       <c r="Z48">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AA48">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="AB48">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC48">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="AD48">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE48">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF48">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AG48">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AK48">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,16 +8296,16 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="O49">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P49">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q49">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R49">
         <v>1.98</v>
@@ -8323,22 +8323,22 @@
         <v>1.27</v>
       </c>
       <c r="W49">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X49">
         <v>1.06</v>
       </c>
       <c r="Y49">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Z49">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="AA49">
         <v>2.4</v>
       </c>
       <c r="AB49">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC49">
         <v>4.8</v>
@@ -8350,10 +8350,10 @@
         <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG49">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="O53">
         <v>3.75</v>
       </c>
       <c r="P53">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="Q53">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="R53">
         <v>2.4</v>
       </c>
       <c r="S53">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T53">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U53">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="V53">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W53">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z53">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA53">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB53">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC53">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="AD53">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AE53">
         <v>1.22</v>
       </c>
       <c r="AF53">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AG53">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK53">
         <v>1.6</v>
@@ -9111,40 +9111,40 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="O54">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="P54">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q54">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="R54">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="S54">
         <v>1.22</v>
       </c>
       <c r="T54">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="U54">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="V54">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="W54">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z54">
         <v>6.1</v>
@@ -9159,16 +9159,16 @@
         <v>2.02</v>
       </c>
       <c r="AD54">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE54">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AF54">
         <v>1.36</v>
       </c>
       <c r="AG54">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.5</v>
+        <v>3.03</v>
       </c>
       <c r="O55">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P55">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="Q55">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="R55">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="S55">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T55">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U55">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="V55">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="W55">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X55">
         <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z55">
         <v>4.2</v>
       </c>
       <c r="AA55">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AB55">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC55">
         <v>2.63</v>
       </c>
       <c r="AD55">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE55">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF55">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG55">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK55">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.9</v>
+        <v>2.33</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P56">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="Q56">
-        <v>3.49</v>
+        <v>3</v>
       </c>
       <c r="R56">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="S56">
         <v>1.3</v>
       </c>
       <c r="T56">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U56">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V56">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="W56">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z56">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="AA56">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB56">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AC56">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AD56">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE56">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF56">
         <v>1.53</v>
       </c>
       <c r="AG56">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AK56">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9612,13 +9612,13 @@
         <v>2.85</v>
       </c>
       <c r="R57">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="S57">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T57">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U57">
         <v>2.85</v>
@@ -9627,7 +9627,7 @@
         <v>1.37</v>
       </c>
       <c r="W57">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X57">
         <v>1.03</v>
@@ -9639,13 +9639,13 @@
         <v>3.4</v>
       </c>
       <c r="AA57">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB57">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC57">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AD57">
         <v>1.3</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK57">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9766,7 +9766,7 @@
         <v>2.5</v>
       </c>
       <c r="O58">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P58">
         <v>2.5</v>
@@ -9775,10 +9775,10 @@
         <v>3.2</v>
       </c>
       <c r="R58">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S58">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="T58">
         <v>2.88</v>
@@ -9790,7 +9790,7 @@
         <v>1.39</v>
       </c>
       <c r="W58">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X58">
         <v>1.06</v>
@@ -9802,13 +9802,13 @@
         <v>3.4</v>
       </c>
       <c r="AA58">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB58">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC58">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="AD58">
         <v>1.29</v>
@@ -9817,10 +9817,10 @@
         <v>1.07</v>
       </c>
       <c r="AF58">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG58">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK58">
         <v>1.44</v>
@@ -9926,34 +9926,34 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="O59">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P59">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q59">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R59">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="S59">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T59">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="U59">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="V59">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="W59">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X59">
         <v>1.01</v>
@@ -9965,7 +9965,7 @@
         <v>7.5</v>
       </c>
       <c r="AA59">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB59">
         <v>3.1</v>
@@ -9974,10 +9974,10 @@
         <v>1.9</v>
       </c>
       <c r="AD59">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AE59">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AF59">
         <v>1.36</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK59">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -12700,10 +12700,10 @@
         <v>2.6</v>
       </c>
       <c r="O76">
-        <v>3.66</v>
+        <v>2.25</v>
       </c>
       <c r="P76">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="O77">
         <v>3.4</v>
       </c>
       <c r="P77">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q77">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R77">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S77">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T77">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U77">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="V77">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W77">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X77">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y77">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z77">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AA77">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AB77">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="AC77">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AD77">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE77">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF77">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AG77">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.3</v>
       </c>
       <c r="AK77">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,61 +13023,61 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="O78">
-        <v>4.26</v>
+        <v>4</v>
       </c>
       <c r="P78">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q78">
         <v>2.5</v>
       </c>
       <c r="R78">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="S78">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T78">
-        <v>5.25</v>
+        <v>4.55</v>
       </c>
       <c r="U78">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V78">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="W78">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X78">
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z78">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA78">
         <v>1.25</v>
       </c>
       <c r="AB78">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="AC78">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AD78">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE78">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF78">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AG78">
         <v>3.5</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK78">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="O79">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="P79">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="Q79">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="R79">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="S79">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T79">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U79">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="V79">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="W79">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X79">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
         <v>1.18</v>
       </c>
       <c r="Z79">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA79">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AB79">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AC79">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="AD79">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AE79">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AF79">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AG79">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="O80">
+        <v>3.4</v>
+      </c>
+      <c r="P80">
         <v>3.5</v>
-      </c>
-      <c r="P80">
-        <v>3.1</v>
       </c>
       <c r="Q80">
         <v>2.55</v>
       </c>
       <c r="R80">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S80">
         <v>1.25</v>
       </c>
       <c r="T80">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U80">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="V80">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="W80">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X80">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y80">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z80">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AA80">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB80">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="AC80">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AD80">
+        <v>1.38</v>
+      </c>
+      <c r="AE80">
+        <v>1.18</v>
+      </c>
+      <c r="AF80">
         <v>1.57</v>
       </c>
-      <c r="AE80">
-        <v>1.2</v>
-      </c>
-      <c r="AF80">
-        <v>1.44</v>
-      </c>
       <c r="AG80">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK80">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="O81">
         <v>3.2</v>
       </c>
       <c r="P81">
-        <v>4</v>
+        <v>4.24</v>
       </c>
       <c r="Q81">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="R81">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S81">
         <v>1.43</v>
@@ -13533,7 +13533,7 @@
         <v>2.75</v>
       </c>
       <c r="U81">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="V81">
         <v>1.32</v>
@@ -13542,7 +13542,7 @@
         <v>1.05</v>
       </c>
       <c r="X81">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y81">
         <v>1.42</v>
@@ -13563,10 +13563,10 @@
         <v>1.2</v>
       </c>
       <c r="AE81">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF81">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG81">
         <v>1.72</v>
@@ -13675,10 +13675,10 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="O82">
-        <v>3.8</v>
+        <v>4.26</v>
       </c>
       <c r="P82">
         <v>4.05</v>
@@ -13690,19 +13690,19 @@
         <v>2.63</v>
       </c>
       <c r="S82">
+        <v>1.19</v>
+      </c>
+      <c r="T82">
+        <v>3.94</v>
+      </c>
+      <c r="U82">
+        <v>2.01</v>
+      </c>
+      <c r="V82">
+        <v>1.71</v>
+      </c>
+      <c r="W82">
         <v>1.2</v>
-      </c>
-      <c r="T82">
-        <v>4.33</v>
-      </c>
-      <c r="U82">
-        <v>2</v>
-      </c>
-      <c r="V82">
-        <v>1.73</v>
-      </c>
-      <c r="W82">
-        <v>1.18</v>
       </c>
       <c r="X82">
         <v>1.01</v>
@@ -13711,19 +13711,19 @@
         <v>1.12</v>
       </c>
       <c r="Z82">
-        <v>6.41</v>
+        <v>6.54</v>
       </c>
       <c r="AA82">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AB82">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="AC82">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AD82">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AE82">
         <v>1.3</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK82">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,34 +13838,34 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O83">
-        <v>5</v>
+        <v>5.57</v>
       </c>
       <c r="P83">
-        <v>5.5</v>
+        <v>7.3</v>
       </c>
       <c r="Q83">
         <v>1.7</v>
       </c>
       <c r="R83">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="S83">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T83">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="U83">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="V83">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="W83">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X83">
         <v>1.01</v>
@@ -13874,28 +13874,28 @@
         <v>1.1</v>
       </c>
       <c r="Z83">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="AA83">
         <v>1.36</v>
       </c>
       <c r="AB83">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AC83">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD83">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="AE83">
         <v>1.36</v>
       </c>
       <c r="AF83">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG83">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AK83">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,34 +14001,34 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="O84">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="P84">
-        <v>6.55</v>
+        <v>6.76</v>
       </c>
       <c r="Q84">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="R84">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S84">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T84">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U84">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="V84">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="W84">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X84">
         <v>1.01</v>
@@ -14037,28 +14037,28 @@
         <v>1.11</v>
       </c>
       <c r="Z84">
-        <v>7.5</v>
+        <v>7.27</v>
       </c>
       <c r="AA84">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB84">
-        <v>3.13</v>
+        <v>3.27</v>
       </c>
       <c r="AC84">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AD84">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AE84">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF84">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG84">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK84">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,16 +14164,16 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="O85">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P85">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q85">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="R85">
         <v>2.45</v>
@@ -14182,46 +14182,46 @@
         <v>1.22</v>
       </c>
       <c r="T85">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U85">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="V85">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W85">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y85">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z85">
         <v>5.5</v>
       </c>
       <c r="AA85">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB85">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AC85">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AD85">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AE85">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF85">
         <v>1.44</v>
       </c>
       <c r="AG85">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK85">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL85">
         <v>0</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -612,54 +612,54 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="O2">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="P2">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q2">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="R2">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S2">
         <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U2">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
         <v>1.05</v>
@@ -668,74 +668,74 @@
         <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z2">
         <v>2.9</v>
       </c>
       <c r="AA2">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AB2">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC2">
-        <v>3.72</v>
+        <v>4.3</v>
       </c>
       <c r="AD2">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE2">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
         <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15"]</t>
         </is>
       </c>
       <c r="AJ2">
+        <v>1.47</v>
+      </c>
+      <c r="AK2">
         <v>1.4</v>
       </c>
-      <c r="AK2">
-        <v>1.44</v>
-      </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -794,68 +794,68 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O3">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
         <v>2.95</v>
       </c>
       <c r="Q3">
+        <v>3.1</v>
+      </c>
+      <c r="R3">
+        <v>2</v>
+      </c>
+      <c r="S3">
+        <v>1.5</v>
+      </c>
+      <c r="T3">
+        <v>2.41</v>
+      </c>
+      <c r="U3">
+        <v>2.95</v>
+      </c>
+      <c r="V3">
+        <v>1.3</v>
+      </c>
+      <c r="W3">
+        <v>1</v>
+      </c>
+      <c r="X3">
+        <v>1.03</v>
+      </c>
+      <c r="Y3">
+        <v>1.39</v>
+      </c>
+      <c r="Z3">
         <v>2.8</v>
       </c>
-      <c r="R3">
-        <v>2.1</v>
-      </c>
-      <c r="S3">
-        <v>1.44</v>
-      </c>
-      <c r="T3">
-        <v>2.59</v>
-      </c>
-      <c r="U3">
-        <v>2.89</v>
-      </c>
-      <c r="V3">
-        <v>1.32</v>
-      </c>
-      <c r="W3">
-        <v>1.05</v>
-      </c>
-      <c r="X3">
+      <c r="AA3">
+        <v>2.35</v>
+      </c>
+      <c r="AB3">
+        <v>1.58</v>
+      </c>
+      <c r="AC3">
+        <v>4.33</v>
+      </c>
+      <c r="AD3">
+        <v>1.21</v>
+      </c>
+      <c r="AE3">
         <v>1.06</v>
       </c>
-      <c r="Y3">
-        <v>1.3</v>
-      </c>
-      <c r="Z3">
-        <v>3.15</v>
-      </c>
-      <c r="AA3">
-        <v>2.24</v>
-      </c>
-      <c r="AB3">
-        <v>1.67</v>
-      </c>
-      <c r="AC3">
-        <v>4.1</v>
-      </c>
-      <c r="AD3">
-        <v>1.22</v>
-      </c>
-      <c r="AE3">
-        <v>1.07</v>
-      </c>
       <c r="AF3">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG3">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,34 +871,34 @@
         <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -953,115 +953,115 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Q4">
-        <v>4.64</v>
+        <v>4.75</v>
       </c>
       <c r="R4">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="U4">
+        <v>2.88</v>
+      </c>
+      <c r="V4">
+        <v>1.36</v>
+      </c>
+      <c r="W4">
+        <v>1.06</v>
+      </c>
+      <c r="X4">
+        <v>1.01</v>
+      </c>
+      <c r="Y4">
+        <v>1.26</v>
+      </c>
+      <c r="Z4">
+        <v>3.24</v>
+      </c>
+      <c r="AA4">
+        <v>1.97</v>
+      </c>
+      <c r="AB4">
+        <v>1.92</v>
+      </c>
+      <c r="AC4">
+        <v>3.45</v>
+      </c>
+      <c r="AD4">
+        <v>1.33</v>
+      </c>
+      <c r="AE4">
+        <v>1.07</v>
+      </c>
+      <c r="AF4">
+        <v>1.8</v>
+      </c>
+      <c r="AG4">
+        <v>1.95</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>["63"]</t>
+        </is>
+      </c>
+      <c r="AJ4">
+        <v>1.25</v>
+      </c>
+      <c r="AK4">
+        <v>1.22</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
         <v>3</v>
       </c>
-      <c r="V4">
-        <v>1.33</v>
-      </c>
-      <c r="W4">
-        <v>1.05</v>
-      </c>
-      <c r="X4">
-        <v>1.04</v>
-      </c>
-      <c r="Y4">
-        <v>1.33</v>
-      </c>
-      <c r="Z4">
-        <v>3.25</v>
-      </c>
-      <c r="AA4">
-        <v>2.09</v>
-      </c>
-      <c r="AB4">
-        <v>1.75</v>
-      </c>
-      <c r="AC4">
-        <v>3.6</v>
-      </c>
-      <c r="AD4">
-        <v>1.29</v>
-      </c>
-      <c r="AE4">
-        <v>1.1</v>
-      </c>
-      <c r="AF4">
-        <v>1.82</v>
-      </c>
-      <c r="AG4">
-        <v>1.86</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.8</v>
-      </c>
-      <c r="AK4">
-        <v>1.25</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>-1</v>
-      </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,130 +1101,130 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="O5">
-        <v>4.05</v>
+        <v>4.45</v>
       </c>
       <c r="P5">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="R5">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="S5">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T5">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="U5">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V5">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>3.76</v>
+        <v>4.5</v>
       </c>
       <c r="AA5">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB5">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC5">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AD5">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE5">
         <v>1.14</v>
       </c>
       <c r="AF5">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AG5">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47", "65", "75"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "86"]</t>
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         <v>1.85</v>
       </c>
       <c r="Q6">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="R6">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
         <v>1.33</v>
@@ -1308,40 +1308,40 @@
         <v>3.12</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V6">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W6">
         <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
         <v>1.19</v>
       </c>
       <c r="Z6">
-        <v>3.98</v>
+        <v>4.07</v>
       </c>
       <c r="AA6">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB6">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC6">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="AD6">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE6">
         <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG6">
         <v>2.13</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O7">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="P7">
-        <v>7.08</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R7">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="S7">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T7">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="U7">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V7">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W7">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z7">
-        <v>5.42</v>
+        <v>5.08</v>
       </c>
       <c r="AA7">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AB7">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AC7">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AD7">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE7">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF7">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG7">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="O11">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P11">
-        <v>4.94</v>
+        <v>4.5</v>
       </c>
       <c r="Q11">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="R11">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="S11">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U11">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="V11">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
         <v>1.12</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z11">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="AA11">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB11">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AC11">
-        <v>2.41</v>
+        <v>2.57</v>
       </c>
       <c r="AD11">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE11">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK11">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="O12">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P12">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="Q12">
         <v>3.8</v>
@@ -2280,40 +2280,40 @@
         <v>2.1</v>
       </c>
       <c r="S12">
+        <v>1.35</v>
+      </c>
+      <c r="T12">
+        <v>2.62</v>
+      </c>
+      <c r="U12">
+        <v>2.75</v>
+      </c>
+      <c r="V12">
         <v>1.36</v>
       </c>
-      <c r="T12">
-        <v>2.75</v>
-      </c>
-      <c r="U12">
-        <v>2.79</v>
-      </c>
-      <c r="V12">
-        <v>1.35</v>
-      </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z12">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA12">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AB12">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AC12">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD12">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE12">
         <v>1.06</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AK12">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
+        <v>2.71</v>
+      </c>
+      <c r="O13">
+        <v>2.9</v>
+      </c>
+      <c r="P13">
+        <v>2.4</v>
+      </c>
+      <c r="Q13">
         <v>3.15</v>
       </c>
-      <c r="O13">
-        <v>3.15</v>
-      </c>
-      <c r="P13">
-        <v>2.11</v>
-      </c>
-      <c r="Q13">
-        <v>3.3</v>
-      </c>
       <c r="R13">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="S13">
+        <v>1.36</v>
+      </c>
+      <c r="T13">
+        <v>2.9</v>
+      </c>
+      <c r="U13">
+        <v>2.88</v>
+      </c>
+      <c r="V13">
+        <v>1.36</v>
+      </c>
+      <c r="W13">
+        <v>1.04</v>
+      </c>
+      <c r="X13">
+        <v>1.05</v>
+      </c>
+      <c r="Y13">
         <v>1.33</v>
       </c>
-      <c r="T13">
-        <v>2.89</v>
-      </c>
-      <c r="U13">
-        <v>2.5</v>
-      </c>
-      <c r="V13">
+      <c r="Z13">
+        <v>3</v>
+      </c>
+      <c r="AA13">
+        <v>2.05</v>
+      </c>
+      <c r="AB13">
+        <v>1.67</v>
+      </c>
+      <c r="AC13">
+        <v>3.5</v>
+      </c>
+      <c r="AD13">
+        <v>1.29</v>
+      </c>
+      <c r="AE13">
+        <v>1.05</v>
+      </c>
+      <c r="AF13">
+        <v>1.78</v>
+      </c>
+      <c r="AG13">
+        <v>1.91</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>1.44</v>
+      </c>
+      <c r="AK13">
         <v>1.4</v>
-      </c>
-      <c r="W13">
-        <v>1.08</v>
-      </c>
-      <c r="X13">
-        <v>1.04</v>
-      </c>
-      <c r="Y13">
-        <v>1.25</v>
-      </c>
-      <c r="Z13">
-        <v>3.6</v>
-      </c>
-      <c r="AA13">
-        <v>1.8</v>
-      </c>
-      <c r="AB13">
-        <v>1.85</v>
-      </c>
-      <c r="AC13">
-        <v>2.9</v>
-      </c>
-      <c r="AD13">
-        <v>1.33</v>
-      </c>
-      <c r="AE13">
-        <v>1.11</v>
-      </c>
-      <c r="AF13">
-        <v>1.62</v>
-      </c>
-      <c r="AG13">
-        <v>2.1</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.3</v>
-      </c>
-      <c r="AK13">
-        <v>1.33</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="O14">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="P14">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="Q14">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="R14">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S14">
         <v>1.34</v>
@@ -2612,16 +2612,16 @@
         <v>2.95</v>
       </c>
       <c r="U14">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V14">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W14">
         <v>1.07</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
         <v>1.21</v>
@@ -2630,25 +2630,25 @@
         <v>3.58</v>
       </c>
       <c r="AA14">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AB14">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC14">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD14">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE14">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
         <v>1.64</v>
       </c>
       <c r="AG14">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
         <v>1.75</v>
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O15">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q15">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="R15">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="S15">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T15">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="U15">
         <v>2.75</v>
       </c>
       <c r="V15">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W15">
         <v>1.05</v>
@@ -2793,13 +2793,13 @@
         <v>3.08</v>
       </c>
       <c r="AA15">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB15">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC15">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="AD15">
         <v>1.25</v>
@@ -2808,10 +2808,10 @@
         <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG15">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.24</v>
       </c>
       <c r="AK15">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3080,37 +3080,37 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="O17">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P17">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q17">
-        <v>4.33</v>
+        <v>4.95</v>
       </c>
       <c r="R17">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="S17">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="T17">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="U17">
-        <v>3.34</v>
+        <v>2.75</v>
       </c>
       <c r="V17">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X17">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y17">
         <v>1.43</v>
@@ -3119,22 +3119,22 @@
         <v>2.46</v>
       </c>
       <c r="AA17">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="AB17">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC17">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="AD17">
         <v>1.14</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF17">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AG17">
         <v>1.67</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK17">
         <v>1.19</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.8</v>
+        <v>1.12</v>
       </c>
       <c r="O18">
-        <v>3.75</v>
+        <v>7.5</v>
       </c>
       <c r="P18">
-        <v>1.7</v>
+        <v>14</v>
       </c>
       <c r="Q18">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="R18">
-        <v>2.48</v>
+        <v>3.28</v>
       </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="T18">
-        <v>3.34</v>
+        <v>4.33</v>
       </c>
       <c r="U18">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="V18">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="W18">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Z18">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA18">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AB18">
-        <v>2.26</v>
+        <v>2.63</v>
       </c>
       <c r="AC18">
-        <v>2.34</v>
+        <v>1.77</v>
       </c>
       <c r="AD18">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AE18">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AF18">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG18">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AK18">
-        <v>1.22</v>
+        <v>5.5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,80 +3406,80 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.13</v>
+        <v>3.8</v>
       </c>
       <c r="O19">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>15.5</v>
+        <v>1.74</v>
       </c>
       <c r="Q19">
-        <v>1.41</v>
+        <v>3.68</v>
       </c>
       <c r="R19">
-        <v>3.4</v>
+        <v>2.23</v>
       </c>
       <c r="S19">
+        <v>1.25</v>
+      </c>
+      <c r="T19">
+        <v>3.34</v>
+      </c>
+      <c r="U19">
+        <v>2.2</v>
+      </c>
+      <c r="V19">
+        <v>1.57</v>
+      </c>
+      <c r="W19">
         <v>1.14</v>
       </c>
-      <c r="T19">
-        <v>4.3</v>
-      </c>
-      <c r="U19">
-        <v>1.87</v>
-      </c>
-      <c r="V19">
-        <v>1.83</v>
-      </c>
-      <c r="W19">
+      <c r="X19">
+        <v>1.03</v>
+      </c>
+      <c r="Y19">
+        <v>1.11</v>
+      </c>
+      <c r="Z19">
+        <v>3.3</v>
+      </c>
+      <c r="AA19">
+        <v>1.6</v>
+      </c>
+      <c r="AB19">
+        <v>2.2</v>
+      </c>
+      <c r="AC19">
+        <v>2.04</v>
+      </c>
+      <c r="AD19">
+        <v>1.44</v>
+      </c>
+      <c r="AE19">
+        <v>1.18</v>
+      </c>
+      <c r="AF19">
+        <v>1.53</v>
+      </c>
+      <c r="AG19">
+        <v>2.3</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>1.25</v>
+      </c>
+      <c r="AK19">
         <v>1.22</v>
-      </c>
-      <c r="X19">
-        <v>1.01</v>
-      </c>
-      <c r="Y19">
-        <v>1.05</v>
-      </c>
-      <c r="Z19">
-        <v>6.55</v>
-      </c>
-      <c r="AA19">
-        <v>1.33</v>
-      </c>
-      <c r="AB19">
-        <v>3.2</v>
-      </c>
-      <c r="AC19">
-        <v>1.77</v>
-      </c>
-      <c r="AD19">
-        <v>1.99</v>
-      </c>
-      <c r="AE19">
-        <v>1.39</v>
-      </c>
-      <c r="AF19">
-        <v>1.95</v>
-      </c>
-      <c r="AG19">
-        <v>1.75</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.06</v>
-      </c>
-      <c r="AK19">
-        <v>5.5</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,40 +3578,40 @@
         <v>2.6</v>
       </c>
       <c r="Q20">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="R20">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
         <v>1.25</v>
       </c>
       <c r="T20">
-        <v>3.45</v>
+        <v>2.75</v>
       </c>
       <c r="U20">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="V20">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z20">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AA20">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB20">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC20">
         <v>2.38</v>
@@ -3620,13 +3620,13 @@
         <v>1.5</v>
       </c>
       <c r="AE20">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF20">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AG20">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="AK20">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3735,61 +3735,61 @@
         <v>1.23</v>
       </c>
       <c r="O21">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="P21">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q21">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R21">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="S21">
         <v>1.16</v>
       </c>
       <c r="T21">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="U21">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="V21">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="W21">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z21">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AA21">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AB21">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AC21">
         <v>1.67</v>
       </c>
       <c r="AD21">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AE21">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG21">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK21">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,55 +3895,55 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="O22">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="P22">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Q22">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="R22">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="S22">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T22">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="U22">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="V22">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="W22">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X22">
         <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Z22">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="AA22">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AB22">
         <v>5</v>
       </c>
       <c r="AC22">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AD22">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="AE22">
         <v>1.83</v>
@@ -4061,31 +4061,31 @@
         <v>1.2</v>
       </c>
       <c r="O23">
-        <v>6.35</v>
+        <v>6.4</v>
       </c>
       <c r="P23">
-        <v>9.1</v>
+        <v>9.25</v>
       </c>
       <c r="Q23">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="R23">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="S23">
         <v>1.13</v>
       </c>
       <c r="T23">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="U23">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="V23">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="W23">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X23">
         <v>1.01</v>
@@ -4094,28 +4094,28 @@
         <v>1.05</v>
       </c>
       <c r="Z23">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AA23">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AB23">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AC23">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AD23">
         <v>2</v>
       </c>
       <c r="AE23">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AF23">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG23">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.05</v>
       </c>
       <c r="AK23">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,52 +4221,52 @@
         </is>
       </c>
       <c r="N24">
+        <v>2.1</v>
+      </c>
+      <c r="O24">
+        <v>3.25</v>
+      </c>
+      <c r="P24">
+        <v>3</v>
+      </c>
+      <c r="Q24">
         <v>2.63</v>
-      </c>
-      <c r="O24">
-        <v>3.1</v>
-      </c>
-      <c r="P24">
-        <v>2.4</v>
-      </c>
-      <c r="Q24">
-        <v>2.99</v>
       </c>
       <c r="R24">
         <v>2.2</v>
       </c>
       <c r="S24">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U24">
         <v>2.56</v>
       </c>
       <c r="V24">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
         <v>1.22</v>
       </c>
       <c r="Z24">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AA24">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AB24">
         <v>1.98</v>
       </c>
       <c r="AC24">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD24">
         <v>1.33</v>
@@ -4275,10 +4275,10 @@
         <v>1.09</v>
       </c>
       <c r="AF24">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4710,52 +4710,52 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P27">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q27">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="R27">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="S27">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="U27">
         <v>2.47</v>
       </c>
       <c r="V27">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W27">
         <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z27">
         <v>3.58</v>
       </c>
       <c r="AA27">
+        <v>1.87</v>
+      </c>
+      <c r="AB27">
         <v>1.85</v>
       </c>
-      <c r="AB27">
-        <v>1.95</v>
-      </c>
       <c r="AC27">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AD27">
         <v>1.33</v>
@@ -4764,10 +4764,10 @@
         <v>1.09</v>
       </c>
       <c r="AF27">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P28">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="Q28">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="R28">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="S28">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
-        <v>3.05</v>
+        <v>2.77</v>
       </c>
       <c r="U28">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="V28">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z28">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="AA28">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="AB28">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AC28">
-        <v>2.84</v>
+        <v>3.31</v>
       </c>
       <c r="AD28">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AE28">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AF28">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG28">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK28">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5039,31 +5039,31 @@
         <v>1.7</v>
       </c>
       <c r="O29">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="Q29">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="R29">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S29">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T29">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U29">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="V29">
         <v>1.54</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
         <v>1.03</v>
@@ -5072,28 +5072,28 @@
         <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA29">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB29">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC29">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD29">
         <v>1.47</v>
       </c>
       <c r="AE29">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF29">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AG29">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P30">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="Q30">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R30">
         <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T30">
         <v>3.4</v>
       </c>
       <c r="U30">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V30">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
         <v>1.04</v>
       </c>
       <c r="Y30">
+        <v>1.15</v>
+      </c>
+      <c r="Z30">
+        <v>4.25</v>
+      </c>
+      <c r="AA30">
+        <v>1.58</v>
+      </c>
+      <c r="AB30">
+        <v>2.2</v>
+      </c>
+      <c r="AC30">
+        <v>2.6</v>
+      </c>
+      <c r="AD30">
+        <v>1.5</v>
+      </c>
+      <c r="AE30">
         <v>1.14</v>
-      </c>
-      <c r="Z30">
-        <v>4.3</v>
-      </c>
-      <c r="AA30">
-        <v>1.61</v>
-      </c>
-      <c r="AB30">
-        <v>2.31</v>
-      </c>
-      <c r="AC30">
-        <v>2.4</v>
-      </c>
-      <c r="AD30">
-        <v>1.49</v>
-      </c>
-      <c r="AE30">
-        <v>1.2</v>
       </c>
       <c r="AF30">
         <v>1.53</v>
       </c>
       <c r="AG30">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK30">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5365,61 +5365,61 @@
         <v>2.02</v>
       </c>
       <c r="O31">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="P31">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q31">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R31">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
         <v>3.1</v>
       </c>
       <c r="U31">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V31">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W31">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X31">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>4.42</v>
+        <v>4.33</v>
       </c>
       <c r="AA31">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB31">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AC31">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AD31">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE31">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF31">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG31">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK31">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.9</v>
+        <v>3.05</v>
       </c>
       <c r="O37">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>3.18</v>
+        <v>2.4</v>
       </c>
       <c r="Q37">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U37">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="V37">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="AA37">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AB37">
-        <v>2.19</v>
+        <v>1.87</v>
       </c>
       <c r="AC37">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="AD37">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF37">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG37">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.91</v>
+        <v>1.31</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.05</v>
+        <v>1.9</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="P38">
-        <v>2.4</v>
+        <v>3.18</v>
       </c>
       <c r="Q38">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="R38">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T38">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U38">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="V38">
+        <v>1.47</v>
+      </c>
+      <c r="W38">
+        <v>1.08</v>
+      </c>
+      <c r="X38">
+        <v>1</v>
+      </c>
+      <c r="Y38">
+        <v>1.22</v>
+      </c>
+      <c r="Z38">
+        <v>3.7</v>
+      </c>
+      <c r="AA38">
+        <v>1.75</v>
+      </c>
+      <c r="AB38">
+        <v>2.19</v>
+      </c>
+      <c r="AC38">
+        <v>2.72</v>
+      </c>
+      <c r="AD38">
         <v>1.41</v>
       </c>
-      <c r="W38">
-        <v>1.06</v>
-      </c>
-      <c r="X38">
-        <v>1.05</v>
-      </c>
-      <c r="Y38">
-        <v>1.25</v>
-      </c>
-      <c r="Z38">
-        <v>3.45</v>
-      </c>
-      <c r="AA38">
-        <v>1.94</v>
-      </c>
-      <c r="AB38">
-        <v>1.87</v>
-      </c>
-      <c r="AC38">
-        <v>3.25</v>
-      </c>
-      <c r="AD38">
-        <v>1.33</v>
-      </c>
       <c r="AE38">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF38">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG38">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.31</v>
+        <v>1.91</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.99</v>
+        <v>4.4</v>
       </c>
       <c r="O40">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Q40">
-        <v>5.2</v>
+        <v>5.55</v>
       </c>
       <c r="R40">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S40">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T40">
-        <v>2.7</v>
+        <v>3.06</v>
       </c>
       <c r="U40">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="V40">
         <v>1.41</v>
       </c>
       <c r="W40">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y40">
+        <v>1.28</v>
+      </c>
+      <c r="Z40">
+        <v>3.4</v>
+      </c>
+      <c r="AA40">
+        <v>1.93</v>
+      </c>
+      <c r="AB40">
+        <v>1.89</v>
+      </c>
+      <c r="AC40">
+        <v>3</v>
+      </c>
+      <c r="AD40">
         <v>1.3</v>
-      </c>
-      <c r="Z40">
-        <v>3.6</v>
-      </c>
-      <c r="AA40">
-        <v>1.94</v>
-      </c>
-      <c r="AB40">
-        <v>1.88</v>
-      </c>
-      <c r="AC40">
-        <v>3.4</v>
-      </c>
-      <c r="AD40">
-        <v>1.33</v>
       </c>
       <c r="AE40">
         <v>1.11</v>
       </c>
       <c r="AF40">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG40">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>2.13</v>
+        <v>1.29</v>
       </c>
       <c r="AK40">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,61 +6992,61 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="O41">
         <v>17</v>
       </c>
       <c r="P41">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="Q41">
         <v>1.24</v>
       </c>
       <c r="R41">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="S41">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="T41">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="U41">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="V41">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="W41">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X41">
         <v>1</v>
       </c>
       <c r="Y41">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z41">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AA41">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AB41">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AC41">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AD41">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AE41">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AF41">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AG41">
         <v>1.5</v>
@@ -7155,19 +7155,19 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O42">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="P42">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q42">
         <v>2.3</v>
       </c>
       <c r="R42">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="S42">
         <v>1.32</v>
@@ -7176,37 +7176,37 @@
         <v>3.28</v>
       </c>
       <c r="U42">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="V42">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W42">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA42">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB42">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AC42">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AD42">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE42">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF42">
         <v>1.62</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="O43">
         <v>4.1</v>
       </c>
       <c r="P43">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="Q43">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R43">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="S43">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T43">
         <v>3.5</v>
       </c>
       <c r="U43">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="V43">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W43">
         <v>1.13</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
         <v>1.2</v>
       </c>
       <c r="Z43">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA43">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB43">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="AC43">
         <v>2.38</v>
       </c>
       <c r="AD43">
+        <v>1.51</v>
+      </c>
+      <c r="AE43">
+        <v>1.2</v>
+      </c>
+      <c r="AF43">
         <v>1.57</v>
       </c>
-      <c r="AE43">
-        <v>1.16</v>
-      </c>
-      <c r="AF43">
-        <v>1.6</v>
-      </c>
       <c r="AG43">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK43">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="O47">
         <v>3.1</v>
@@ -7979,10 +7979,10 @@
         <v>2.75</v>
       </c>
       <c r="Q47">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="R47">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="S47">
         <v>1.44</v>
@@ -7997,22 +7997,22 @@
         <v>1.3</v>
       </c>
       <c r="W47">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
         <v>1.08</v>
       </c>
       <c r="Y47">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Z47">
         <v>2.74</v>
       </c>
       <c r="AA47">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB47">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC47">
         <v>4</v>
@@ -8027,7 +8027,7 @@
         <v>1.85</v>
       </c>
       <c r="AG47">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
+        <v>2.58</v>
+      </c>
+      <c r="O48">
+        <v>3</v>
+      </c>
+      <c r="P48">
+        <v>2.3</v>
+      </c>
+      <c r="Q48">
+        <v>3.5</v>
+      </c>
+      <c r="R48">
+        <v>1.98</v>
+      </c>
+      <c r="S48">
         <v>1.5</v>
       </c>
-      <c r="O48">
-        <v>3.2</v>
-      </c>
-      <c r="P48">
-        <v>5.1</v>
-      </c>
-      <c r="Q48">
-        <v>2.14</v>
-      </c>
-      <c r="R48">
-        <v>2.06</v>
-      </c>
-      <c r="S48">
-        <v>1.45</v>
-      </c>
       <c r="T48">
-        <v>2.69</v>
+        <v>2.39</v>
       </c>
       <c r="U48">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="V48">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="W48">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y48">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z48">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="AA48">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="AB48">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC48">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="AD48">
         <v>1.19</v>
       </c>
       <c r="AE48">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF48">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG48">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK48">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.58</v>
+        <v>1.5</v>
       </c>
       <c r="O49">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P49">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="Q49">
-        <v>3.5</v>
+        <v>2.14</v>
       </c>
       <c r="R49">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="S49">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="T49">
-        <v>2.39</v>
+        <v>2.69</v>
       </c>
       <c r="U49">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="V49">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="W49">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X49">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z49">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="AA49">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AB49">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AC49">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="AD49">
         <v>1.19</v>
       </c>
       <c r="AE49">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF49">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AG49">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK49">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8462,7 +8462,7 @@
         <v>2</v>
       </c>
       <c r="O50">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P50">
         <v>3.05</v>
@@ -8471,7 +8471,7 @@
         <v>2.8</v>
       </c>
       <c r="R50">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S50">
         <v>1.32</v>
@@ -8480,7 +8480,7 @@
         <v>2.96</v>
       </c>
       <c r="U50">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="V50">
         <v>1.42</v>
@@ -8504,7 +8504,7 @@
         <v>1.95</v>
       </c>
       <c r="AC50">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD50">
         <v>1.36</v>
@@ -8628,34 +8628,34 @@
         <v>3.7</v>
       </c>
       <c r="P51">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q51">
         <v>2.05</v>
       </c>
       <c r="R51">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="S51">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T51">
         <v>3</v>
       </c>
       <c r="U51">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V51">
         <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z51">
         <v>3.6</v>
@@ -8664,16 +8664,16 @@
         <v>1.8</v>
       </c>
       <c r="AB51">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AC51">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD51">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE51">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
         <v>1.8</v>
@@ -8695,7 +8695,7 @@
         <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,25 +8785,25 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O52">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q52">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R52">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S52">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T52">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U52">
         <v>2.2</v>
@@ -8812,7 +8812,7 @@
         <v>1.6</v>
       </c>
       <c r="W52">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X52">
         <v>1.02</v>
@@ -8821,28 +8821,28 @@
         <v>1.14</v>
       </c>
       <c r="Z52">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA52">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AB52">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AC52">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AD52">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE52">
         <v>1.22</v>
       </c>
       <c r="AF52">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG52">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8957,10 +8957,10 @@
         <v>2.71</v>
       </c>
       <c r="Q53">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="R53">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S53">
         <v>1.25</v>
@@ -8990,13 +8990,13 @@
         <v>1.5</v>
       </c>
       <c r="AB53">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AC53">
         <v>2.38</v>
       </c>
       <c r="AD53">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE53">
         <v>1.22</v>
@@ -9138,7 +9138,7 @@
         <v>1.71</v>
       </c>
       <c r="W54">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X54">
         <v>1.02</v>
@@ -9184,7 +9184,7 @@
         <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9283,16 +9283,16 @@
         <v>2.2</v>
       </c>
       <c r="Q55">
-        <v>3.26</v>
+        <v>3.29</v>
       </c>
       <c r="R55">
         <v>2.42</v>
       </c>
       <c r="S55">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T55">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U55">
         <v>2.3</v>
@@ -9440,16 +9440,16 @@
         <v>2.33</v>
       </c>
       <c r="O56">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="P56">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="Q56">
         <v>3</v>
       </c>
       <c r="R56">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="S56">
         <v>1.3</v>
@@ -9482,7 +9482,7 @@
         <v>2.14</v>
       </c>
       <c r="AC56">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AD56">
         <v>1.42</v>
@@ -9491,10 +9491,10 @@
         <v>1.15</v>
       </c>
       <c r="AF56">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG56">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.27</v>
       </c>
       <c r="AK56">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9965,7 +9965,7 @@
         <v>7.5</v>
       </c>
       <c r="AA59">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB59">
         <v>3.1</v>
@@ -9980,10 +9980,10 @@
         <v>1.38</v>
       </c>
       <c r="AF59">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AG59">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G75">
@@ -12703,7 +12703,7 @@
         <v>2.25</v>
       </c>
       <c r="P76">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="O77">
         <v>3.4</v>
@@ -12869,16 +12869,16 @@
         <v>2.5</v>
       </c>
       <c r="Q77">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="R77">
         <v>2.2</v>
       </c>
       <c r="S77">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T77">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="U77">
         <v>2.45</v>
@@ -12893,31 +12893,31 @@
         <v>1.04</v>
       </c>
       <c r="Y77">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z77">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA77">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB77">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC77">
         <v>3</v>
       </c>
       <c r="AD77">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE77">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF77">
         <v>1.6</v>
       </c>
       <c r="AG77">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -13023,16 +13023,16 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O78">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P78">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q78">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R78">
         <v>2.66</v>
@@ -13044,10 +13044,10 @@
         <v>4.55</v>
       </c>
       <c r="U78">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="V78">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="W78">
         <v>1.28</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,19 +13186,19 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O79">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P79">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="Q79">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="R79">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S79">
         <v>1.25</v>
@@ -13207,10 +13207,10 @@
         <v>3.75</v>
       </c>
       <c r="U79">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="V79">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W79">
         <v>1.15</v>
@@ -13259,7 +13259,7 @@
         <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O80">
         <v>3.4</v>
       </c>
       <c r="P80">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q80">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="R80">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S80">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T80">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U80">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="V80">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W80">
         <v>1.08</v>
       </c>
       <c r="X80">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z80">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AA80">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB80">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC80">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AD80">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE80">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF80">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG80">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK80">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13838,19 +13838,19 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="O83">
-        <v>5.57</v>
+        <v>5.89</v>
       </c>
       <c r="P83">
-        <v>7.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q83">
         <v>1.7</v>
       </c>
       <c r="R83">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="S83">
         <v>1.17</v>
@@ -13859,7 +13859,7 @@
         <v>4.8</v>
       </c>
       <c r="U83">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="V83">
         <v>1.93</v>
@@ -13874,10 +13874,10 @@
         <v>1.1</v>
       </c>
       <c r="Z83">
-        <v>7.4</v>
+        <v>7.43</v>
       </c>
       <c r="AA83">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB83">
         <v>3.3</v>
@@ -14001,10 +14001,10 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="O84">
-        <v>5</v>
+        <v>5.45</v>
       </c>
       <c r="P84">
         <v>6.76</v>
@@ -14019,7 +14019,7 @@
         <v>1.17</v>
       </c>
       <c r="T84">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="U84">
         <v>1.93</v>
@@ -14037,16 +14037,16 @@
         <v>1.11</v>
       </c>
       <c r="Z84">
-        <v>7.27</v>
+        <v>7.26</v>
       </c>
       <c r="AA84">
         <v>1.3</v>
       </c>
       <c r="AB84">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="AC84">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AD84">
         <v>1.94</v>
@@ -14055,7 +14055,7 @@
         <v>1.36</v>
       </c>
       <c r="AF84">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG84">
         <v>2.5</v>
@@ -14182,7 +14182,7 @@
         <v>1.22</v>
       </c>
       <c r="T85">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U85">
         <v>2.05</v>
@@ -14194,7 +14194,7 @@
         <v>1.18</v>
       </c>
       <c r="X85">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
         <v>1.09</v>
@@ -14206,22 +14206,22 @@
         <v>1.48</v>
       </c>
       <c r="AB85">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC85">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD85">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AE85">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF85">
         <v>1.44</v>
       </c>
       <c r="AG85">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>1.21</v>
       </c>
       <c r="AK85">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL85">
         <v>0</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -1264,57 +1264,57 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>3.13</v>
+        <v>3.45</v>
       </c>
       <c r="O6">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q6">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="R6">
         <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>3.12</v>
+        <v>3.02</v>
       </c>
       <c r="U6">
-        <v>2.56</v>
+        <v>2.35</v>
       </c>
       <c r="V6">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
         <v>1.03</v>
@@ -1323,71 +1323,71 @@
         <v>1.19</v>
       </c>
       <c r="Z6">
-        <v>4.07</v>
+        <v>3.74</v>
       </c>
       <c r="AA6">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB6">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC6">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="AD6">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF6">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG6">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "24", "64"]</t>
         </is>
       </c>
       <c r="AJ6">
         <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1442,115 +1442,115 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O7">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="P7">
-        <v>7</v>
+        <v>7.08</v>
       </c>
       <c r="Q7">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="R7">
-        <v>2.74</v>
+        <v>2.57</v>
       </c>
       <c r="S7">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="T7">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="U7">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="V7">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="W7">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z7">
-        <v>5.08</v>
+        <v>4.95</v>
       </c>
       <c r="AA7">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB7">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AC7">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AD7">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE7">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF7">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AG7">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "32"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48"]</t>
         </is>
       </c>
       <c r="AJ7">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AK7">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1602,30 +1602,30 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
         <v>3.5</v>
       </c>
       <c r="O8">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="P8">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q8">
-        <v>4.39</v>
+        <v>4.81</v>
       </c>
       <c r="R8">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="S8">
         <v>1.68</v>
@@ -1640,16 +1640,16 @@
         <v>1.16</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="Z8">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="AA8">
         <v>3</v>
@@ -1658,62 +1658,62 @@
         <v>1.36</v>
       </c>
       <c r="AC8">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AD8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE8">
         <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="AG8">
         <v>1.55</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60", "65"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53"]</t>
         </is>
       </c>
       <c r="AJ8">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AK8">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1765,66 +1765,66 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
         <v>1.4</v>
       </c>
       <c r="O9">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P9">
-        <v>7.97</v>
+        <v>7.75</v>
       </c>
       <c r="Q9">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="R9">
         <v>2.05</v>
       </c>
       <c r="S9">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="T9">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="U9">
-        <v>3.38</v>
+        <v>3.21</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="W9">
         <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y9">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z9">
-        <v>2.71</v>
+        <v>2.65</v>
       </c>
       <c r="AA9">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AB9">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC9">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD9">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE9">
         <v>1</v>
@@ -1833,11 +1833,11 @@
         <v>2.71</v>
       </c>
       <c r="AG9">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -1846,37 +1846,37 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AK9">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,130 +1916,130 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="O10">
-        <v>5.33</v>
+        <v>4.7</v>
       </c>
       <c r="P10">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="Q10">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="R10">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="V10">
+        <v>1.4</v>
+      </c>
+      <c r="W10">
+        <v>1.1</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
+        <v>1.24</v>
+      </c>
+      <c r="Z10">
+        <v>3.34</v>
+      </c>
+      <c r="AA10">
+        <v>1.85</v>
+      </c>
+      <c r="AB10">
+        <v>1.95</v>
+      </c>
+      <c r="AC10">
+        <v>2.9</v>
+      </c>
+      <c r="AD10">
+        <v>1.38</v>
+      </c>
+      <c r="AE10">
+        <v>1.06</v>
+      </c>
+      <c r="AF10">
+        <v>2.2</v>
+      </c>
+      <c r="AG10">
+        <v>1.64</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>["21", "63", "86"]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
+        <v>1.1</v>
+      </c>
+      <c r="AK10">
+        <v>2.94</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>4</v>
+      </c>
+      <c r="AN10">
+        <v>1</v>
+      </c>
+      <c r="AO10">
+        <v>16</v>
+      </c>
+      <c r="AP10">
+        <v>8</v>
+      </c>
+      <c r="AQ10">
         <v>1.46</v>
       </c>
-      <c r="W10">
-        <v>1.07</v>
-      </c>
-      <c r="X10">
-        <v>1.02</v>
-      </c>
-      <c r="Y10">
-        <v>1.16</v>
-      </c>
-      <c r="Z10">
-        <v>4.15</v>
-      </c>
-      <c r="AA10">
-        <v>1.65</v>
-      </c>
-      <c r="AB10">
-        <v>2.15</v>
-      </c>
-      <c r="AC10">
-        <v>2.62</v>
-      </c>
-      <c r="AD10">
-        <v>1.45</v>
-      </c>
-      <c r="AE10">
-        <v>1.17</v>
-      </c>
-      <c r="AF10">
-        <v>1.95</v>
-      </c>
-      <c r="AG10">
-        <v>1.75</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.13</v>
-      </c>
-      <c r="AK10">
-        <v>3.5</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>-1</v>
-      </c>
-      <c r="AN10">
-        <v>-1</v>
-      </c>
-      <c r="AO10">
-        <v>-1</v>
-      </c>
-      <c r="AP10">
-        <v>-1</v>
-      </c>
-      <c r="AQ10">
-        <v>0</v>
-      </c>
       <c r="AR10">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,91 +2079,91 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="O11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P11">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q11">
-        <v>2.04</v>
+        <v>1.79</v>
       </c>
       <c r="R11">
+        <v>2.52</v>
+      </c>
+      <c r="S11">
+        <v>1.22</v>
+      </c>
+      <c r="T11">
+        <v>3.75</v>
+      </c>
+      <c r="U11">
+        <v>2.2</v>
+      </c>
+      <c r="V11">
+        <v>1.57</v>
+      </c>
+      <c r="W11">
+        <v>1.15</v>
+      </c>
+      <c r="X11">
+        <v>1.01</v>
+      </c>
+      <c r="Y11">
+        <v>1.17</v>
+      </c>
+      <c r="Z11">
+        <v>4.78</v>
+      </c>
+      <c r="AA11">
+        <v>1.5</v>
+      </c>
+      <c r="AB11">
+        <v>2.28</v>
+      </c>
+      <c r="AC11">
         <v>2.29</v>
       </c>
-      <c r="S11">
-        <v>1.28</v>
-      </c>
-      <c r="T11">
-        <v>3.14</v>
-      </c>
-      <c r="U11">
-        <v>2.38</v>
-      </c>
-      <c r="V11">
-        <v>1.5</v>
-      </c>
-      <c r="W11">
-        <v>1.12</v>
-      </c>
-      <c r="X11">
-        <v>1.03</v>
-      </c>
-      <c r="Y11">
-        <v>1.16</v>
-      </c>
-      <c r="Z11">
-        <v>4.5</v>
-      </c>
-      <c r="AA11">
-        <v>1.62</v>
-      </c>
-      <c r="AB11">
-        <v>2.2</v>
-      </c>
-      <c r="AC11">
-        <v>2.57</v>
-      </c>
       <c r="AD11">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF11">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "38", "88"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2172,37 +2172,37 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK11">
-        <v>2.26</v>
+        <v>2.62</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,16 +2242,16 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2274,28 +2274,28 @@
         <v>2.1</v>
       </c>
       <c r="Q12">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="R12">
         <v>2.1</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U12">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
         <v>1.26</v>
@@ -2304,68 +2304,68 @@
         <v>3.2</v>
       </c>
       <c r="AA12">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AB12">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC12">
         <v>3.2</v>
       </c>
       <c r="AD12">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
         <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33"]</t>
         </is>
       </c>
       <c r="AJ12">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AK12">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,48 +2405,48 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>2.71</v>
+        <v>2.95</v>
       </c>
       <c r="O13">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P13">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q13">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="R13">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="S13">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T13">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="U13">
         <v>2.88</v>
@@ -2455,13 +2455,13 @@
         <v>1.36</v>
       </c>
       <c r="W13">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y13">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z13">
         <v>3</v>
@@ -2473,32 +2473,32 @@
         <v>1.67</v>
       </c>
       <c r="AC13">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD13">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE13">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF13">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG13">
         <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "23", "49"]</t>
         </is>
       </c>
       <c r="AJ13">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AK13">
         <v>1.4</v>
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2917,58 +2917,58 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="O16">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P16">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="Q16">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R16">
         <v>2.2</v>
       </c>
       <c r="S16">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T16">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="U16">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="V16">
         <v>1.45</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
         <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z16">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA16">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB16">
         <v>2</v>
       </c>
       <c r="AC16">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AD16">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE16">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF16">
         <v>1.57</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AK16">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.12</v>
+        <v>2.4</v>
       </c>
       <c r="O18">
-        <v>7.5</v>
+        <v>3.7</v>
       </c>
       <c r="P18">
-        <v>14</v>
+        <v>2.45</v>
       </c>
       <c r="Q18">
+        <v>2.9</v>
+      </c>
+      <c r="R18">
+        <v>2.4</v>
+      </c>
+      <c r="S18">
+        <v>1.18</v>
+      </c>
+      <c r="T18">
+        <v>2.8</v>
+      </c>
+      <c r="U18">
+        <v>1.87</v>
+      </c>
+      <c r="V18">
+        <v>1.5</v>
+      </c>
+      <c r="W18">
+        <v>1.14</v>
+      </c>
+      <c r="X18">
+        <v>1.03</v>
+      </c>
+      <c r="Y18">
+        <v>1.15</v>
+      </c>
+      <c r="Z18">
+        <v>3.4</v>
+      </c>
+      <c r="AA18">
         <v>1.4</v>
       </c>
-      <c r="R18">
-        <v>3.28</v>
-      </c>
-      <c r="S18">
-        <v>1.14</v>
-      </c>
-      <c r="T18">
-        <v>4.33</v>
-      </c>
-      <c r="U18">
-        <v>1.88</v>
-      </c>
-      <c r="V18">
-        <v>1.88</v>
-      </c>
-      <c r="W18">
+      <c r="AB18">
+        <v>2.05</v>
+      </c>
+      <c r="AC18">
+        <v>2.2</v>
+      </c>
+      <c r="AD18">
+        <v>1.57</v>
+      </c>
+      <c r="AE18">
         <v>1.22</v>
       </c>
-      <c r="X18">
-        <v>1.01</v>
-      </c>
-      <c r="Y18">
-        <v>1.05</v>
-      </c>
-      <c r="Z18">
-        <v>6.6</v>
-      </c>
-      <c r="AA18">
-        <v>1.3</v>
-      </c>
-      <c r="AB18">
-        <v>2.63</v>
-      </c>
-      <c r="AC18">
-        <v>1.77</v>
-      </c>
-      <c r="AD18">
-        <v>1.85</v>
-      </c>
-      <c r="AE18">
-        <v>1.36</v>
-      </c>
       <c r="AF18">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AG18">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK18">
-        <v>5.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.8</v>
+        <v>1.12</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>7.75</v>
       </c>
       <c r="P19">
-        <v>1.74</v>
+        <v>11</v>
       </c>
       <c r="Q19">
-        <v>3.68</v>
+        <v>1.4</v>
       </c>
       <c r="R19">
-        <v>2.23</v>
+        <v>3.52</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="T19">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U19">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="V19">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="W19">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19">
         <v>1.03</v>
       </c>
-      <c r="Y19">
-        <v>1.11</v>
-      </c>
       <c r="Z19">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="AA19">
+        <v>1.21</v>
+      </c>
+      <c r="AB19">
+        <v>2.9</v>
+      </c>
+      <c r="AC19">
         <v>1.6</v>
       </c>
-      <c r="AB19">
-        <v>2.2</v>
-      </c>
-      <c r="AC19">
-        <v>2.04</v>
-      </c>
       <c r="AD19">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AE19">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AF19">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG19">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK19">
-        <v>1.22</v>
+        <v>5</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,37 +3569,37 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="O20">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="Q20">
-        <v>2.75</v>
+        <v>3.68</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S20">
         <v>1.25</v>
       </c>
       <c r="T20">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="U20">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="V20">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="W20">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
         <v>1.17</v>
@@ -3608,10 +3608,10 @@
         <v>4.6</v>
       </c>
       <c r="AA20">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB20">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AC20">
         <v>2.38</v>
@@ -3620,13 +3620,13 @@
         <v>1.5</v>
       </c>
       <c r="AE20">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF20">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AG20">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.08</v>
+        <v>1.65</v>
       </c>
       <c r="AK20">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="O21">
         <v>6.9</v>
       </c>
       <c r="P21">
-        <v>9.949999999999999</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R21">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="S21">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T21">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="U21">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V21">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="W21">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Z21">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA21">
         <v>1.25</v>
       </c>
       <c r="AB21">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AC21">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AD21">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AE21">
+        <v>1.55</v>
+      </c>
+      <c r="AF21">
         <v>1.53</v>
       </c>
-      <c r="AF21">
-        <v>1.62</v>
-      </c>
       <c r="AG21">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AK21">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3898,61 +3898,61 @@
         <v>1.07</v>
       </c>
       <c r="O22">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="P22">
         <v>20</v>
       </c>
       <c r="Q22">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="R22">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="S22">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="T22">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="V22">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="W22">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X22">
         <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Z22">
-        <v>13</v>
+        <v>8.9</v>
       </c>
       <c r="AA22">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AB22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC22">
         <v>1.4</v>
       </c>
       <c r="AD22">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="AE22">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AF22">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG22">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4221,28 +4221,28 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O24">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P24">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="Q24">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R24">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T24">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="U24">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="V24">
         <v>1.44</v>
@@ -4251,7 +4251,7 @@
         <v>1.1</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
         <v>1.22</v>
@@ -4278,7 +4278,7 @@
         <v>1.58</v>
       </c>
       <c r="AG24">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="O25">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="P25">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q25">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R25">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="S25">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="T25">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="U25">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="V25">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W25">
         <v>1.01</v>
       </c>
       <c r="X25">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Y25">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="Z25">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="AA25">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AB25">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AC25">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="AD25">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AE25">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF25">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AG25">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AK25">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>6.72</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P26">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="Q26">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="S26">
         <v>1.38</v>
       </c>
       <c r="T26">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U26">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="V26">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W26">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="AA26">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AB26">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AC26">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD26">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE26">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AG26">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK26">
         <v>1.07</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="O32">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="P32">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Q32">
         <v>1.67</v>
       </c>
       <c r="R32">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S32">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U32">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="V32">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X32">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA32">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB32">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AC32">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="AD32">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF32">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AG32">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK32">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5691,77 +5691,77 @@
         <v>3.8</v>
       </c>
       <c r="O33">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="Q33">
-        <v>4.15</v>
+        <v>3.53</v>
       </c>
       <c r="R33">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
         <v>1.24</v>
       </c>
       <c r="T33">
-        <v>3.32</v>
+        <v>3.42</v>
       </c>
       <c r="U33">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="V33">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
         <v>1.09</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
+        <v>1.17</v>
+      </c>
+      <c r="Z33">
+        <v>4.8</v>
+      </c>
+      <c r="AA33">
+        <v>1.53</v>
+      </c>
+      <c r="AB33">
+        <v>2.25</v>
+      </c>
+      <c r="AC33">
+        <v>2.38</v>
+      </c>
+      <c r="AD33">
+        <v>1.5</v>
+      </c>
+      <c r="AE33">
+        <v>1.18</v>
+      </c>
+      <c r="AF33">
+        <v>1.5</v>
+      </c>
+      <c r="AG33">
+        <v>2.3</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
+        <v>1.91</v>
+      </c>
+      <c r="AK33">
         <v>1.2</v>
-      </c>
-      <c r="Z33">
-        <v>4</v>
-      </c>
-      <c r="AA33">
-        <v>1.65</v>
-      </c>
-      <c r="AB33">
-        <v>2.16</v>
-      </c>
-      <c r="AC33">
-        <v>2.63</v>
-      </c>
-      <c r="AD33">
-        <v>1.4</v>
-      </c>
-      <c r="AE33">
-        <v>1.15</v>
-      </c>
-      <c r="AF33">
-        <v>1.57</v>
-      </c>
-      <c r="AG33">
-        <v>2.2</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33">
-        <v>1.25</v>
-      </c>
-      <c r="AK33">
-        <v>1.25</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="O34">
-        <v>7.29</v>
+        <v>9</v>
       </c>
       <c r="P34">
-        <v>11.06</v>
+        <v>14</v>
       </c>
       <c r="Q34">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="R34">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="S34">
         <v>1.17</v>
       </c>
       <c r="T34">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="U34">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="V34">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W34">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z34">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="AA34">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AB34">
         <v>3.4</v>
       </c>
       <c r="AC34">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AD34">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AE34">
         <v>1.4</v>
       </c>
       <c r="AF34">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG34">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AK34">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="O35">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="P35">
         <v>3.4</v>
       </c>
       <c r="Q35">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="R35">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="S35">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="T35">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="U35">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="V35">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W35">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y35">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="Z35">
-        <v>2.36</v>
+        <v>2.69</v>
       </c>
       <c r="AA35">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="AB35">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AC35">
-        <v>4.75</v>
+        <v>3.82</v>
       </c>
       <c r="AD35">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE35">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF35">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="AG35">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.36</v>
       </c>
       <c r="AK35">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.05</v>
+        <v>1.9</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="P37">
-        <v>2.4</v>
+        <v>3.18</v>
       </c>
       <c r="Q37">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="R37">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="S37">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="V37">
+        <v>1.47</v>
+      </c>
+      <c r="W37">
+        <v>1.08</v>
+      </c>
+      <c r="X37">
+        <v>1</v>
+      </c>
+      <c r="Y37">
+        <v>1.22</v>
+      </c>
+      <c r="Z37">
+        <v>3.7</v>
+      </c>
+      <c r="AA37">
+        <v>1.75</v>
+      </c>
+      <c r="AB37">
+        <v>2.19</v>
+      </c>
+      <c r="AC37">
+        <v>2.72</v>
+      </c>
+      <c r="AD37">
         <v>1.41</v>
       </c>
-      <c r="W37">
-        <v>1.06</v>
-      </c>
-      <c r="X37">
-        <v>1.05</v>
-      </c>
-      <c r="Y37">
-        <v>1.25</v>
-      </c>
-      <c r="Z37">
-        <v>3.45</v>
-      </c>
-      <c r="AA37">
-        <v>1.94</v>
-      </c>
-      <c r="AB37">
-        <v>1.87</v>
-      </c>
-      <c r="AC37">
-        <v>3.25</v>
-      </c>
-      <c r="AD37">
-        <v>1.33</v>
-      </c>
       <c r="AE37">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF37">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG37">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>1.31</v>
+        <v>1.91</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.9</v>
+        <v>3.05</v>
       </c>
       <c r="O38">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
-        <v>3.18</v>
+        <v>2.4</v>
       </c>
       <c r="Q38">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="S38">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T38">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U38">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="V38">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y38">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z38">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="AA38">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AB38">
-        <v>2.19</v>
+        <v>1.87</v>
       </c>
       <c r="AC38">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="AD38">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE38">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF38">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG38">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.91</v>
+        <v>1.31</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.4</v>
+        <v>5.75</v>
       </c>
       <c r="O40">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P40">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="Q40">
-        <v>5.55</v>
+        <v>6.1</v>
       </c>
       <c r="R40">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S40">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T40">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="U40">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="V40">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X40">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z40">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="AA40">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AB40">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AC40">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AD40">
         <v>1.3</v>
       </c>
       <c r="AE40">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF40">
         <v>1.91</v>
       </c>
       <c r="AG40">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK40">
         <v>1.12</v>
@@ -6992,61 +6992,61 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="O41">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="P41">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="Q41">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="R41">
-        <v>4.76</v>
+        <v>4.8</v>
       </c>
       <c r="S41">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="T41">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="U41">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="V41">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="W41">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="X41">
         <v>1</v>
       </c>
       <c r="Y41">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z41">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AA41">
         <v>1.14</v>
       </c>
       <c r="AB41">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AC41">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AD41">
-        <v>2.42</v>
+        <v>2.85</v>
       </c>
       <c r="AE41">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AF41">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AG41">
         <v>1.5</v>
@@ -7065,7 +7065,7 @@
         <v>1.02</v>
       </c>
       <c r="AK41">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,34 +7155,34 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="O42">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P42">
-        <v>4.2</v>
+        <v>4.63</v>
       </c>
       <c r="Q42">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="R42">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T42">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="U42">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="V42">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W42">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X42">
         <v>1.01</v>
@@ -7191,28 +7191,28 @@
         <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA42">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB42">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC42">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD42">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AE42">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF42">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG42">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="O43">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P43">
-        <v>4.55</v>
+        <v>4.15</v>
       </c>
       <c r="Q43">
         <v>2.25</v>
@@ -7333,49 +7333,49 @@
         <v>2.4</v>
       </c>
       <c r="S43">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T43">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="U43">
-        <v>2.36</v>
+        <v>2.13</v>
       </c>
       <c r="V43">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W43">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X43">
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z43">
-        <v>4.8</v>
+        <v>5.05</v>
       </c>
       <c r="AA43">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB43">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AC43">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AD43">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AE43">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF43">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG43">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.2</v>
       </c>
       <c r="AK43">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.58</v>
+        <v>1.5</v>
       </c>
       <c r="O48">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P48">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="Q48">
-        <v>3.5</v>
+        <v>2.14</v>
       </c>
       <c r="R48">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="S48">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="T48">
-        <v>2.39</v>
+        <v>2.69</v>
       </c>
       <c r="U48">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="V48">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="W48">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X48">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z48">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="AA48">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AB48">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AC48">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="AD48">
         <v>1.19</v>
       </c>
       <c r="AE48">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF48">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AG48">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK48">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
+        <v>2.58</v>
+      </c>
+      <c r="O49">
+        <v>3</v>
+      </c>
+      <c r="P49">
+        <v>2.3</v>
+      </c>
+      <c r="Q49">
+        <v>3.5</v>
+      </c>
+      <c r="R49">
+        <v>1.98</v>
+      </c>
+      <c r="S49">
         <v>1.5</v>
       </c>
-      <c r="O49">
-        <v>3.2</v>
-      </c>
-      <c r="P49">
-        <v>5.1</v>
-      </c>
-      <c r="Q49">
-        <v>2.14</v>
-      </c>
-      <c r="R49">
-        <v>2.06</v>
-      </c>
-      <c r="S49">
-        <v>1.45</v>
-      </c>
       <c r="T49">
-        <v>2.69</v>
+        <v>2.39</v>
       </c>
       <c r="U49">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="V49">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="W49">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y49">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z49">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="AA49">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="AB49">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AC49">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="AD49">
         <v>1.19</v>
       </c>
       <c r="AE49">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG49">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK49">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8963,22 +8963,22 @@
         <v>2.45</v>
       </c>
       <c r="S53">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T53">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="U53">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="V53">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W53">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X53">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
         <v>1.15</v>
@@ -8993,7 +8993,7 @@
         <v>2.45</v>
       </c>
       <c r="AC53">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD53">
         <v>1.6</v>
@@ -9123,22 +9123,22 @@
         <v>2.45</v>
       </c>
       <c r="R54">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S54">
         <v>1.22</v>
       </c>
       <c r="T54">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="U54">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="V54">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="W54">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X54">
         <v>1.02</v>
@@ -9150,7 +9150,7 @@
         <v>6.1</v>
       </c>
       <c r="AA54">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB54">
         <v>2.7</v>
@@ -9159,7 +9159,7 @@
         <v>2.02</v>
       </c>
       <c r="AD54">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE54">
         <v>1.31</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.03</v>
+        <v>2.33</v>
       </c>
       <c r="O55">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P55">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q55">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="R55">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="S55">
         <v>1.3</v>
       </c>
       <c r="T55">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U55">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V55">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="W55">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X55">
         <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z55">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AA55">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB55">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC55">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD55">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE55">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF55">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AG55">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK55">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.33</v>
+        <v>3.44</v>
       </c>
       <c r="O56">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="P56">
-        <v>2.67</v>
+        <v>1.95</v>
       </c>
       <c r="Q56">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="R56">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S56">
         <v>1.3</v>
       </c>
       <c r="T56">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U56">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V56">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="W56">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X56">
         <v>1.04</v>
       </c>
       <c r="Y56">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z56">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="AA56">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB56">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AC56">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AD56">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE56">
         <v>1.15</v>
       </c>
       <c r="AF56">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AG56">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK56">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9929,7 +9929,7 @@
         <v>1.62</v>
       </c>
       <c r="O59">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P59">
         <v>3.8</v>
@@ -9941,40 +9941,40 @@
         <v>2.7</v>
       </c>
       <c r="S59">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T59">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="U59">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="V59">
         <v>1.85</v>
       </c>
       <c r="W59">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X59">
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z59">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA59">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB59">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AC59">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AD59">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AE59">
         <v>1.38</v>
@@ -9983,7 +9983,7 @@
         <v>1.38</v>
       </c>
       <c r="AG59">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK59">
         <v>2.1</v>
@@ -12700,7 +12700,7 @@
         <v>2.6</v>
       </c>
       <c r="O76">
-        <v>2.25</v>
+        <v>3.55</v>
       </c>
       <c r="P76">
         <v>2.47</v>
@@ -12736,10 +12736,10 @@
         <v>0</v>
       </c>
       <c r="AA76">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB76">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC76">
         <v>0</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O77">
         <v>3.4</v>
@@ -12869,16 +12869,16 @@
         <v>2.5</v>
       </c>
       <c r="Q77">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="R77">
         <v>2.2</v>
       </c>
       <c r="S77">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T77">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="U77">
         <v>2.45</v>
@@ -12893,22 +12893,22 @@
         <v>1.04</v>
       </c>
       <c r="Y77">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z77">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA77">
         <v>1.75</v>
       </c>
       <c r="AB77">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC77">
         <v>3</v>
       </c>
       <c r="AD77">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE77">
         <v>1.11</v>
@@ -13029,25 +13029,25 @@
         <v>3.9</v>
       </c>
       <c r="P78">
+        <v>2.6</v>
+      </c>
+      <c r="Q78">
         <v>2.5</v>
       </c>
-      <c r="Q78">
-        <v>2.6</v>
-      </c>
       <c r="R78">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="S78">
         <v>1.17</v>
       </c>
       <c r="T78">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="U78">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V78">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="W78">
         <v>1.28</v>
@@ -13068,13 +13068,13 @@
         <v>3.8</v>
       </c>
       <c r="AC78">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AD78">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AE78">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF78">
         <v>1.25</v>
@@ -13096,7 +13096,7 @@
         <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,19 +13186,19 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O79">
         <v>3.5</v>
       </c>
       <c r="P79">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q79">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="R79">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S79">
         <v>1.25</v>
@@ -13207,7 +13207,7 @@
         <v>3.75</v>
       </c>
       <c r="U79">
-        <v>2.16</v>
+        <v>2.29</v>
       </c>
       <c r="V79">
         <v>1.61</v>
@@ -13228,10 +13228,10 @@
         <v>1.57</v>
       </c>
       <c r="AB79">
+        <v>2.38</v>
+      </c>
+      <c r="AC79">
         <v>2.3</v>
-      </c>
-      <c r="AC79">
-        <v>2.38</v>
       </c>
       <c r="AD79">
         <v>1.53</v>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK79">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13352,16 +13352,16 @@
         <v>1.95</v>
       </c>
       <c r="O80">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P80">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="Q80">
-        <v>2.57</v>
+        <v>2.49</v>
       </c>
       <c r="R80">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S80">
         <v>1.29</v>
@@ -13370,7 +13370,7 @@
         <v>3.3</v>
       </c>
       <c r="U80">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="V80">
         <v>1.45</v>
@@ -13379,7 +13379,7 @@
         <v>1.08</v>
       </c>
       <c r="X80">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y80">
         <v>1.22</v>
@@ -13391,13 +13391,13 @@
         <v>1.66</v>
       </c>
       <c r="AB80">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC80">
         <v>2.88</v>
       </c>
       <c r="AD80">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE80">
         <v>1.15</v>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK80">
         <v>1.85</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="O82">
-        <v>4.26</v>
+        <v>4.31</v>
       </c>
       <c r="P82">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="Q82">
         <v>2.2</v>
@@ -13699,10 +13699,10 @@
         <v>2.01</v>
       </c>
       <c r="V82">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W82">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X82">
         <v>1.01</v>
@@ -13711,10 +13711,10 @@
         <v>1.12</v>
       </c>
       <c r="Z82">
-        <v>6.54</v>
+        <v>6.55</v>
       </c>
       <c r="AA82">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB82">
         <v>2.99</v>
@@ -13729,10 +13729,10 @@
         <v>1.3</v>
       </c>
       <c r="AF82">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG82">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13838,19 +13838,19 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="O83">
-        <v>5.89</v>
+        <v>5.25</v>
       </c>
       <c r="P83">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q83">
         <v>1.7</v>
       </c>
       <c r="R83">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="S83">
         <v>1.17</v>
@@ -13889,13 +13889,13 @@
         <v>1.94</v>
       </c>
       <c r="AE83">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF83">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG83">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK83">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,34 +14001,34 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="O84">
-        <v>5.45</v>
+        <v>4.8</v>
       </c>
       <c r="P84">
-        <v>6.76</v>
+        <v>6.6</v>
       </c>
       <c r="Q84">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R84">
         <v>2.75</v>
       </c>
       <c r="S84">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T84">
         <v>4.4</v>
       </c>
       <c r="U84">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V84">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="W84">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X84">
         <v>1.01</v>
@@ -14037,13 +14037,13 @@
         <v>1.11</v>
       </c>
       <c r="Z84">
-        <v>7.26</v>
+        <v>7.13</v>
       </c>
       <c r="AA84">
         <v>1.3</v>
       </c>
       <c r="AB84">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="AC84">
         <v>1.85</v>
@@ -14052,13 +14052,13 @@
         <v>1.94</v>
       </c>
       <c r="AE84">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF84">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG84">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>1.11</v>
       </c>
       <c r="AK84">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,19 +14164,19 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O85">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P85">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q85">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="R85">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S85">
         <v>1.22</v>
@@ -14188,7 +14188,7 @@
         <v>2.05</v>
       </c>
       <c r="V85">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W85">
         <v>1.18</v>
@@ -14197,19 +14197,19 @@
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z85">
-        <v>5.5</v>
+        <v>6.15</v>
       </c>
       <c r="AA85">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB85">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AC85">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD85">
         <v>1.75</v>
@@ -14218,7 +14218,7 @@
         <v>1.31</v>
       </c>
       <c r="AF85">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG85">
         <v>2.88</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK85">
         <v>1.57</v>

--- a/jogos_2026-09-09.xlsx
+++ b/jogos_2026-09-09.xlsx
@@ -2568,130 +2568,130 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="O14">
-        <v>3.52</v>
+        <v>3.66</v>
       </c>
       <c r="P14">
-        <v>3.58</v>
+        <v>4.09</v>
       </c>
       <c r="Q14">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="R14">
         <v>2.2</v>
       </c>
       <c r="S14">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T14">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="U14">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="V14">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z14">
-        <v>3.58</v>
+        <v>3.89</v>
       </c>
       <c r="AA14">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AB14">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC14">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="AD14">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE14">
         <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AG14">
         <v>2.05</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
+          <t>["44", "55", "70"]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,130 +2731,130 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="O15">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q15">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="R15">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S15">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T15">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="U15">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="V15">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
+        <v>1.08</v>
+      </c>
+      <c r="X15">
+        <v>1.03</v>
+      </c>
+      <c r="Y15">
+        <v>1.31</v>
+      </c>
+      <c r="Z15">
+        <v>3</v>
+      </c>
+      <c r="AA15">
+        <v>2.05</v>
+      </c>
+      <c r="AB15">
+        <v>1.7</v>
+      </c>
+      <c r="AC15">
+        <v>3.7</v>
+      </c>
+      <c r="AD15">
+        <v>1.22</v>
+      </c>
+      <c r="AE15">
         <v>1.05</v>
       </c>
-      <c r="X15">
-        <v>1.02</v>
-      </c>
-      <c r="Y15">
-        <v>1.28</v>
-      </c>
-      <c r="Z15">
-        <v>3.08</v>
-      </c>
-      <c r="AA15">
-        <v>1.93</v>
-      </c>
-      <c r="AB15">
-        <v>1.76</v>
-      </c>
-      <c r="AC15">
-        <v>2.75</v>
-      </c>
-      <c r="AD15">
-        <v>1.25</v>
-      </c>
-      <c r="AE15">
-        <v>1.06</v>
-      </c>
       <c r="AF15">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AG15">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "30", "69", "73", "90+4"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89"]</t>
         </is>
       </c>
       <c r="AJ15">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK15">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,26 +2894,26 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,12 +2978,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "87"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -3069,60 +3069,60 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="O17">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="P17">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q17">
-        <v>4.95</v>
+        <v>4.55</v>
       </c>
       <c r="R17">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="S17">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="T17">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="U17">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V17">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W17">
         <v>1.01</v>
       </c>
       <c r="X17">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z17">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="AA17">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AB17">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AC17">
         <v>4.5</v>
@@ -3134,53 +3134,53 @@
         <v>1.01</v>
       </c>
       <c r="AF17">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AG17">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
+          <t>["47", "72"]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ17">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AK17">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3211,63 +3211,63 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O18">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="Q18">
-        <v>2.9</v>
+        <v>3.68</v>
       </c>
       <c r="R18">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S18">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="U18">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="V18">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W18">
         <v>1.14</v>
@@ -3276,31 +3276,31 @@
         <v>1.03</v>
       </c>
       <c r="Y18">
+        <v>1.17</v>
+      </c>
+      <c r="Z18">
+        <v>4.6</v>
+      </c>
+      <c r="AA18">
+        <v>1.6</v>
+      </c>
+      <c r="AB18">
+        <v>2.19</v>
+      </c>
+      <c r="AC18">
+        <v>2.38</v>
+      </c>
+      <c r="AD18">
+        <v>1.5</v>
+      </c>
+      <c r="AE18">
         <v>1.15</v>
       </c>
-      <c r="Z18">
-        <v>3.4</v>
-      </c>
-      <c r="AA18">
-        <v>1.4</v>
-      </c>
-      <c r="AB18">
-        <v>2.05</v>
-      </c>
-      <c r="AC18">
-        <v>2.2</v>
-      </c>
-      <c r="AD18">
-        <v>1.57</v>
-      </c>
-      <c r="AE18">
-        <v>1.22</v>
-      </c>
       <c r="AF18">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AG18">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3309,41 +3309,41 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "56"]</t>
         </is>
       </c>
       <c r="AJ18">
-        <v>1.2</v>
+        <v>1.65</v>
       </c>
       <c r="AK18">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,26 +3383,26 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "40", "81", "88"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
@@ -3485,28 +3485,28 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3537,63 +3537,63 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P20">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="Q20">
-        <v>3.68</v>
+        <v>2.9</v>
       </c>
       <c r="R20">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S20">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T20">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="U20">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="V20">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W20">
         <v>1.14</v>
@@ -3602,74 +3602,74 @@
         <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z20">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA20">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AB20">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AC20">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AD20">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE20">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF20">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AG20">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "42", "51"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["78", "80"]</t>
         </is>
       </c>
       <c r="AJ20">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,16 +3709,16 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "26", "32"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22"]</t>
         </is>
       </c>
       <c r="AJ21">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3872,26 +3872,26 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "22", "57", "77", "85"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["82"]</t>
         </is>
       </c>
       <c r="AJ22">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -4047,42 +4047,42 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="O23">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="P23">
-        <v>9.25</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R23">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="S23">
         <v>1.13</v>
       </c>
       <c r="T23">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="U23">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="V23">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="W23">
         <v>1.26</v>
@@ -4097,29 +4097,29 @@
         <v>8.5</v>
       </c>
       <c r="AA23">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AB23">
         <v>3.6</v>
       </c>
       <c r="AC23">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AD23">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AE23">
         <v>1.45</v>
       </c>
       <c r="AF23">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG23">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
@@ -4131,34 +4131,34 @@
         <v>1.05</v>
       </c>
       <c r="AK23">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -4210,14 +4210,14 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["62", "87"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4352,22 +4352,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4376,115 +4376,115 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="O25">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="P25">
-        <v>2.45</v>
+        <v>1.35</v>
       </c>
       <c r="Q25">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>1.82</v>
+        <v>2.34</v>
       </c>
       <c r="S25">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="T25">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="V25">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="W25">
+        <v>1.05</v>
+      </c>
+      <c r="X25">
         <v>1.01</v>
       </c>
-      <c r="X25">
-        <v>1.14</v>
-      </c>
       <c r="Y25">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="Z25">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="AA25">
-        <v>2.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB25">
-        <v>1.24</v>
+        <v>1.83</v>
       </c>
       <c r="AC25">
-        <v>7.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD25">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AE25">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AF25">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AG25">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39"]</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58"]</t>
         </is>
       </c>
       <c r="AJ25">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AK25">
-        <v>1.3</v>
+        <v>1.07</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4515,22 +4515,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4539,115 +4539,115 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="O26">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
       <c r="P26">
-        <v>1.35</v>
+        <v>2.45</v>
       </c>
       <c r="Q26">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="R26">
-        <v>2.34</v>
+        <v>1.82</v>
       </c>
       <c r="S26">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="T26">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="U26">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="V26">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X26">
+        <v>1.14</v>
+      </c>
+      <c r="Y26">
+        <v>1.78</v>
+      </c>
+      <c r="Z26">
+        <v>1.93</v>
+      </c>
+      <c r="AA26">
+        <v>2.95</v>
+      </c>
+      <c r="AB26">
+        <v>1.24</v>
+      </c>
+      <c r="AC26">
+        <v>7.5</v>
+      </c>
+      <c r="AD26">
+        <v>1.03</v>
+      </c>
+      <c r="AE26">
         <v>1.01</v>
       </c>
-      <c r="Y26">
-        <v>1.25</v>
-      </c>
-      <c r="Z26">
-        <v>3.4</v>
-      </c>
-      <c r="AA26">
-        <v>1.91</v>
-      </c>
-      <c r="AB26">
-        <v>1.83</v>
-      </c>
-      <c r="AC26">
-        <v>3.7</v>
-      </c>
-      <c r="AD26">
-        <v>1.23</v>
-      </c>
-      <c r="AE26">
-        <v>1.1</v>
-      </c>
       <c r="AF26">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AG26">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33", "42"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56"]</t>
         </is>
       </c>
       <c r="AJ26">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AK26">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4706,62 +4706,62 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="O27">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P27">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="Q27">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R27">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S27">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T27">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="U27">
-        <v>2.47</v>
+        <v>2.68</v>
       </c>
       <c r="V27">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X27">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>3.58</v>
+        <v>3.86</v>
       </c>
       <c r="AA27">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AB27">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AC27">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD27">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE27">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF27">
         <v>1.67</v>
@@ -4780,37 +4780,37 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK27">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4853,13 +4853,13 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -4869,111 +4869,111 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="O28">
+        <v>3.4</v>
+      </c>
+      <c r="P28">
         <v>3.2</v>
       </c>
-      <c r="P28">
-        <v>2.8</v>
-      </c>
       <c r="Q28">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="R28">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>2.77</v>
+        <v>3.05</v>
       </c>
       <c r="U28">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z28">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA28">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="AB28">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="AC28">
-        <v>3.31</v>
+        <v>2.76</v>
       </c>
       <c r="AD28">
+        <v>1.4</v>
+      </c>
+      <c r="AE28">
+        <v>1.15</v>
+      </c>
+      <c r="AF28">
+        <v>1.57</v>
+      </c>
+      <c r="AG28">
+        <v>2.25</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>["33"]</t>
+        </is>
+      </c>
+      <c r="AJ28">
         <v>1.29</v>
       </c>
-      <c r="AE28">
-        <v>1.1</v>
-      </c>
-      <c r="AF28">
+      <c r="AK28">
         <v>1.7</v>
       </c>
-      <c r="AG28">
-        <v>2.05</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.34</v>
-      </c>
-      <c r="AK28">
-        <v>1.65</v>
-      </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5013,130 +5013,130 @@
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29">
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="O29">
+        <v>3.4</v>
+      </c>
+      <c r="P29">
         <v>3.6</v>
       </c>
-      <c r="P29">
-        <v>3.95</v>
-      </c>
       <c r="Q29">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="R29">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S29">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T29">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U29">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="V29">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W29">
         <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
         <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA29">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB29">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC29">
         <v>2.7</v>
       </c>
       <c r="AD29">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AE29">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF29">
         <v>1.62</v>
       </c>
       <c r="AG29">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11"]</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "90+4"]</t>
         </is>
       </c>
       <c r="AJ29">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
+        <v>1.98</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
         <v>2</v>
       </c>
-      <c r="AL29">
-        <v>0</v>
-      </c>
-      <c r="AM29">
-        <v>-1</v>
-      </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5176,36 +5176,36 @@
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="O30">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P30">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q30">
         <v>2.5</v>
@@ -5214,28 +5214,28 @@
         <v>2.25</v>
       </c>
       <c r="S30">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U30">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="V30">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X30">
         <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z30">
-        <v>4.25</v>
+        <v>4.55</v>
       </c>
       <c r="AA30">
         <v>1.58</v>
@@ -5244,62 +5244,62 @@
         <v>2.2</v>
       </c>
       <c r="AC30">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="AD30">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE30">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF30">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AG30">
         <v>2.55</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51", "85"]</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42"]</t>
         </is>
       </c>
       <c r="AJ30">
         <v>1.23</v>
       </c>
       <c r="AK30">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5339,26 +5339,26 @@
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
@@ -5368,7 +5368,7 @@
         <v>3.45</v>
       </c>
       <c r="P31">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q31">
         <v>2.5</v>
@@ -5380,7 +5380,7 @@
         <v>1.29</v>
       </c>
       <c r="T31">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U31">
         <v>2.3</v>
@@ -5392,25 +5392,25 @@
         <v>1.12</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
         <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA31">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB31">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC31">
-        <v>2.65</v>
+        <v>2.46</v>
       </c>
       <c r="AD31">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE31">
         <v>1.19</v>
@@ -5423,16 +5423,16 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63", "85"]</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "55", "70", "88"]</t>
         </is>
       </c>
       <c r="AJ31">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
         <v>1.67</v>
@@ -5441,16 +5441,16 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ31">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -5514,14 +5514,14 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32">
         <v>0</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58", "79", "90+2"]</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
@@ -5604,28 +5604,28 @@
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5665,16 +5665,16 @@
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35"]</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "45+6"]</t>
         </is>
       </c>
       <c r="AJ33">
@@ -5767,28 +5767,28 @@
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN33">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP33">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -5828,26 +5828,26 @@
         </is>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N34">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "58"]</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75"]</t>
         </is>
       </c>
       <c r="AJ34">
@@ -5930,28 +5930,28 @@
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN34">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -6006,11 +6006,11 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43"]</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47"]</t>
         </is>
       </c>
       <c r="AJ35">
@@ -6093,28 +6093,28 @@
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6349,49 +6349,49 @@
         <v>3.18</v>
       </c>
       <c r="Q37">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="U37">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V37">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="AA37">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AB37">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AC37">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AD37">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AE37">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
         <v>1.67</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P38">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q38">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="R38">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="S38">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="T38">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U38">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="V38">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W38">
+        <v>1.05</v>
+      </c>
+      <c r="X38">
         <v>1.06</v>
       </c>
-      <c r="X38">
-        <v>1.05</v>
-      </c>
       <c r="Y38">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z38">
+        <v>3.3</v>
+      </c>
+      <c r="AA38">
+        <v>2</v>
+      </c>
+      <c r="AB38">
+        <v>1.8</v>
+      </c>
+      <c r="AC38">
         <v>3.45</v>
       </c>
-      <c r="AA38">
-        <v>1.94</v>
-      </c>
-      <c r="AB38">
-        <v>1.87</v>
-      </c>
-      <c r="AC38">
-        <v>3.25</v>
-      </c>
       <c r="AD38">
+        <v>1.3</v>
+      </c>
+      <c r="AE38">
+        <v>1.1</v>
+      </c>
+      <c r="AF38">
+        <v>1.79</v>
+      </c>
+      <c r="AG38">
+        <v>1.92</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.33</v>
       </c>
-      <c r="AE38">
-        <v>1.11</v>
-      </c>
-      <c r="AF38">
-        <v>1.71</v>
-      </c>
-      <c r="AG38">
-        <v>2.02</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.25</v>
-      </c>
       <c r="AK38">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,55 +6666,55 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="O39">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="P39">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q39">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R39">
-        <v>2.69</v>
+        <v>2.89</v>
       </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T39">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U39">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="V39">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="W39">
         <v>1.14</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z39">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="AA39">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AB39">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC39">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD39">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AE39">
         <v>1.29</v>
@@ -6723,7 +6723,7 @@
         <v>1.7</v>
       </c>
       <c r="AG39">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.08</v>
       </c>
       <c r="AK39">
-        <v>3.32</v>
+        <v>3.14</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="O41">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="P41">
-        <v>44</v>
+        <v>4.63</v>
       </c>
       <c r="Q41">
-        <v>1.19</v>
+        <v>2.24</v>
       </c>
       <c r="R41">
-        <v>4.8</v>
+        <v>2.41</v>
       </c>
       <c r="S41">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="T41">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="U41">
-        <v>1.5</v>
+        <v>2.32</v>
       </c>
       <c r="V41">
-        <v>2.33</v>
+        <v>1.62</v>
       </c>
       <c r="W41">
-        <v>1.45</v>
+        <v>1.14</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="Z41">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AA41">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="AB41">
-        <v>5.25</v>
+        <v>2.38</v>
       </c>
       <c r="AC41">
-        <v>1.43</v>
+        <v>2.38</v>
       </c>
       <c r="AD41">
-        <v>2.85</v>
+        <v>1.61</v>
       </c>
       <c r="AE41">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="AF41">
-        <v>2.6</v>
+        <v>1.52</v>
       </c>
       <c r="AG41">
-        <v>1.5</v>
+        <v>2.37</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>14</v>
+        <v>2.1</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="O42">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P42">
-        <v>4.63</v>
+        <v>4.15</v>
       </c>
       <c r="Q42">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="R42">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T42">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="U42">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="V42">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W42">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
         <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AA42">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB42">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AC42">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AD42">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE42">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF42">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG42">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK42">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,65 +7318,65 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="O43">
-        <v>4.2</v>
+        <v>21</v>
       </c>
       <c r="P43">
-        <v>4.15</v>
+        <v>44</v>
       </c>
       <c r="Q43">
-        <v>2.25</v>
+        <v>1.19</v>
       </c>
       <c r="R43">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="S43">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="T43">
-        <v>3.28</v>
+        <v>6.5</v>
       </c>
       <c r="U43">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="V43">
-        <v>1.61</v>
+        <v>2.33</v>
       </c>
       <c r="W43">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="Y43">
         <v>1.03</v>
       </c>
-      <c r="Y43">
-        <v>1.18</v>
-      </c>
       <c r="Z43">
-        <v>5.05</v>
+        <v>15</v>
       </c>
       <c r="AA43">
-        <v>1.53</v>
+        <v>1.14</v>
       </c>
       <c r="AB43">
-        <v>2.5</v>
+        <v>5.25</v>
       </c>
       <c r="AC43">
-        <v>2.35</v>
+        <v>1.43</v>
       </c>
       <c r="AD43">
-        <v>1.62</v>
+        <v>2.85</v>
       </c>
       <c r="AE43">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AF43">
+        <v>2.6</v>
+      </c>
+      <c r="AG43">
         <v>1.5</v>
       </c>
-      <c r="AG43">
-        <v>2.6</v>
-      </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AK43">
-        <v>2.21</v>
+        <v>14</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O44">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P44">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q44">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="R44">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S44">
         <v>1.36</v>
       </c>
       <c r="T44">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="U44">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="V44">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
+        <v>1.32</v>
+      </c>
+      <c r="Z44">
+        <v>3.12</v>
+      </c>
+      <c r="AA44">
+        <v>2.05</v>
+      </c>
+      <c r="AB44">
+        <v>1.85</v>
+      </c>
+      <c r="AC44">
+        <v>3.3</v>
+      </c>
+      <c r="AD44">
         <v>1.3</v>
       </c>
-      <c r="Z44">
-        <v>3.3</v>
-      </c>
-      <c r="AA44">
-        <v>1.91</v>
-      </c>
-      <c r="AB44">
-        <v>1.86</v>
-      </c>
-      <c r="AC44">
-        <v>3.5</v>
-      </c>
-      <c r="AD44">
-        <v>1.27</v>
-      </c>
       <c r="AE44">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF44">
         <v>1.75</v>
       </c>
       <c r="AG44">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK44">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,80 +7644,80 @@
         </is>
       </c>
       <c r="N45">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="O45">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="P45">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Q45">
-        <v>5.5</v>
+        <v>6.14</v>
       </c>
       <c r="R45">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S45">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T45">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="U45">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V45">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W45">
+        <v>1.15</v>
+      </c>
+      <c r="X45">
+        <v>1.01</v>
+      </c>
+      <c r="Y45">
+        <v>1.11</v>
+      </c>
+      <c r="Z45">
+        <v>5.25</v>
+      </c>
+      <c r="AA45">
+        <v>1.48</v>
+      </c>
+      <c r="AB45">
+        <v>2.55</v>
+      </c>
+      <c r="AC45">
+        <v>2.35</v>
+      </c>
+      <c r="AD45">
+        <v>1.53</v>
+      </c>
+      <c r="AE45">
+        <v>1.23</v>
+      </c>
+      <c r="AF45">
+        <v>1.58</v>
+      </c>
+      <c r="AG45">
+        <v>2.11</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
         <v>1.14</v>
       </c>
-      <c r="X45">
-        <v>1.03</v>
-      </c>
-      <c r="Y45">
-        <v>1.1</v>
-      </c>
-      <c r="Z45">
-        <v>5</v>
-      </c>
-      <c r="AA45">
-        <v>1.53</v>
-      </c>
-      <c r="AB45">
-        <v>2.5</v>
-      </c>
-      <c r="AC45">
-        <v>2.23</v>
-      </c>
-      <c r="AD45">
-        <v>1.63</v>
-      </c>
-      <c r="AE45">
-        <v>1.25</v>
-      </c>
-      <c r="AF45">
-        <v>1.62</v>
-      </c>
-      <c r="AG45">
-        <v>2.17</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>1.2</v>
-      </c>
       <c r="AK45">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,65 +7807,65 @@
         </is>
       </c>
       <c r="N46">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O46">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="P46">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Q46">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R46">
         <v>2.8</v>
       </c>
       <c r="S46">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="T46">
-        <v>3.5</v>
+        <v>3.98</v>
       </c>
       <c r="U46">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="V46">
+        <v>1.69</v>
+      </c>
+      <c r="W46">
+        <v>1.16</v>
+      </c>
+      <c r="X46">
+        <v>1.01</v>
+      </c>
+      <c r="Y46">
+        <v>1.08</v>
+      </c>
+      <c r="Z46">
+        <v>5.75</v>
+      </c>
+      <c r="AA46">
+        <v>1.44</v>
+      </c>
+      <c r="AB46">
+        <v>2.75</v>
+      </c>
+      <c r="AC46">
+        <v>2.17</v>
+      </c>
+      <c r="AD46">
+        <v>1.7</v>
+      </c>
+      <c r="AE46">
+        <v>1.28</v>
+      </c>
+      <c r="AF46">
+        <v>2.22</v>
+      </c>
+      <c r="AG46">
         <v>1.68</v>
       </c>
-      <c r="W46">
-        <v>1.14</v>
-      </c>
-      <c r="X46">
-        <v>1.02</v>
-      </c>
-      <c r="Y46">
-        <v>1.12</v>
-      </c>
-      <c r="Z46">
-        <v>4.82</v>
-      </c>
-      <c r="AA46">
-        <v>1.42</v>
-      </c>
-      <c r="AB46">
-        <v>2.51</v>
-      </c>
-      <c r="AC46">
-        <v>2.15</v>
-      </c>
-      <c r="AD46">
-        <v>1.62</v>
-      </c>
-      <c r="AE46">
-        <v>1.24</v>
-      </c>
-      <c r="AF46">
-        <v>2.1</v>
-      </c>
-      <c r="AG46">
-        <v>1.67</v>
-      </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="AK46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,19 +7970,19 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O47">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P47">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="Q47">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R47">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S47">
         <v>1.44</v>
@@ -7991,31 +7991,31 @@
         <v>2.5</v>
       </c>
       <c r="U47">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="V47">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W47">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X47">
         <v>1.08</v>
       </c>
       <c r="Y47">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z47">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AA47">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB47">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC47">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD47">
         <v>1.2</v>
@@ -8024,10 +8024,10 @@
         <v>1.06</v>
       </c>
       <c r="AF47">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG47">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>1.36</v>
       </c>
       <c r="AK47">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="O48">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P48">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q48">
-        <v>2.14</v>
+        <v>3.6</v>
       </c>
       <c r="R48">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="S48">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T48">
         <v>2.69</v>
       </c>
       <c r="U48">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="V48">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W48">
         <v>1.02</v>
       </c>
       <c r="X48">
+        <v>1.06</v>
+      </c>
+      <c r="Y48">
+        <v>1.38</v>
+      </c>
+      <c r="Z48">
+        <v>2.9</v>
+      </c>
+      <c r="AA48">
+        <v>2.2</v>
+      </c>
+      <c r="AB48">
+        <v>1.65</v>
+      </c>
+      <c r="AC48">
+        <v>4.2</v>
+      </c>
+      <c r="AD48">
+        <v>1.23</v>
+      </c>
+      <c r="AE48">
         <v>1.02</v>
       </c>
-      <c r="Y48">
+      <c r="AF48">
+        <v>1.88</v>
+      </c>
+      <c r="AG48">
+        <v>1.8</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.53</v>
+      </c>
+      <c r="AK48">
         <v>1.33</v>
-      </c>
-      <c r="Z48">
-        <v>2.83</v>
-      </c>
-      <c r="AA48">
-        <v>2.26</v>
-      </c>
-      <c r="AB48">
-        <v>1.66</v>
-      </c>
-      <c r="AC48">
-        <v>4.15</v>
-      </c>
-      <c r="AD48">
-        <v>1.19</v>
-      </c>
-      <c r="AE48">
-        <v>1.03</v>
-      </c>
-      <c r="AF48">
-        <v>1.98</v>
-      </c>
-      <c r="AG48">
-        <v>1.67</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.26</v>
-      </c>
-      <c r="AK48">
-        <v>2.2</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.58</v>
+        <v>1.53</v>
       </c>
       <c r="O49">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="P49">
-        <v>2.3</v>
+        <v>5.8</v>
       </c>
       <c r="Q49">
-        <v>3.5</v>
+        <v>2.19</v>
       </c>
       <c r="R49">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="S49">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T49">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="U49">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="V49">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W49">
+        <v>1.01</v>
+      </c>
+      <c r="X49">
         <v>1.05</v>
       </c>
-      <c r="X49">
-        <v>1.06</v>
-      </c>
       <c r="Y49">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z49">
-        <v>2.63</v>
+        <v>2.95</v>
       </c>
       <c r="AA49">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="AB49">
         <v>1.57</v>
       </c>
       <c r="AC49">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AD49">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE49">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF49">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AG49">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK49">
-        <v>1.4</v>
+        <v>2.23</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8462,58 +8462,58 @@
         <v>2</v>
       </c>
       <c r="O50">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="P50">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="Q50">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="R50">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T50">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="U50">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V50">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W50">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z50">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA50">
         <v>1.75</v>
       </c>
       <c r="AB50">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC50">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD50">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE50">
         <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG50">
         <v>2.15</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK50">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8628,52 +8628,52 @@
         <v>3.7</v>
       </c>
       <c r="P51">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q51">
         <v>2.05</v>
       </c>
       <c r="R51">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="S51">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U51">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V51">
         <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y51">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z51">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AA51">
+        <v>1.75</v>
+      </c>
+      <c r="AB51">
         <v>1.8</v>
       </c>
-      <c r="AB51">
-        <v>1.92</v>
-      </c>
       <c r="AC51">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD51">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF51">
         <v>1.8</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK51">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,49 +8785,49 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O52">
         <v>3.5</v>
       </c>
       <c r="P52">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="Q52">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R52">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S52">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U52">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V52">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W52">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA52">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB52">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AC52">
         <v>2.15</v>
@@ -8836,7 +8836,7 @@
         <v>1.6</v>
       </c>
       <c r="AE52">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AF52">
         <v>1.4</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK52">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.33</v>
+        <v>3.44</v>
       </c>
       <c r="O55">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P55">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="Q55">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="R55">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S55">
         <v>1.3</v>
       </c>
       <c r="T55">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U55">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V55">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="W55">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X55">
         <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z55">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="AA55">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB55">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC55">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AD55">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE55">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF55">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AG55">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK55">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>3.44</v>
+        <v>2.33</v>
       </c>
       <c r="O56">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P56">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="Q56">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="R56">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="S56">
         <v>1.3</v>
       </c>
       <c r="T56">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U56">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V56">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="W56">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X56">
         <v>1.04</v>
       </c>
       <c r="Y56">
+        <v>1.17</v>
+      </c>
+      <c r="Z56">
+        <v>4.05</v>
+      </c>
+      <c r="AA56">
+        <v>1.68</v>
+      </c>
+      <c r="AB56">
+        <v>2.2</v>
+      </c>
+      <c r="AC56">
+        <v>2.55</v>
+      </c>
+      <c r="AD56">
+        <v>1.48</v>
+      </c>
+      <c r="AE56">
         <v>1.18</v>
       </c>
-      <c r="Z56">
-        <v>3.96</v>
-      </c>
-      <c r="AA56">
-        <v>1.66</v>
-      </c>
-      <c r="AB56">
-        <v>2</v>
-      </c>
-      <c r="AC56">
-        <v>2.8</v>
-      </c>
-      <c r="AD56">
-        <v>1.4</v>
-      </c>
-      <c r="AE56">
-        <v>1.15</v>
-      </c>
       <c r="AF56">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AG56">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK56">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9606,19 +9606,19 @@
         <v>3.35</v>
       </c>
       <c r="P57">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="Q57">
         <v>2.85</v>
       </c>
       <c r="R57">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="S57">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T57">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U57">
         <v>2.85</v>
@@ -9627,31 +9627,31 @@
         <v>1.37</v>
       </c>
       <c r="W57">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X57">
         <v>1.03</v>
       </c>
       <c r="Y57">
+        <v>1.25</v>
+      </c>
+      <c r="Z57">
+        <v>3.28</v>
+      </c>
+      <c r="AA57">
+        <v>1.99</v>
+      </c>
+      <c r="AB57">
+        <v>1.85</v>
+      </c>
+      <c r="AC57">
+        <v>3.4</v>
+      </c>
+      <c r="AD57">
         <v>1.29</v>
       </c>
-      <c r="Z57">
-        <v>3.4</v>
-      </c>
-      <c r="AA57">
-        <v>1.97</v>
-      </c>
-      <c r="AB57">
-        <v>1.8</v>
-      </c>
-      <c r="AC57">
-        <v>3.3</v>
-      </c>
-      <c r="AD57">
-        <v>1.3</v>
-      </c>
       <c r="AE57">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF57">
         <v>1.71</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK57">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O58">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P58">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q58">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="R58">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S58">
+        <v>1.33</v>
+      </c>
+      <c r="T58">
+        <v>3</v>
+      </c>
+      <c r="U58">
+        <v>2.56</v>
+      </c>
+      <c r="V58">
         <v>1.42</v>
       </c>
-      <c r="T58">
-        <v>2.88</v>
-      </c>
-      <c r="U58">
-        <v>2.73</v>
-      </c>
-      <c r="V58">
-        <v>1.39</v>
-      </c>
       <c r="W58">
+        <v>1.08</v>
+      </c>
+      <c r="X58">
         <v>1.05</v>
       </c>
-      <c r="X58">
-        <v>1.06</v>
-      </c>
       <c r="Y58">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z58">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AA58">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AB58">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC58">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="AD58">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE58">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF58">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AG58">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.28</v>
       </c>
       <c r="AK58">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -13512,49 +13512,49 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="O81">
         <v>3.2</v>
       </c>
       <c r="P81">
-        <v>4.24</v>
+        <v>4.4</v>
       </c>
       <c r="Q81">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="R81">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S81">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T81">
         <v>2.75</v>
       </c>
       <c r="U81">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V81">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W81">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X81">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y81">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z81">
         <v>2.88</v>
       </c>
       <c r="AA81">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB81">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC81">
         <v>4.33</v>
@@ -13563,13 +13563,13 @@
         <v>1.2</v>
       </c>
       <c r="AE81">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF81">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG81">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK81">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL81">
         <v>0</v>
